--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="375">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -751,6 +751,15 @@
     <t>['33']</t>
   </si>
   <si>
+    <t>['12', '25', '32', '64', '69', '89', '90+1']</t>
+  </si>
+  <si>
+    <t>['1', '6', '45+2', '90']</t>
+  </si>
+  <si>
+    <t>['12', '90+7']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1116,6 +1125,21 @@
   <si>
     <t>['78']</t>
   </si>
+  <si>
+    <t>['61', '82']</t>
+  </si>
+  <si>
+    <t>['21', '87']</t>
+  </si>
+  <si>
+    <t>['30', '75']</t>
+  </si>
+  <si>
+    <t>['29', '87']</t>
+  </si>
+  <si>
+    <t>['64', '89']</t>
+  </si>
 </sst>
 </file>
 
@@ -1476,7 +1500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP230"/>
+  <dimension ref="A1:BP238"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1810,10 +1834,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ2">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1938,7 +1962,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2016,10 +2040,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ3">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2350,7 +2374,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2428,10 +2452,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ5">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2634,10 +2658,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ6">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2762,7 +2786,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2840,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ7">
         <v>1.58</v>
@@ -2968,7 +2992,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3049,7 +3073,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ8">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3252,10 +3276,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ9">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3380,7 +3404,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3667,7 +3691,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ11">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3792,7 +3816,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4491,7 +4515,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ15">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -5028,7 +5052,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5234,7 +5258,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5312,7 +5336,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AQ19">
         <v>1.75</v>
@@ -5518,7 +5542,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ20">
         <v>1.75</v>
@@ -5933,7 +5957,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ22">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR22">
         <v>1.72</v>
@@ -6058,7 +6082,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6139,7 +6163,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ23">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR23">
         <v>0.86</v>
@@ -6264,7 +6288,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6342,10 +6366,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ24">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR24">
         <v>0.77</v>
@@ -6548,7 +6572,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ25">
         <v>0.75</v>
@@ -6754,10 +6778,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ26">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="AR26">
         <v>1.29</v>
@@ -6882,7 +6906,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6960,7 +6984,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ27">
         <v>1.58</v>
@@ -7088,7 +7112,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7294,7 +7318,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7375,7 +7399,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ29">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR29">
         <v>1.08</v>
@@ -7578,10 +7602,10 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ30">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR30">
         <v>0.47</v>
@@ -7706,7 +7730,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7784,10 +7808,10 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ31">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR31">
         <v>1.62</v>
@@ -7912,7 +7936,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8324,7 +8348,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -8405,7 +8429,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ34">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR34">
         <v>1.29</v>
@@ -9148,7 +9172,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9354,7 +9378,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9432,7 +9456,7 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ39">
         <v>1.75</v>
@@ -9560,7 +9584,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9766,7 +9790,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9844,7 +9868,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AQ41">
         <v>1.75</v>
@@ -9972,7 +9996,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10178,7 +10202,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -11826,7 +11850,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -12032,7 +12056,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12110,7 +12134,7 @@
         <v>3</v>
       </c>
       <c r="AP52">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ52">
         <v>1.5</v>
@@ -12238,7 +12262,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12316,10 +12340,10 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ53">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR53">
         <v>1.65</v>
@@ -12522,10 +12546,10 @@
         <v>0.5</v>
       </c>
       <c r="AP54">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ54">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR54">
         <v>1.48</v>
@@ -12650,7 +12674,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -12731,7 +12755,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ55">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR55">
         <v>1.6</v>
@@ -12934,7 +12958,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ56">
         <v>1.18</v>
@@ -13062,7 +13086,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13143,7 +13167,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ57">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR57">
         <v>1.39</v>
@@ -13268,7 +13292,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13346,10 +13370,10 @@
         <v>3</v>
       </c>
       <c r="AP58">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AQ58">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR58">
         <v>1.42</v>
@@ -13474,7 +13498,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13552,10 +13576,10 @@
         <v>3</v>
       </c>
       <c r="AP59">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ59">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR59">
         <v>0.95</v>
@@ -13680,7 +13704,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13758,10 +13782,10 @@
         <v>0.5</v>
       </c>
       <c r="AP60">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ60">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR60">
         <v>1.43</v>
@@ -13886,7 +13910,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -13964,10 +13988,10 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ61">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="AR61">
         <v>1.76</v>
@@ -14092,7 +14116,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14173,7 +14197,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ62">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR62">
         <v>1.29</v>
@@ -14504,7 +14528,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14585,7 +14609,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ64">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR64">
         <v>2.4</v>
@@ -14710,7 +14734,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14916,7 +14940,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14994,7 +15018,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ66">
         <v>0.75</v>
@@ -15203,7 +15227,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ67">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="AR67">
         <v>2.4</v>
@@ -15406,7 +15430,7 @@
         <v>1.33</v>
       </c>
       <c r="AP68">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ68">
         <v>1.75</v>
@@ -15946,7 +15970,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16027,7 +16051,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ71">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR71">
         <v>1.59</v>
@@ -16152,7 +16176,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q72">
         <v>1.95</v>
@@ -16358,7 +16382,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16439,7 +16463,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ73">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR73">
         <v>2.01</v>
@@ -16564,7 +16588,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16642,7 +16666,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ74">
         <v>0.73</v>
@@ -16770,7 +16794,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16848,10 +16872,10 @@
         <v>1.33</v>
       </c>
       <c r="AP75">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ75">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR75">
         <v>0.91</v>
@@ -16976,7 +17000,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17057,7 +17081,7 @@
         <v>0.36</v>
       </c>
       <c r="AQ76">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR76">
         <v>0.91</v>
@@ -17182,7 +17206,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17260,7 +17284,7 @@
         <v>0.33</v>
       </c>
       <c r="AP77">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ77">
         <v>0.91</v>
@@ -17466,7 +17490,7 @@
         <v>2.33</v>
       </c>
       <c r="AP78">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ78">
         <v>1.83</v>
@@ -17594,7 +17618,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17672,7 +17696,7 @@
         <v>2.33</v>
       </c>
       <c r="AP79">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AQ79">
         <v>1.5</v>
@@ -17800,7 +17824,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18084,10 +18108,10 @@
         <v>0.33</v>
       </c>
       <c r="AP81">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ81">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR81">
         <v>1.42</v>
@@ -18212,7 +18236,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18499,7 +18523,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ83">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="AR83">
         <v>2.31</v>
@@ -18624,7 +18648,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18830,7 +18854,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -19036,7 +19060,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19114,7 +19138,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ86">
         <v>0.82</v>
@@ -19320,10 +19344,10 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ87">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR87">
         <v>1.26</v>
@@ -19448,7 +19472,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19735,7 +19759,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ89">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR89">
         <v>1.28</v>
@@ -19860,7 +19884,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20066,7 +20090,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20147,7 +20171,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ91">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR91">
         <v>2.46</v>
@@ -20350,7 +20374,7 @@
         <v>1.75</v>
       </c>
       <c r="AP92">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ92">
         <v>1.83</v>
@@ -20762,7 +20786,7 @@
         <v>2.5</v>
       </c>
       <c r="AP94">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ94">
         <v>1.5</v>
@@ -20968,10 +20992,10 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ95">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR95">
         <v>1.12</v>
@@ -21177,7 +21201,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ96">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR96">
         <v>1.78</v>
@@ -21380,7 +21404,7 @@
         <v>1.25</v>
       </c>
       <c r="AP97">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ97">
         <v>1.18</v>
@@ -21508,7 +21532,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21586,10 +21610,10 @@
         <v>0.25</v>
       </c>
       <c r="AP98">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AQ98">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR98">
         <v>1.11</v>
@@ -21714,7 +21738,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -21795,7 +21819,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ99">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR99">
         <v>1.99</v>
@@ -21920,7 +21944,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -21998,7 +22022,7 @@
         <v>2.25</v>
       </c>
       <c r="AP100">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ100">
         <v>1.75</v>
@@ -22332,7 +22356,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22410,7 +22434,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ102">
         <v>1.58</v>
@@ -22538,7 +22562,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22619,7 +22643,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ103">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR103">
         <v>1.37</v>
@@ -23028,10 +23052,10 @@
         <v>0</v>
       </c>
       <c r="AP105">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AQ105">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="AR105">
         <v>1.17</v>
@@ -23443,7 +23467,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ107">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR107">
         <v>1.75</v>
@@ -23646,10 +23670,10 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ108">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR108">
         <v>1.48</v>
@@ -23774,7 +23798,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -23852,7 +23876,7 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ109">
         <v>1.75</v>
@@ -23980,7 +24004,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24186,7 +24210,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q111">
         <v>3.25</v>
@@ -24392,7 +24416,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24598,7 +24622,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -24882,7 +24906,7 @@
         <v>0</v>
       </c>
       <c r="AP114">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ114">
         <v>0.73</v>
@@ -25216,7 +25240,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25294,10 +25318,10 @@
         <v>1.4</v>
       </c>
       <c r="AP116">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ116">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR116">
         <v>1.57</v>
@@ -25422,7 +25446,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25503,7 +25527,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ117">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR117">
         <v>1.41</v>
@@ -25628,7 +25652,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25709,7 +25733,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ118">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR118">
         <v>2.34</v>
@@ -25834,7 +25858,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -25915,7 +25939,7 @@
         <v>0.36</v>
       </c>
       <c r="AQ119">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR119">
         <v>1.07</v>
@@ -26040,7 +26064,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26118,7 +26142,7 @@
         <v>1</v>
       </c>
       <c r="AP120">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ120">
         <v>1.18</v>
@@ -26246,7 +26270,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26324,7 +26348,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ121">
         <v>1.18</v>
@@ -26452,7 +26476,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26533,7 +26557,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ122">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="AR122">
         <v>1.46</v>
@@ -26658,7 +26682,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -26736,7 +26760,7 @@
         <v>0.83</v>
       </c>
       <c r="AP123">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AQ123">
         <v>1.58</v>
@@ -26942,7 +26966,7 @@
         <v>0.83</v>
       </c>
       <c r="AP124">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ124">
         <v>0.82</v>
@@ -27148,10 +27172,10 @@
         <v>0.83</v>
       </c>
       <c r="AP125">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ125">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR125">
         <v>1.7</v>
@@ -27276,7 +27300,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27482,7 +27506,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -27766,7 +27790,7 @@
         <v>0.83</v>
       </c>
       <c r="AP128">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ128">
         <v>0.91</v>
@@ -27975,7 +27999,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ129">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR129">
         <v>1.64</v>
@@ -28100,7 +28124,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28181,7 +28205,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ130">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR130">
         <v>1.95</v>
@@ -28512,7 +28536,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28590,10 +28614,10 @@
         <v>0.5</v>
       </c>
       <c r="AP132">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ132">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR132">
         <v>1.18</v>
@@ -28924,7 +28948,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29130,7 +29154,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -29208,10 +29232,10 @@
         <v>2.67</v>
       </c>
       <c r="AP135">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ135">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR135">
         <v>1.25</v>
@@ -29620,7 +29644,7 @@
         <v>0.83</v>
       </c>
       <c r="AP137">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ137">
         <v>0.75</v>
@@ -30241,7 +30265,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ140">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR140">
         <v>1.88</v>
@@ -30444,10 +30468,10 @@
         <v>1.17</v>
       </c>
       <c r="AP141">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ141">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR141">
         <v>1.64</v>
@@ -30572,7 +30596,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30778,7 +30802,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30856,7 +30880,7 @@
         <v>1.29</v>
       </c>
       <c r="AP143">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ143">
         <v>1.75</v>
@@ -31065,7 +31089,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ144">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="AR144">
         <v>1.54</v>
@@ -31190,7 +31214,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31268,7 +31292,7 @@
         <v>1.57</v>
       </c>
       <c r="AP145">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ145">
         <v>1.92</v>
@@ -31396,7 +31420,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31602,7 +31626,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31680,7 +31704,7 @@
         <v>1.14</v>
       </c>
       <c r="AP147">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ147">
         <v>1.58</v>
@@ -31808,7 +31832,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -31889,7 +31913,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ148">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR148">
         <v>1.08</v>
@@ -32014,7 +32038,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32426,7 +32450,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -32504,7 +32528,7 @@
         <v>0.71</v>
       </c>
       <c r="AP151">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AQ151">
         <v>0.82</v>
@@ -32916,10 +32940,10 @@
         <v>0.71</v>
       </c>
       <c r="AP153">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ153">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR153">
         <v>1.32</v>
@@ -33044,7 +33068,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33125,7 +33149,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ154">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR154">
         <v>1.76</v>
@@ -33250,7 +33274,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33328,10 +33352,10 @@
         <v>1.43</v>
       </c>
       <c r="AP155">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ155">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR155">
         <v>1.52</v>
@@ -33456,7 +33480,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33537,7 +33561,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ156">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR156">
         <v>1.53</v>
@@ -33662,7 +33686,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33868,7 +33892,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -33949,7 +33973,7 @@
         <v>0.36</v>
       </c>
       <c r="AQ158">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR158">
         <v>1.06</v>
@@ -34358,7 +34382,7 @@
         <v>1.14</v>
       </c>
       <c r="AP160">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ160">
         <v>1.18</v>
@@ -34692,7 +34716,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -34770,7 +34794,7 @@
         <v>1.75</v>
       </c>
       <c r="AP162">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ162">
         <v>1.92</v>
@@ -34898,7 +34922,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -34979,7 +35003,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ163">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR163">
         <v>1.48</v>
@@ -35104,7 +35128,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35182,7 +35206,7 @@
         <v>1.13</v>
       </c>
       <c r="AP164">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ164">
         <v>1.75</v>
@@ -35310,7 +35334,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35597,7 +35621,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ166">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="AR166">
         <v>1.59</v>
@@ -35722,7 +35746,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35928,7 +35952,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36006,7 +36030,7 @@
         <v>1.38</v>
       </c>
       <c r="AP168">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ168">
         <v>1.58</v>
@@ -36212,7 +36236,7 @@
         <v>2.38</v>
       </c>
       <c r="AP169">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ169">
         <v>1.75</v>
@@ -36340,7 +36364,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36421,7 +36445,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ170">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR170">
         <v>1.79</v>
@@ -36752,7 +36776,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37036,10 +37060,10 @@
         <v>1.25</v>
       </c>
       <c r="AP173">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ173">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR173">
         <v>1.56</v>
@@ -37242,10 +37266,10 @@
         <v>1.25</v>
       </c>
       <c r="AP174">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ174">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR174">
         <v>1.48</v>
@@ -37370,7 +37394,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -37451,7 +37475,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ175">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR175">
         <v>1.78</v>
@@ -37654,10 +37678,10 @@
         <v>1.13</v>
       </c>
       <c r="AP176">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ176">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR176">
         <v>1.74</v>
@@ -37860,7 +37884,7 @@
         <v>1.13</v>
       </c>
       <c r="AP177">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AQ177">
         <v>1.18</v>
@@ -37988,7 +38012,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38069,7 +38093,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ178">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR178">
         <v>1.73</v>
@@ -38606,7 +38630,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38812,7 +38836,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39099,7 +39123,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ183">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="AR183">
         <v>1.34</v>
@@ -39224,7 +39248,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39430,7 +39454,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39508,7 +39532,7 @@
         <v>1.89</v>
       </c>
       <c r="AP185">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ185">
         <v>1.92</v>
@@ -39636,7 +39660,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -39717,7 +39741,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ186">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR186">
         <v>1.43</v>
@@ -39920,7 +39944,7 @@
         <v>2.22</v>
       </c>
       <c r="AP187">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ187">
         <v>1.75</v>
@@ -40048,7 +40072,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40129,7 +40153,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ188">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR188">
         <v>1.51</v>
@@ -40254,7 +40278,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40332,7 +40356,7 @@
         <v>1.33</v>
       </c>
       <c r="AP189">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ189">
         <v>1.75</v>
@@ -40460,7 +40484,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40538,7 +40562,7 @@
         <v>1.67</v>
       </c>
       <c r="AP190">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ190">
         <v>1.83</v>
@@ -40666,7 +40690,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -40950,7 +40974,7 @@
         <v>0.78</v>
       </c>
       <c r="AP192">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ192">
         <v>0.91</v>
@@ -41078,7 +41102,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41159,7 +41183,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ193">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR193">
         <v>1.51</v>
@@ -41490,7 +41514,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41696,7 +41720,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -42108,7 +42132,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42314,7 +42338,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42520,7 +42544,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42598,7 +42622,7 @@
         <v>2</v>
       </c>
       <c r="AP200">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AQ200">
         <v>1.92</v>
@@ -42726,7 +42750,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -42932,7 +42956,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43013,7 +43037,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ202">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR202">
         <v>1.35</v>
@@ -43138,7 +43162,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43216,7 +43240,7 @@
         <v>1.4</v>
       </c>
       <c r="AP203">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ203">
         <v>1.5</v>
@@ -43344,7 +43368,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43422,10 +43446,10 @@
         <v>2.56</v>
       </c>
       <c r="AP204">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ204">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR204">
         <v>1.5</v>
@@ -43550,7 +43574,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -43631,7 +43655,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ205">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR205">
         <v>1.11</v>
@@ -43834,7 +43858,7 @@
         <v>0.9</v>
       </c>
       <c r="AP206">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ206">
         <v>0.75</v>
@@ -43962,7 +43986,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44040,10 +44064,10 @@
         <v>1.11</v>
       </c>
       <c r="AP207">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ207">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR207">
         <v>1.34</v>
@@ -44249,7 +44273,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ208">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR208">
         <v>1.98</v>
@@ -44374,7 +44398,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44452,10 +44476,10 @@
         <v>1.3</v>
       </c>
       <c r="AP209">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ209">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR209">
         <v>1.16</v>
@@ -44658,10 +44682,10 @@
         <v>0.2</v>
       </c>
       <c r="AP210">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ210">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="AR210">
         <v>1.48</v>
@@ -44786,7 +44810,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -44864,7 +44888,7 @@
         <v>1.45</v>
       </c>
       <c r="AP211">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ211">
         <v>1.58</v>
@@ -44992,7 +45016,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45073,7 +45097,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ212">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR212">
         <v>1.29</v>
@@ -45198,7 +45222,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45276,10 +45300,10 @@
         <v>2.4</v>
       </c>
       <c r="AP213">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ213">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AR213">
         <v>1.61</v>
@@ -45404,7 +45428,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45485,7 +45509,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ214">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR214">
         <v>1.2</v>
@@ -45610,7 +45634,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -45691,7 +45715,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ215">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR215">
         <v>1.97</v>
@@ -45816,7 +45840,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -45894,10 +45918,10 @@
         <v>1.45</v>
       </c>
       <c r="AP216">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ216">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR216">
         <v>1.58</v>
@@ -46022,7 +46046,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46100,10 +46124,10 @@
         <v>0.18</v>
       </c>
       <c r="AP217">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ217">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="AR217">
         <v>1.44</v>
@@ -46228,7 +46252,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46306,10 +46330,10 @@
         <v>1</v>
       </c>
       <c r="AP218">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ218">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR218">
         <v>1.33</v>
@@ -46434,7 +46458,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46512,7 +46536,7 @@
         <v>1.36</v>
       </c>
       <c r="AP219">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AQ219">
         <v>1.5</v>
@@ -46640,7 +46664,7 @@
         <v>240</v>
       </c>
       <c r="P220" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q220">
         <v>1.73</v>
@@ -46924,7 +46948,7 @@
         <v>2.09</v>
       </c>
       <c r="AP221">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ221">
         <v>1.92</v>
@@ -47052,7 +47076,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -47464,7 +47488,7 @@
         <v>107</v>
       </c>
       <c r="P224" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q224">
         <v>6</v>
@@ -47670,7 +47694,7 @@
         <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q225">
         <v>6.5</v>
@@ -47748,7 +47772,7 @@
         <v>1.73</v>
       </c>
       <c r="AP225">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AQ225">
         <v>1.83</v>
@@ -47876,7 +47900,7 @@
         <v>243</v>
       </c>
       <c r="P226" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q226">
         <v>2.38</v>
@@ -48082,7 +48106,7 @@
         <v>155</v>
       </c>
       <c r="P227" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48288,7 +48312,7 @@
         <v>244</v>
       </c>
       <c r="P228" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q228">
         <v>1.91</v>
@@ -48369,7 +48393,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ228">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR228">
         <v>1.71</v>
@@ -48700,7 +48724,7 @@
         <v>91</v>
       </c>
       <c r="P230" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q230">
         <v>2.88</v>
@@ -48857,6 +48881,1654 @@
       </c>
       <c r="BP230">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="231" spans="1:68">
+      <c r="A231" s="1">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>7466917</v>
+      </c>
+      <c r="C231" t="s">
+        <v>68</v>
+      </c>
+      <c r="D231" t="s">
+        <v>69</v>
+      </c>
+      <c r="E231" s="2">
+        <v>45689.39583333334</v>
+      </c>
+      <c r="F231">
+        <v>24</v>
+      </c>
+      <c r="G231" t="s">
+        <v>75</v>
+      </c>
+      <c r="H231" t="s">
+        <v>80</v>
+      </c>
+      <c r="I231">
+        <v>3</v>
+      </c>
+      <c r="J231">
+        <v>0</v>
+      </c>
+      <c r="K231">
+        <v>3</v>
+      </c>
+      <c r="L231">
+        <v>7</v>
+      </c>
+      <c r="M231">
+        <v>0</v>
+      </c>
+      <c r="N231">
+        <v>7</v>
+      </c>
+      <c r="O231" t="s">
+        <v>245</v>
+      </c>
+      <c r="P231" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q231">
+        <v>3.1</v>
+      </c>
+      <c r="R231">
+        <v>2.2</v>
+      </c>
+      <c r="S231">
+        <v>3.4</v>
+      </c>
+      <c r="T231">
+        <v>1.36</v>
+      </c>
+      <c r="U231">
+        <v>3</v>
+      </c>
+      <c r="V231">
+        <v>2.75</v>
+      </c>
+      <c r="W231">
+        <v>1.4</v>
+      </c>
+      <c r="X231">
+        <v>8</v>
+      </c>
+      <c r="Y231">
+        <v>1.08</v>
+      </c>
+      <c r="Z231">
+        <v>2.4</v>
+      </c>
+      <c r="AA231">
+        <v>3.5</v>
+      </c>
+      <c r="AB231">
+        <v>2.75</v>
+      </c>
+      <c r="AC231">
+        <v>1.06</v>
+      </c>
+      <c r="AD231">
+        <v>11</v>
+      </c>
+      <c r="AE231">
+        <v>1.31</v>
+      </c>
+      <c r="AF231">
+        <v>3.6</v>
+      </c>
+      <c r="AG231">
+        <v>2</v>
+      </c>
+      <c r="AH231">
+        <v>1.75</v>
+      </c>
+      <c r="AI231">
+        <v>1.7</v>
+      </c>
+      <c r="AJ231">
+        <v>2.05</v>
+      </c>
+      <c r="AK231">
+        <v>1.43</v>
+      </c>
+      <c r="AL231">
+        <v>1.29</v>
+      </c>
+      <c r="AM231">
+        <v>1.53</v>
+      </c>
+      <c r="AN231">
+        <v>1.91</v>
+      </c>
+      <c r="AO231">
+        <v>1.58</v>
+      </c>
+      <c r="AP231">
+        <v>2</v>
+      </c>
+      <c r="AQ231">
+        <v>1.46</v>
+      </c>
+      <c r="AR231">
+        <v>1.47</v>
+      </c>
+      <c r="AS231">
+        <v>1.36</v>
+      </c>
+      <c r="AT231">
+        <v>2.83</v>
+      </c>
+      <c r="AU231">
+        <v>10</v>
+      </c>
+      <c r="AV231">
+        <v>6</v>
+      </c>
+      <c r="AW231">
+        <v>5</v>
+      </c>
+      <c r="AX231">
+        <v>5</v>
+      </c>
+      <c r="AY231">
+        <v>16</v>
+      </c>
+      <c r="AZ231">
+        <v>13</v>
+      </c>
+      <c r="BA231">
+        <v>4</v>
+      </c>
+      <c r="BB231">
+        <v>6</v>
+      </c>
+      <c r="BC231">
+        <v>10</v>
+      </c>
+      <c r="BD231">
+        <v>1.94</v>
+      </c>
+      <c r="BE231">
+        <v>6.75</v>
+      </c>
+      <c r="BF231">
+        <v>2.02</v>
+      </c>
+      <c r="BG231">
+        <v>1.18</v>
+      </c>
+      <c r="BH231">
+        <v>4.1</v>
+      </c>
+      <c r="BI231">
+        <v>1.33</v>
+      </c>
+      <c r="BJ231">
+        <v>2.95</v>
+      </c>
+      <c r="BK231">
+        <v>1.54</v>
+      </c>
+      <c r="BL231">
+        <v>2.3</v>
+      </c>
+      <c r="BM231">
+        <v>1.85</v>
+      </c>
+      <c r="BN231">
+        <v>1.83</v>
+      </c>
+      <c r="BO231">
+        <v>2.3</v>
+      </c>
+      <c r="BP231">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="232" spans="1:68">
+      <c r="A232" s="1">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>7466916</v>
+      </c>
+      <c r="C232" t="s">
+        <v>68</v>
+      </c>
+      <c r="D232" t="s">
+        <v>69</v>
+      </c>
+      <c r="E232" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F232">
+        <v>24</v>
+      </c>
+      <c r="G232" t="s">
+        <v>74</v>
+      </c>
+      <c r="H232" t="s">
+        <v>83</v>
+      </c>
+      <c r="I232">
+        <v>1</v>
+      </c>
+      <c r="J232">
+        <v>0</v>
+      </c>
+      <c r="K232">
+        <v>1</v>
+      </c>
+      <c r="L232">
+        <v>1</v>
+      </c>
+      <c r="M232">
+        <v>2</v>
+      </c>
+      <c r="N232">
+        <v>3</v>
+      </c>
+      <c r="O232" t="s">
+        <v>95</v>
+      </c>
+      <c r="P232" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q232">
+        <v>2.2</v>
+      </c>
+      <c r="R232">
+        <v>2.4</v>
+      </c>
+      <c r="S232">
+        <v>4.75</v>
+      </c>
+      <c r="T232">
+        <v>1.3</v>
+      </c>
+      <c r="U232">
+        <v>3.4</v>
+      </c>
+      <c r="V232">
+        <v>2.38</v>
+      </c>
+      <c r="W232">
+        <v>1.53</v>
+      </c>
+      <c r="X232">
+        <v>6</v>
+      </c>
+      <c r="Y232">
+        <v>1.13</v>
+      </c>
+      <c r="Z232">
+        <v>1.67</v>
+      </c>
+      <c r="AA232">
+        <v>4</v>
+      </c>
+      <c r="AB232">
+        <v>4.4</v>
+      </c>
+      <c r="AC232">
+        <v>1.03</v>
+      </c>
+      <c r="AD232">
+        <v>17</v>
+      </c>
+      <c r="AE232">
+        <v>1.21</v>
+      </c>
+      <c r="AF232">
+        <v>4.7</v>
+      </c>
+      <c r="AG232">
+        <v>1.7</v>
+      </c>
+      <c r="AH232">
+        <v>2.05</v>
+      </c>
+      <c r="AI232">
+        <v>1.62</v>
+      </c>
+      <c r="AJ232">
+        <v>2.2</v>
+      </c>
+      <c r="AK232">
+        <v>1.18</v>
+      </c>
+      <c r="AL232">
+        <v>1.23</v>
+      </c>
+      <c r="AM232">
+        <v>2.15</v>
+      </c>
+      <c r="AN232">
+        <v>1.82</v>
+      </c>
+      <c r="AO232">
+        <v>1.45</v>
+      </c>
+      <c r="AP232">
+        <v>1.67</v>
+      </c>
+      <c r="AQ232">
+        <v>1.58</v>
+      </c>
+      <c r="AR232">
+        <v>1.61</v>
+      </c>
+      <c r="AS232">
+        <v>1.47</v>
+      </c>
+      <c r="AT232">
+        <v>3.08</v>
+      </c>
+      <c r="AU232">
+        <v>5</v>
+      </c>
+      <c r="AV232">
+        <v>5</v>
+      </c>
+      <c r="AW232">
+        <v>7</v>
+      </c>
+      <c r="AX232">
+        <v>11</v>
+      </c>
+      <c r="AY232">
+        <v>14</v>
+      </c>
+      <c r="AZ232">
+        <v>23</v>
+      </c>
+      <c r="BA232">
+        <v>3</v>
+      </c>
+      <c r="BB232">
+        <v>7</v>
+      </c>
+      <c r="BC232">
+        <v>10</v>
+      </c>
+      <c r="BD232">
+        <v>1.52</v>
+      </c>
+      <c r="BE232">
+        <v>7</v>
+      </c>
+      <c r="BF232">
+        <v>2.75</v>
+      </c>
+      <c r="BG232">
+        <v>1.19</v>
+      </c>
+      <c r="BH232">
+        <v>4.1</v>
+      </c>
+      <c r="BI232">
+        <v>1.33</v>
+      </c>
+      <c r="BJ232">
+        <v>2.95</v>
+      </c>
+      <c r="BK232">
+        <v>1.54</v>
+      </c>
+      <c r="BL232">
+        <v>2.3</v>
+      </c>
+      <c r="BM232">
+        <v>1.85</v>
+      </c>
+      <c r="BN232">
+        <v>1.83</v>
+      </c>
+      <c r="BO232">
+        <v>2.32</v>
+      </c>
+      <c r="BP232">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="233" spans="1:68">
+      <c r="A233" s="1">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>7466914</v>
+      </c>
+      <c r="C233" t="s">
+        <v>68</v>
+      </c>
+      <c r="D233" t="s">
+        <v>69</v>
+      </c>
+      <c r="E233" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F233">
+        <v>24</v>
+      </c>
+      <c r="G233" t="s">
+        <v>73</v>
+      </c>
+      <c r="H233" t="s">
+        <v>79</v>
+      </c>
+      <c r="I233">
+        <v>3</v>
+      </c>
+      <c r="J233">
+        <v>0</v>
+      </c>
+      <c r="K233">
+        <v>3</v>
+      </c>
+      <c r="L233">
+        <v>4</v>
+      </c>
+      <c r="M233">
+        <v>0</v>
+      </c>
+      <c r="N233">
+        <v>4</v>
+      </c>
+      <c r="O233" t="s">
+        <v>246</v>
+      </c>
+      <c r="P233" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q233">
+        <v>2.4</v>
+      </c>
+      <c r="R233">
+        <v>2.2</v>
+      </c>
+      <c r="S233">
+        <v>5</v>
+      </c>
+      <c r="T233">
+        <v>1.4</v>
+      </c>
+      <c r="U233">
+        <v>2.75</v>
+      </c>
+      <c r="V233">
+        <v>3</v>
+      </c>
+      <c r="W233">
+        <v>1.36</v>
+      </c>
+      <c r="X233">
+        <v>8</v>
+      </c>
+      <c r="Y233">
+        <v>1.08</v>
+      </c>
+      <c r="Z233">
+        <v>1.7</v>
+      </c>
+      <c r="AA233">
+        <v>3.8</v>
+      </c>
+      <c r="AB233">
+        <v>4.75</v>
+      </c>
+      <c r="AC233">
+        <v>1.06</v>
+      </c>
+      <c r="AD233">
+        <v>10</v>
+      </c>
+      <c r="AE233">
+        <v>1.36</v>
+      </c>
+      <c r="AF233">
+        <v>3.3</v>
+      </c>
+      <c r="AG233">
+        <v>1.95</v>
+      </c>
+      <c r="AH233">
+        <v>1.8</v>
+      </c>
+      <c r="AI233">
+        <v>1.95</v>
+      </c>
+      <c r="AJ233">
+        <v>1.8</v>
+      </c>
+      <c r="AK233">
+        <v>1.18</v>
+      </c>
+      <c r="AL233">
+        <v>1.27</v>
+      </c>
+      <c r="AM233">
+        <v>2.05</v>
+      </c>
+      <c r="AN233">
+        <v>1.18</v>
+      </c>
+      <c r="AO233">
+        <v>0.73</v>
+      </c>
+      <c r="AP233">
+        <v>1.33</v>
+      </c>
+      <c r="AQ233">
+        <v>0.67</v>
+      </c>
+      <c r="AR233">
+        <v>1.37</v>
+      </c>
+      <c r="AS233">
+        <v>1.03</v>
+      </c>
+      <c r="AT233">
+        <v>2.4</v>
+      </c>
+      <c r="AU233">
+        <v>8</v>
+      </c>
+      <c r="AV233">
+        <v>2</v>
+      </c>
+      <c r="AW233">
+        <v>6</v>
+      </c>
+      <c r="AX233">
+        <v>8</v>
+      </c>
+      <c r="AY233">
+        <v>14</v>
+      </c>
+      <c r="AZ233">
+        <v>11</v>
+      </c>
+      <c r="BA233">
+        <v>5</v>
+      </c>
+      <c r="BB233">
+        <v>6</v>
+      </c>
+      <c r="BC233">
+        <v>11</v>
+      </c>
+      <c r="BD233">
+        <v>1.41</v>
+      </c>
+      <c r="BE233">
+        <v>7</v>
+      </c>
+      <c r="BF233">
+        <v>3.3</v>
+      </c>
+      <c r="BG233">
+        <v>1.24</v>
+      </c>
+      <c r="BH233">
+        <v>3.55</v>
+      </c>
+      <c r="BI233">
+        <v>1.44</v>
+      </c>
+      <c r="BJ233">
+        <v>2.55</v>
+      </c>
+      <c r="BK233">
+        <v>1.71</v>
+      </c>
+      <c r="BL233">
+        <v>2</v>
+      </c>
+      <c r="BM233">
+        <v>2.08</v>
+      </c>
+      <c r="BN233">
+        <v>1.65</v>
+      </c>
+      <c r="BO233">
+        <v>2.65</v>
+      </c>
+      <c r="BP233">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="234" spans="1:68">
+      <c r="A234" s="1">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>7467147</v>
+      </c>
+      <c r="C234" t="s">
+        <v>68</v>
+      </c>
+      <c r="D234" t="s">
+        <v>69</v>
+      </c>
+      <c r="E234" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F234">
+        <v>24</v>
+      </c>
+      <c r="G234" t="s">
+        <v>71</v>
+      </c>
+      <c r="H234" t="s">
+        <v>84</v>
+      </c>
+      <c r="I234">
+        <v>1</v>
+      </c>
+      <c r="J234">
+        <v>1</v>
+      </c>
+      <c r="K234">
+        <v>2</v>
+      </c>
+      <c r="L234">
+        <v>1</v>
+      </c>
+      <c r="M234">
+        <v>2</v>
+      </c>
+      <c r="N234">
+        <v>3</v>
+      </c>
+      <c r="O234" t="s">
+        <v>151</v>
+      </c>
+      <c r="P234" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q234">
+        <v>2.6</v>
+      </c>
+      <c r="R234">
+        <v>2.25</v>
+      </c>
+      <c r="S234">
+        <v>4.33</v>
+      </c>
+      <c r="T234">
+        <v>1.36</v>
+      </c>
+      <c r="U234">
+        <v>3</v>
+      </c>
+      <c r="V234">
+        <v>2.75</v>
+      </c>
+      <c r="W234">
+        <v>1.4</v>
+      </c>
+      <c r="X234">
+        <v>7</v>
+      </c>
+      <c r="Y234">
+        <v>1.1</v>
+      </c>
+      <c r="Z234">
+        <v>1.91</v>
+      </c>
+      <c r="AA234">
+        <v>3.6</v>
+      </c>
+      <c r="AB234">
+        <v>3.8</v>
+      </c>
+      <c r="AC234">
+        <v>1.04</v>
+      </c>
+      <c r="AD234">
+        <v>13</v>
+      </c>
+      <c r="AE234">
+        <v>1.27</v>
+      </c>
+      <c r="AF234">
+        <v>4</v>
+      </c>
+      <c r="AG234">
+        <v>1.75</v>
+      </c>
+      <c r="AH234">
+        <v>2</v>
+      </c>
+      <c r="AI234">
+        <v>1.7</v>
+      </c>
+      <c r="AJ234">
+        <v>2.05</v>
+      </c>
+      <c r="AK234">
+        <v>1.26</v>
+      </c>
+      <c r="AL234">
+        <v>1.29</v>
+      </c>
+      <c r="AM234">
+        <v>1.82</v>
+      </c>
+      <c r="AN234">
+        <v>0.58</v>
+      </c>
+      <c r="AO234">
+        <v>0.17</v>
+      </c>
+      <c r="AP234">
+        <v>0.54</v>
+      </c>
+      <c r="AQ234">
+        <v>0.38</v>
+      </c>
+      <c r="AR234">
+        <v>1.13</v>
+      </c>
+      <c r="AS234">
+        <v>1.06</v>
+      </c>
+      <c r="AT234">
+        <v>2.19</v>
+      </c>
+      <c r="AU234">
+        <v>7</v>
+      </c>
+      <c r="AV234">
+        <v>5</v>
+      </c>
+      <c r="AW234">
+        <v>9</v>
+      </c>
+      <c r="AX234">
+        <v>5</v>
+      </c>
+      <c r="AY234">
+        <v>20</v>
+      </c>
+      <c r="AZ234">
+        <v>13</v>
+      </c>
+      <c r="BA234">
+        <v>1</v>
+      </c>
+      <c r="BB234">
+        <v>2</v>
+      </c>
+      <c r="BC234">
+        <v>3</v>
+      </c>
+      <c r="BD234">
+        <v>1.65</v>
+      </c>
+      <c r="BE234">
+        <v>6.75</v>
+      </c>
+      <c r="BF234">
+        <v>2.48</v>
+      </c>
+      <c r="BG234">
+        <v>1.18</v>
+      </c>
+      <c r="BH234">
+        <v>4.1</v>
+      </c>
+      <c r="BI234">
+        <v>1.33</v>
+      </c>
+      <c r="BJ234">
+        <v>2.95</v>
+      </c>
+      <c r="BK234">
+        <v>1.55</v>
+      </c>
+      <c r="BL234">
+        <v>2.28</v>
+      </c>
+      <c r="BM234">
+        <v>1.86</v>
+      </c>
+      <c r="BN234">
+        <v>1.82</v>
+      </c>
+      <c r="BO234">
+        <v>2.32</v>
+      </c>
+      <c r="BP234">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="235" spans="1:68">
+      <c r="A235" s="1">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>7467146</v>
+      </c>
+      <c r="C235" t="s">
+        <v>68</v>
+      </c>
+      <c r="D235" t="s">
+        <v>69</v>
+      </c>
+      <c r="E235" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F235">
+        <v>24</v>
+      </c>
+      <c r="G235" t="s">
+        <v>88</v>
+      </c>
+      <c r="H235" t="s">
+        <v>89</v>
+      </c>
+      <c r="I235">
+        <v>0</v>
+      </c>
+      <c r="J235">
+        <v>1</v>
+      </c>
+      <c r="K235">
+        <v>1</v>
+      </c>
+      <c r="L235">
+        <v>0</v>
+      </c>
+      <c r="M235">
+        <v>2</v>
+      </c>
+      <c r="N235">
+        <v>2</v>
+      </c>
+      <c r="O235" t="s">
+        <v>91</v>
+      </c>
+      <c r="P235" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q235">
+        <v>4.5</v>
+      </c>
+      <c r="R235">
+        <v>2.5</v>
+      </c>
+      <c r="S235">
+        <v>2.2</v>
+      </c>
+      <c r="T235">
+        <v>1.25</v>
+      </c>
+      <c r="U235">
+        <v>3.75</v>
+      </c>
+      <c r="V235">
+        <v>2.2</v>
+      </c>
+      <c r="W235">
+        <v>1.62</v>
+      </c>
+      <c r="X235">
+        <v>5</v>
+      </c>
+      <c r="Y235">
+        <v>1.17</v>
+      </c>
+      <c r="Z235">
+        <v>4.4</v>
+      </c>
+      <c r="AA235">
+        <v>4.2</v>
+      </c>
+      <c r="AB235">
+        <v>1.67</v>
+      </c>
+      <c r="AC235">
+        <v>1.02</v>
+      </c>
+      <c r="AD235">
+        <v>22</v>
+      </c>
+      <c r="AE235">
+        <v>1.16</v>
+      </c>
+      <c r="AF235">
+        <v>5.7</v>
+      </c>
+      <c r="AG235">
+        <v>1.6</v>
+      </c>
+      <c r="AH235">
+        <v>2.25</v>
+      </c>
+      <c r="AI235">
+        <v>1.53</v>
+      </c>
+      <c r="AJ235">
+        <v>2.38</v>
+      </c>
+      <c r="AK235">
+        <v>2.1</v>
+      </c>
+      <c r="AL235">
+        <v>1.22</v>
+      </c>
+      <c r="AM235">
+        <v>1.22</v>
+      </c>
+      <c r="AN235">
+        <v>1.91</v>
+      </c>
+      <c r="AO235">
+        <v>2.45</v>
+      </c>
+      <c r="AP235">
+        <v>1.75</v>
+      </c>
+      <c r="AQ235">
+        <v>2.5</v>
+      </c>
+      <c r="AR235">
+        <v>1.81</v>
+      </c>
+      <c r="AS235">
+        <v>2.11</v>
+      </c>
+      <c r="AT235">
+        <v>3.92</v>
+      </c>
+      <c r="AU235">
+        <v>4</v>
+      </c>
+      <c r="AV235">
+        <v>8</v>
+      </c>
+      <c r="AW235">
+        <v>11</v>
+      </c>
+      <c r="AX235">
+        <v>12</v>
+      </c>
+      <c r="AY235">
+        <v>18</v>
+      </c>
+      <c r="AZ235">
+        <v>27</v>
+      </c>
+      <c r="BA235">
+        <v>3</v>
+      </c>
+      <c r="BB235">
+        <v>3</v>
+      </c>
+      <c r="BC235">
+        <v>6</v>
+      </c>
+      <c r="BD235">
+        <v>2.7</v>
+      </c>
+      <c r="BE235">
+        <v>7</v>
+      </c>
+      <c r="BF235">
+        <v>1.53</v>
+      </c>
+      <c r="BG235">
+        <v>1.14</v>
+      </c>
+      <c r="BH235">
+        <v>4.8</v>
+      </c>
+      <c r="BI235">
+        <v>1.26</v>
+      </c>
+      <c r="BJ235">
+        <v>3.4</v>
+      </c>
+      <c r="BK235">
+        <v>1.44</v>
+      </c>
+      <c r="BL235">
+        <v>2.55</v>
+      </c>
+      <c r="BM235">
+        <v>1.72</v>
+      </c>
+      <c r="BN235">
+        <v>1.98</v>
+      </c>
+      <c r="BO235">
+        <v>2.08</v>
+      </c>
+      <c r="BP235">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="236" spans="1:68">
+      <c r="A236" s="1">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>7466918</v>
+      </c>
+      <c r="C236" t="s">
+        <v>68</v>
+      </c>
+      <c r="D236" t="s">
+        <v>69</v>
+      </c>
+      <c r="E236" s="2">
+        <v>45689.60416666666</v>
+      </c>
+      <c r="F236">
+        <v>24</v>
+      </c>
+      <c r="G236" t="s">
+        <v>87</v>
+      </c>
+      <c r="H236" t="s">
+        <v>86</v>
+      </c>
+      <c r="I236">
+        <v>1</v>
+      </c>
+      <c r="J236">
+        <v>0</v>
+      </c>
+      <c r="K236">
+        <v>1</v>
+      </c>
+      <c r="L236">
+        <v>2</v>
+      </c>
+      <c r="M236">
+        <v>0</v>
+      </c>
+      <c r="N236">
+        <v>2</v>
+      </c>
+      <c r="O236" t="s">
+        <v>247</v>
+      </c>
+      <c r="P236" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q236">
+        <v>3.75</v>
+      </c>
+      <c r="R236">
+        <v>2.3</v>
+      </c>
+      <c r="S236">
+        <v>2.63</v>
+      </c>
+      <c r="T236">
+        <v>1.33</v>
+      </c>
+      <c r="U236">
+        <v>3.25</v>
+      </c>
+      <c r="V236">
+        <v>2.5</v>
+      </c>
+      <c r="W236">
+        <v>1.5</v>
+      </c>
+      <c r="X236">
+        <v>6.5</v>
+      </c>
+      <c r="Y236">
+        <v>1.11</v>
+      </c>
+      <c r="Z236">
+        <v>3.4</v>
+      </c>
+      <c r="AA236">
+        <v>3.6</v>
+      </c>
+      <c r="AB236">
+        <v>2</v>
+      </c>
+      <c r="AC236">
+        <v>1.04</v>
+      </c>
+      <c r="AD236">
+        <v>14</v>
+      </c>
+      <c r="AE236">
+        <v>1.23</v>
+      </c>
+      <c r="AF236">
+        <v>4.45</v>
+      </c>
+      <c r="AG236">
+        <v>1.6</v>
+      </c>
+      <c r="AH236">
+        <v>2.25</v>
+      </c>
+      <c r="AI236">
+        <v>1.57</v>
+      </c>
+      <c r="AJ236">
+        <v>2.25</v>
+      </c>
+      <c r="AK236">
+        <v>1.71</v>
+      </c>
+      <c r="AL236">
+        <v>1.29</v>
+      </c>
+      <c r="AM236">
+        <v>1.31</v>
+      </c>
+      <c r="AN236">
+        <v>0.64</v>
+      </c>
+      <c r="AO236">
+        <v>1.27</v>
+      </c>
+      <c r="AP236">
+        <v>0.83</v>
+      </c>
+      <c r="AQ236">
+        <v>1.17</v>
+      </c>
+      <c r="AR236">
+        <v>1.21</v>
+      </c>
+      <c r="AS236">
+        <v>1.13</v>
+      </c>
+      <c r="AT236">
+        <v>2.34</v>
+      </c>
+      <c r="AU236">
+        <v>6</v>
+      </c>
+      <c r="AV236">
+        <v>4</v>
+      </c>
+      <c r="AW236">
+        <v>3</v>
+      </c>
+      <c r="AX236">
+        <v>7</v>
+      </c>
+      <c r="AY236">
+        <v>9</v>
+      </c>
+      <c r="AZ236">
+        <v>16</v>
+      </c>
+      <c r="BA236">
+        <v>5</v>
+      </c>
+      <c r="BB236">
+        <v>8</v>
+      </c>
+      <c r="BC236">
+        <v>13</v>
+      </c>
+      <c r="BD236">
+        <v>2.65</v>
+      </c>
+      <c r="BE236">
+        <v>7</v>
+      </c>
+      <c r="BF236">
+        <v>1.55</v>
+      </c>
+      <c r="BG236">
+        <v>1.19</v>
+      </c>
+      <c r="BH236">
+        <v>4.1</v>
+      </c>
+      <c r="BI236">
+        <v>1.33</v>
+      </c>
+      <c r="BJ236">
+        <v>2.95</v>
+      </c>
+      <c r="BK236">
+        <v>1.55</v>
+      </c>
+      <c r="BL236">
+        <v>2.25</v>
+      </c>
+      <c r="BM236">
+        <v>1.88</v>
+      </c>
+      <c r="BN236">
+        <v>1.81</v>
+      </c>
+      <c r="BO236">
+        <v>2.32</v>
+      </c>
+      <c r="BP236">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="237" spans="1:68">
+      <c r="A237" s="1">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>7466912</v>
+      </c>
+      <c r="C237" t="s">
+        <v>68</v>
+      </c>
+      <c r="D237" t="s">
+        <v>69</v>
+      </c>
+      <c r="E237" s="2">
+        <v>45690.45833333334</v>
+      </c>
+      <c r="F237">
+        <v>24</v>
+      </c>
+      <c r="G237" t="s">
+        <v>77</v>
+      </c>
+      <c r="H237" t="s">
+        <v>81</v>
+      </c>
+      <c r="I237">
+        <v>0</v>
+      </c>
+      <c r="J237">
+        <v>1</v>
+      </c>
+      <c r="K237">
+        <v>1</v>
+      </c>
+      <c r="L237">
+        <v>0</v>
+      </c>
+      <c r="M237">
+        <v>2</v>
+      </c>
+      <c r="N237">
+        <v>2</v>
+      </c>
+      <c r="O237" t="s">
+        <v>91</v>
+      </c>
+      <c r="P237" t="s">
+        <v>373</v>
+      </c>
+      <c r="Q237">
+        <v>2.5</v>
+      </c>
+      <c r="R237">
+        <v>2.63</v>
+      </c>
+      <c r="S237">
+        <v>3.25</v>
+      </c>
+      <c r="T237">
+        <v>1.2</v>
+      </c>
+      <c r="U237">
+        <v>4.33</v>
+      </c>
+      <c r="V237">
+        <v>1.91</v>
+      </c>
+      <c r="W237">
+        <v>1.8</v>
+      </c>
+      <c r="X237">
+        <v>4</v>
+      </c>
+      <c r="Y237">
+        <v>1.22</v>
+      </c>
+      <c r="Z237">
+        <v>2.4</v>
+      </c>
+      <c r="AA237">
+        <v>3.8</v>
+      </c>
+      <c r="AB237">
+        <v>2.62</v>
+      </c>
+      <c r="AC237">
+        <v>1.01</v>
+      </c>
+      <c r="AD237">
+        <v>29</v>
+      </c>
+      <c r="AE237">
+        <v>1.1</v>
+      </c>
+      <c r="AF237">
+        <v>7.6</v>
+      </c>
+      <c r="AG237">
+        <v>1.3</v>
+      </c>
+      <c r="AH237">
+        <v>3.33</v>
+      </c>
+      <c r="AI237">
+        <v>1.33</v>
+      </c>
+      <c r="AJ237">
+        <v>3.25</v>
+      </c>
+      <c r="AK237">
+        <v>1.36</v>
+      </c>
+      <c r="AL237">
+        <v>1.25</v>
+      </c>
+      <c r="AM237">
+        <v>1.7</v>
+      </c>
+      <c r="AN237">
+        <v>1.92</v>
+      </c>
+      <c r="AO237">
+        <v>0.91</v>
+      </c>
+      <c r="AP237">
+        <v>1.77</v>
+      </c>
+      <c r="AQ237">
+        <v>1.08</v>
+      </c>
+      <c r="AR237">
+        <v>1.59</v>
+      </c>
+      <c r="AS237">
+        <v>1.63</v>
+      </c>
+      <c r="AT237">
+        <v>3.22</v>
+      </c>
+      <c r="AU237">
+        <v>5</v>
+      </c>
+      <c r="AV237">
+        <v>3</v>
+      </c>
+      <c r="AW237">
+        <v>16</v>
+      </c>
+      <c r="AX237">
+        <v>11</v>
+      </c>
+      <c r="AY237">
+        <v>28</v>
+      </c>
+      <c r="AZ237">
+        <v>20</v>
+      </c>
+      <c r="BA237">
+        <v>10</v>
+      </c>
+      <c r="BB237">
+        <v>3</v>
+      </c>
+      <c r="BC237">
+        <v>13</v>
+      </c>
+      <c r="BD237">
+        <v>1.98</v>
+      </c>
+      <c r="BE237">
+        <v>7</v>
+      </c>
+      <c r="BF237">
+        <v>1.95</v>
+      </c>
+      <c r="BG237">
+        <v>1.08</v>
+      </c>
+      <c r="BH237">
+        <v>5.8</v>
+      </c>
+      <c r="BI237">
+        <v>1.16</v>
+      </c>
+      <c r="BJ237">
+        <v>4.3</v>
+      </c>
+      <c r="BK237">
+        <v>1.3</v>
+      </c>
+      <c r="BL237">
+        <v>3.15</v>
+      </c>
+      <c r="BM237">
+        <v>1.48</v>
+      </c>
+      <c r="BN237">
+        <v>2.43</v>
+      </c>
+      <c r="BO237">
+        <v>1.75</v>
+      </c>
+      <c r="BP237">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="238" spans="1:68">
+      <c r="A238" s="1">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>7466915</v>
+      </c>
+      <c r="C238" t="s">
+        <v>68</v>
+      </c>
+      <c r="D238" t="s">
+        <v>69</v>
+      </c>
+      <c r="E238" s="2">
+        <v>45690.45833333334</v>
+      </c>
+      <c r="F238">
+        <v>24</v>
+      </c>
+      <c r="G238" t="s">
+        <v>70</v>
+      </c>
+      <c r="H238" t="s">
+        <v>82</v>
+      </c>
+      <c r="I238">
+        <v>0</v>
+      </c>
+      <c r="J238">
+        <v>0</v>
+      </c>
+      <c r="K238">
+        <v>0</v>
+      </c>
+      <c r="L238">
+        <v>0</v>
+      </c>
+      <c r="M238">
+        <v>2</v>
+      </c>
+      <c r="N238">
+        <v>2</v>
+      </c>
+      <c r="O238" t="s">
+        <v>91</v>
+      </c>
+      <c r="P238" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q238">
+        <v>2.75</v>
+      </c>
+      <c r="R238">
+        <v>2.2</v>
+      </c>
+      <c r="S238">
+        <v>3.75</v>
+      </c>
+      <c r="T238">
+        <v>1.36</v>
+      </c>
+      <c r="U238">
+        <v>3</v>
+      </c>
+      <c r="V238">
+        <v>2.75</v>
+      </c>
+      <c r="W238">
+        <v>1.4</v>
+      </c>
+      <c r="X238">
+        <v>7</v>
+      </c>
+      <c r="Y238">
+        <v>1.1</v>
+      </c>
+      <c r="Z238">
+        <v>1.95</v>
+      </c>
+      <c r="AA238">
+        <v>3.6</v>
+      </c>
+      <c r="AB238">
+        <v>3.7</v>
+      </c>
+      <c r="AC238">
+        <v>1.06</v>
+      </c>
+      <c r="AD238">
+        <v>11</v>
+      </c>
+      <c r="AE238">
+        <v>1.29</v>
+      </c>
+      <c r="AF238">
+        <v>3.8</v>
+      </c>
+      <c r="AG238">
+        <v>1.85</v>
+      </c>
+      <c r="AH238">
+        <v>1.85</v>
+      </c>
+      <c r="AI238">
+        <v>1.67</v>
+      </c>
+      <c r="AJ238">
+        <v>2.1</v>
+      </c>
+      <c r="AK238">
+        <v>1.31</v>
+      </c>
+      <c r="AL238">
+        <v>1.3</v>
+      </c>
+      <c r="AM238">
+        <v>1.7</v>
+      </c>
+      <c r="AN238">
+        <v>1.33</v>
+      </c>
+      <c r="AO238">
+        <v>1.45</v>
+      </c>
+      <c r="AP238">
+        <v>1.23</v>
+      </c>
+      <c r="AQ238">
+        <v>1.58</v>
+      </c>
+      <c r="AR238">
+        <v>1.51</v>
+      </c>
+      <c r="AS238">
+        <v>1.4</v>
+      </c>
+      <c r="AT238">
+        <v>2.91</v>
+      </c>
+      <c r="AU238">
+        <v>3</v>
+      </c>
+      <c r="AV238">
+        <v>4</v>
+      </c>
+      <c r="AW238">
+        <v>16</v>
+      </c>
+      <c r="AX238">
+        <v>8</v>
+      </c>
+      <c r="AY238">
+        <v>25</v>
+      </c>
+      <c r="AZ238">
+        <v>13</v>
+      </c>
+      <c r="BA238">
+        <v>11</v>
+      </c>
+      <c r="BB238">
+        <v>0</v>
+      </c>
+      <c r="BC238">
+        <v>11</v>
+      </c>
+      <c r="BD238">
+        <v>1.57</v>
+      </c>
+      <c r="BE238">
+        <v>6.75</v>
+      </c>
+      <c r="BF238">
+        <v>2.63</v>
+      </c>
+      <c r="BG238">
+        <v>1.19</v>
+      </c>
+      <c r="BH238">
+        <v>4</v>
+      </c>
+      <c r="BI238">
+        <v>1.35</v>
+      </c>
+      <c r="BJ238">
+        <v>2.9</v>
+      </c>
+      <c r="BK238">
+        <v>1.58</v>
+      </c>
+      <c r="BL238">
+        <v>2.2</v>
+      </c>
+      <c r="BM238">
+        <v>1.9</v>
+      </c>
+      <c r="BN238">
+        <v>1.78</v>
+      </c>
+      <c r="BO238">
+        <v>2.38</v>
+      </c>
+      <c r="BP238">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="377">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -760,6 +760,12 @@
     <t>['12', '90+7']</t>
   </si>
   <si>
+    <t>['2', '56', '62', '76', '90+3']</t>
+  </si>
+  <si>
+    <t>['64', '74']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1500,7 +1506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP238"/>
+  <dimension ref="A1:BP240"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1962,7 +1968,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2246,7 +2252,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ4">
         <v>0.75</v>
@@ -2374,7 +2380,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2786,7 +2792,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2992,7 +2998,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3404,7 +3410,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3482,10 +3488,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ10">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3816,7 +3822,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4309,7 +4315,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ14">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -5052,7 +5058,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5258,7 +5264,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5954,7 +5960,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ22">
         <v>1.46</v>
@@ -6082,7 +6088,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6288,7 +6294,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6906,7 +6912,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7112,7 +7118,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7193,7 +7199,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ28">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR28">
         <v>1.25</v>
@@ -7318,7 +7324,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7396,7 +7402,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ29">
         <v>1.58</v>
@@ -7730,7 +7736,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7936,7 +7942,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8348,7 +8354,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -8635,7 +8641,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ35">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR35">
         <v>1.87</v>
@@ -9172,7 +9178,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9378,7 +9384,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9584,7 +9590,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9790,7 +9796,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9996,7 +10002,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10202,7 +10208,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -11850,7 +11856,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -12056,7 +12062,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12137,7 +12143,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ52">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR52">
         <v>0.75</v>
@@ -12262,7 +12268,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12674,7 +12680,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -12752,7 +12758,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ55">
         <v>0.67</v>
@@ -12961,7 +12967,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ56">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR56">
         <v>1.59</v>
@@ -13086,7 +13092,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13164,7 +13170,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ57">
         <v>1.46</v>
@@ -13292,7 +13298,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13498,7 +13504,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13704,7 +13710,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13910,7 +13916,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14116,7 +14122,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14528,7 +14534,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14734,7 +14740,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14940,7 +14946,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -15224,7 +15230,7 @@
         <v>0</v>
       </c>
       <c r="AP67">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ67">
         <v>0.38</v>
@@ -15636,7 +15642,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ69">
         <v>1.92</v>
@@ -15970,7 +15976,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16176,7 +16182,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q72">
         <v>1.95</v>
@@ -16257,7 +16263,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ72">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR72">
         <v>1.91</v>
@@ -16382,7 +16388,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16588,7 +16594,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16794,7 +16800,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -17000,7 +17006,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17206,7 +17212,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17618,7 +17624,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17699,7 +17705,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ79">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR79">
         <v>1.27</v>
@@ -17824,7 +17830,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18236,7 +18242,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18648,7 +18654,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18854,7 +18860,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -19060,7 +19066,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19472,7 +19478,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19550,7 +19556,7 @@
         <v>1.25</v>
       </c>
       <c r="AP88">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ88">
         <v>1.75</v>
@@ -19884,7 +19890,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20090,7 +20096,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20168,7 +20174,7 @@
         <v>3</v>
       </c>
       <c r="AP91">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ91">
         <v>2.5</v>
@@ -20789,7 +20795,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ94">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR94">
         <v>1.6</v>
@@ -21407,7 +21413,7 @@
         <v>2</v>
       </c>
       <c r="AQ97">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR97">
         <v>1.51</v>
@@ -21532,7 +21538,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21738,7 +21744,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -21944,7 +21950,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22356,7 +22362,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22562,7 +22568,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23261,7 +23267,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ106">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR106">
         <v>1.54</v>
@@ -23798,7 +23804,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -24004,7 +24010,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24210,7 +24216,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q111">
         <v>3.25</v>
@@ -24288,7 +24294,7 @@
         <v>1.4</v>
       </c>
       <c r="AP111">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ111">
         <v>1.83</v>
@@ -24416,7 +24422,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24622,7 +24628,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -25112,7 +25118,7 @@
         <v>2.2</v>
       </c>
       <c r="AP115">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ115">
         <v>1.92</v>
@@ -25240,7 +25246,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25446,7 +25452,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25652,7 +25658,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25858,7 +25864,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -26064,7 +26070,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26270,7 +26276,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26351,7 +26357,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ121">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR121">
         <v>1.12</v>
@@ -26476,7 +26482,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26682,7 +26688,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -27300,7 +27306,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27506,7 +27512,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -27996,7 +28002,7 @@
         <v>1.67</v>
       </c>
       <c r="AP129">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ129">
         <v>1.17</v>
@@ -28124,7 +28130,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28411,7 +28417,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ131">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR131">
         <v>1.72</v>
@@ -28536,7 +28542,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28823,7 +28829,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ133">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR133">
         <v>1.02</v>
@@ -28948,7 +28954,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29154,7 +29160,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -30056,7 +30062,7 @@
         <v>1</v>
       </c>
       <c r="AP139">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ139">
         <v>1.18</v>
@@ -30596,7 +30602,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30677,7 +30683,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ142">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR142">
         <v>1.38</v>
@@ -30802,7 +30808,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -31214,7 +31220,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31420,7 +31426,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31626,7 +31632,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31832,7 +31838,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -32038,7 +32044,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32450,7 +32456,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -32734,7 +32740,7 @@
         <v>0.71</v>
       </c>
       <c r="AP152">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ152">
         <v>0.91</v>
@@ -33068,7 +33074,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33274,7 +33280,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33480,7 +33486,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33686,7 +33692,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33892,7 +33898,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34176,7 +34182,7 @@
         <v>0.14</v>
       </c>
       <c r="AP159">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ159">
         <v>0.73</v>
@@ -34385,7 +34391,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ160">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR160">
         <v>1.69</v>
@@ -34591,7 +34597,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ161">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR161">
         <v>1.54</v>
@@ -34716,7 +34722,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -34922,7 +34928,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35128,7 +35134,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35334,7 +35340,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35746,7 +35752,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35952,7 +35958,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36364,7 +36370,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36776,7 +36782,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -36857,7 +36863,7 @@
         <v>0.36</v>
       </c>
       <c r="AQ172">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR172">
         <v>1.06</v>
@@ -37394,7 +37400,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -37472,7 +37478,7 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ175">
         <v>1.58</v>
@@ -38012,7 +38018,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38502,7 +38508,7 @@
         <v>1</v>
       </c>
       <c r="AP180">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ180">
         <v>0.82</v>
@@ -38630,7 +38636,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38711,7 +38717,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ181">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR181">
         <v>1.08</v>
@@ -38836,7 +38842,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39248,7 +39254,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39454,7 +39460,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39660,7 +39666,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -40072,7 +40078,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40278,7 +40284,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40484,7 +40490,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40690,7 +40696,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -41102,7 +41108,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41514,7 +41520,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41720,7 +41726,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -41801,7 +41807,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ196">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR196">
         <v>2.09</v>
@@ -42132,7 +42138,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42338,7 +42344,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42544,7 +42550,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42750,7 +42756,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -42828,7 +42834,7 @@
         <v>1.5</v>
       </c>
       <c r="AP201">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ201">
         <v>1.58</v>
@@ -42956,7 +42962,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43162,7 +43168,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43243,7 +43249,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ203">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR203">
         <v>1.57</v>
@@ -43368,7 +43374,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43574,7 +43580,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -43986,7 +43992,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44270,7 +44276,7 @@
         <v>1.11</v>
       </c>
       <c r="AP208">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ208">
         <v>1.08</v>
@@ -44398,7 +44404,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44810,7 +44816,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45016,7 +45022,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45222,7 +45228,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45428,7 +45434,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45634,7 +45640,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -45712,7 +45718,7 @@
         <v>1.3</v>
       </c>
       <c r="AP215">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ215">
         <v>1.17</v>
@@ -45840,7 +45846,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -46046,7 +46052,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46252,7 +46258,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46458,7 +46464,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46539,7 +46545,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ219">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR219">
         <v>1.13</v>
@@ -46664,7 +46670,7 @@
         <v>240</v>
       </c>
       <c r="P220" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q220">
         <v>1.73</v>
@@ -46742,7 +46748,7 @@
         <v>0.82</v>
       </c>
       <c r="AP220">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ220">
         <v>0.75</v>
@@ -47076,7 +47082,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -47488,7 +47494,7 @@
         <v>107</v>
       </c>
       <c r="P224" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q224">
         <v>6</v>
@@ -47694,7 +47700,7 @@
         <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q225">
         <v>6.5</v>
@@ -47900,7 +47906,7 @@
         <v>243</v>
       </c>
       <c r="P226" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q226">
         <v>2.38</v>
@@ -48106,7 +48112,7 @@
         <v>155</v>
       </c>
       <c r="P227" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48312,7 +48318,7 @@
         <v>244</v>
       </c>
       <c r="P228" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q228">
         <v>1.91</v>
@@ -48599,7 +48605,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ229">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR229">
         <v>1.51</v>
@@ -48724,7 +48730,7 @@
         <v>91</v>
       </c>
       <c r="P230" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q230">
         <v>2.88</v>
@@ -49136,7 +49142,7 @@
         <v>95</v>
       </c>
       <c r="P232" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q232">
         <v>2.2</v>
@@ -49548,7 +49554,7 @@
         <v>151</v>
       </c>
       <c r="P234" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q234">
         <v>2.6</v>
@@ -49754,7 +49760,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q235">
         <v>4.5</v>
@@ -50166,7 +50172,7 @@
         <v>91</v>
       </c>
       <c r="P237" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50372,7 +50378,7 @@
         <v>91</v>
       </c>
       <c r="P238" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q238">
         <v>2.75</v>
@@ -50529,6 +50535,418 @@
       </c>
       <c r="BP238">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="239" spans="1:68">
+      <c r="A239" s="1">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>7466911</v>
+      </c>
+      <c r="C239" t="s">
+        <v>68</v>
+      </c>
+      <c r="D239" t="s">
+        <v>69</v>
+      </c>
+      <c r="E239" s="2">
+        <v>45690.5625</v>
+      </c>
+      <c r="F239">
+        <v>24</v>
+      </c>
+      <c r="G239" t="s">
+        <v>72</v>
+      </c>
+      <c r="H239" t="s">
+        <v>85</v>
+      </c>
+      <c r="I239">
+        <v>1</v>
+      </c>
+      <c r="J239">
+        <v>0</v>
+      </c>
+      <c r="K239">
+        <v>1</v>
+      </c>
+      <c r="L239">
+        <v>5</v>
+      </c>
+      <c r="M239">
+        <v>1</v>
+      </c>
+      <c r="N239">
+        <v>6</v>
+      </c>
+      <c r="O239" t="s">
+        <v>248</v>
+      </c>
+      <c r="P239" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q239">
+        <v>2.63</v>
+      </c>
+      <c r="R239">
+        <v>2.25</v>
+      </c>
+      <c r="S239">
+        <v>3.75</v>
+      </c>
+      <c r="T239">
+        <v>1.36</v>
+      </c>
+      <c r="U239">
+        <v>3</v>
+      </c>
+      <c r="V239">
+        <v>2.63</v>
+      </c>
+      <c r="W239">
+        <v>1.44</v>
+      </c>
+      <c r="X239">
+        <v>7</v>
+      </c>
+      <c r="Y239">
+        <v>1.1</v>
+      </c>
+      <c r="Z239">
+        <v>2.1</v>
+      </c>
+      <c r="AA239">
+        <v>3.5</v>
+      </c>
+      <c r="AB239">
+        <v>3.3</v>
+      </c>
+      <c r="AC239">
+        <v>1.05</v>
+      </c>
+      <c r="AD239">
+        <v>12</v>
+      </c>
+      <c r="AE239">
+        <v>1.27</v>
+      </c>
+      <c r="AF239">
+        <v>4</v>
+      </c>
+      <c r="AG239">
+        <v>1.85</v>
+      </c>
+      <c r="AH239">
+        <v>1.85</v>
+      </c>
+      <c r="AI239">
+        <v>1.67</v>
+      </c>
+      <c r="AJ239">
+        <v>2.1</v>
+      </c>
+      <c r="AK239">
+        <v>1.31</v>
+      </c>
+      <c r="AL239">
+        <v>1.28</v>
+      </c>
+      <c r="AM239">
+        <v>1.72</v>
+      </c>
+      <c r="AN239">
+        <v>2.27</v>
+      </c>
+      <c r="AO239">
+        <v>1.5</v>
+      </c>
+      <c r="AP239">
+        <v>2.33</v>
+      </c>
+      <c r="AQ239">
+        <v>1.38</v>
+      </c>
+      <c r="AR239">
+        <v>2</v>
+      </c>
+      <c r="AS239">
+        <v>1.89</v>
+      </c>
+      <c r="AT239">
+        <v>3.89</v>
+      </c>
+      <c r="AU239">
+        <v>8</v>
+      </c>
+      <c r="AV239">
+        <v>5</v>
+      </c>
+      <c r="AW239">
+        <v>5</v>
+      </c>
+      <c r="AX239">
+        <v>3</v>
+      </c>
+      <c r="AY239">
+        <v>15</v>
+      </c>
+      <c r="AZ239">
+        <v>8</v>
+      </c>
+      <c r="BA239">
+        <v>5</v>
+      </c>
+      <c r="BB239">
+        <v>2</v>
+      </c>
+      <c r="BC239">
+        <v>7</v>
+      </c>
+      <c r="BD239">
+        <v>1.74</v>
+      </c>
+      <c r="BE239">
+        <v>6.75</v>
+      </c>
+      <c r="BF239">
+        <v>2.3</v>
+      </c>
+      <c r="BG239">
+        <v>1.27</v>
+      </c>
+      <c r="BH239">
+        <v>3.3</v>
+      </c>
+      <c r="BI239">
+        <v>1.48</v>
+      </c>
+      <c r="BJ239">
+        <v>2.45</v>
+      </c>
+      <c r="BK239">
+        <v>1.77</v>
+      </c>
+      <c r="BL239">
+        <v>1.92</v>
+      </c>
+      <c r="BM239">
+        <v>2.23</v>
+      </c>
+      <c r="BN239">
+        <v>1.57</v>
+      </c>
+      <c r="BO239">
+        <v>2.88</v>
+      </c>
+      <c r="BP239">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="240" spans="1:68">
+      <c r="A240" s="1">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>7466913</v>
+      </c>
+      <c r="C240" t="s">
+        <v>68</v>
+      </c>
+      <c r="D240" t="s">
+        <v>69</v>
+      </c>
+      <c r="E240" s="2">
+        <v>45691.70833333334</v>
+      </c>
+      <c r="F240">
+        <v>24</v>
+      </c>
+      <c r="G240" t="s">
+        <v>78</v>
+      </c>
+      <c r="H240" t="s">
+        <v>76</v>
+      </c>
+      <c r="I240">
+        <v>0</v>
+      </c>
+      <c r="J240">
+        <v>1</v>
+      </c>
+      <c r="K240">
+        <v>1</v>
+      </c>
+      <c r="L240">
+        <v>2</v>
+      </c>
+      <c r="M240">
+        <v>1</v>
+      </c>
+      <c r="N240">
+        <v>3</v>
+      </c>
+      <c r="O240" t="s">
+        <v>249</v>
+      </c>
+      <c r="P240" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q240">
+        <v>1.8</v>
+      </c>
+      <c r="R240">
+        <v>2.75</v>
+      </c>
+      <c r="S240">
+        <v>6.5</v>
+      </c>
+      <c r="T240">
+        <v>1.22</v>
+      </c>
+      <c r="U240">
+        <v>4</v>
+      </c>
+      <c r="V240">
+        <v>2.1</v>
+      </c>
+      <c r="W240">
+        <v>1.67</v>
+      </c>
+      <c r="X240">
+        <v>4.5</v>
+      </c>
+      <c r="Y240">
+        <v>1.18</v>
+      </c>
+      <c r="Z240">
+        <v>1.3</v>
+      </c>
+      <c r="AA240">
+        <v>5.8</v>
+      </c>
+      <c r="AB240">
+        <v>7.5</v>
+      </c>
+      <c r="AC240">
+        <v>1.01</v>
+      </c>
+      <c r="AD240">
+        <v>28</v>
+      </c>
+      <c r="AE240">
+        <v>1.13</v>
+      </c>
+      <c r="AF240">
+        <v>6.4</v>
+      </c>
+      <c r="AG240">
+        <v>1.55</v>
+      </c>
+      <c r="AH240">
+        <v>2.3</v>
+      </c>
+      <c r="AI240">
+        <v>1.62</v>
+      </c>
+      <c r="AJ240">
+        <v>2.2</v>
+      </c>
+      <c r="AK240">
+        <v>1.1</v>
+      </c>
+      <c r="AL240">
+        <v>1.15</v>
+      </c>
+      <c r="AM240">
+        <v>2.95</v>
+      </c>
+      <c r="AN240">
+        <v>1.73</v>
+      </c>
+      <c r="AO240">
+        <v>1.18</v>
+      </c>
+      <c r="AP240">
+        <v>1.83</v>
+      </c>
+      <c r="AQ240">
+        <v>1.08</v>
+      </c>
+      <c r="AR240">
+        <v>1.89</v>
+      </c>
+      <c r="AS240">
+        <v>1.47</v>
+      </c>
+      <c r="AT240">
+        <v>3.36</v>
+      </c>
+      <c r="AU240">
+        <v>4</v>
+      </c>
+      <c r="AV240">
+        <v>5</v>
+      </c>
+      <c r="AW240">
+        <v>19</v>
+      </c>
+      <c r="AX240">
+        <v>9</v>
+      </c>
+      <c r="AY240">
+        <v>32</v>
+      </c>
+      <c r="AZ240">
+        <v>18</v>
+      </c>
+      <c r="BA240">
+        <v>4</v>
+      </c>
+      <c r="BB240">
+        <v>3</v>
+      </c>
+      <c r="BC240">
+        <v>7</v>
+      </c>
+      <c r="BD240">
+        <v>1.27</v>
+      </c>
+      <c r="BE240">
+        <v>8</v>
+      </c>
+      <c r="BF240">
+        <v>4.1</v>
+      </c>
+      <c r="BG240">
+        <v>1.21</v>
+      </c>
+      <c r="BH240">
+        <v>3.8</v>
+      </c>
+      <c r="BI240">
+        <v>1.37</v>
+      </c>
+      <c r="BJ240">
+        <v>2.8</v>
+      </c>
+      <c r="BK240">
+        <v>1.6</v>
+      </c>
+      <c r="BL240">
+        <v>2.17</v>
+      </c>
+      <c r="BM240">
+        <v>1.96</v>
+      </c>
+      <c r="BN240">
+        <v>1.74</v>
+      </c>
+      <c r="BO240">
+        <v>2.43</v>
+      </c>
+      <c r="BP240">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="379">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -766,6 +766,9 @@
     <t>['64', '74']</t>
   </si>
   <si>
+    <t>['11', '90+8']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1146,6 +1149,9 @@
   <si>
     <t>['64', '89']</t>
   </si>
+  <si>
+    <t>['16', '73']</t>
+  </si>
 </sst>
 </file>
 
@@ -1506,7 +1512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP240"/>
+  <dimension ref="A1:BP241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1968,7 +1974,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2049,7 +2055,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ3">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2380,7 +2386,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2458,7 +2464,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ5">
         <v>1.46</v>
@@ -2792,7 +2798,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2998,7 +3004,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3410,7 +3416,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3822,7 +3828,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -5058,7 +5064,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5264,7 +5270,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -6088,7 +6094,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6294,7 +6300,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6912,7 +6918,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6990,7 +6996,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ27">
         <v>1.58</v>
@@ -7118,7 +7124,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7324,7 +7330,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7736,7 +7742,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7817,7 +7823,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ31">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR31">
         <v>1.62</v>
@@ -7942,7 +7948,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8354,7 +8360,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -9178,7 +9184,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9384,7 +9390,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9590,7 +9596,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9796,7 +9802,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -10002,7 +10008,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10208,7 +10214,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -11856,7 +11862,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -12062,7 +12068,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12268,7 +12274,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12552,7 +12558,7 @@
         <v>0.5</v>
       </c>
       <c r="AP54">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ54">
         <v>1.58</v>
@@ -12680,7 +12686,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -13092,7 +13098,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13298,7 +13304,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13379,7 +13385,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ58">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR58">
         <v>1.42</v>
@@ -13504,7 +13510,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13710,7 +13716,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13916,7 +13922,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14122,7 +14128,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14203,7 +14209,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ62">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR62">
         <v>1.29</v>
@@ -14534,7 +14540,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14740,7 +14746,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14946,7 +14952,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -15436,7 +15442,7 @@
         <v>1.33</v>
       </c>
       <c r="AP68">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ68">
         <v>1.75</v>
@@ -15976,7 +15982,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16182,7 +16188,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q72">
         <v>1.95</v>
@@ -16388,7 +16394,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16594,7 +16600,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16800,7 +16806,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -17006,7 +17012,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17212,7 +17218,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17624,7 +17630,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17830,7 +17836,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18242,7 +18248,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18654,7 +18660,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18860,7 +18866,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -19066,7 +19072,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19350,7 +19356,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ87">
         <v>1.58</v>
@@ -19478,7 +19484,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19890,7 +19896,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20096,7 +20102,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20177,7 +20183,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ91">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR91">
         <v>2.46</v>
@@ -21538,7 +21544,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21744,7 +21750,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -21950,7 +21956,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22362,7 +22368,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22568,7 +22574,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23804,7 +23810,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -24010,7 +24016,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24216,7 +24222,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q111">
         <v>3.25</v>
@@ -24422,7 +24428,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24628,7 +24634,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -24912,7 +24918,7 @@
         <v>0</v>
       </c>
       <c r="AP114">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ114">
         <v>0.73</v>
@@ -25246,7 +25252,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25452,7 +25458,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25658,7 +25664,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25864,7 +25870,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -25945,7 +25951,7 @@
         <v>0.36</v>
       </c>
       <c r="AQ119">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR119">
         <v>1.07</v>
@@ -26070,7 +26076,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26276,7 +26282,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26482,7 +26488,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26688,7 +26694,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -27306,7 +27312,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27512,7 +27518,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -28130,7 +28136,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28542,7 +28548,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28954,7 +28960,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29160,7 +29166,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -29241,7 +29247,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ135">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR135">
         <v>1.25</v>
@@ -29650,7 +29656,7 @@
         <v>0.83</v>
       </c>
       <c r="AP137">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ137">
         <v>0.75</v>
@@ -30602,7 +30608,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30808,7 +30814,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -31220,7 +31226,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31426,7 +31432,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31632,7 +31638,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31838,7 +31844,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -32044,7 +32050,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32456,7 +32462,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -33074,7 +33080,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33280,7 +33286,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33486,7 +33492,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33692,7 +33698,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33898,7 +33904,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34722,7 +34728,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -34928,7 +34934,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35134,7 +35140,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35340,7 +35346,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35752,7 +35758,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35958,7 +35964,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36242,7 +36248,7 @@
         <v>2.38</v>
       </c>
       <c r="AP169">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ169">
         <v>1.75</v>
@@ -36370,7 +36376,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36451,7 +36457,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ170">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR170">
         <v>1.79</v>
@@ -36782,7 +36788,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37400,7 +37406,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -38018,7 +38024,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38636,7 +38642,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38842,7 +38848,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39254,7 +39260,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39460,7 +39466,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39538,7 +39544,7 @@
         <v>1.89</v>
       </c>
       <c r="AP185">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ185">
         <v>1.92</v>
@@ -39666,7 +39672,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -39747,7 +39753,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ186">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR186">
         <v>1.43</v>
@@ -40078,7 +40084,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40284,7 +40290,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40490,7 +40496,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40696,7 +40702,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -41108,7 +41114,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41520,7 +41526,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41726,7 +41732,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -42138,7 +42144,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42344,7 +42350,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42550,7 +42556,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42756,7 +42762,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -42962,7 +42968,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43168,7 +43174,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43374,7 +43380,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43455,7 +43461,7 @@
         <v>2</v>
       </c>
       <c r="AQ204">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR204">
         <v>1.5</v>
@@ -43580,7 +43586,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -43992,7 +43998,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44070,7 +44076,7 @@
         <v>1.11</v>
       </c>
       <c r="AP207">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ207">
         <v>1.17</v>
@@ -44404,7 +44410,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44816,7 +44822,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45022,7 +45028,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45228,7 +45234,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45309,7 +45315,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ213">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR213">
         <v>1.61</v>
@@ -45434,7 +45440,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45640,7 +45646,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -45846,7 +45852,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -46052,7 +46058,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46258,7 +46264,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46336,7 +46342,7 @@
         <v>1</v>
       </c>
       <c r="AP218">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ218">
         <v>1.08</v>
@@ -46464,7 +46470,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46670,7 +46676,7 @@
         <v>240</v>
       </c>
       <c r="P220" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q220">
         <v>1.73</v>
@@ -47082,7 +47088,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -47494,7 +47500,7 @@
         <v>107</v>
       </c>
       <c r="P224" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q224">
         <v>6</v>
@@ -47700,7 +47706,7 @@
         <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q225">
         <v>6.5</v>
@@ -47906,7 +47912,7 @@
         <v>243</v>
       </c>
       <c r="P226" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q226">
         <v>2.38</v>
@@ -48112,7 +48118,7 @@
         <v>155</v>
       </c>
       <c r="P227" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48318,7 +48324,7 @@
         <v>244</v>
       </c>
       <c r="P228" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q228">
         <v>1.91</v>
@@ -48730,7 +48736,7 @@
         <v>91</v>
       </c>
       <c r="P230" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q230">
         <v>2.88</v>
@@ -49142,7 +49148,7 @@
         <v>95</v>
       </c>
       <c r="P232" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q232">
         <v>2.2</v>
@@ -49426,7 +49432,7 @@
         <v>0.73</v>
       </c>
       <c r="AP233">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ233">
         <v>0.67</v>
@@ -49554,7 +49560,7 @@
         <v>151</v>
       </c>
       <c r="P234" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q234">
         <v>2.6</v>
@@ -49760,7 +49766,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q235">
         <v>4.5</v>
@@ -49841,7 +49847,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ235">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR235">
         <v>1.81</v>
@@ -50172,7 +50178,7 @@
         <v>91</v>
       </c>
       <c r="P237" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50378,7 +50384,7 @@
         <v>91</v>
       </c>
       <c r="P238" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q238">
         <v>2.75</v>
@@ -50790,7 +50796,7 @@
         <v>249</v>
       </c>
       <c r="P240" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q240">
         <v>1.8</v>
@@ -50947,6 +50953,212 @@
       </c>
       <c r="BP240">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="241" spans="1:68">
+      <c r="A241" s="1">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>7466820</v>
+      </c>
+      <c r="C241" t="s">
+        <v>68</v>
+      </c>
+      <c r="D241" t="s">
+        <v>69</v>
+      </c>
+      <c r="E241" s="2">
+        <v>45700.6875</v>
+      </c>
+      <c r="F241">
+        <v>15</v>
+      </c>
+      <c r="G241" t="s">
+        <v>73</v>
+      </c>
+      <c r="H241" t="s">
+        <v>89</v>
+      </c>
+      <c r="I241">
+        <v>1</v>
+      </c>
+      <c r="J241">
+        <v>1</v>
+      </c>
+      <c r="K241">
+        <v>2</v>
+      </c>
+      <c r="L241">
+        <v>2</v>
+      </c>
+      <c r="M241">
+        <v>2</v>
+      </c>
+      <c r="N241">
+        <v>4</v>
+      </c>
+      <c r="O241" t="s">
+        <v>250</v>
+      </c>
+      <c r="P241" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q241">
+        <v>6</v>
+      </c>
+      <c r="R241">
+        <v>2.5</v>
+      </c>
+      <c r="S241">
+        <v>1.95</v>
+      </c>
+      <c r="T241">
+        <v>1.3</v>
+      </c>
+      <c r="U241">
+        <v>3.4</v>
+      </c>
+      <c r="V241">
+        <v>2.5</v>
+      </c>
+      <c r="W241">
+        <v>1.5</v>
+      </c>
+      <c r="X241">
+        <v>6</v>
+      </c>
+      <c r="Y241">
+        <v>1.13</v>
+      </c>
+      <c r="Z241">
+        <v>6.5</v>
+      </c>
+      <c r="AA241">
+        <v>4.6</v>
+      </c>
+      <c r="AB241">
+        <v>1.4</v>
+      </c>
+      <c r="AC241">
+        <v>1.03</v>
+      </c>
+      <c r="AD241">
+        <v>11</v>
+      </c>
+      <c r="AE241">
+        <v>1.2</v>
+      </c>
+      <c r="AF241">
+        <v>4.33</v>
+      </c>
+      <c r="AG241">
+        <v>1.65</v>
+      </c>
+      <c r="AH241">
+        <v>2.1</v>
+      </c>
+      <c r="AI241">
+        <v>1.8</v>
+      </c>
+      <c r="AJ241">
+        <v>1.95</v>
+      </c>
+      <c r="AK241">
+        <v>2.62</v>
+      </c>
+      <c r="AL241">
+        <v>1.15</v>
+      </c>
+      <c r="AM241">
+        <v>1.11</v>
+      </c>
+      <c r="AN241">
+        <v>1.33</v>
+      </c>
+      <c r="AO241">
+        <v>2.5</v>
+      </c>
+      <c r="AP241">
+        <v>1.31</v>
+      </c>
+      <c r="AQ241">
+        <v>2.38</v>
+      </c>
+      <c r="AR241">
+        <v>1.39</v>
+      </c>
+      <c r="AS241">
+        <v>2.11</v>
+      </c>
+      <c r="AT241">
+        <v>3.5</v>
+      </c>
+      <c r="AU241">
+        <v>4</v>
+      </c>
+      <c r="AV241">
+        <v>5</v>
+      </c>
+      <c r="AW241">
+        <v>7</v>
+      </c>
+      <c r="AX241">
+        <v>2</v>
+      </c>
+      <c r="AY241">
+        <v>13</v>
+      </c>
+      <c r="AZ241">
+        <v>9</v>
+      </c>
+      <c r="BA241">
+        <v>2</v>
+      </c>
+      <c r="BB241">
+        <v>3</v>
+      </c>
+      <c r="BC241">
+        <v>5</v>
+      </c>
+      <c r="BD241">
+        <v>3.65</v>
+      </c>
+      <c r="BE241">
+        <v>7.5</v>
+      </c>
+      <c r="BF241">
+        <v>1.32</v>
+      </c>
+      <c r="BG241">
+        <v>1.18</v>
+      </c>
+      <c r="BH241">
+        <v>4.2</v>
+      </c>
+      <c r="BI241">
+        <v>1.3</v>
+      </c>
+      <c r="BJ241">
+        <v>3.05</v>
+      </c>
+      <c r="BK241">
+        <v>1.52</v>
+      </c>
+      <c r="BL241">
+        <v>2.33</v>
+      </c>
+      <c r="BM241">
+        <v>1.82</v>
+      </c>
+      <c r="BN241">
+        <v>1.87</v>
+      </c>
+      <c r="BO241">
+        <v>2.23</v>
+      </c>
+      <c r="BP241">
+        <v>1.56</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="380">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -769,6 +769,9 @@
     <t>['11', '90+8']</t>
   </si>
   <si>
+    <t>['27', '38', '63']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1512,7 +1515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP241"/>
+  <dimension ref="A1:BP242"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1974,7 +1977,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2386,7 +2389,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2798,7 +2801,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -3004,7 +3007,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3416,7 +3419,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3828,7 +3831,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -3906,7 +3909,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ12">
         <v>1.18</v>
@@ -5064,7 +5067,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5270,7 +5273,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5351,7 +5354,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ19">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -6094,7 +6097,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6300,7 +6303,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6918,7 +6921,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7124,7 +7127,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7330,7 +7333,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7742,7 +7745,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7948,7 +7951,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8232,7 +8235,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ33">
         <v>0.82</v>
@@ -8360,7 +8363,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -9184,7 +9187,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9390,7 +9393,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9471,7 +9474,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ39">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR39">
         <v>1.56</v>
@@ -9596,7 +9599,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9802,7 +9805,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -10008,7 +10011,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10089,7 +10092,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ42">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR42">
         <v>1.11</v>
@@ -10214,7 +10217,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -11734,7 +11737,7 @@
         <v>3</v>
       </c>
       <c r="AP50">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ50">
         <v>1.92</v>
@@ -11862,7 +11865,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -12068,7 +12071,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12274,7 +12277,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12686,7 +12689,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -13098,7 +13101,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13304,7 +13307,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13510,7 +13513,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13716,7 +13719,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13922,7 +13925,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14128,7 +14131,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14540,7 +14543,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14746,7 +14749,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14952,7 +14955,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -15982,7 +15985,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16060,7 +16063,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ71">
         <v>1.08</v>
@@ -16188,7 +16191,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q72">
         <v>1.95</v>
@@ -16394,7 +16397,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16600,7 +16603,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16806,7 +16809,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -17012,7 +17015,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17218,7 +17221,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17630,7 +17633,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17836,7 +17839,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -17917,7 +17920,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ80">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR80">
         <v>1.97</v>
@@ -18248,7 +18251,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18660,7 +18663,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18738,7 +18741,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ84">
         <v>0.75</v>
@@ -18866,7 +18869,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -19072,7 +19075,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19484,7 +19487,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19896,7 +19899,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20102,7 +20105,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -21544,7 +21547,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21750,7 +21753,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -21956,7 +21959,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22037,7 +22040,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ100">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR100">
         <v>1.55</v>
@@ -22368,7 +22371,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22574,7 +22577,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23270,7 +23273,7 @@
         <v>2</v>
       </c>
       <c r="AP106">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ106">
         <v>1.38</v>
@@ -23810,7 +23813,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -24016,7 +24019,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24222,7 +24225,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q111">
         <v>3.25</v>
@@ -24428,7 +24431,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24509,7 +24512,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ112">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR112">
         <v>1.12</v>
@@ -24634,7 +24637,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -25252,7 +25255,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25458,7 +25461,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25664,7 +25667,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25870,7 +25873,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -26076,7 +26079,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26282,7 +26285,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26488,7 +26491,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26566,7 +26569,7 @@
         <v>0</v>
       </c>
       <c r="AP122">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ122">
         <v>0.38</v>
@@ -26694,7 +26697,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -27312,7 +27315,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27518,7 +27521,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -28136,7 +28139,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28548,7 +28551,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28960,7 +28963,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29041,7 +29044,7 @@
         <v>0.36</v>
       </c>
       <c r="AQ134">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR134">
         <v>1.08</v>
@@ -29166,7 +29169,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -30608,7 +30611,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30814,7 +30817,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -31226,7 +31229,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31432,7 +31435,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31638,7 +31641,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31844,7 +31847,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -32050,7 +32053,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32131,7 +32134,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ149">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR149">
         <v>1.84</v>
@@ -32462,7 +32465,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -33080,7 +33083,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33286,7 +33289,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33492,7 +33495,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33570,7 +33573,7 @@
         <v>0.86</v>
       </c>
       <c r="AP156">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ156">
         <v>1.58</v>
@@ -33698,7 +33701,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33904,7 +33907,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34728,7 +34731,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -34934,7 +34937,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35140,7 +35143,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35346,7 +35349,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35758,7 +35761,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35964,7 +35967,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36251,7 +36254,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ169">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR169">
         <v>1.39</v>
@@ -36376,7 +36379,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36788,7 +36791,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37406,7 +37409,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -38024,7 +38027,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38308,7 +38311,7 @@
         <v>0.13</v>
       </c>
       <c r="AP179">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ179">
         <v>0.73</v>
@@ -38642,7 +38645,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38848,7 +38851,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39260,7 +39263,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39466,7 +39469,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39672,7 +39675,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -39959,7 +39962,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ187">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR187">
         <v>1.17</v>
@@ -40084,7 +40087,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40290,7 +40293,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40496,7 +40499,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40702,7 +40705,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -41114,7 +41117,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41401,7 +41404,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ194">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR194">
         <v>1.41</v>
@@ -41526,7 +41529,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41732,7 +41735,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -42016,7 +42019,7 @@
         <v>1.8</v>
       </c>
       <c r="AP197">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ197">
         <v>1.83</v>
@@ -42144,7 +42147,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42350,7 +42353,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42556,7 +42559,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42762,7 +42765,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -42968,7 +42971,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43174,7 +43177,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43380,7 +43383,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43586,7 +43589,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -43998,7 +44001,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44410,7 +44413,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44822,7 +44825,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45028,7 +45031,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45234,7 +45237,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45440,7 +45443,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45646,7 +45649,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -45852,7 +45855,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -46058,7 +46061,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46264,7 +46267,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46470,7 +46473,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46676,7 +46679,7 @@
         <v>240</v>
       </c>
       <c r="P220" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q220">
         <v>1.73</v>
@@ -47088,7 +47091,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -47166,7 +47169,7 @@
         <v>0.7</v>
       </c>
       <c r="AP222">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ222">
         <v>0.91</v>
@@ -47500,7 +47503,7 @@
         <v>107</v>
       </c>
       <c r="P224" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q224">
         <v>6</v>
@@ -47706,7 +47709,7 @@
         <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q225">
         <v>6.5</v>
@@ -47912,7 +47915,7 @@
         <v>243</v>
       </c>
       <c r="P226" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q226">
         <v>2.38</v>
@@ -47993,7 +47996,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ226">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR226">
         <v>2.02</v>
@@ -48118,7 +48121,7 @@
         <v>155</v>
       </c>
       <c r="P227" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48324,7 +48327,7 @@
         <v>244</v>
       </c>
       <c r="P228" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q228">
         <v>1.91</v>
@@ -48736,7 +48739,7 @@
         <v>91</v>
       </c>
       <c r="P230" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q230">
         <v>2.88</v>
@@ -49148,7 +49151,7 @@
         <v>95</v>
       </c>
       <c r="P232" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q232">
         <v>2.2</v>
@@ -49560,7 +49563,7 @@
         <v>151</v>
       </c>
       <c r="P234" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q234">
         <v>2.6</v>
@@ -49766,7 +49769,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q235">
         <v>4.5</v>
@@ -50178,7 +50181,7 @@
         <v>91</v>
       </c>
       <c r="P237" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50384,7 +50387,7 @@
         <v>91</v>
       </c>
       <c r="P238" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q238">
         <v>2.75</v>
@@ -50796,7 +50799,7 @@
         <v>249</v>
       </c>
       <c r="P240" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q240">
         <v>1.8</v>
@@ -51002,7 +51005,7 @@
         <v>250</v>
       </c>
       <c r="P241" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q241">
         <v>6</v>
@@ -51159,6 +51162,212 @@
       </c>
       <c r="BP241">
         <v>1.56</v>
+      </c>
+    </row>
+    <row r="242" spans="1:68">
+      <c r="A242" s="1">
+        <v>241</v>
+      </c>
+      <c r="B242">
+        <v>7466920</v>
+      </c>
+      <c r="C242" t="s">
+        <v>68</v>
+      </c>
+      <c r="D242" t="s">
+        <v>69</v>
+      </c>
+      <c r="E242" s="2">
+        <v>45702.70833333334</v>
+      </c>
+      <c r="F242">
+        <v>25</v>
+      </c>
+      <c r="G242" t="s">
+        <v>80</v>
+      </c>
+      <c r="H242" t="s">
+        <v>78</v>
+      </c>
+      <c r="I242">
+        <v>2</v>
+      </c>
+      <c r="J242">
+        <v>0</v>
+      </c>
+      <c r="K242">
+        <v>2</v>
+      </c>
+      <c r="L242">
+        <v>3</v>
+      </c>
+      <c r="M242">
+        <v>0</v>
+      </c>
+      <c r="N242">
+        <v>3</v>
+      </c>
+      <c r="O242" t="s">
+        <v>251</v>
+      </c>
+      <c r="P242" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q242">
+        <v>3.25</v>
+      </c>
+      <c r="R242">
+        <v>2.4</v>
+      </c>
+      <c r="S242">
+        <v>2.75</v>
+      </c>
+      <c r="T242">
+        <v>1.25</v>
+      </c>
+      <c r="U242">
+        <v>3.75</v>
+      </c>
+      <c r="V242">
+        <v>2.25</v>
+      </c>
+      <c r="W242">
+        <v>1.57</v>
+      </c>
+      <c r="X242">
+        <v>5.5</v>
+      </c>
+      <c r="Y242">
+        <v>1.14</v>
+      </c>
+      <c r="Z242">
+        <v>2.8</v>
+      </c>
+      <c r="AA242">
+        <v>3.6</v>
+      </c>
+      <c r="AB242">
+        <v>2.38</v>
+      </c>
+      <c r="AC242">
+        <v>1.02</v>
+      </c>
+      <c r="AD242">
+        <v>18</v>
+      </c>
+      <c r="AE242">
+        <v>1.17</v>
+      </c>
+      <c r="AF242">
+        <v>5.4</v>
+      </c>
+      <c r="AG242">
+        <v>1.74</v>
+      </c>
+      <c r="AH242">
+        <v>2.1</v>
+      </c>
+      <c r="AI242">
+        <v>1.44</v>
+      </c>
+      <c r="AJ242">
+        <v>2.63</v>
+      </c>
+      <c r="AK242">
+        <v>1.63</v>
+      </c>
+      <c r="AL242">
+        <v>1.26</v>
+      </c>
+      <c r="AM242">
+        <v>1.39</v>
+      </c>
+      <c r="AN242">
+        <v>1.36</v>
+      </c>
+      <c r="AO242">
+        <v>1.75</v>
+      </c>
+      <c r="AP242">
+        <v>1.5</v>
+      </c>
+      <c r="AQ242">
+        <v>1.62</v>
+      </c>
+      <c r="AR242">
+        <v>1.61</v>
+      </c>
+      <c r="AS242">
+        <v>1.57</v>
+      </c>
+      <c r="AT242">
+        <v>3.18</v>
+      </c>
+      <c r="AU242">
+        <v>6</v>
+      </c>
+      <c r="AV242">
+        <v>0</v>
+      </c>
+      <c r="AW242">
+        <v>8</v>
+      </c>
+      <c r="AX242">
+        <v>9</v>
+      </c>
+      <c r="AY242">
+        <v>16</v>
+      </c>
+      <c r="AZ242">
+        <v>11</v>
+      </c>
+      <c r="BA242">
+        <v>2</v>
+      </c>
+      <c r="BB242">
+        <v>9</v>
+      </c>
+      <c r="BC242">
+        <v>11</v>
+      </c>
+      <c r="BD242">
+        <v>2.12</v>
+      </c>
+      <c r="BE242">
+        <v>6.5</v>
+      </c>
+      <c r="BF242">
+        <v>1.86</v>
+      </c>
+      <c r="BG242">
+        <v>1.22</v>
+      </c>
+      <c r="BH242">
+        <v>3.7</v>
+      </c>
+      <c r="BI242">
+        <v>1.41</v>
+      </c>
+      <c r="BJ242">
+        <v>2.65</v>
+      </c>
+      <c r="BK242">
+        <v>1.66</v>
+      </c>
+      <c r="BL242">
+        <v>2.07</v>
+      </c>
+      <c r="BM242">
+        <v>2.02</v>
+      </c>
+      <c r="BN242">
+        <v>1.68</v>
+      </c>
+      <c r="BO242">
+        <v>2.55</v>
+      </c>
+      <c r="BP242">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="386">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -772,6 +772,15 @@
     <t>['27', '38', '63']</t>
   </si>
   <si>
+    <t>['19', '24', '33', '84']</t>
+  </si>
+  <si>
+    <t>['15', '62']</t>
+  </si>
+  <si>
+    <t>['47']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1155,6 +1164,15 @@
   <si>
     <t>['16', '73']</t>
   </si>
+  <si>
+    <t>['81', '87']</t>
+  </si>
+  <si>
+    <t>['14', '16', '83']</t>
+  </si>
+  <si>
+    <t>['42', '80']</t>
+  </si>
 </sst>
 </file>
 
@@ -1515,7 +1533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP242"/>
+  <dimension ref="A1:BP249"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1977,7 +1995,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2389,7 +2407,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2801,7 +2819,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2882,7 +2900,7 @@
         <v>2</v>
       </c>
       <c r="AQ7">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3007,7 +3025,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3085,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ8">
         <v>1.17</v>
@@ -3419,7 +3437,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3703,7 +3721,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ11">
         <v>1.08</v>
@@ -3831,7 +3849,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4118,7 +4136,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ13">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4321,7 +4339,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ14">
         <v>1.08</v>
@@ -4527,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ15">
         <v>0.67</v>
@@ -4733,10 +4751,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ16">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4939,10 +4957,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ17">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5067,7 +5085,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5145,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
+        <v>1.85</v>
+      </c>
+      <c r="AQ18">
         <v>1.92</v>
-      </c>
-      <c r="AQ18">
-        <v>1.83</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5273,7 +5291,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5560,7 +5578,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ20">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5766,7 +5784,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ21">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -6097,7 +6115,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6175,7 +6193,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ23">
         <v>1.17</v>
@@ -6303,7 +6321,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6921,7 +6939,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7002,7 +7020,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ27">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR27">
         <v>0.83</v>
@@ -7127,7 +7145,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7205,7 +7223,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ28">
         <v>1.38</v>
@@ -7333,7 +7351,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7745,7 +7763,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7951,7 +7969,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8029,7 +8047,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ32">
         <v>1.18</v>
@@ -8238,7 +8256,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ33">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR33">
         <v>1.6</v>
@@ -8363,7 +8381,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -8441,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ34">
         <v>0.67</v>
@@ -8647,7 +8665,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ35">
         <v>1.08</v>
@@ -8856,7 +8874,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ36">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR36">
         <v>1.93</v>
@@ -9059,10 +9077,10 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ37">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR37">
         <v>1.98</v>
@@ -9187,7 +9205,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9265,10 +9283,10 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ38">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR38">
         <v>0.92</v>
@@ -9393,7 +9411,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9599,7 +9617,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9680,7 +9698,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ40">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR40">
         <v>1.93</v>
@@ -9805,7 +9823,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9886,7 +9904,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ41">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR41">
         <v>1.34</v>
@@ -10011,7 +10029,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10089,7 +10107,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ42">
         <v>1.62</v>
@@ -10217,7 +10235,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10295,10 +10313,10 @@
         <v>2</v>
       </c>
       <c r="AP43">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ43">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR43">
         <v>1.79</v>
@@ -10501,10 +10519,10 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ44">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR44">
         <v>1</v>
@@ -10710,7 +10728,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ45">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR45">
         <v>1.78</v>
@@ -10913,10 +10931,10 @@
         <v>0.5</v>
       </c>
       <c r="AP46">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ46">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR46">
         <v>0.83</v>
@@ -11122,7 +11140,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ47">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR47">
         <v>1.75</v>
@@ -11325,7 +11343,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ48">
         <v>0.75</v>
@@ -11531,7 +11549,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ49">
         <v>1.18</v>
@@ -11740,7 +11758,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ50">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR50">
         <v>1.67</v>
@@ -11865,7 +11883,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -11943,10 +11961,10 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ51">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR51">
         <v>2.05</v>
@@ -12071,7 +12089,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12277,7 +12295,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12689,7 +12707,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -13101,7 +13119,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13307,7 +13325,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13513,7 +13531,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13719,7 +13737,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13925,7 +13943,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14131,7 +14149,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14209,7 +14227,7 @@
         <v>3</v>
       </c>
       <c r="AP62">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ62">
         <v>2.38</v>
@@ -14415,10 +14433,10 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ63">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR63">
         <v>1.12</v>
@@ -14543,7 +14561,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14621,7 +14639,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ64">
         <v>1.58</v>
@@ -14749,7 +14767,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14827,10 +14845,10 @@
         <v>0.67</v>
       </c>
       <c r="AP65">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ65">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR65">
         <v>1.33</v>
@@ -14955,7 +14973,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -15448,7 +15466,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ68">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR68">
         <v>1.37</v>
@@ -15654,7 +15672,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ69">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR69">
         <v>1.45</v>
@@ -15857,7 +15875,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ70">
         <v>1.18</v>
@@ -15985,7 +16003,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16191,7 +16209,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q72">
         <v>1.95</v>
@@ -16397,7 +16415,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16475,7 +16493,7 @@
         <v>2.33</v>
       </c>
       <c r="AP73">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ73">
         <v>1.17</v>
@@ -16603,7 +16621,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16684,7 +16702,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ74">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR74">
         <v>1.31</v>
@@ -16809,7 +16827,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -17015,7 +17033,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17093,7 +17111,7 @@
         <v>0.33</v>
       </c>
       <c r="AP76">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ76">
         <v>0.67</v>
@@ -17221,7 +17239,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17302,7 +17320,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ77">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR77">
         <v>1.11</v>
@@ -17508,7 +17526,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ78">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR78">
         <v>1.65</v>
@@ -17633,7 +17651,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17839,7 +17857,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18251,7 +18269,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18329,10 +18347,10 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ82">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR82">
         <v>1.04</v>
@@ -18535,7 +18553,7 @@
         <v>0</v>
       </c>
       <c r="AP83">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ83">
         <v>0.38</v>
@@ -18663,7 +18681,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18869,7 +18887,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -18947,10 +18965,10 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ85">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR85">
         <v>1.28</v>
@@ -19075,7 +19093,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19156,7 +19174,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ86">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR86">
         <v>1.7</v>
@@ -19487,7 +19505,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19568,7 +19586,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ88">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR88">
         <v>1.67</v>
@@ -19771,7 +19789,7 @@
         <v>1</v>
       </c>
       <c r="AP89">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ89">
         <v>1.08</v>
@@ -19899,7 +19917,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -19977,7 +19995,7 @@
         <v>1.25</v>
       </c>
       <c r="AP90">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ90">
         <v>1.18</v>
@@ -20105,7 +20123,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20392,7 +20410,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ92">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR92">
         <v>1.13</v>
@@ -20595,10 +20613,10 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ93">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR93">
         <v>1.09</v>
@@ -21547,7 +21565,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21753,7 +21771,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -21959,7 +21977,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22243,10 +22261,10 @@
         <v>0</v>
       </c>
       <c r="AP101">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ101">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR101">
         <v>1.81</v>
@@ -22371,7 +22389,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22452,7 +22470,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ102">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR102">
         <v>1.76</v>
@@ -22577,7 +22595,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22655,7 +22673,7 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ103">
         <v>1.58</v>
@@ -22861,10 +22879,10 @@
         <v>0.8</v>
       </c>
       <c r="AP104">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ104">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR104">
         <v>1.57</v>
@@ -23813,7 +23831,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -23894,7 +23912,7 @@
         <v>2</v>
       </c>
       <c r="AQ109">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR109">
         <v>1.61</v>
@@ -24019,7 +24037,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24100,7 +24118,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ110">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR110">
         <v>1.96</v>
@@ -24225,7 +24243,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q111">
         <v>3.25</v>
@@ -24306,7 +24324,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ111">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR111">
         <v>1.72</v>
@@ -24431,7 +24449,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24509,7 +24527,7 @@
         <v>2</v>
       </c>
       <c r="AP112">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ112">
         <v>1.62</v>
@@ -24637,7 +24655,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -24715,7 +24733,7 @@
         <v>0.4</v>
       </c>
       <c r="AP113">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ113">
         <v>0.75</v>
@@ -24924,7 +24942,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ114">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR114">
         <v>1.26</v>
@@ -25130,7 +25148,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ115">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR115">
         <v>2.22</v>
@@ -25255,7 +25273,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25461,7 +25479,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25539,7 +25557,7 @@
         <v>0.4</v>
       </c>
       <c r="AP117">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ117">
         <v>1.58</v>
@@ -25667,7 +25685,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25745,7 +25763,7 @@
         <v>0.8</v>
       </c>
       <c r="AP118">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ118">
         <v>1.08</v>
@@ -25873,7 +25891,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -25951,7 +25969,7 @@
         <v>2.6</v>
       </c>
       <c r="AP119">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ119">
         <v>2.38</v>
@@ -26079,7 +26097,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26285,7 +26303,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26491,7 +26509,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26697,7 +26715,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -26778,7 +26796,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ123">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR123">
         <v>1.13</v>
@@ -26984,7 +27002,7 @@
         <v>2</v>
       </c>
       <c r="AQ124">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR124">
         <v>1.52</v>
@@ -27315,7 +27333,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27393,10 +27411,10 @@
         <v>1.33</v>
       </c>
       <c r="AP126">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ126">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR126">
         <v>1.38</v>
@@ -27521,7 +27539,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -27599,10 +27617,10 @@
         <v>1.33</v>
       </c>
       <c r="AP127">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ127">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR127">
         <v>1.54</v>
@@ -27808,7 +27826,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ128">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR128">
         <v>1.43</v>
@@ -28139,7 +28157,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28551,7 +28569,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28835,7 +28853,7 @@
         <v>1.33</v>
       </c>
       <c r="AP133">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ133">
         <v>1.08</v>
@@ -28963,7 +28981,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29041,7 +29059,7 @@
         <v>2.17</v>
       </c>
       <c r="AP134">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ134">
         <v>1.62</v>
@@ -29169,7 +29187,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -29453,10 +29471,10 @@
         <v>1.83</v>
       </c>
       <c r="AP136">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ136">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR136">
         <v>2.3</v>
@@ -29865,10 +29883,10 @@
         <v>0.17</v>
       </c>
       <c r="AP138">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ138">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR138">
         <v>1.44</v>
@@ -30277,7 +30295,7 @@
         <v>1.67</v>
       </c>
       <c r="AP140">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ140">
         <v>1.46</v>
@@ -30611,7 +30629,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30689,7 +30707,7 @@
         <v>1.43</v>
       </c>
       <c r="AP142">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ142">
         <v>1.38</v>
@@ -30817,7 +30835,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30898,7 +30916,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ143">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR143">
         <v>1.7</v>
@@ -31101,7 +31119,7 @@
         <v>0.14</v>
       </c>
       <c r="AP144">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ144">
         <v>0.38</v>
@@ -31229,7 +31247,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31310,7 +31328,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ145">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR145">
         <v>1.4</v>
@@ -31435,7 +31453,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31513,10 +31531,10 @@
         <v>1.57</v>
       </c>
       <c r="AP146">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ146">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR146">
         <v>1.74</v>
@@ -31641,7 +31659,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31722,7 +31740,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ147">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR147">
         <v>1.16</v>
@@ -31847,7 +31865,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -31925,7 +31943,7 @@
         <v>1.43</v>
       </c>
       <c r="AP148">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ148">
         <v>1.46</v>
@@ -32053,7 +32071,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32337,7 +32355,7 @@
         <v>0.71</v>
       </c>
       <c r="AP150">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ150">
         <v>0.75</v>
@@ -32465,7 +32483,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -32546,7 +32564,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ151">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR151">
         <v>1.14</v>
@@ -32752,7 +32770,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ152">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR152">
         <v>2.08</v>
@@ -33083,7 +33101,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33289,7 +33307,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33495,7 +33513,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33701,7 +33719,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33779,7 +33797,7 @@
         <v>0.86</v>
       </c>
       <c r="AP157">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ157">
         <v>1.18</v>
@@ -33907,7 +33925,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -33985,7 +34003,7 @@
         <v>1</v>
       </c>
       <c r="AP158">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ158">
         <v>1.08</v>
@@ -34194,7 +34212,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ159">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR159">
         <v>1.69</v>
@@ -34603,7 +34621,7 @@
         <v>1.38</v>
       </c>
       <c r="AP161">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ161">
         <v>1.38</v>
@@ -34731,7 +34749,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -34812,7 +34830,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ162">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR162">
         <v>1.71</v>
@@ -34937,7 +34955,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35015,7 +35033,7 @@
         <v>1.38</v>
       </c>
       <c r="AP163">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ163">
         <v>1.46</v>
@@ -35143,7 +35161,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35224,7 +35242,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ164">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR164">
         <v>1.2</v>
@@ -35349,7 +35367,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35427,10 +35445,10 @@
         <v>1.5</v>
       </c>
       <c r="AP165">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ165">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR165">
         <v>1.31</v>
@@ -35633,7 +35651,7 @@
         <v>0.13</v>
       </c>
       <c r="AP166">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ166">
         <v>0.38</v>
@@ -35761,7 +35779,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35839,7 +35857,7 @@
         <v>0.63</v>
       </c>
       <c r="AP167">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ167">
         <v>0.75</v>
@@ -35967,7 +35985,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36048,7 +36066,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ168">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR168">
         <v>1.46</v>
@@ -36379,7 +36397,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36663,10 +36681,10 @@
         <v>0.75</v>
       </c>
       <c r="AP171">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ171">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR171">
         <v>2.11</v>
@@ -36791,7 +36809,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -36869,7 +36887,7 @@
         <v>1.13</v>
       </c>
       <c r="AP172">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ172">
         <v>1.08</v>
@@ -37409,7 +37427,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -38027,7 +38045,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38314,7 +38332,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ179">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR179">
         <v>1.54</v>
@@ -38520,7 +38538,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ180">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR180">
         <v>2.03</v>
@@ -38645,7 +38663,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38723,7 +38741,7 @@
         <v>1.22</v>
       </c>
       <c r="AP181">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ181">
         <v>1.38</v>
@@ -38851,7 +38869,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39135,7 +39153,7 @@
         <v>0.22</v>
       </c>
       <c r="AP183">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ183">
         <v>0.38</v>
@@ -39263,7 +39281,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39341,10 +39359,10 @@
         <v>1.56</v>
       </c>
       <c r="AP184">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ184">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR184">
         <v>1.59</v>
@@ -39469,7 +39487,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39550,7 +39568,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ185">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR185">
         <v>1.32</v>
@@ -39675,7 +39693,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -39753,7 +39771,7 @@
         <v>2.5</v>
       </c>
       <c r="AP186">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ186">
         <v>2.38</v>
@@ -40087,7 +40105,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40165,7 +40183,7 @@
         <v>1.33</v>
       </c>
       <c r="AP188">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ188">
         <v>1.46</v>
@@ -40293,7 +40311,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40374,7 +40392,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ189">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR189">
         <v>1.54</v>
@@ -40499,7 +40517,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40580,7 +40598,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ190">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR190">
         <v>1.66</v>
@@ -40705,7 +40723,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -40786,7 +40804,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ191">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR191">
         <v>1.71</v>
@@ -40992,7 +41010,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ192">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR192">
         <v>1.73</v>
@@ -41117,7 +41135,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41195,7 +41213,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP193">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ193">
         <v>0.67</v>
@@ -41401,7 +41419,7 @@
         <v>2</v>
       </c>
       <c r="AP194">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ194">
         <v>1.62</v>
@@ -41529,7 +41547,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41607,10 +41625,10 @@
         <v>0.22</v>
       </c>
       <c r="AP195">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ195">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR195">
         <v>1.14</v>
@@ -41735,7 +41753,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -41813,7 +41831,7 @@
         <v>1.33</v>
       </c>
       <c r="AP196">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ196">
         <v>1.08</v>
@@ -42022,7 +42040,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ197">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR197">
         <v>1.62</v>
@@ -42147,7 +42165,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42225,10 +42243,10 @@
         <v>0.89</v>
       </c>
       <c r="AP198">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ198">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR198">
         <v>1.57</v>
@@ -42353,7 +42371,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42559,7 +42577,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42640,7 +42658,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ200">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR200">
         <v>1.18</v>
@@ -42765,7 +42783,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -42846,7 +42864,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ201">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR201">
         <v>1.75</v>
@@ -42971,7 +42989,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43049,7 +43067,7 @@
         <v>1.44</v>
       </c>
       <c r="AP202">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ202">
         <v>1.58</v>
@@ -43177,7 +43195,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43383,7 +43401,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43589,7 +43607,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -43667,7 +43685,7 @@
         <v>1.11</v>
       </c>
       <c r="AP205">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ205">
         <v>1.58</v>
@@ -44001,7 +44019,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44413,7 +44431,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44825,7 +44843,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -44906,7 +44924,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ211">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR211">
         <v>1.61</v>
@@ -45031,7 +45049,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45109,7 +45127,7 @@
         <v>1.3</v>
       </c>
       <c r="AP212">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ212">
         <v>1.58</v>
@@ -45237,7 +45255,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45443,7 +45461,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45521,7 +45539,7 @@
         <v>1.3</v>
       </c>
       <c r="AP214">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ214">
         <v>1.58</v>
@@ -45649,7 +45667,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -45855,7 +45873,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -46061,7 +46079,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46267,7 +46285,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46473,7 +46491,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46679,7 +46697,7 @@
         <v>240</v>
       </c>
       <c r="P220" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q220">
         <v>1.73</v>
@@ -46966,7 +46984,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ221">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR221">
         <v>1.77</v>
@@ -47091,7 +47109,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -47172,7 +47190,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ222">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR222">
         <v>1.58</v>
@@ -47378,7 +47396,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ223">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR223">
         <v>1.79</v>
@@ -47503,7 +47521,7 @@
         <v>107</v>
       </c>
       <c r="P224" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q224">
         <v>6</v>
@@ -47581,10 +47599,10 @@
         <v>1.64</v>
       </c>
       <c r="AP224">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ224">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR224">
         <v>1.11</v>
@@ -47709,7 +47727,7 @@
         <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q225">
         <v>6.5</v>
@@ -47790,7 +47808,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ225">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR225">
         <v>1.21</v>
@@ -47915,7 +47933,7 @@
         <v>243</v>
       </c>
       <c r="P226" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q226">
         <v>2.38</v>
@@ -47993,7 +48011,7 @@
         <v>1.91</v>
       </c>
       <c r="AP226">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ226">
         <v>1.62</v>
@@ -48121,7 +48139,7 @@
         <v>155</v>
       </c>
       <c r="P227" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48199,10 +48217,10 @@
         <v>0.5</v>
       </c>
       <c r="AP227">
+        <v>0.85</v>
+      </c>
+      <c r="AQ227">
         <v>0.92</v>
-      </c>
-      <c r="AQ227">
-        <v>0.73</v>
       </c>
       <c r="AR227">
         <v>1.4</v>
@@ -48327,7 +48345,7 @@
         <v>244</v>
       </c>
       <c r="P228" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q228">
         <v>1.91</v>
@@ -48611,7 +48629,7 @@
         <v>1.2</v>
       </c>
       <c r="AP229">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ229">
         <v>1.08</v>
@@ -48739,7 +48757,7 @@
         <v>91</v>
       </c>
       <c r="P230" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q230">
         <v>2.88</v>
@@ -48817,7 +48835,7 @@
         <v>1</v>
       </c>
       <c r="AP230">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ230">
         <v>1.18</v>
@@ -49151,7 +49169,7 @@
         <v>95</v>
       </c>
       <c r="P232" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Q232">
         <v>2.2</v>
@@ -49563,7 +49581,7 @@
         <v>151</v>
       </c>
       <c r="P234" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q234">
         <v>2.6</v>
@@ -49769,7 +49787,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q235">
         <v>4.5</v>
@@ -50181,7 +50199,7 @@
         <v>91</v>
       </c>
       <c r="P237" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50387,7 +50405,7 @@
         <v>91</v>
       </c>
       <c r="P238" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q238">
         <v>2.75</v>
@@ -50799,7 +50817,7 @@
         <v>249</v>
       </c>
       <c r="P240" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q240">
         <v>1.8</v>
@@ -51005,7 +51023,7 @@
         <v>250</v>
       </c>
       <c r="P241" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Q241">
         <v>6</v>
@@ -51368,6 +51386,1448 @@
       </c>
       <c r="BP242">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="243" spans="1:68">
+      <c r="A243" s="1">
+        <v>242</v>
+      </c>
+      <c r="B243">
+        <v>7466923</v>
+      </c>
+      <c r="C243" t="s">
+        <v>68</v>
+      </c>
+      <c r="D243" t="s">
+        <v>69</v>
+      </c>
+      <c r="E243" s="2">
+        <v>45703.39583333334</v>
+      </c>
+      <c r="F243">
+        <v>25</v>
+      </c>
+      <c r="G243" t="s">
+        <v>79</v>
+      </c>
+      <c r="H243" t="s">
+        <v>72</v>
+      </c>
+      <c r="I243">
+        <v>0</v>
+      </c>
+      <c r="J243">
+        <v>0</v>
+      </c>
+      <c r="K243">
+        <v>0</v>
+      </c>
+      <c r="L243">
+        <v>0</v>
+      </c>
+      <c r="M243">
+        <v>2</v>
+      </c>
+      <c r="N243">
+        <v>2</v>
+      </c>
+      <c r="O243" t="s">
+        <v>91</v>
+      </c>
+      <c r="P243" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q243">
+        <v>9</v>
+      </c>
+      <c r="R243">
+        <v>2.63</v>
+      </c>
+      <c r="S243">
+        <v>1.73</v>
+      </c>
+      <c r="T243">
+        <v>1.29</v>
+      </c>
+      <c r="U243">
+        <v>3.5</v>
+      </c>
+      <c r="V243">
+        <v>2.38</v>
+      </c>
+      <c r="W243">
+        <v>1.53</v>
+      </c>
+      <c r="X243">
+        <v>5.5</v>
+      </c>
+      <c r="Y243">
+        <v>1.14</v>
+      </c>
+      <c r="Z243">
+        <v>9</v>
+      </c>
+      <c r="AA243">
+        <v>5.75</v>
+      </c>
+      <c r="AB243">
+        <v>1.29</v>
+      </c>
+      <c r="AC243">
+        <v>1.02</v>
+      </c>
+      <c r="AD243">
+        <v>19</v>
+      </c>
+      <c r="AE243">
+        <v>1.19</v>
+      </c>
+      <c r="AF243">
+        <v>5</v>
+      </c>
+      <c r="AG243">
+        <v>1.63</v>
+      </c>
+      <c r="AH243">
+        <v>2.28</v>
+      </c>
+      <c r="AI243">
+        <v>2.05</v>
+      </c>
+      <c r="AJ243">
+        <v>1.7</v>
+      </c>
+      <c r="AK243">
+        <v>3.7</v>
+      </c>
+      <c r="AL243">
+        <v>1.13</v>
+      </c>
+      <c r="AM243">
+        <v>1.06</v>
+      </c>
+      <c r="AN243">
+        <v>0.75</v>
+      </c>
+      <c r="AO243">
+        <v>1.83</v>
+      </c>
+      <c r="AP243">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AQ243">
+        <v>1.92</v>
+      </c>
+      <c r="AR243">
+        <v>1.2</v>
+      </c>
+      <c r="AS243">
+        <v>1.29</v>
+      </c>
+      <c r="AT243">
+        <v>2.49</v>
+      </c>
+      <c r="AU243">
+        <v>3</v>
+      </c>
+      <c r="AV243">
+        <v>6</v>
+      </c>
+      <c r="AW243">
+        <v>4</v>
+      </c>
+      <c r="AX243">
+        <v>6</v>
+      </c>
+      <c r="AY243">
+        <v>9</v>
+      </c>
+      <c r="AZ243">
+        <v>16</v>
+      </c>
+      <c r="BA243">
+        <v>3</v>
+      </c>
+      <c r="BB243">
+        <v>7</v>
+      </c>
+      <c r="BC243">
+        <v>10</v>
+      </c>
+      <c r="BD243">
+        <v>5.1</v>
+      </c>
+      <c r="BE243">
+        <v>9</v>
+      </c>
+      <c r="BF243">
+        <v>1.18</v>
+      </c>
+      <c r="BG243">
+        <v>1.25</v>
+      </c>
+      <c r="BH243">
+        <v>3.4</v>
+      </c>
+      <c r="BI243">
+        <v>1.44</v>
+      </c>
+      <c r="BJ243">
+        <v>2.55</v>
+      </c>
+      <c r="BK243">
+        <v>1.72</v>
+      </c>
+      <c r="BL243">
+        <v>1.98</v>
+      </c>
+      <c r="BM243">
+        <v>2.1</v>
+      </c>
+      <c r="BN243">
+        <v>1.63</v>
+      </c>
+      <c r="BO243">
+        <v>2.65</v>
+      </c>
+      <c r="BP243">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="244" spans="1:68">
+      <c r="A244" s="1">
+        <v>243</v>
+      </c>
+      <c r="B244">
+        <v>7466926</v>
+      </c>
+      <c r="C244" t="s">
+        <v>68</v>
+      </c>
+      <c r="D244" t="s">
+        <v>69</v>
+      </c>
+      <c r="E244" s="2">
+        <v>45703.5</v>
+      </c>
+      <c r="F244">
+        <v>25</v>
+      </c>
+      <c r="G244" t="s">
+        <v>84</v>
+      </c>
+      <c r="H244" t="s">
+        <v>88</v>
+      </c>
+      <c r="I244">
+        <v>0</v>
+      </c>
+      <c r="J244">
+        <v>2</v>
+      </c>
+      <c r="K244">
+        <v>2</v>
+      </c>
+      <c r="L244">
+        <v>1</v>
+      </c>
+      <c r="M244">
+        <v>3</v>
+      </c>
+      <c r="N244">
+        <v>4</v>
+      </c>
+      <c r="O244" t="s">
+        <v>203</v>
+      </c>
+      <c r="P244" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q244">
+        <v>5</v>
+      </c>
+      <c r="R244">
+        <v>2.5</v>
+      </c>
+      <c r="S244">
+        <v>2.05</v>
+      </c>
+      <c r="T244">
+        <v>1.25</v>
+      </c>
+      <c r="U244">
+        <v>3.75</v>
+      </c>
+      <c r="V244">
+        <v>2.25</v>
+      </c>
+      <c r="W244">
+        <v>1.57</v>
+      </c>
+      <c r="X244">
+        <v>5.5</v>
+      </c>
+      <c r="Y244">
+        <v>1.14</v>
+      </c>
+      <c r="Z244">
+        <v>4.33</v>
+      </c>
+      <c r="AA244">
+        <v>4</v>
+      </c>
+      <c r="AB244">
+        <v>1.7</v>
+      </c>
+      <c r="AC244">
+        <v>1.02</v>
+      </c>
+      <c r="AD244">
+        <v>20</v>
+      </c>
+      <c r="AE244">
+        <v>1.17</v>
+      </c>
+      <c r="AF244">
+        <v>5.5</v>
+      </c>
+      <c r="AG244">
+        <v>1.55</v>
+      </c>
+      <c r="AH244">
+        <v>2.3</v>
+      </c>
+      <c r="AI244">
+        <v>1.57</v>
+      </c>
+      <c r="AJ244">
+        <v>2.25</v>
+      </c>
+      <c r="AK244">
+        <v>2.3</v>
+      </c>
+      <c r="AL244">
+        <v>1.21</v>
+      </c>
+      <c r="AM244">
+        <v>1.17</v>
+      </c>
+      <c r="AN244">
+        <v>0.36</v>
+      </c>
+      <c r="AO244">
+        <v>1.58</v>
+      </c>
+      <c r="AP244">
+        <v>0.33</v>
+      </c>
+      <c r="AQ244">
+        <v>1.69</v>
+      </c>
+      <c r="AR244">
+        <v>1.15</v>
+      </c>
+      <c r="AS244">
+        <v>1.63</v>
+      </c>
+      <c r="AT244">
+        <v>2.78</v>
+      </c>
+      <c r="AU244">
+        <v>5</v>
+      </c>
+      <c r="AV244">
+        <v>8</v>
+      </c>
+      <c r="AW244">
+        <v>7</v>
+      </c>
+      <c r="AX244">
+        <v>7</v>
+      </c>
+      <c r="AY244">
+        <v>15</v>
+      </c>
+      <c r="AZ244">
+        <v>19</v>
+      </c>
+      <c r="BA244">
+        <v>4</v>
+      </c>
+      <c r="BB244">
+        <v>6</v>
+      </c>
+      <c r="BC244">
+        <v>10</v>
+      </c>
+      <c r="BD244">
+        <v>3.2</v>
+      </c>
+      <c r="BE244">
+        <v>7.5</v>
+      </c>
+      <c r="BF244">
+        <v>1.41</v>
+      </c>
+      <c r="BG244">
+        <v>1.14</v>
+      </c>
+      <c r="BH244">
+        <v>4.8</v>
+      </c>
+      <c r="BI244">
+        <v>1.25</v>
+      </c>
+      <c r="BJ244">
+        <v>3.45</v>
+      </c>
+      <c r="BK244">
+        <v>1.41</v>
+      </c>
+      <c r="BL244">
+        <v>2.63</v>
+      </c>
+      <c r="BM244">
+        <v>1.66</v>
+      </c>
+      <c r="BN244">
+        <v>2.06</v>
+      </c>
+      <c r="BO244">
+        <v>2.02</v>
+      </c>
+      <c r="BP244">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="245" spans="1:68">
+      <c r="A245" s="1">
+        <v>244</v>
+      </c>
+      <c r="B245">
+        <v>7466925</v>
+      </c>
+      <c r="C245" t="s">
+        <v>68</v>
+      </c>
+      <c r="D245" t="s">
+        <v>69</v>
+      </c>
+      <c r="E245" s="2">
+        <v>45703.5</v>
+      </c>
+      <c r="F245">
+        <v>25</v>
+      </c>
+      <c r="G245" t="s">
+        <v>85</v>
+      </c>
+      <c r="H245" t="s">
+        <v>74</v>
+      </c>
+      <c r="I245">
+        <v>3</v>
+      </c>
+      <c r="J245">
+        <v>0</v>
+      </c>
+      <c r="K245">
+        <v>3</v>
+      </c>
+      <c r="L245">
+        <v>4</v>
+      </c>
+      <c r="M245">
+        <v>0</v>
+      </c>
+      <c r="N245">
+        <v>4</v>
+      </c>
+      <c r="O245" t="s">
+        <v>252</v>
+      </c>
+      <c r="P245" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q245">
+        <v>2.3</v>
+      </c>
+      <c r="R245">
+        <v>2.5</v>
+      </c>
+      <c r="S245">
+        <v>4</v>
+      </c>
+      <c r="T245">
+        <v>1.25</v>
+      </c>
+      <c r="U245">
+        <v>3.75</v>
+      </c>
+      <c r="V245">
+        <v>2.1</v>
+      </c>
+      <c r="W245">
+        <v>1.67</v>
+      </c>
+      <c r="X245">
+        <v>4.5</v>
+      </c>
+      <c r="Y245">
+        <v>1.18</v>
+      </c>
+      <c r="Z245">
+        <v>1.65</v>
+      </c>
+      <c r="AA245">
+        <v>4.33</v>
+      </c>
+      <c r="AB245">
+        <v>4.5</v>
+      </c>
+      <c r="AC245">
+        <v>1.01</v>
+      </c>
+      <c r="AD245">
+        <v>24</v>
+      </c>
+      <c r="AE245">
+        <v>1.14</v>
+      </c>
+      <c r="AF245">
+        <v>6.2</v>
+      </c>
+      <c r="AG245">
+        <v>1.67</v>
+      </c>
+      <c r="AH245">
+        <v>2.21</v>
+      </c>
+      <c r="AI245">
+        <v>1.44</v>
+      </c>
+      <c r="AJ245">
+        <v>2.63</v>
+      </c>
+      <c r="AK245">
+        <v>1.23</v>
+      </c>
+      <c r="AL245">
+        <v>1.23</v>
+      </c>
+      <c r="AM245">
+        <v>2.05</v>
+      </c>
+      <c r="AN245">
+        <v>2.09</v>
+      </c>
+      <c r="AO245">
+        <v>1.75</v>
+      </c>
+      <c r="AP245">
+        <v>2.17</v>
+      </c>
+      <c r="AQ245">
+        <v>1.62</v>
+      </c>
+      <c r="AR245">
+        <v>1.98</v>
+      </c>
+      <c r="AS245">
+        <v>1.47</v>
+      </c>
+      <c r="AT245">
+        <v>3.45</v>
+      </c>
+      <c r="AU245">
+        <v>8</v>
+      </c>
+      <c r="AV245">
+        <v>2</v>
+      </c>
+      <c r="AW245">
+        <v>4</v>
+      </c>
+      <c r="AX245">
+        <v>2</v>
+      </c>
+      <c r="AY245">
+        <v>14</v>
+      </c>
+      <c r="AZ245">
+        <v>5</v>
+      </c>
+      <c r="BA245">
+        <v>7</v>
+      </c>
+      <c r="BB245">
+        <v>4</v>
+      </c>
+      <c r="BC245">
+        <v>11</v>
+      </c>
+      <c r="BD245">
+        <v>1.34</v>
+      </c>
+      <c r="BE245">
+        <v>7.5</v>
+      </c>
+      <c r="BF245">
+        <v>3.45</v>
+      </c>
+      <c r="BG245">
+        <v>1.15</v>
+      </c>
+      <c r="BH245">
+        <v>4.6</v>
+      </c>
+      <c r="BI245">
+        <v>1.27</v>
+      </c>
+      <c r="BJ245">
+        <v>3.3</v>
+      </c>
+      <c r="BK245">
+        <v>1.47</v>
+      </c>
+      <c r="BL245">
+        <v>2.48</v>
+      </c>
+      <c r="BM245">
+        <v>1.73</v>
+      </c>
+      <c r="BN245">
+        <v>1.96</v>
+      </c>
+      <c r="BO245">
+        <v>2.1</v>
+      </c>
+      <c r="BP245">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="246" spans="1:68">
+      <c r="A246" s="1">
+        <v>245</v>
+      </c>
+      <c r="B246">
+        <v>7466928</v>
+      </c>
+      <c r="C246" t="s">
+        <v>68</v>
+      </c>
+      <c r="D246" t="s">
+        <v>69</v>
+      </c>
+      <c r="E246" s="2">
+        <v>45703.5</v>
+      </c>
+      <c r="F246">
+        <v>25</v>
+      </c>
+      <c r="G246" t="s">
+        <v>76</v>
+      </c>
+      <c r="H246" t="s">
+        <v>77</v>
+      </c>
+      <c r="I246">
+        <v>0</v>
+      </c>
+      <c r="J246">
+        <v>1</v>
+      </c>
+      <c r="K246">
+        <v>1</v>
+      </c>
+      <c r="L246">
+        <v>0</v>
+      </c>
+      <c r="M246">
+        <v>1</v>
+      </c>
+      <c r="N246">
+        <v>1</v>
+      </c>
+      <c r="O246" t="s">
+        <v>91</v>
+      </c>
+      <c r="P246" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q246">
+        <v>2.88</v>
+      </c>
+      <c r="R246">
+        <v>2.38</v>
+      </c>
+      <c r="S246">
+        <v>3.2</v>
+      </c>
+      <c r="T246">
+        <v>1.3</v>
+      </c>
+      <c r="U246">
+        <v>3.4</v>
+      </c>
+      <c r="V246">
+        <v>2.38</v>
+      </c>
+      <c r="W246">
+        <v>1.53</v>
+      </c>
+      <c r="X246">
+        <v>6</v>
+      </c>
+      <c r="Y246">
+        <v>1.13</v>
+      </c>
+      <c r="Z246">
+        <v>2.3</v>
+      </c>
+      <c r="AA246">
+        <v>3.5</v>
+      </c>
+      <c r="AB246">
+        <v>2.9</v>
+      </c>
+      <c r="AC246">
+        <v>1.03</v>
+      </c>
+      <c r="AD246">
+        <v>17</v>
+      </c>
+      <c r="AE246">
+        <v>1.19</v>
+      </c>
+      <c r="AF246">
+        <v>5</v>
+      </c>
+      <c r="AG246">
+        <v>1.6</v>
+      </c>
+      <c r="AH246">
+        <v>2.25</v>
+      </c>
+      <c r="AI246">
+        <v>1.5</v>
+      </c>
+      <c r="AJ246">
+        <v>2.5</v>
+      </c>
+      <c r="AK246">
+        <v>1.41</v>
+      </c>
+      <c r="AL246">
+        <v>1.28</v>
+      </c>
+      <c r="AM246">
+        <v>1.58</v>
+      </c>
+      <c r="AN246">
+        <v>1.17</v>
+      </c>
+      <c r="AO246">
+        <v>0.73</v>
+      </c>
+      <c r="AP246">
+        <v>1.08</v>
+      </c>
+      <c r="AQ246">
+        <v>0.92</v>
+      </c>
+      <c r="AR246">
+        <v>1.24</v>
+      </c>
+      <c r="AS246">
+        <v>1.14</v>
+      </c>
+      <c r="AT246">
+        <v>2.38</v>
+      </c>
+      <c r="AU246">
+        <v>4</v>
+      </c>
+      <c r="AV246">
+        <v>6</v>
+      </c>
+      <c r="AW246">
+        <v>10</v>
+      </c>
+      <c r="AX246">
+        <v>9</v>
+      </c>
+      <c r="AY246">
+        <v>21</v>
+      </c>
+      <c r="AZ246">
+        <v>20</v>
+      </c>
+      <c r="BA246">
+        <v>9</v>
+      </c>
+      <c r="BB246">
+        <v>2</v>
+      </c>
+      <c r="BC246">
+        <v>11</v>
+      </c>
+      <c r="BD246">
+        <v>1.68</v>
+      </c>
+      <c r="BE246">
+        <v>6.75</v>
+      </c>
+      <c r="BF246">
+        <v>2.4</v>
+      </c>
+      <c r="BG246">
+        <v>1.14</v>
+      </c>
+      <c r="BH246">
+        <v>4.6</v>
+      </c>
+      <c r="BI246">
+        <v>1.28</v>
+      </c>
+      <c r="BJ246">
+        <v>3.3</v>
+      </c>
+      <c r="BK246">
+        <v>1.48</v>
+      </c>
+      <c r="BL246">
+        <v>2.45</v>
+      </c>
+      <c r="BM246">
+        <v>1.76</v>
+      </c>
+      <c r="BN246">
+        <v>1.94</v>
+      </c>
+      <c r="BO246">
+        <v>2.17</v>
+      </c>
+      <c r="BP246">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="247" spans="1:68">
+      <c r="A247" s="1">
+        <v>246</v>
+      </c>
+      <c r="B247">
+        <v>7466922</v>
+      </c>
+      <c r="C247" t="s">
+        <v>68</v>
+      </c>
+      <c r="D247" t="s">
+        <v>69</v>
+      </c>
+      <c r="E247" s="2">
+        <v>45703.5</v>
+      </c>
+      <c r="F247">
+        <v>25</v>
+      </c>
+      <c r="G247" t="s">
+        <v>83</v>
+      </c>
+      <c r="H247" t="s">
+        <v>75</v>
+      </c>
+      <c r="I247">
+        <v>1</v>
+      </c>
+      <c r="J247">
+        <v>1</v>
+      </c>
+      <c r="K247">
+        <v>2</v>
+      </c>
+      <c r="L247">
+        <v>2</v>
+      </c>
+      <c r="M247">
+        <v>1</v>
+      </c>
+      <c r="N247">
+        <v>3</v>
+      </c>
+      <c r="O247" t="s">
+        <v>253</v>
+      </c>
+      <c r="P247" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q247">
+        <v>2.88</v>
+      </c>
+      <c r="R247">
+        <v>2.1</v>
+      </c>
+      <c r="S247">
+        <v>4</v>
+      </c>
+      <c r="T247">
+        <v>1.44</v>
+      </c>
+      <c r="U247">
+        <v>2.63</v>
+      </c>
+      <c r="V247">
+        <v>3.25</v>
+      </c>
+      <c r="W247">
+        <v>1.33</v>
+      </c>
+      <c r="X247">
+        <v>9</v>
+      </c>
+      <c r="Y247">
+        <v>1.07</v>
+      </c>
+      <c r="Z247">
+        <v>2.1</v>
+      </c>
+      <c r="AA247">
+        <v>3.3</v>
+      </c>
+      <c r="AB247">
+        <v>3.5</v>
+      </c>
+      <c r="AC247">
+        <v>1.07</v>
+      </c>
+      <c r="AD247">
+        <v>10</v>
+      </c>
+      <c r="AE247">
+        <v>1.35</v>
+      </c>
+      <c r="AF247">
+        <v>3.35</v>
+      </c>
+      <c r="AG247">
+        <v>1.95</v>
+      </c>
+      <c r="AH247">
+        <v>1.75</v>
+      </c>
+      <c r="AI247">
+        <v>1.8</v>
+      </c>
+      <c r="AJ247">
+        <v>1.95</v>
+      </c>
+      <c r="AK247">
+        <v>1.32</v>
+      </c>
+      <c r="AL247">
+        <v>1.31</v>
+      </c>
+      <c r="AM247">
+        <v>1.66</v>
+      </c>
+      <c r="AN247">
+        <v>1.42</v>
+      </c>
+      <c r="AO247">
+        <v>1.92</v>
+      </c>
+      <c r="AP247">
+        <v>1.54</v>
+      </c>
+      <c r="AQ247">
+        <v>1.77</v>
+      </c>
+      <c r="AR247">
+        <v>1.54</v>
+      </c>
+      <c r="AS247">
+        <v>1.35</v>
+      </c>
+      <c r="AT247">
+        <v>2.89</v>
+      </c>
+      <c r="AU247">
+        <v>11</v>
+      </c>
+      <c r="AV247">
+        <v>3</v>
+      </c>
+      <c r="AW247">
+        <v>14</v>
+      </c>
+      <c r="AX247">
+        <v>6</v>
+      </c>
+      <c r="AY247">
+        <v>29</v>
+      </c>
+      <c r="AZ247">
+        <v>11</v>
+      </c>
+      <c r="BA247">
+        <v>8</v>
+      </c>
+      <c r="BB247">
+        <v>4</v>
+      </c>
+      <c r="BC247">
+        <v>12</v>
+      </c>
+      <c r="BD247">
+        <v>1.52</v>
+      </c>
+      <c r="BE247">
+        <v>7</v>
+      </c>
+      <c r="BF247">
+        <v>2.8</v>
+      </c>
+      <c r="BG247">
+        <v>1.19</v>
+      </c>
+      <c r="BH247">
+        <v>4.1</v>
+      </c>
+      <c r="BI247">
+        <v>1.35</v>
+      </c>
+      <c r="BJ247">
+        <v>2.9</v>
+      </c>
+      <c r="BK247">
+        <v>1.57</v>
+      </c>
+      <c r="BL247">
+        <v>2.23</v>
+      </c>
+      <c r="BM247">
+        <v>1.9</v>
+      </c>
+      <c r="BN247">
+        <v>1.79</v>
+      </c>
+      <c r="BO247">
+        <v>2.33</v>
+      </c>
+      <c r="BP247">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="248" spans="1:68">
+      <c r="A248" s="1">
+        <v>247</v>
+      </c>
+      <c r="B248">
+        <v>7466919</v>
+      </c>
+      <c r="C248" t="s">
+        <v>68</v>
+      </c>
+      <c r="D248" t="s">
+        <v>69</v>
+      </c>
+      <c r="E248" s="2">
+        <v>45703.5</v>
+      </c>
+      <c r="F248">
+        <v>25</v>
+      </c>
+      <c r="G248" t="s">
+        <v>86</v>
+      </c>
+      <c r="H248" t="s">
+        <v>71</v>
+      </c>
+      <c r="I248">
+        <v>0</v>
+      </c>
+      <c r="J248">
+        <v>0</v>
+      </c>
+      <c r="K248">
+        <v>0</v>
+      </c>
+      <c r="L248">
+        <v>1</v>
+      </c>
+      <c r="M248">
+        <v>1</v>
+      </c>
+      <c r="N248">
+        <v>2</v>
+      </c>
+      <c r="O248" t="s">
+        <v>170</v>
+      </c>
+      <c r="P248" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q248">
+        <v>1.91</v>
+      </c>
+      <c r="R248">
+        <v>2.5</v>
+      </c>
+      <c r="S248">
+        <v>6.5</v>
+      </c>
+      <c r="T248">
+        <v>1.29</v>
+      </c>
+      <c r="U248">
+        <v>3.5</v>
+      </c>
+      <c r="V248">
+        <v>2.38</v>
+      </c>
+      <c r="W248">
+        <v>1.53</v>
+      </c>
+      <c r="X248">
+        <v>5.5</v>
+      </c>
+      <c r="Y248">
+        <v>1.14</v>
+      </c>
+      <c r="Z248">
+        <v>1.33</v>
+      </c>
+      <c r="AA248">
+        <v>5</v>
+      </c>
+      <c r="AB248">
+        <v>8</v>
+      </c>
+      <c r="AC248">
+        <v>1.03</v>
+      </c>
+      <c r="AD248">
+        <v>18</v>
+      </c>
+      <c r="AE248">
+        <v>1.2</v>
+      </c>
+      <c r="AF248">
+        <v>4.9</v>
+      </c>
+      <c r="AG248">
+        <v>1.74</v>
+      </c>
+      <c r="AH248">
+        <v>2.1</v>
+      </c>
+      <c r="AI248">
+        <v>1.8</v>
+      </c>
+      <c r="AJ248">
+        <v>1.95</v>
+      </c>
+      <c r="AK248">
+        <v>1.1</v>
+      </c>
+      <c r="AL248">
+        <v>1.18</v>
+      </c>
+      <c r="AM248">
+        <v>2.8</v>
+      </c>
+      <c r="AN248">
+        <v>1.92</v>
+      </c>
+      <c r="AO248">
+        <v>0.82</v>
+      </c>
+      <c r="AP248">
+        <v>1.85</v>
+      </c>
+      <c r="AQ248">
+        <v>0.83</v>
+      </c>
+      <c r="AR248">
+        <v>1.52</v>
+      </c>
+      <c r="AS248">
+        <v>0.9</v>
+      </c>
+      <c r="AT248">
+        <v>2.42</v>
+      </c>
+      <c r="AU248">
+        <v>7</v>
+      </c>
+      <c r="AV248">
+        <v>4</v>
+      </c>
+      <c r="AW248">
+        <v>19</v>
+      </c>
+      <c r="AX248">
+        <v>1</v>
+      </c>
+      <c r="AY248">
+        <v>34</v>
+      </c>
+      <c r="AZ248">
+        <v>6</v>
+      </c>
+      <c r="BA248">
+        <v>16</v>
+      </c>
+      <c r="BB248">
+        <v>1</v>
+      </c>
+      <c r="BC248">
+        <v>17</v>
+      </c>
+      <c r="BD248">
+        <v>1.23</v>
+      </c>
+      <c r="BE248">
+        <v>8.5</v>
+      </c>
+      <c r="BF248">
+        <v>4.4</v>
+      </c>
+      <c r="BG248">
+        <v>1.14</v>
+      </c>
+      <c r="BH248">
+        <v>4.8</v>
+      </c>
+      <c r="BI248">
+        <v>1.25</v>
+      </c>
+      <c r="BJ248">
+        <v>3.45</v>
+      </c>
+      <c r="BK248">
+        <v>1.43</v>
+      </c>
+      <c r="BL248">
+        <v>2.55</v>
+      </c>
+      <c r="BM248">
+        <v>1.66</v>
+      </c>
+      <c r="BN248">
+        <v>2.06</v>
+      </c>
+      <c r="BO248">
+        <v>2</v>
+      </c>
+      <c r="BP248">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="249" spans="1:68">
+      <c r="A249" s="1">
+        <v>248</v>
+      </c>
+      <c r="B249">
+        <v>7466921</v>
+      </c>
+      <c r="C249" t="s">
+        <v>68</v>
+      </c>
+      <c r="D249" t="s">
+        <v>69</v>
+      </c>
+      <c r="E249" s="2">
+        <v>45703.60416666666</v>
+      </c>
+      <c r="F249">
+        <v>25</v>
+      </c>
+      <c r="G249" t="s">
+        <v>82</v>
+      </c>
+      <c r="H249" t="s">
+        <v>73</v>
+      </c>
+      <c r="I249">
+        <v>0</v>
+      </c>
+      <c r="J249">
+        <v>1</v>
+      </c>
+      <c r="K249">
+        <v>1</v>
+      </c>
+      <c r="L249">
+        <v>1</v>
+      </c>
+      <c r="M249">
+        <v>2</v>
+      </c>
+      <c r="N249">
+        <v>3</v>
+      </c>
+      <c r="O249" t="s">
+        <v>254</v>
+      </c>
+      <c r="P249" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q249">
+        <v>2.63</v>
+      </c>
+      <c r="R249">
+        <v>2.05</v>
+      </c>
+      <c r="S249">
+        <v>4.75</v>
+      </c>
+      <c r="T249">
+        <v>1.5</v>
+      </c>
+      <c r="U249">
+        <v>2.5</v>
+      </c>
+      <c r="V249">
+        <v>3.4</v>
+      </c>
+      <c r="W249">
+        <v>1.3</v>
+      </c>
+      <c r="X249">
+        <v>10</v>
+      </c>
+      <c r="Y249">
+        <v>1.06</v>
+      </c>
+      <c r="Z249">
+        <v>1.91</v>
+      </c>
+      <c r="AA249">
+        <v>3.3</v>
+      </c>
+      <c r="AB249">
+        <v>4.2</v>
+      </c>
+      <c r="AC249">
+        <v>1.09</v>
+      </c>
+      <c r="AD249">
+        <v>8.6</v>
+      </c>
+      <c r="AE249">
+        <v>1.42</v>
+      </c>
+      <c r="AF249">
+        <v>3</v>
+      </c>
+      <c r="AG249">
+        <v>2.05</v>
+      </c>
+      <c r="AH249">
+        <v>1.7</v>
+      </c>
+      <c r="AI249">
+        <v>1.95</v>
+      </c>
+      <c r="AJ249">
+        <v>1.8</v>
+      </c>
+      <c r="AK249">
+        <v>1.23</v>
+      </c>
+      <c r="AL249">
+        <v>1.32</v>
+      </c>
+      <c r="AM249">
+        <v>1.82</v>
+      </c>
+      <c r="AN249">
+        <v>0.92</v>
+      </c>
+      <c r="AO249">
+        <v>0.91</v>
+      </c>
+      <c r="AP249">
+        <v>0.85</v>
+      </c>
+      <c r="AQ249">
+        <v>1.08</v>
+      </c>
+      <c r="AR249">
+        <v>1.43</v>
+      </c>
+      <c r="AS249">
+        <v>1.04</v>
+      </c>
+      <c r="AT249">
+        <v>2.47</v>
+      </c>
+      <c r="AU249">
+        <v>7</v>
+      </c>
+      <c r="AV249">
+        <v>7</v>
+      </c>
+      <c r="AW249">
+        <v>11</v>
+      </c>
+      <c r="AX249">
+        <v>5</v>
+      </c>
+      <c r="AY249">
+        <v>23</v>
+      </c>
+      <c r="AZ249">
+        <v>16</v>
+      </c>
+      <c r="BA249">
+        <v>6</v>
+      </c>
+      <c r="BB249">
+        <v>2</v>
+      </c>
+      <c r="BC249">
+        <v>8</v>
+      </c>
+      <c r="BD249">
+        <v>1.5</v>
+      </c>
+      <c r="BE249">
+        <v>7</v>
+      </c>
+      <c r="BF249">
+        <v>2.8</v>
+      </c>
+      <c r="BG249">
+        <v>1.2</v>
+      </c>
+      <c r="BH249">
+        <v>3.95</v>
+      </c>
+      <c r="BI249">
+        <v>1.35</v>
+      </c>
+      <c r="BJ249">
+        <v>2.88</v>
+      </c>
+      <c r="BK249">
+        <v>1.58</v>
+      </c>
+      <c r="BL249">
+        <v>2.18</v>
+      </c>
+      <c r="BM249">
+        <v>1.93</v>
+      </c>
+      <c r="BN249">
+        <v>1.76</v>
+      </c>
+      <c r="BO249">
+        <v>2.4</v>
+      </c>
+      <c r="BP249">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="387">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -781,6 +781,9 @@
     <t>['47']</t>
   </si>
   <si>
+    <t>['15', '37']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1533,7 +1536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP249"/>
+  <dimension ref="A1:BP251"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1995,7 +1998,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2282,7 +2285,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ4">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2407,7 +2410,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2819,7 +2822,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -3025,7 +3028,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3437,7 +3440,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3849,7 +3852,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -3930,7 +3933,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ12">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4133,7 +4136,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ13">
         <v>1.08</v>
@@ -5085,7 +5088,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5291,7 +5294,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5781,7 +5784,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ21">
         <v>0.92</v>
@@ -6115,7 +6118,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6321,7 +6324,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6608,7 +6611,7 @@
         <v>2</v>
       </c>
       <c r="AQ25">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR25">
         <v>1.78</v>
@@ -6939,7 +6942,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7145,7 +7148,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7351,7 +7354,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7763,7 +7766,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7969,7 +7972,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8050,7 +8053,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ32">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR32">
         <v>0.65</v>
@@ -8381,7 +8384,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -8871,7 +8874,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ36">
         <v>1.77</v>
@@ -9205,7 +9208,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9411,7 +9414,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9617,7 +9620,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9695,7 +9698,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ40">
         <v>1.92</v>
@@ -9823,7 +9826,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -10029,7 +10032,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10235,7 +10238,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10725,7 +10728,7 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ45">
         <v>1.69</v>
@@ -11137,7 +11140,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ47">
         <v>0.92</v>
@@ -11346,7 +11349,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ48">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR48">
         <v>1.44</v>
@@ -11552,7 +11555,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ49">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR49">
         <v>1.39</v>
@@ -11883,7 +11886,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -12089,7 +12092,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12295,7 +12298,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12707,7 +12710,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -13119,7 +13122,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13325,7 +13328,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13531,7 +13534,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13737,7 +13740,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13943,7 +13946,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14149,7 +14152,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14561,7 +14564,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14767,7 +14770,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14973,7 +14976,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -15054,7 +15057,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ66">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR66">
         <v>1.43</v>
@@ -15878,7 +15881,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ70">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR70">
         <v>1.35</v>
@@ -16003,7 +16006,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16209,7 +16212,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q72">
         <v>1.95</v>
@@ -16287,7 +16290,7 @@
         <v>1.67</v>
       </c>
       <c r="AP72">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ72">
         <v>1.08</v>
@@ -16415,7 +16418,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16621,7 +16624,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16827,7 +16830,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -17033,7 +17036,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17239,7 +17242,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17651,7 +17654,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17857,7 +17860,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -17935,7 +17938,7 @@
         <v>3</v>
       </c>
       <c r="AP80">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ80">
         <v>1.62</v>
@@ -18269,7 +18272,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18681,7 +18684,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18762,7 +18765,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ84">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR84">
         <v>1.51</v>
@@ -18887,7 +18890,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -19093,7 +19096,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19505,7 +19508,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19917,7 +19920,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -19998,7 +20001,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ90">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR90">
         <v>1.61</v>
@@ -20123,7 +20126,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -21231,7 +21234,7 @@
         <v>1.75</v>
       </c>
       <c r="AP96">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ96">
         <v>1.46</v>
@@ -21565,7 +21568,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21771,7 +21774,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -21849,7 +21852,7 @@
         <v>2.5</v>
       </c>
       <c r="AP99">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ99">
         <v>1.17</v>
@@ -21977,7 +21980,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22389,7 +22392,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22595,7 +22598,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23497,7 +23500,7 @@
         <v>2</v>
       </c>
       <c r="AP107">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ107">
         <v>1.17</v>
@@ -23831,7 +23834,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -24037,7 +24040,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24115,7 +24118,7 @@
         <v>0.4</v>
       </c>
       <c r="AP110">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ110">
         <v>0.83</v>
@@ -24243,7 +24246,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q111">
         <v>3.25</v>
@@ -24449,7 +24452,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24655,7 +24658,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -24736,7 +24739,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ113">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR113">
         <v>1.98</v>
@@ -25273,7 +25276,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25479,7 +25482,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25685,7 +25688,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25891,7 +25894,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -26097,7 +26100,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26178,7 +26181,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ120">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR120">
         <v>1.13</v>
@@ -26303,7 +26306,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26509,7 +26512,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26715,7 +26718,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -27333,7 +27336,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27539,7 +27542,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -28157,7 +28160,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28235,7 +28238,7 @@
         <v>1.33</v>
       </c>
       <c r="AP130">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ130">
         <v>1.58</v>
@@ -28441,7 +28444,7 @@
         <v>1.67</v>
       </c>
       <c r="AP131">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ131">
         <v>1.38</v>
@@ -28569,7 +28572,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28981,7 +28984,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29187,7 +29190,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -29680,7 +29683,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ137">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR137">
         <v>1.42</v>
@@ -30092,7 +30095,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ139">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR139">
         <v>2.18</v>
@@ -30629,7 +30632,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30835,7 +30838,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -31247,7 +31250,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31453,7 +31456,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31659,7 +31662,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31865,7 +31868,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -32071,7 +32074,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32149,7 +32152,7 @@
         <v>2.29</v>
       </c>
       <c r="AP149">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ149">
         <v>1.62</v>
@@ -32358,7 +32361,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ150">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR150">
         <v>1.48</v>
@@ -32483,7 +32486,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -33101,7 +33104,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33179,7 +33182,7 @@
         <v>1.29</v>
       </c>
       <c r="AP154">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ154">
         <v>1.58</v>
@@ -33307,7 +33310,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33513,7 +33516,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33719,7 +33722,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33800,7 +33803,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ157">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR157">
         <v>2.25</v>
@@ -33925,7 +33928,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34749,7 +34752,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -34955,7 +34958,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35161,7 +35164,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35367,7 +35370,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35779,7 +35782,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35860,7 +35863,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ167">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR167">
         <v>1.06</v>
@@ -35985,7 +35988,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36397,7 +36400,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36475,7 +36478,7 @@
         <v>2.43</v>
       </c>
       <c r="AP170">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ170">
         <v>2.38</v>
@@ -36809,7 +36812,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37427,7 +37430,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -37920,7 +37923,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ177">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR177">
         <v>1.19</v>
@@ -38045,7 +38048,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38123,7 +38126,7 @@
         <v>0.63</v>
       </c>
       <c r="AP178">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ178">
         <v>0.67</v>
@@ -38663,7 +38666,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38869,7 +38872,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -38947,10 +38950,10 @@
         <v>0.89</v>
       </c>
       <c r="AP182">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ182">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR182">
         <v>1.74</v>
@@ -39281,7 +39284,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39487,7 +39490,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39693,7 +39696,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -40105,7 +40108,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40311,7 +40314,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40517,7 +40520,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40723,7 +40726,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -40801,7 +40804,7 @@
         <v>1.5</v>
       </c>
       <c r="AP191">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ191">
         <v>1.62</v>
@@ -41135,7 +41138,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41547,7 +41550,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41753,7 +41756,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -42165,7 +42168,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42371,7 +42374,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42449,10 +42452,10 @@
         <v>1</v>
       </c>
       <c r="AP199">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ199">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR199">
         <v>1.79</v>
@@ -42577,7 +42580,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42783,7 +42786,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -42989,7 +42992,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43195,7 +43198,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43401,7 +43404,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43607,7 +43610,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -43894,7 +43897,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ206">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR206">
         <v>1.56</v>
@@ -44019,7 +44022,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44431,7 +44434,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44843,7 +44846,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45049,7 +45052,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45255,7 +45258,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45461,7 +45464,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45667,7 +45670,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -45873,7 +45876,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -46079,7 +46082,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46285,7 +46288,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46491,7 +46494,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46697,7 +46700,7 @@
         <v>240</v>
       </c>
       <c r="P220" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q220">
         <v>1.73</v>
@@ -46778,7 +46781,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ220">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR220">
         <v>1.85</v>
@@ -47109,7 +47112,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -47393,7 +47396,7 @@
         <v>0.9</v>
       </c>
       <c r="AP223">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ223">
         <v>0.83</v>
@@ -47521,7 +47524,7 @@
         <v>107</v>
       </c>
       <c r="P224" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q224">
         <v>6</v>
@@ -47727,7 +47730,7 @@
         <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q225">
         <v>6.5</v>
@@ -47933,7 +47936,7 @@
         <v>243</v>
       </c>
       <c r="P226" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q226">
         <v>2.38</v>
@@ -48139,7 +48142,7 @@
         <v>155</v>
       </c>
       <c r="P227" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48345,7 +48348,7 @@
         <v>244</v>
       </c>
       <c r="P228" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q228">
         <v>1.91</v>
@@ -48423,7 +48426,7 @@
         <v>0.5</v>
       </c>
       <c r="AP228">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ228">
         <v>0.67</v>
@@ -48757,7 +48760,7 @@
         <v>91</v>
       </c>
       <c r="P230" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q230">
         <v>2.88</v>
@@ -48838,7 +48841,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ230">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR230">
         <v>1.57</v>
@@ -49169,7 +49172,7 @@
         <v>95</v>
       </c>
       <c r="P232" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q232">
         <v>2.2</v>
@@ -49581,7 +49584,7 @@
         <v>151</v>
       </c>
       <c r="P234" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q234">
         <v>2.6</v>
@@ -49787,7 +49790,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q235">
         <v>4.5</v>
@@ -50199,7 +50202,7 @@
         <v>91</v>
       </c>
       <c r="P237" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50405,7 +50408,7 @@
         <v>91</v>
       </c>
       <c r="P238" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q238">
         <v>2.75</v>
@@ -50817,7 +50820,7 @@
         <v>249</v>
       </c>
       <c r="P240" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q240">
         <v>1.8</v>
@@ -51023,7 +51026,7 @@
         <v>250</v>
       </c>
       <c r="P241" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q241">
         <v>6</v>
@@ -51435,7 +51438,7 @@
         <v>91</v>
       </c>
       <c r="P243" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q243">
         <v>9</v>
@@ -51641,7 +51644,7 @@
         <v>203</v>
       </c>
       <c r="P244" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q244">
         <v>5</v>
@@ -52671,7 +52674,7 @@
         <v>254</v>
       </c>
       <c r="P249" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q249">
         <v>2.63</v>
@@ -52828,6 +52831,418 @@
       </c>
       <c r="BP249">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="250" spans="1:68">
+      <c r="A250" s="1">
+        <v>249</v>
+      </c>
+      <c r="B250">
+        <v>7466924</v>
+      </c>
+      <c r="C250" t="s">
+        <v>68</v>
+      </c>
+      <c r="D250" t="s">
+        <v>69</v>
+      </c>
+      <c r="E250" s="2">
+        <v>45704.45833333334</v>
+      </c>
+      <c r="F250">
+        <v>25</v>
+      </c>
+      <c r="G250" t="s">
+        <v>89</v>
+      </c>
+      <c r="H250" t="s">
+        <v>87</v>
+      </c>
+      <c r="I250">
+        <v>2</v>
+      </c>
+      <c r="J250">
+        <v>0</v>
+      </c>
+      <c r="K250">
+        <v>2</v>
+      </c>
+      <c r="L250">
+        <v>2</v>
+      </c>
+      <c r="M250">
+        <v>1</v>
+      </c>
+      <c r="N250">
+        <v>3</v>
+      </c>
+      <c r="O250" t="s">
+        <v>255</v>
+      </c>
+      <c r="P250" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q250">
+        <v>1.57</v>
+      </c>
+      <c r="R250">
+        <v>3</v>
+      </c>
+      <c r="S250">
+        <v>9.5</v>
+      </c>
+      <c r="T250">
+        <v>1.2</v>
+      </c>
+      <c r="U250">
+        <v>4.33</v>
+      </c>
+      <c r="V250">
+        <v>2</v>
+      </c>
+      <c r="W250">
+        <v>1.73</v>
+      </c>
+      <c r="X250">
+        <v>4</v>
+      </c>
+      <c r="Y250">
+        <v>1.22</v>
+      </c>
+      <c r="Z250">
+        <v>1.15</v>
+      </c>
+      <c r="AA250">
+        <v>8.5</v>
+      </c>
+      <c r="AB250">
+        <v>12</v>
+      </c>
+      <c r="AC250">
+        <v>1.01</v>
+      </c>
+      <c r="AD250">
+        <v>26</v>
+      </c>
+      <c r="AE250">
+        <v>1.11</v>
+      </c>
+      <c r="AF250">
+        <v>7.2</v>
+      </c>
+      <c r="AG250">
+        <v>1.35</v>
+      </c>
+      <c r="AH250">
+        <v>3.04</v>
+      </c>
+      <c r="AI250">
+        <v>1.91</v>
+      </c>
+      <c r="AJ250">
+        <v>1.91</v>
+      </c>
+      <c r="AK250">
+        <v>1.04</v>
+      </c>
+      <c r="AL250">
+        <v>1.09</v>
+      </c>
+      <c r="AM250">
+        <v>4.5</v>
+      </c>
+      <c r="AN250">
+        <v>2.36</v>
+      </c>
+      <c r="AO250">
+        <v>0.75</v>
+      </c>
+      <c r="AP250">
+        <v>2.42</v>
+      </c>
+      <c r="AQ250">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR250">
+        <v>1.85</v>
+      </c>
+      <c r="AS250">
+        <v>1.27</v>
+      </c>
+      <c r="AT250">
+        <v>3.12</v>
+      </c>
+      <c r="AU250">
+        <v>4</v>
+      </c>
+      <c r="AV250">
+        <v>5</v>
+      </c>
+      <c r="AW250">
+        <v>7</v>
+      </c>
+      <c r="AX250">
+        <v>12</v>
+      </c>
+      <c r="AY250">
+        <v>12</v>
+      </c>
+      <c r="AZ250">
+        <v>22</v>
+      </c>
+      <c r="BA250">
+        <v>4</v>
+      </c>
+      <c r="BB250">
+        <v>3</v>
+      </c>
+      <c r="BC250">
+        <v>7</v>
+      </c>
+      <c r="BD250">
+        <v>1.13</v>
+      </c>
+      <c r="BE250">
+        <v>14.5</v>
+      </c>
+      <c r="BF250">
+        <v>7.6</v>
+      </c>
+      <c r="BG250">
+        <v>1.08</v>
+      </c>
+      <c r="BH250">
+        <v>5.7</v>
+      </c>
+      <c r="BI250">
+        <v>1.18</v>
+      </c>
+      <c r="BJ250">
+        <v>3.84</v>
+      </c>
+      <c r="BK250">
+        <v>1.36</v>
+      </c>
+      <c r="BL250">
+        <v>2.7</v>
+      </c>
+      <c r="BM250">
+        <v>1.63</v>
+      </c>
+      <c r="BN250">
+        <v>2.09</v>
+      </c>
+      <c r="BO250">
+        <v>2.04</v>
+      </c>
+      <c r="BP250">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="251" spans="1:68">
+      <c r="A251" s="1">
+        <v>250</v>
+      </c>
+      <c r="B251">
+        <v>7466927</v>
+      </c>
+      <c r="C251" t="s">
+        <v>68</v>
+      </c>
+      <c r="D251" t="s">
+        <v>69</v>
+      </c>
+      <c r="E251" s="2">
+        <v>45704.5625</v>
+      </c>
+      <c r="F251">
+        <v>25</v>
+      </c>
+      <c r="G251" t="s">
+        <v>81</v>
+      </c>
+      <c r="H251" t="s">
+        <v>70</v>
+      </c>
+      <c r="I251">
+        <v>1</v>
+      </c>
+      <c r="J251">
+        <v>0</v>
+      </c>
+      <c r="K251">
+        <v>1</v>
+      </c>
+      <c r="L251">
+        <v>1</v>
+      </c>
+      <c r="M251">
+        <v>0</v>
+      </c>
+      <c r="N251">
+        <v>1</v>
+      </c>
+      <c r="O251" t="s">
+        <v>221</v>
+      </c>
+      <c r="P251" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q251">
+        <v>2.88</v>
+      </c>
+      <c r="R251">
+        <v>2.5</v>
+      </c>
+      <c r="S251">
+        <v>3.1</v>
+      </c>
+      <c r="T251">
+        <v>1.25</v>
+      </c>
+      <c r="U251">
+        <v>3.75</v>
+      </c>
+      <c r="V251">
+        <v>2.2</v>
+      </c>
+      <c r="W251">
+        <v>1.62</v>
+      </c>
+      <c r="X251">
+        <v>5</v>
+      </c>
+      <c r="Y251">
+        <v>1.17</v>
+      </c>
+      <c r="Z251">
+        <v>2.38</v>
+      </c>
+      <c r="AA251">
+        <v>3.7</v>
+      </c>
+      <c r="AB251">
+        <v>2.7</v>
+      </c>
+      <c r="AC251">
+        <v>1.02</v>
+      </c>
+      <c r="AD251">
+        <v>21</v>
+      </c>
+      <c r="AE251">
+        <v>1.14</v>
+      </c>
+      <c r="AF251">
+        <v>6</v>
+      </c>
+      <c r="AG251">
+        <v>1.5</v>
+      </c>
+      <c r="AH251">
+        <v>2.63</v>
+      </c>
+      <c r="AI251">
+        <v>1.4</v>
+      </c>
+      <c r="AJ251">
+        <v>2.75</v>
+      </c>
+      <c r="AK251">
+        <v>1.46</v>
+      </c>
+      <c r="AL251">
+        <v>1.27</v>
+      </c>
+      <c r="AM251">
+        <v>1.55</v>
+      </c>
+      <c r="AN251">
+        <v>1.17</v>
+      </c>
+      <c r="AO251">
+        <v>1.18</v>
+      </c>
+      <c r="AP251">
+        <v>1.31</v>
+      </c>
+      <c r="AQ251">
+        <v>1.08</v>
+      </c>
+      <c r="AR251">
+        <v>1.71</v>
+      </c>
+      <c r="AS251">
+        <v>1.31</v>
+      </c>
+      <c r="AT251">
+        <v>3.02</v>
+      </c>
+      <c r="AU251">
+        <v>8</v>
+      </c>
+      <c r="AV251">
+        <v>7</v>
+      </c>
+      <c r="AW251">
+        <v>15</v>
+      </c>
+      <c r="AX251">
+        <v>10</v>
+      </c>
+      <c r="AY251">
+        <v>33</v>
+      </c>
+      <c r="AZ251">
+        <v>20</v>
+      </c>
+      <c r="BA251">
+        <v>10</v>
+      </c>
+      <c r="BB251">
+        <v>5</v>
+      </c>
+      <c r="BC251">
+        <v>15</v>
+      </c>
+      <c r="BD251">
+        <v>1.83</v>
+      </c>
+      <c r="BE251">
+        <v>9.4</v>
+      </c>
+      <c r="BF251">
+        <v>2.3</v>
+      </c>
+      <c r="BG251">
+        <v>1.06</v>
+      </c>
+      <c r="BH251">
+        <v>6.05</v>
+      </c>
+      <c r="BI251">
+        <v>1.17</v>
+      </c>
+      <c r="BJ251">
+        <v>4.05</v>
+      </c>
+      <c r="BK251">
+        <v>1.33</v>
+      </c>
+      <c r="BL251">
+        <v>2.83</v>
+      </c>
+      <c r="BM251">
+        <v>1.59</v>
+      </c>
+      <c r="BN251">
+        <v>2.16</v>
+      </c>
+      <c r="BO251">
+        <v>1.99</v>
+      </c>
+      <c r="BP251">
+        <v>1.73</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="389">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -784,6 +784,9 @@
     <t>['15', '37']</t>
   </si>
   <si>
+    <t>['38', '45+3']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1176,6 +1179,9 @@
   <si>
     <t>['42', '80']</t>
   </si>
+  <si>
+    <t>['29', '61']</t>
+  </si>
 </sst>
 </file>
 
@@ -1536,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP251"/>
+  <dimension ref="A1:BP252"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1998,7 +2004,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2079,7 +2085,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ3">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2410,7 +2416,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2822,7 +2828,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -3028,7 +3034,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3440,7 +3446,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3852,7 +3858,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -5088,7 +5094,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5166,7 +5172,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ18">
         <v>1.92</v>
@@ -5294,7 +5300,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -6118,7 +6124,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6324,7 +6330,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6942,7 +6948,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7148,7 +7154,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7354,7 +7360,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7766,7 +7772,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7847,7 +7853,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ31">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR31">
         <v>1.62</v>
@@ -7972,7 +7978,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8384,7 +8390,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -9208,7 +9214,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9286,7 +9292,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ38">
         <v>1.08</v>
@@ -9414,7 +9420,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9620,7 +9626,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9826,7 +9832,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -10032,7 +10038,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10238,7 +10244,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -11346,7 +11352,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ48">
         <v>0.6899999999999999</v>
@@ -11886,7 +11892,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -12092,7 +12098,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12298,7 +12304,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12710,7 +12716,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -13122,7 +13128,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13328,7 +13334,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13409,7 +13415,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ58">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR58">
         <v>1.42</v>
@@ -13534,7 +13540,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13740,7 +13746,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13946,7 +13952,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14152,7 +14158,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14233,7 +14239,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ62">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR62">
         <v>1.29</v>
@@ -14564,7 +14570,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14770,7 +14776,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14976,7 +14982,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -15878,7 +15884,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ70">
         <v>1.08</v>
@@ -16006,7 +16012,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16212,7 +16218,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q72">
         <v>1.95</v>
@@ -16418,7 +16424,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16624,7 +16630,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16830,7 +16836,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -17036,7 +17042,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17242,7 +17248,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17654,7 +17660,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17860,7 +17866,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18272,7 +18278,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18684,7 +18690,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18890,7 +18896,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -18968,7 +18974,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ85">
         <v>1.69</v>
@@ -19096,7 +19102,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19508,7 +19514,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19920,7 +19926,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20126,7 +20132,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20207,7 +20213,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ91">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR91">
         <v>2.46</v>
@@ -21568,7 +21574,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21774,7 +21780,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -21980,7 +21986,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22392,7 +22398,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22598,7 +22604,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23834,7 +23840,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -24040,7 +24046,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24246,7 +24252,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q111">
         <v>3.25</v>
@@ -24452,7 +24458,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24658,7 +24664,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -25276,7 +25282,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25482,7 +25488,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25560,7 +25566,7 @@
         <v>0.4</v>
       </c>
       <c r="AP117">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ117">
         <v>1.58</v>
@@ -25688,7 +25694,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25894,7 +25900,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -25975,7 +25981,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ119">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR119">
         <v>1.07</v>
@@ -26100,7 +26106,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26306,7 +26312,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26512,7 +26518,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26718,7 +26724,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -27336,7 +27342,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27542,7 +27548,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -28160,7 +28166,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28572,7 +28578,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28984,7 +28990,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29190,7 +29196,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -29271,7 +29277,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ135">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR135">
         <v>1.25</v>
@@ -29886,7 +29892,7 @@
         <v>0.17</v>
       </c>
       <c r="AP138">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ138">
         <v>0.92</v>
@@ -30632,7 +30638,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30838,7 +30844,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -31122,7 +31128,7 @@
         <v>0.14</v>
       </c>
       <c r="AP144">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ144">
         <v>0.38</v>
@@ -31250,7 +31256,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31456,7 +31462,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31662,7 +31668,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31868,7 +31874,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -32074,7 +32080,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32486,7 +32492,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -33104,7 +33110,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33310,7 +33316,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33516,7 +33522,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33722,7 +33728,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33928,7 +33934,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34624,7 +34630,7 @@
         <v>1.38</v>
       </c>
       <c r="AP161">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ161">
         <v>1.38</v>
@@ -34752,7 +34758,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -34958,7 +34964,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35164,7 +35170,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35370,7 +35376,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35782,7 +35788,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35988,7 +35994,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36400,7 +36406,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36481,7 +36487,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ170">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR170">
         <v>1.79</v>
@@ -36812,7 +36818,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37430,7 +37436,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -38048,7 +38054,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38666,7 +38672,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38872,7 +38878,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39284,7 +39290,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39490,7 +39496,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39696,7 +39702,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -39777,7 +39783,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ186">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR186">
         <v>1.43</v>
@@ -40108,7 +40114,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40186,7 +40192,7 @@
         <v>1.33</v>
       </c>
       <c r="AP188">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ188">
         <v>1.46</v>
@@ -40314,7 +40320,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40520,7 +40526,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40726,7 +40732,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -41138,7 +41144,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41216,7 +41222,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP193">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ193">
         <v>0.67</v>
@@ -41550,7 +41556,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41756,7 +41762,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -42168,7 +42174,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42374,7 +42380,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42580,7 +42586,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42786,7 +42792,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -42992,7 +42998,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43198,7 +43204,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43404,7 +43410,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43485,7 +43491,7 @@
         <v>2</v>
       </c>
       <c r="AQ204">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR204">
         <v>1.5</v>
@@ -43610,7 +43616,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -44022,7 +44028,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44434,7 +44440,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44846,7 +44852,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45052,7 +45058,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45258,7 +45264,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45339,7 +45345,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ213">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR213">
         <v>1.61</v>
@@ -45464,7 +45470,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45670,7 +45676,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -45876,7 +45882,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -46082,7 +46088,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46288,7 +46294,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46494,7 +46500,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46700,7 +46706,7 @@
         <v>240</v>
       </c>
       <c r="P220" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q220">
         <v>1.73</v>
@@ -47112,7 +47118,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -47524,7 +47530,7 @@
         <v>107</v>
       </c>
       <c r="P224" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q224">
         <v>6</v>
@@ -47730,7 +47736,7 @@
         <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q225">
         <v>6.5</v>
@@ -47936,7 +47942,7 @@
         <v>243</v>
       </c>
       <c r="P226" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q226">
         <v>2.38</v>
@@ -48142,7 +48148,7 @@
         <v>155</v>
       </c>
       <c r="P227" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48348,7 +48354,7 @@
         <v>244</v>
       </c>
       <c r="P228" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q228">
         <v>1.91</v>
@@ -48632,7 +48638,7 @@
         <v>1.2</v>
       </c>
       <c r="AP229">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ229">
         <v>1.08</v>
@@ -48760,7 +48766,7 @@
         <v>91</v>
       </c>
       <c r="P230" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q230">
         <v>2.88</v>
@@ -49172,7 +49178,7 @@
         <v>95</v>
       </c>
       <c r="P232" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q232">
         <v>2.2</v>
@@ -49584,7 +49590,7 @@
         <v>151</v>
       </c>
       <c r="P234" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q234">
         <v>2.6</v>
@@ -49790,7 +49796,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q235">
         <v>4.5</v>
@@ -49871,7 +49877,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ235">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR235">
         <v>1.81</v>
@@ -50202,7 +50208,7 @@
         <v>91</v>
       </c>
       <c r="P237" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50408,7 +50414,7 @@
         <v>91</v>
       </c>
       <c r="P238" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q238">
         <v>2.75</v>
@@ -50820,7 +50826,7 @@
         <v>249</v>
       </c>
       <c r="P240" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q240">
         <v>1.8</v>
@@ -51026,7 +51032,7 @@
         <v>250</v>
       </c>
       <c r="P241" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q241">
         <v>6</v>
@@ -51107,7 +51113,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ241">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AR241">
         <v>1.39</v>
@@ -51438,7 +51444,7 @@
         <v>91</v>
       </c>
       <c r="P243" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q243">
         <v>9</v>
@@ -51644,7 +51650,7 @@
         <v>203</v>
       </c>
       <c r="P244" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q244">
         <v>5</v>
@@ -52546,7 +52552,7 @@
         <v>0.82</v>
       </c>
       <c r="AP248">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ248">
         <v>0.83</v>
@@ -52674,7 +52680,7 @@
         <v>254</v>
       </c>
       <c r="P249" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q249">
         <v>2.63</v>
@@ -52880,7 +52886,7 @@
         <v>255</v>
       </c>
       <c r="P250" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q250">
         <v>1.57</v>
@@ -53243,6 +53249,212 @@
       </c>
       <c r="BP251">
         <v>1.73</v>
+      </c>
+    </row>
+    <row r="252" spans="1:68">
+      <c r="A252" s="1">
+        <v>251</v>
+      </c>
+      <c r="B252">
+        <v>7466961</v>
+      </c>
+      <c r="C252" t="s">
+        <v>68</v>
+      </c>
+      <c r="D252" t="s">
+        <v>69</v>
+      </c>
+      <c r="E252" s="2">
+        <v>45707.6875</v>
+      </c>
+      <c r="F252">
+        <v>29</v>
+      </c>
+      <c r="G252" t="s">
+        <v>86</v>
+      </c>
+      <c r="H252" t="s">
+        <v>89</v>
+      </c>
+      <c r="I252">
+        <v>2</v>
+      </c>
+      <c r="J252">
+        <v>1</v>
+      </c>
+      <c r="K252">
+        <v>3</v>
+      </c>
+      <c r="L252">
+        <v>2</v>
+      </c>
+      <c r="M252">
+        <v>2</v>
+      </c>
+      <c r="N252">
+        <v>4</v>
+      </c>
+      <c r="O252" t="s">
+        <v>256</v>
+      </c>
+      <c r="P252" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q252">
+        <v>4</v>
+      </c>
+      <c r="R252">
+        <v>2.4</v>
+      </c>
+      <c r="S252">
+        <v>2.38</v>
+      </c>
+      <c r="T252">
+        <v>1.29</v>
+      </c>
+      <c r="U252">
+        <v>3.5</v>
+      </c>
+      <c r="V252">
+        <v>2.25</v>
+      </c>
+      <c r="W252">
+        <v>1.57</v>
+      </c>
+      <c r="X252">
+        <v>5.5</v>
+      </c>
+      <c r="Y252">
+        <v>1.14</v>
+      </c>
+      <c r="Z252">
+        <v>3.6</v>
+      </c>
+      <c r="AA252">
+        <v>4</v>
+      </c>
+      <c r="AB252">
+        <v>1.85</v>
+      </c>
+      <c r="AC252">
+        <v>1.02</v>
+      </c>
+      <c r="AD252">
+        <v>20</v>
+      </c>
+      <c r="AE252">
+        <v>1.18</v>
+      </c>
+      <c r="AF252">
+        <v>5.2</v>
+      </c>
+      <c r="AG252">
+        <v>1.55</v>
+      </c>
+      <c r="AH252">
+        <v>2.3</v>
+      </c>
+      <c r="AI252">
+        <v>1.53</v>
+      </c>
+      <c r="AJ252">
+        <v>2.38</v>
+      </c>
+      <c r="AK252">
+        <v>1.98</v>
+      </c>
+      <c r="AL252">
+        <v>1.24</v>
+      </c>
+      <c r="AM252">
+        <v>1.24</v>
+      </c>
+      <c r="AN252">
+        <v>1.85</v>
+      </c>
+      <c r="AO252">
+        <v>2.38</v>
+      </c>
+      <c r="AP252">
+        <v>1.79</v>
+      </c>
+      <c r="AQ252">
+        <v>2.29</v>
+      </c>
+      <c r="AR252">
+        <v>1.61</v>
+      </c>
+      <c r="AS252">
+        <v>2.03</v>
+      </c>
+      <c r="AT252">
+        <v>3.64</v>
+      </c>
+      <c r="AU252">
+        <v>5</v>
+      </c>
+      <c r="AV252">
+        <v>4</v>
+      </c>
+      <c r="AW252">
+        <v>5</v>
+      </c>
+      <c r="AX252">
+        <v>14</v>
+      </c>
+      <c r="AY252">
+        <v>11</v>
+      </c>
+      <c r="AZ252">
+        <v>21</v>
+      </c>
+      <c r="BA252">
+        <v>6</v>
+      </c>
+      <c r="BB252">
+        <v>8</v>
+      </c>
+      <c r="BC252">
+        <v>14</v>
+      </c>
+      <c r="BD252">
+        <v>2.55</v>
+      </c>
+      <c r="BE252">
+        <v>6.75</v>
+      </c>
+      <c r="BF252">
+        <v>1.6</v>
+      </c>
+      <c r="BG252">
+        <v>1.2</v>
+      </c>
+      <c r="BH252">
+        <v>3.9</v>
+      </c>
+      <c r="BI252">
+        <v>1.36</v>
+      </c>
+      <c r="BJ252">
+        <v>2.8</v>
+      </c>
+      <c r="BK252">
+        <v>1.6</v>
+      </c>
+      <c r="BL252">
+        <v>2.17</v>
+      </c>
+      <c r="BM252">
+        <v>1.95</v>
+      </c>
+      <c r="BN252">
+        <v>1.75</v>
+      </c>
+      <c r="BO252">
+        <v>2.43</v>
+      </c>
+      <c r="BP252">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="390">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1182,6 +1182,9 @@
   <si>
     <t>['29', '61']</t>
   </si>
+  <si>
+    <t>['17', '27', '32', '89']</t>
+  </si>
 </sst>
 </file>
 
@@ -1542,7 +1545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP252"/>
+  <dimension ref="A1:BP253"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3730,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ11">
         <v>1.08</v>
@@ -5793,7 +5796,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ21">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -6202,7 +6205,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ23">
         <v>1.17</v>
@@ -9089,7 +9092,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ37">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR37">
         <v>1.98</v>
@@ -10528,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ44">
         <v>1.08</v>
@@ -11149,7 +11152,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ47">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR47">
         <v>1.75</v>
@@ -14442,7 +14445,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ63">
         <v>1.69</v>
@@ -16711,7 +16714,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ74">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR74">
         <v>1.31</v>
@@ -18356,7 +18359,7 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ82">
         <v>1.77</v>
@@ -22273,7 +22276,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ101">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR101">
         <v>1.81</v>
@@ -24536,7 +24539,7 @@
         <v>2</v>
       </c>
       <c r="AP112">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ112">
         <v>1.62</v>
@@ -24951,7 +24954,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ114">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR114">
         <v>1.26</v>
@@ -28862,7 +28865,7 @@
         <v>1.33</v>
       </c>
       <c r="AP133">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ133">
         <v>1.08</v>
@@ -29895,7 +29898,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ138">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR138">
         <v>1.44</v>
@@ -31952,7 +31955,7 @@
         <v>1.43</v>
       </c>
       <c r="AP148">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ148">
         <v>1.46</v>
@@ -34221,7 +34224,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ159">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR159">
         <v>1.69</v>
@@ -35866,7 +35869,7 @@
         <v>0.63</v>
       </c>
       <c r="AP167">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ167">
         <v>0.6899999999999999</v>
@@ -38341,7 +38344,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ179">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR179">
         <v>1.54</v>
@@ -38750,7 +38753,7 @@
         <v>1.22</v>
       </c>
       <c r="AP181">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ181">
         <v>1.38</v>
@@ -41637,7 +41640,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ195">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR195">
         <v>1.14</v>
@@ -43694,7 +43697,7 @@
         <v>1.11</v>
       </c>
       <c r="AP205">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ205">
         <v>1.58</v>
@@ -45548,7 +45551,7 @@
         <v>1.3</v>
       </c>
       <c r="AP214">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ214">
         <v>1.58</v>
@@ -48229,7 +48232,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ227">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR227">
         <v>1.4</v>
@@ -51522,7 +51525,7 @@
         <v>1.83</v>
       </c>
       <c r="AP243">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ243">
         <v>1.92</v>
@@ -52143,7 +52146,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ246">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR246">
         <v>1.24</v>
@@ -53454,6 +53457,212 @@
         <v>2.43</v>
       </c>
       <c r="BP252">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="253" spans="1:68">
+      <c r="A253" s="1">
+        <v>252</v>
+      </c>
+      <c r="B253">
+        <v>7466935</v>
+      </c>
+      <c r="C253" t="s">
+        <v>68</v>
+      </c>
+      <c r="D253" t="s">
+        <v>69</v>
+      </c>
+      <c r="E253" s="2">
+        <v>45709.70833333334</v>
+      </c>
+      <c r="F253">
+        <v>26</v>
+      </c>
+      <c r="G253" t="s">
+        <v>79</v>
+      </c>
+      <c r="H253" t="s">
+        <v>77</v>
+      </c>
+      <c r="I253">
+        <v>0</v>
+      </c>
+      <c r="J253">
+        <v>3</v>
+      </c>
+      <c r="K253">
+        <v>3</v>
+      </c>
+      <c r="L253">
+        <v>0</v>
+      </c>
+      <c r="M253">
+        <v>4</v>
+      </c>
+      <c r="N253">
+        <v>4</v>
+      </c>
+      <c r="O253" t="s">
+        <v>91</v>
+      </c>
+      <c r="P253" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q253">
+        <v>3.6</v>
+      </c>
+      <c r="R253">
+        <v>2.38</v>
+      </c>
+      <c r="S253">
+        <v>2.6</v>
+      </c>
+      <c r="T253">
+        <v>1.29</v>
+      </c>
+      <c r="U253">
+        <v>3.5</v>
+      </c>
+      <c r="V253">
+        <v>2.38</v>
+      </c>
+      <c r="W253">
+        <v>1.53</v>
+      </c>
+      <c r="X253">
+        <v>5.5</v>
+      </c>
+      <c r="Y253">
+        <v>1.14</v>
+      </c>
+      <c r="Z253">
+        <v>3.25</v>
+      </c>
+      <c r="AA253">
+        <v>3.7</v>
+      </c>
+      <c r="AB253">
+        <v>2.05</v>
+      </c>
+      <c r="AC253">
+        <v>1.03</v>
+      </c>
+      <c r="AD253">
+        <v>17</v>
+      </c>
+      <c r="AE253">
+        <v>1.19</v>
+      </c>
+      <c r="AF253">
+        <v>5</v>
+      </c>
+      <c r="AG253">
+        <v>1.57</v>
+      </c>
+      <c r="AH253">
+        <v>2.25</v>
+      </c>
+      <c r="AI253">
+        <v>1.5</v>
+      </c>
+      <c r="AJ253">
+        <v>2.5</v>
+      </c>
+      <c r="AK253">
+        <v>1.72</v>
+      </c>
+      <c r="AL253">
+        <v>1.26</v>
+      </c>
+      <c r="AM253">
+        <v>1.33</v>
+      </c>
+      <c r="AN253">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AO253">
+        <v>0.92</v>
+      </c>
+      <c r="AP253">
+        <v>0.64</v>
+      </c>
+      <c r="AQ253">
+        <v>1.08</v>
+      </c>
+      <c r="AR253">
+        <v>1.19</v>
+      </c>
+      <c r="AS253">
+        <v>1.19</v>
+      </c>
+      <c r="AT253">
+        <v>2.38</v>
+      </c>
+      <c r="AU253">
+        <v>4</v>
+      </c>
+      <c r="AV253">
+        <v>7</v>
+      </c>
+      <c r="AW253">
+        <v>5</v>
+      </c>
+      <c r="AX253">
+        <v>8</v>
+      </c>
+      <c r="AY253">
+        <v>11</v>
+      </c>
+      <c r="AZ253">
+        <v>18</v>
+      </c>
+      <c r="BA253">
+        <v>5</v>
+      </c>
+      <c r="BB253">
+        <v>6</v>
+      </c>
+      <c r="BC253">
+        <v>11</v>
+      </c>
+      <c r="BD253">
+        <v>2.28</v>
+      </c>
+      <c r="BE253">
+        <v>6.5</v>
+      </c>
+      <c r="BF253">
+        <v>1.75</v>
+      </c>
+      <c r="BG253">
+        <v>1.2</v>
+      </c>
+      <c r="BH253">
+        <v>3.9</v>
+      </c>
+      <c r="BI253">
+        <v>1.36</v>
+      </c>
+      <c r="BJ253">
+        <v>2.8</v>
+      </c>
+      <c r="BK253">
+        <v>1.6</v>
+      </c>
+      <c r="BL253">
+        <v>2.17</v>
+      </c>
+      <c r="BM253">
+        <v>1.95</v>
+      </c>
+      <c r="BN253">
+        <v>1.75</v>
+      </c>
+      <c r="BO253">
+        <v>2.43</v>
+      </c>
+      <c r="BP253">
         <v>1.48</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="397">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -787,6 +787,12 @@
     <t>['38', '45+3']</t>
   </si>
   <si>
+    <t>['19', '33']</t>
+  </si>
+  <si>
+    <t>['57', '89']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1185,6 +1191,21 @@
   <si>
     <t>['17', '27', '32', '89']</t>
   </si>
+  <si>
+    <t>['72', '80']</t>
+  </si>
+  <si>
+    <t>['23', '56', '71', '82']</t>
+  </si>
+  <si>
+    <t>['18', '26', '77', '84']</t>
+  </si>
+  <si>
+    <t>['44']</t>
+  </si>
+  <si>
+    <t>['37', '66']</t>
+  </si>
 </sst>
 </file>
 
@@ -1545,7 +1566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP253"/>
+  <dimension ref="A1:BP260"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2007,7 +2028,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2085,7 +2106,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ3">
         <v>2.29</v>
@@ -2291,10 +2312,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ4">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2419,7 +2440,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2497,10 +2518,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ5">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2831,7 +2852,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -3037,7 +3058,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3324,7 +3345,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ9">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3449,7 +3470,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3736,7 +3757,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ11">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3861,7 +3882,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4354,7 +4375,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ14">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4557,7 +4578,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ15">
         <v>0.67</v>
@@ -4763,7 +4784,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AQ16">
         <v>1.77</v>
@@ -5097,7 +5118,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5175,7 +5196,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ18">
         <v>1.92</v>
@@ -5303,7 +5324,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5384,7 +5405,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ19">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5587,7 +5608,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ20">
         <v>1.62</v>
@@ -5999,10 +6020,10 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ22">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR22">
         <v>1.72</v>
@@ -6127,7 +6148,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6333,7 +6354,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6411,7 +6432,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ24">
         <v>1.58</v>
@@ -6620,7 +6641,7 @@
         <v>2</v>
       </c>
       <c r="AQ25">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR25">
         <v>1.78</v>
@@ -6951,7 +6972,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7029,7 +7050,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ27">
         <v>1.69</v>
@@ -7157,7 +7178,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7363,7 +7384,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7444,7 +7465,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ29">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR29">
         <v>1.08</v>
@@ -7650,7 +7671,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ30">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR30">
         <v>0.47</v>
@@ -7775,7 +7796,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7981,7 +8002,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8059,7 +8080,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AQ32">
         <v>1.08</v>
@@ -8393,7 +8414,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -8677,10 +8698,10 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ35">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR35">
         <v>1.87</v>
@@ -9217,7 +9238,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9295,7 +9316,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ38">
         <v>1.08</v>
@@ -9423,7 +9444,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9501,10 +9522,10 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ39">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR39">
         <v>1.56</v>
@@ -9629,7 +9650,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9835,7 +9856,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -10041,7 +10062,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10122,7 +10143,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ42">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR42">
         <v>1.11</v>
@@ -10247,7 +10268,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10325,7 +10346,7 @@
         <v>2</v>
       </c>
       <c r="AP43">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ43">
         <v>1.62</v>
@@ -10943,7 +10964,7 @@
         <v>0.5</v>
       </c>
       <c r="AP46">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AQ46">
         <v>0.83</v>
@@ -11355,10 +11376,10 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ48">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR48">
         <v>1.44</v>
@@ -11895,7 +11916,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -12101,7 +12122,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12307,7 +12328,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12591,10 +12612,10 @@
         <v>0.5</v>
       </c>
       <c r="AP54">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ54">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR54">
         <v>1.48</v>
@@ -12719,7 +12740,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -12797,7 +12818,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ55">
         <v>0.67</v>
@@ -13006,7 +13027,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ56">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR56">
         <v>1.59</v>
@@ -13131,7 +13152,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13212,7 +13233,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ57">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR57">
         <v>1.39</v>
@@ -13337,7 +13358,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13543,7 +13564,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13621,7 +13642,7 @@
         <v>3</v>
       </c>
       <c r="AP59">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ59">
         <v>1.17</v>
@@ -13749,7 +13770,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13830,7 +13851,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ60">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR60">
         <v>1.43</v>
@@ -13955,7 +13976,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14033,7 +14054,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ61">
         <v>0.38</v>
@@ -14161,7 +14182,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14573,7 +14594,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14779,7 +14800,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14985,7 +15006,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -15066,7 +15087,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ66">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR66">
         <v>1.43</v>
@@ -15269,7 +15290,7 @@
         <v>0</v>
       </c>
       <c r="AP67">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ67">
         <v>0.38</v>
@@ -15475,7 +15496,7 @@
         <v>1.33</v>
       </c>
       <c r="AP68">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ68">
         <v>1.62</v>
@@ -15887,7 +15908,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ70">
         <v>1.08</v>
@@ -16015,7 +16036,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16096,7 +16117,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ71">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR71">
         <v>1.59</v>
@@ -16221,7 +16242,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q72">
         <v>1.95</v>
@@ -16302,7 +16323,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ72">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR72">
         <v>1.91</v>
@@ -16427,7 +16448,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16505,7 +16526,7 @@
         <v>2.33</v>
       </c>
       <c r="AP73">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ73">
         <v>1.17</v>
@@ -16633,7 +16654,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16839,7 +16860,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16920,7 +16941,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ75">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR75">
         <v>0.91</v>
@@ -17045,7 +17066,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17123,7 +17144,7 @@
         <v>0.33</v>
       </c>
       <c r="AP76">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AQ76">
         <v>0.67</v>
@@ -17251,7 +17272,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17329,7 +17350,7 @@
         <v>0.33</v>
       </c>
       <c r="AP77">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ77">
         <v>1.08</v>
@@ -17535,7 +17556,7 @@
         <v>2.33</v>
       </c>
       <c r="AP78">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ78">
         <v>1.92</v>
@@ -17663,7 +17684,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17869,7 +17890,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -17950,7 +17971,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ80">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR80">
         <v>1.97</v>
@@ -18156,7 +18177,7 @@
         <v>2</v>
       </c>
       <c r="AQ81">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR81">
         <v>1.42</v>
@@ -18281,7 +18302,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18693,7 +18714,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18774,7 +18795,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ84">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR84">
         <v>1.51</v>
@@ -18899,7 +18920,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -18977,7 +18998,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ85">
         <v>1.69</v>
@@ -19105,7 +19126,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19389,7 +19410,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ87">
         <v>1.58</v>
@@ -19517,7 +19538,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19804,7 +19825,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ89">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR89">
         <v>1.28</v>
@@ -19929,7 +19950,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20135,7 +20156,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20213,7 +20234,7 @@
         <v>3</v>
       </c>
       <c r="AP91">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ91">
         <v>2.29</v>
@@ -20625,7 +20646,7 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AQ93">
         <v>1.08</v>
@@ -20831,7 +20852,7 @@
         <v>2.5</v>
       </c>
       <c r="AP94">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ94">
         <v>1.38</v>
@@ -21037,7 +21058,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ95">
         <v>0.67</v>
@@ -21246,7 +21267,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ96">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR96">
         <v>1.78</v>
@@ -21452,7 +21473,7 @@
         <v>2</v>
       </c>
       <c r="AQ97">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR97">
         <v>1.51</v>
@@ -21577,7 +21598,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21658,7 +21679,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ98">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR98">
         <v>1.11</v>
@@ -21783,7 +21804,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -21989,7 +22010,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22070,7 +22091,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ100">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR100">
         <v>1.55</v>
@@ -22273,7 +22294,7 @@
         <v>0</v>
       </c>
       <c r="AP101">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ101">
         <v>1.08</v>
@@ -22401,7 +22422,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22607,7 +22628,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23843,7 +23864,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -24049,7 +24070,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24255,7 +24276,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q111">
         <v>3.25</v>
@@ -24461,7 +24482,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24542,7 +24563,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ112">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR112">
         <v>1.12</v>
@@ -24667,7 +24688,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -24745,10 +24766,10 @@
         <v>0.4</v>
       </c>
       <c r="AP113">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ113">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR113">
         <v>1.98</v>
@@ -24951,7 +24972,7 @@
         <v>0</v>
       </c>
       <c r="AP114">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ114">
         <v>1.08</v>
@@ -25157,7 +25178,7 @@
         <v>2.2</v>
       </c>
       <c r="AP115">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ115">
         <v>1.77</v>
@@ -25285,7 +25306,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25363,10 +25384,10 @@
         <v>1.4</v>
       </c>
       <c r="AP116">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ116">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR116">
         <v>1.57</v>
@@ -25491,7 +25512,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25569,10 +25590,10 @@
         <v>0.4</v>
       </c>
       <c r="AP117">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ117">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR117">
         <v>1.41</v>
@@ -25697,7 +25718,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25778,7 +25799,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ118">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR118">
         <v>2.34</v>
@@ -25903,7 +25924,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -25981,7 +26002,7 @@
         <v>2.6</v>
       </c>
       <c r="AP119">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AQ119">
         <v>2.29</v>
@@ -26109,7 +26130,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26187,7 +26208,7 @@
         <v>1</v>
       </c>
       <c r="AP120">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ120">
         <v>1.08</v>
@@ -26315,7 +26336,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26396,7 +26417,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ121">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR121">
         <v>1.12</v>
@@ -26521,7 +26542,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26727,7 +26748,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -27345,7 +27366,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27551,7 +27572,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -28169,7 +28190,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28581,7 +28602,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28659,10 +28680,10 @@
         <v>0.5</v>
       </c>
       <c r="AP132">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ132">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR132">
         <v>1.18</v>
@@ -28868,7 +28889,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ133">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR133">
         <v>1.02</v>
@@ -28993,7 +29014,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29071,10 +29092,10 @@
         <v>2.17</v>
       </c>
       <c r="AP134">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AQ134">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR134">
         <v>1.08</v>
@@ -29199,7 +29220,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -29689,10 +29710,10 @@
         <v>0.83</v>
       </c>
       <c r="AP137">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ137">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR137">
         <v>1.42</v>
@@ -29895,7 +29916,7 @@
         <v>0.17</v>
       </c>
       <c r="AP138">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ138">
         <v>1.08</v>
@@ -30101,7 +30122,7 @@
         <v>1</v>
       </c>
       <c r="AP139">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ139">
         <v>1.08</v>
@@ -30307,10 +30328,10 @@
         <v>1.67</v>
       </c>
       <c r="AP140">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ140">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR140">
         <v>1.88</v>
@@ -30513,10 +30534,10 @@
         <v>1.17</v>
       </c>
       <c r="AP141">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ141">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR141">
         <v>1.64</v>
@@ -30641,7 +30662,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30847,7 +30868,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -31131,7 +31152,7 @@
         <v>0.14</v>
       </c>
       <c r="AP144">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ144">
         <v>0.38</v>
@@ -31259,7 +31280,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31465,7 +31486,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31543,7 +31564,7 @@
         <v>1.57</v>
       </c>
       <c r="AP146">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ146">
         <v>1.92</v>
@@ -31671,7 +31692,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31749,7 +31770,7 @@
         <v>1.14</v>
       </c>
       <c r="AP147">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ147">
         <v>1.69</v>
@@ -31877,7 +31898,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -31958,7 +31979,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ148">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR148">
         <v>1.08</v>
@@ -32083,7 +32104,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32164,7 +32185,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ149">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR149">
         <v>1.84</v>
@@ -32370,7 +32391,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ150">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR150">
         <v>1.48</v>
@@ -32495,7 +32516,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -32779,7 +32800,7 @@
         <v>0.71</v>
       </c>
       <c r="AP152">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ152">
         <v>1.08</v>
@@ -33113,7 +33134,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33319,7 +33340,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33525,7 +33546,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33606,7 +33627,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ156">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR156">
         <v>1.53</v>
@@ -33731,7 +33752,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33937,7 +33958,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34015,10 +34036,10 @@
         <v>1</v>
       </c>
       <c r="AP158">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AQ158">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR158">
         <v>1.06</v>
@@ -34427,10 +34448,10 @@
         <v>1.14</v>
       </c>
       <c r="AP160">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ160">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR160">
         <v>1.69</v>
@@ -34633,7 +34654,7 @@
         <v>1.38</v>
       </c>
       <c r="AP161">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ161">
         <v>1.38</v>
@@ -34761,7 +34782,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -34967,7 +34988,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35048,7 +35069,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ163">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR163">
         <v>1.48</v>
@@ -35173,7 +35194,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35251,7 +35272,7 @@
         <v>1.13</v>
       </c>
       <c r="AP164">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ164">
         <v>1.62</v>
@@ -35379,7 +35400,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35663,7 +35684,7 @@
         <v>0.13</v>
       </c>
       <c r="AP166">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ166">
         <v>0.38</v>
@@ -35791,7 +35812,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35872,7 +35893,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ167">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR167">
         <v>1.06</v>
@@ -35997,7 +36018,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36281,10 +36302,10 @@
         <v>2.38</v>
       </c>
       <c r="AP169">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ169">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR169">
         <v>1.39</v>
@@ -36409,7 +36430,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36821,7 +36842,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -36899,10 +36920,10 @@
         <v>1.13</v>
       </c>
       <c r="AP172">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AQ172">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR172">
         <v>1.06</v>
@@ -37108,7 +37129,7 @@
         <v>2</v>
       </c>
       <c r="AQ173">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR173">
         <v>1.56</v>
@@ -37439,7 +37460,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -37723,10 +37744,10 @@
         <v>1.13</v>
       </c>
       <c r="AP176">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ176">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR176">
         <v>1.74</v>
@@ -38057,7 +38078,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38547,7 +38568,7 @@
         <v>1</v>
       </c>
       <c r="AP180">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ180">
         <v>0.83</v>
@@ -38675,7 +38696,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38881,7 +38902,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -38962,7 +38983,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ182">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR182">
         <v>1.74</v>
@@ -39293,7 +39314,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39371,7 +39392,7 @@
         <v>1.56</v>
       </c>
       <c r="AP184">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ184">
         <v>1.69</v>
@@ -39499,7 +39520,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39577,7 +39598,7 @@
         <v>1.89</v>
       </c>
       <c r="AP185">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ185">
         <v>1.77</v>
@@ -39705,7 +39726,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -39989,10 +40010,10 @@
         <v>2.22</v>
       </c>
       <c r="AP187">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ187">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR187">
         <v>1.17</v>
@@ -40117,7 +40138,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40195,10 +40216,10 @@
         <v>1.33</v>
       </c>
       <c r="AP188">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ188">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR188">
         <v>1.51</v>
@@ -40323,7 +40344,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40529,7 +40550,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40735,7 +40756,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -41019,7 +41040,7 @@
         <v>0.78</v>
       </c>
       <c r="AP192">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ192">
         <v>1.08</v>
@@ -41147,7 +41168,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41225,7 +41246,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP193">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ193">
         <v>0.67</v>
@@ -41434,7 +41455,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ194">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR194">
         <v>1.41</v>
@@ -41559,7 +41580,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41637,7 +41658,7 @@
         <v>0.22</v>
       </c>
       <c r="AP195">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AQ195">
         <v>1.08</v>
@@ -41765,7 +41786,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -41846,7 +41867,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ196">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR196">
         <v>2.09</v>
@@ -42177,7 +42198,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42255,7 +42276,7 @@
         <v>0.89</v>
       </c>
       <c r="AP198">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ198">
         <v>0.83</v>
@@ -42383,7 +42404,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42589,7 +42610,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42795,7 +42816,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -43001,7 +43022,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43207,7 +43228,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43413,7 +43434,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43619,7 +43640,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -43700,7 +43721,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ205">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR205">
         <v>1.11</v>
@@ -43906,7 +43927,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ206">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR206">
         <v>1.56</v>
@@ -44031,7 +44052,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44109,7 +44130,7 @@
         <v>1.11</v>
       </c>
       <c r="AP207">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ207">
         <v>1.17</v>
@@ -44315,10 +44336,10 @@
         <v>1.11</v>
       </c>
       <c r="AP208">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ208">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR208">
         <v>1.98</v>
@@ -44443,7 +44464,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44521,10 +44542,10 @@
         <v>1.3</v>
       </c>
       <c r="AP209">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ209">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR209">
         <v>1.16</v>
@@ -44855,7 +44876,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45061,7 +45082,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45142,7 +45163,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ212">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR212">
         <v>1.29</v>
@@ -45267,7 +45288,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45473,7 +45494,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45679,7 +45700,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -45757,7 +45778,7 @@
         <v>1.3</v>
       </c>
       <c r="AP215">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ215">
         <v>1.17</v>
@@ -45885,7 +45906,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -45966,7 +45987,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ216">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR216">
         <v>1.58</v>
@@ -46091,7 +46112,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46297,7 +46318,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46375,10 +46396,10 @@
         <v>1</v>
       </c>
       <c r="AP218">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ218">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR218">
         <v>1.33</v>
@@ -46503,7 +46524,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46581,7 +46602,7 @@
         <v>1.36</v>
       </c>
       <c r="AP219">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ219">
         <v>1.38</v>
@@ -46709,7 +46730,7 @@
         <v>240</v>
       </c>
       <c r="P220" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q220">
         <v>1.73</v>
@@ -46790,7 +46811,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ220">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR220">
         <v>1.85</v>
@@ -46993,7 +47014,7 @@
         <v>2.09</v>
       </c>
       <c r="AP221">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ221">
         <v>1.77</v>
@@ -47121,7 +47142,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -47533,7 +47554,7 @@
         <v>107</v>
       </c>
       <c r="P224" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q224">
         <v>6</v>
@@ -47611,7 +47632,7 @@
         <v>1.64</v>
       </c>
       <c r="AP224">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AQ224">
         <v>1.62</v>
@@ -47739,7 +47760,7 @@
         <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q225">
         <v>6.5</v>
@@ -47945,7 +47966,7 @@
         <v>243</v>
       </c>
       <c r="P226" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q226">
         <v>2.38</v>
@@ -48026,7 +48047,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ226">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR226">
         <v>2.02</v>
@@ -48151,7 +48172,7 @@
         <v>155</v>
       </c>
       <c r="P227" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48357,7 +48378,7 @@
         <v>244</v>
       </c>
       <c r="P228" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q228">
         <v>1.91</v>
@@ -48641,10 +48662,10 @@
         <v>1.2</v>
       </c>
       <c r="AP229">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ229">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR229">
         <v>1.51</v>
@@ -48769,7 +48790,7 @@
         <v>91</v>
       </c>
       <c r="P230" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q230">
         <v>2.88</v>
@@ -48847,7 +48868,7 @@
         <v>1</v>
       </c>
       <c r="AP230">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ230">
         <v>1.08</v>
@@ -49056,7 +49077,7 @@
         <v>2</v>
       </c>
       <c r="AQ231">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR231">
         <v>1.47</v>
@@ -49181,7 +49202,7 @@
         <v>95</v>
       </c>
       <c r="P232" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q232">
         <v>2.2</v>
@@ -49465,7 +49486,7 @@
         <v>0.73</v>
       </c>
       <c r="AP233">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ233">
         <v>0.67</v>
@@ -49593,7 +49614,7 @@
         <v>151</v>
       </c>
       <c r="P234" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q234">
         <v>2.6</v>
@@ -49671,7 +49692,7 @@
         <v>0.17</v>
       </c>
       <c r="AP234">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ234">
         <v>0.38</v>
@@ -49799,7 +49820,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q235">
         <v>4.5</v>
@@ -49877,7 +49898,7 @@
         <v>2.45</v>
       </c>
       <c r="AP235">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ235">
         <v>2.29</v>
@@ -50211,7 +50232,7 @@
         <v>91</v>
       </c>
       <c r="P237" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50292,7 +50313,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ237">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR237">
         <v>1.59</v>
@@ -50417,7 +50438,7 @@
         <v>91</v>
       </c>
       <c r="P238" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q238">
         <v>2.75</v>
@@ -50498,7 +50519,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ238">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR238">
         <v>1.51</v>
@@ -50701,7 +50722,7 @@
         <v>1.5</v>
       </c>
       <c r="AP239">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ239">
         <v>1.38</v>
@@ -50829,7 +50850,7 @@
         <v>249</v>
       </c>
       <c r="P240" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q240">
         <v>1.8</v>
@@ -50910,7 +50931,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ240">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR240">
         <v>1.89</v>
@@ -51035,7 +51056,7 @@
         <v>250</v>
       </c>
       <c r="P241" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q241">
         <v>6</v>
@@ -51113,7 +51134,7 @@
         <v>2.5</v>
       </c>
       <c r="AP241">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ241">
         <v>2.29</v>
@@ -51322,7 +51343,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ242">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR242">
         <v>1.61</v>
@@ -51447,7 +51468,7 @@
         <v>91</v>
       </c>
       <c r="P243" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q243">
         <v>9</v>
@@ -51653,7 +51674,7 @@
         <v>203</v>
       </c>
       <c r="P244" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q244">
         <v>5</v>
@@ -51731,7 +51752,7 @@
         <v>1.58</v>
       </c>
       <c r="AP244">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AQ244">
         <v>1.69</v>
@@ -52349,7 +52370,7 @@
         <v>1.92</v>
       </c>
       <c r="AP247">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ247">
         <v>1.77</v>
@@ -52555,7 +52576,7 @@
         <v>0.82</v>
       </c>
       <c r="AP248">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ248">
         <v>0.83</v>
@@ -52683,7 +52704,7 @@
         <v>254</v>
       </c>
       <c r="P249" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q249">
         <v>2.63</v>
@@ -52889,7 +52910,7 @@
         <v>255</v>
       </c>
       <c r="P250" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q250">
         <v>1.57</v>
@@ -52970,7 +52991,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ250">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR250">
         <v>1.85</v>
@@ -53301,7 +53322,7 @@
         <v>256</v>
       </c>
       <c r="P252" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q252">
         <v>4</v>
@@ -53379,7 +53400,7 @@
         <v>2.38</v>
       </c>
       <c r="AP252">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ252">
         <v>2.29</v>
@@ -53507,7 +53528,7 @@
         <v>91</v>
       </c>
       <c r="P253" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q253">
         <v>3.6</v>
@@ -53664,6 +53685,1448 @@
       </c>
       <c r="BP253">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="254" spans="1:68">
+      <c r="A254" s="1">
+        <v>253</v>
+      </c>
+      <c r="B254">
+        <v>7466932</v>
+      </c>
+      <c r="C254" t="s">
+        <v>68</v>
+      </c>
+      <c r="D254" t="s">
+        <v>69</v>
+      </c>
+      <c r="E254" s="2">
+        <v>45710.39583333334</v>
+      </c>
+      <c r="F254">
+        <v>26</v>
+      </c>
+      <c r="G254" t="s">
+        <v>73</v>
+      </c>
+      <c r="H254" t="s">
+        <v>70</v>
+      </c>
+      <c r="I254">
+        <v>2</v>
+      </c>
+      <c r="J254">
+        <v>0</v>
+      </c>
+      <c r="K254">
+        <v>2</v>
+      </c>
+      <c r="L254">
+        <v>2</v>
+      </c>
+      <c r="M254">
+        <v>2</v>
+      </c>
+      <c r="N254">
+        <v>4</v>
+      </c>
+      <c r="O254" t="s">
+        <v>257</v>
+      </c>
+      <c r="P254" t="s">
+        <v>392</v>
+      </c>
+      <c r="Q254">
+        <v>3.25</v>
+      </c>
+      <c r="R254">
+        <v>2.05</v>
+      </c>
+      <c r="S254">
+        <v>3.5</v>
+      </c>
+      <c r="T254">
+        <v>1.44</v>
+      </c>
+      <c r="U254">
+        <v>2.63</v>
+      </c>
+      <c r="V254">
+        <v>3.4</v>
+      </c>
+      <c r="W254">
+        <v>1.3</v>
+      </c>
+      <c r="X254">
+        <v>10</v>
+      </c>
+      <c r="Y254">
+        <v>1.06</v>
+      </c>
+      <c r="Z254">
+        <v>3</v>
+      </c>
+      <c r="AA254">
+        <v>3.2</v>
+      </c>
+      <c r="AB254">
+        <v>2.4</v>
+      </c>
+      <c r="AC254">
+        <v>1.08</v>
+      </c>
+      <c r="AD254">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE254">
+        <v>1.4</v>
+      </c>
+      <c r="AF254">
+        <v>3.05</v>
+      </c>
+      <c r="AG254">
+        <v>2</v>
+      </c>
+      <c r="AH254">
+        <v>1.75</v>
+      </c>
+      <c r="AI254">
+        <v>1.91</v>
+      </c>
+      <c r="AJ254">
+        <v>1.91</v>
+      </c>
+      <c r="AK254">
+        <v>1.46</v>
+      </c>
+      <c r="AL254">
+        <v>1.33</v>
+      </c>
+      <c r="AM254">
+        <v>1.46</v>
+      </c>
+      <c r="AN254">
+        <v>1.31</v>
+      </c>
+      <c r="AO254">
+        <v>1.08</v>
+      </c>
+      <c r="AP254">
+        <v>1.29</v>
+      </c>
+      <c r="AQ254">
+        <v>1.08</v>
+      </c>
+      <c r="AR254">
+        <v>1.39</v>
+      </c>
+      <c r="AS254">
+        <v>1.36</v>
+      </c>
+      <c r="AT254">
+        <v>2.75</v>
+      </c>
+      <c r="AU254">
+        <v>9</v>
+      </c>
+      <c r="AV254">
+        <v>4</v>
+      </c>
+      <c r="AW254">
+        <v>1</v>
+      </c>
+      <c r="AX254">
+        <v>6</v>
+      </c>
+      <c r="AY254">
+        <v>11</v>
+      </c>
+      <c r="AZ254">
+        <v>14</v>
+      </c>
+      <c r="BA254">
+        <v>7</v>
+      </c>
+      <c r="BB254">
+        <v>8</v>
+      </c>
+      <c r="BC254">
+        <v>15</v>
+      </c>
+      <c r="BD254">
+        <v>1.91</v>
+      </c>
+      <c r="BE254">
+        <v>6.5</v>
+      </c>
+      <c r="BF254">
+        <v>2.07</v>
+      </c>
+      <c r="BG254">
+        <v>1.23</v>
+      </c>
+      <c r="BH254">
+        <v>3.65</v>
+      </c>
+      <c r="BI254">
+        <v>1.41</v>
+      </c>
+      <c r="BJ254">
+        <v>2.65</v>
+      </c>
+      <c r="BK254">
+        <v>1.66</v>
+      </c>
+      <c r="BL254">
+        <v>2.06</v>
+      </c>
+      <c r="BM254">
+        <v>2.06</v>
+      </c>
+      <c r="BN254">
+        <v>1.66</v>
+      </c>
+      <c r="BO254">
+        <v>2.55</v>
+      </c>
+      <c r="BP254">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="255" spans="1:68">
+      <c r="A255" s="1">
+        <v>254</v>
+      </c>
+      <c r="B255">
+        <v>7466938</v>
+      </c>
+      <c r="C255" t="s">
+        <v>68</v>
+      </c>
+      <c r="D255" t="s">
+        <v>69</v>
+      </c>
+      <c r="E255" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F255">
+        <v>26</v>
+      </c>
+      <c r="G255" t="s">
+        <v>84</v>
+      </c>
+      <c r="H255" t="s">
+        <v>80</v>
+      </c>
+      <c r="I255">
+        <v>0</v>
+      </c>
+      <c r="J255">
+        <v>1</v>
+      </c>
+      <c r="K255">
+        <v>1</v>
+      </c>
+      <c r="L255">
+        <v>0</v>
+      </c>
+      <c r="M255">
+        <v>4</v>
+      </c>
+      <c r="N255">
+        <v>4</v>
+      </c>
+      <c r="O255" t="s">
+        <v>91</v>
+      </c>
+      <c r="P255" t="s">
+        <v>393</v>
+      </c>
+      <c r="Q255">
+        <v>5</v>
+      </c>
+      <c r="R255">
+        <v>2.4</v>
+      </c>
+      <c r="S255">
+        <v>2.1</v>
+      </c>
+      <c r="T255">
+        <v>1.29</v>
+      </c>
+      <c r="U255">
+        <v>3.5</v>
+      </c>
+      <c r="V255">
+        <v>2.38</v>
+      </c>
+      <c r="W255">
+        <v>1.53</v>
+      </c>
+      <c r="X255">
+        <v>5.5</v>
+      </c>
+      <c r="Y255">
+        <v>1.14</v>
+      </c>
+      <c r="Z255">
+        <v>4.33</v>
+      </c>
+      <c r="AA255">
+        <v>4</v>
+      </c>
+      <c r="AB255">
+        <v>1.73</v>
+      </c>
+      <c r="AC255">
+        <v>1.02</v>
+      </c>
+      <c r="AD255">
+        <v>18</v>
+      </c>
+      <c r="AE255">
+        <v>1.19</v>
+      </c>
+      <c r="AF255">
+        <v>5</v>
+      </c>
+      <c r="AG255">
+        <v>1.55</v>
+      </c>
+      <c r="AH255">
+        <v>2.3</v>
+      </c>
+      <c r="AI255">
+        <v>1.67</v>
+      </c>
+      <c r="AJ255">
+        <v>2.1</v>
+      </c>
+      <c r="AK255">
+        <v>2.25</v>
+      </c>
+      <c r="AL255">
+        <v>1.22</v>
+      </c>
+      <c r="AM255">
+        <v>1.17</v>
+      </c>
+      <c r="AN255">
+        <v>0.33</v>
+      </c>
+      <c r="AO255">
+        <v>1.46</v>
+      </c>
+      <c r="AP255">
+        <v>0.31</v>
+      </c>
+      <c r="AQ255">
+        <v>1.57</v>
+      </c>
+      <c r="AR255">
+        <v>1.18</v>
+      </c>
+      <c r="AS255">
+        <v>1.39</v>
+      </c>
+      <c r="AT255">
+        <v>2.57</v>
+      </c>
+      <c r="AU255">
+        <v>2</v>
+      </c>
+      <c r="AV255">
+        <v>13</v>
+      </c>
+      <c r="AW255">
+        <v>5</v>
+      </c>
+      <c r="AX255">
+        <v>6</v>
+      </c>
+      <c r="AY255">
+        <v>10</v>
+      </c>
+      <c r="AZ255">
+        <v>23</v>
+      </c>
+      <c r="BA255">
+        <v>5</v>
+      </c>
+      <c r="BB255">
+        <v>6</v>
+      </c>
+      <c r="BC255">
+        <v>11</v>
+      </c>
+      <c r="BD255">
+        <v>2.8</v>
+      </c>
+      <c r="BE255">
+        <v>7</v>
+      </c>
+      <c r="BF255">
+        <v>1.49</v>
+      </c>
+      <c r="BG255">
+        <v>1.24</v>
+      </c>
+      <c r="BH255">
+        <v>3.55</v>
+      </c>
+      <c r="BI255">
+        <v>1.41</v>
+      </c>
+      <c r="BJ255">
+        <v>2.65</v>
+      </c>
+      <c r="BK255">
+        <v>1.66</v>
+      </c>
+      <c r="BL255">
+        <v>2.06</v>
+      </c>
+      <c r="BM255">
+        <v>2.04</v>
+      </c>
+      <c r="BN255">
+        <v>1.68</v>
+      </c>
+      <c r="BO255">
+        <v>2.55</v>
+      </c>
+      <c r="BP255">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="256" spans="1:68">
+      <c r="A256" s="1">
+        <v>255</v>
+      </c>
+      <c r="B256">
+        <v>7466934</v>
+      </c>
+      <c r="C256" t="s">
+        <v>68</v>
+      </c>
+      <c r="D256" t="s">
+        <v>69</v>
+      </c>
+      <c r="E256" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F256">
+        <v>26</v>
+      </c>
+      <c r="G256" t="s">
+        <v>71</v>
+      </c>
+      <c r="H256" t="s">
+        <v>81</v>
+      </c>
+      <c r="I256">
+        <v>1</v>
+      </c>
+      <c r="J256">
+        <v>2</v>
+      </c>
+      <c r="K256">
+        <v>3</v>
+      </c>
+      <c r="L256">
+        <v>1</v>
+      </c>
+      <c r="M256">
+        <v>4</v>
+      </c>
+      <c r="N256">
+        <v>5</v>
+      </c>
+      <c r="O256" t="s">
+        <v>117</v>
+      </c>
+      <c r="P256" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q256">
+        <v>3.75</v>
+      </c>
+      <c r="R256">
+        <v>2.4</v>
+      </c>
+      <c r="S256">
+        <v>2.5</v>
+      </c>
+      <c r="T256">
+        <v>1.29</v>
+      </c>
+      <c r="U256">
+        <v>3.5</v>
+      </c>
+      <c r="V256">
+        <v>2.25</v>
+      </c>
+      <c r="W256">
+        <v>1.57</v>
+      </c>
+      <c r="X256">
+        <v>5.5</v>
+      </c>
+      <c r="Y256">
+        <v>1.14</v>
+      </c>
+      <c r="Z256">
+        <v>3.4</v>
+      </c>
+      <c r="AA256">
+        <v>3.75</v>
+      </c>
+      <c r="AB256">
+        <v>2</v>
+      </c>
+      <c r="AC256">
+        <v>1.03</v>
+      </c>
+      <c r="AD256">
+        <v>17</v>
+      </c>
+      <c r="AE256">
+        <v>1.18</v>
+      </c>
+      <c r="AF256">
+        <v>5.1</v>
+      </c>
+      <c r="AG256">
+        <v>1.5</v>
+      </c>
+      <c r="AH256">
+        <v>2.48</v>
+      </c>
+      <c r="AI256">
+        <v>1.5</v>
+      </c>
+      <c r="AJ256">
+        <v>2.5</v>
+      </c>
+      <c r="AK256">
+        <v>1.73</v>
+      </c>
+      <c r="AL256">
+        <v>1.26</v>
+      </c>
+      <c r="AM256">
+        <v>1.33</v>
+      </c>
+      <c r="AN256">
+        <v>0.54</v>
+      </c>
+      <c r="AO256">
+        <v>1.08</v>
+      </c>
+      <c r="AP256">
+        <v>0.5</v>
+      </c>
+      <c r="AQ256">
+        <v>1.23</v>
+      </c>
+      <c r="AR256">
+        <v>1.19</v>
+      </c>
+      <c r="AS256">
+        <v>1.6</v>
+      </c>
+      <c r="AT256">
+        <v>2.79</v>
+      </c>
+      <c r="AU256">
+        <v>6</v>
+      </c>
+      <c r="AV256">
+        <v>7</v>
+      </c>
+      <c r="AW256">
+        <v>12</v>
+      </c>
+      <c r="AX256">
+        <v>4</v>
+      </c>
+      <c r="AY256">
+        <v>24</v>
+      </c>
+      <c r="AZ256">
+        <v>14</v>
+      </c>
+      <c r="BA256">
+        <v>4</v>
+      </c>
+      <c r="BB256">
+        <v>4</v>
+      </c>
+      <c r="BC256">
+        <v>8</v>
+      </c>
+      <c r="BD256">
+        <v>2.6</v>
+      </c>
+      <c r="BE256">
+        <v>7</v>
+      </c>
+      <c r="BF256">
+        <v>1.57</v>
+      </c>
+      <c r="BG256">
+        <v>1.11</v>
+      </c>
+      <c r="BH256">
+        <v>5.3</v>
+      </c>
+      <c r="BI256">
+        <v>1.21</v>
+      </c>
+      <c r="BJ256">
+        <v>3.8</v>
+      </c>
+      <c r="BK256">
+        <v>1.38</v>
+      </c>
+      <c r="BL256">
+        <v>2.75</v>
+      </c>
+      <c r="BM256">
+        <v>1.6</v>
+      </c>
+      <c r="BN256">
+        <v>2.17</v>
+      </c>
+      <c r="BO256">
+        <v>1.95</v>
+      </c>
+      <c r="BP256">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="257" spans="1:68">
+      <c r="A257" s="1">
+        <v>256</v>
+      </c>
+      <c r="B257">
+        <v>7466930</v>
+      </c>
+      <c r="C257" t="s">
+        <v>68</v>
+      </c>
+      <c r="D257" t="s">
+        <v>69</v>
+      </c>
+      <c r="E257" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F257">
+        <v>26</v>
+      </c>
+      <c r="G257" t="s">
+        <v>72</v>
+      </c>
+      <c r="H257" t="s">
+        <v>76</v>
+      </c>
+      <c r="I257">
+        <v>0</v>
+      </c>
+      <c r="J257">
+        <v>1</v>
+      </c>
+      <c r="K257">
+        <v>1</v>
+      </c>
+      <c r="L257">
+        <v>0</v>
+      </c>
+      <c r="M257">
+        <v>1</v>
+      </c>
+      <c r="N257">
+        <v>1</v>
+      </c>
+      <c r="O257" t="s">
+        <v>91</v>
+      </c>
+      <c r="P257" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q257">
+        <v>1.73</v>
+      </c>
+      <c r="R257">
+        <v>2.6</v>
+      </c>
+      <c r="S257">
+        <v>9.5</v>
+      </c>
+      <c r="T257">
+        <v>1.3</v>
+      </c>
+      <c r="U257">
+        <v>3.4</v>
+      </c>
+      <c r="V257">
+        <v>2.5</v>
+      </c>
+      <c r="W257">
+        <v>1.5</v>
+      </c>
+      <c r="X257">
+        <v>6</v>
+      </c>
+      <c r="Y257">
+        <v>1.13</v>
+      </c>
+      <c r="Z257">
+        <v>1.25</v>
+      </c>
+      <c r="AA257">
+        <v>6</v>
+      </c>
+      <c r="AB257">
+        <v>10</v>
+      </c>
+      <c r="AC257">
+        <v>1.02</v>
+      </c>
+      <c r="AD257">
+        <v>17</v>
+      </c>
+      <c r="AE257">
+        <v>1.22</v>
+      </c>
+      <c r="AF257">
+        <v>4.6</v>
+      </c>
+      <c r="AG257">
+        <v>1.58</v>
+      </c>
+      <c r="AH257">
+        <v>2.37</v>
+      </c>
+      <c r="AI257">
+        <v>2.2</v>
+      </c>
+      <c r="AJ257">
+        <v>1.62</v>
+      </c>
+      <c r="AK257">
+        <v>1.06</v>
+      </c>
+      <c r="AL257">
+        <v>1.14</v>
+      </c>
+      <c r="AM257">
+        <v>3.5</v>
+      </c>
+      <c r="AN257">
+        <v>2.33</v>
+      </c>
+      <c r="AO257">
+        <v>1.08</v>
+      </c>
+      <c r="AP257">
+        <v>2.15</v>
+      </c>
+      <c r="AQ257">
+        <v>1.23</v>
+      </c>
+      <c r="AR257">
+        <v>1.97</v>
+      </c>
+      <c r="AS257">
+        <v>1.47</v>
+      </c>
+      <c r="AT257">
+        <v>3.44</v>
+      </c>
+      <c r="AU257">
+        <v>3</v>
+      </c>
+      <c r="AV257">
+        <v>3</v>
+      </c>
+      <c r="AW257">
+        <v>18</v>
+      </c>
+      <c r="AX257">
+        <v>3</v>
+      </c>
+      <c r="AY257">
+        <v>28</v>
+      </c>
+      <c r="AZ257">
+        <v>6</v>
+      </c>
+      <c r="BA257">
+        <v>2</v>
+      </c>
+      <c r="BB257">
+        <v>0</v>
+      </c>
+      <c r="BC257">
+        <v>2</v>
+      </c>
+      <c r="BD257">
+        <v>1.16</v>
+      </c>
+      <c r="BE257">
+        <v>9.5</v>
+      </c>
+      <c r="BF257">
+        <v>5.4</v>
+      </c>
+      <c r="BG257">
+        <v>1.2</v>
+      </c>
+      <c r="BH257">
+        <v>3.95</v>
+      </c>
+      <c r="BI257">
+        <v>1.36</v>
+      </c>
+      <c r="BJ257">
+        <v>2.85</v>
+      </c>
+      <c r="BK257">
+        <v>1.58</v>
+      </c>
+      <c r="BL257">
+        <v>2.18</v>
+      </c>
+      <c r="BM257">
+        <v>1.93</v>
+      </c>
+      <c r="BN257">
+        <v>1.76</v>
+      </c>
+      <c r="BO257">
+        <v>2.4</v>
+      </c>
+      <c r="BP257">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="258" spans="1:68">
+      <c r="A258" s="1">
+        <v>257</v>
+      </c>
+      <c r="B258">
+        <v>7466929</v>
+      </c>
+      <c r="C258" t="s">
+        <v>68</v>
+      </c>
+      <c r="D258" t="s">
+        <v>69</v>
+      </c>
+      <c r="E258" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F258">
+        <v>26</v>
+      </c>
+      <c r="G258" t="s">
+        <v>88</v>
+      </c>
+      <c r="H258" t="s">
+        <v>87</v>
+      </c>
+      <c r="I258">
+        <v>0</v>
+      </c>
+      <c r="J258">
+        <v>1</v>
+      </c>
+      <c r="K258">
+        <v>1</v>
+      </c>
+      <c r="L258">
+        <v>0</v>
+      </c>
+      <c r="M258">
+        <v>1</v>
+      </c>
+      <c r="N258">
+        <v>1</v>
+      </c>
+      <c r="O258" t="s">
+        <v>91</v>
+      </c>
+      <c r="P258" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q258">
+        <v>2.1</v>
+      </c>
+      <c r="R258">
+        <v>2.4</v>
+      </c>
+      <c r="S258">
+        <v>5</v>
+      </c>
+      <c r="T258">
+        <v>1.29</v>
+      </c>
+      <c r="U258">
+        <v>3.5</v>
+      </c>
+      <c r="V258">
+        <v>2.38</v>
+      </c>
+      <c r="W258">
+        <v>1.53</v>
+      </c>
+      <c r="X258">
+        <v>5.5</v>
+      </c>
+      <c r="Y258">
+        <v>1.14</v>
+      </c>
+      <c r="Z258">
+        <v>1.62</v>
+      </c>
+      <c r="AA258">
+        <v>4.2</v>
+      </c>
+      <c r="AB258">
+        <v>4.6</v>
+      </c>
+      <c r="AC258">
+        <v>1.03</v>
+      </c>
+      <c r="AD258">
+        <v>17</v>
+      </c>
+      <c r="AE258">
+        <v>1.2</v>
+      </c>
+      <c r="AF258">
+        <v>4.85</v>
+      </c>
+      <c r="AG258">
+        <v>1.55</v>
+      </c>
+      <c r="AH258">
+        <v>2.3</v>
+      </c>
+      <c r="AI258">
+        <v>1.67</v>
+      </c>
+      <c r="AJ258">
+        <v>2.1</v>
+      </c>
+      <c r="AK258">
+        <v>1.17</v>
+      </c>
+      <c r="AL258">
+        <v>1.22</v>
+      </c>
+      <c r="AM258">
+        <v>2.25</v>
+      </c>
+      <c r="AN258">
+        <v>1.75</v>
+      </c>
+      <c r="AO258">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP258">
+        <v>1.62</v>
+      </c>
+      <c r="AQ258">
+        <v>0.86</v>
+      </c>
+      <c r="AR258">
+        <v>1.79</v>
+      </c>
+      <c r="AS258">
+        <v>1.31</v>
+      </c>
+      <c r="AT258">
+        <v>3.1</v>
+      </c>
+      <c r="AU258">
+        <v>4</v>
+      </c>
+      <c r="AV258">
+        <v>6</v>
+      </c>
+      <c r="AW258">
+        <v>5</v>
+      </c>
+      <c r="AX258">
+        <v>8</v>
+      </c>
+      <c r="AY258">
+        <v>9</v>
+      </c>
+      <c r="AZ258">
+        <v>15</v>
+      </c>
+      <c r="BA258">
+        <v>6</v>
+      </c>
+      <c r="BB258">
+        <v>7</v>
+      </c>
+      <c r="BC258">
+        <v>13</v>
+      </c>
+      <c r="BD258">
+        <v>1.33</v>
+      </c>
+      <c r="BE258">
+        <v>8</v>
+      </c>
+      <c r="BF258">
+        <v>3.55</v>
+      </c>
+      <c r="BG258">
+        <v>1.15</v>
+      </c>
+      <c r="BH258">
+        <v>4.6</v>
+      </c>
+      <c r="BI258">
+        <v>1.26</v>
+      </c>
+      <c r="BJ258">
+        <v>3.4</v>
+      </c>
+      <c r="BK258">
+        <v>1.46</v>
+      </c>
+      <c r="BL258">
+        <v>2.5</v>
+      </c>
+      <c r="BM258">
+        <v>1.71</v>
+      </c>
+      <c r="BN258">
+        <v>2</v>
+      </c>
+      <c r="BO258">
+        <v>2.07</v>
+      </c>
+      <c r="BP258">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="259" spans="1:68">
+      <c r="A259" s="1">
+        <v>258</v>
+      </c>
+      <c r="B259">
+        <v>7466933</v>
+      </c>
+      <c r="C259" t="s">
+        <v>68</v>
+      </c>
+      <c r="D259" t="s">
+        <v>69</v>
+      </c>
+      <c r="E259" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F259">
+        <v>26</v>
+      </c>
+      <c r="G259" t="s">
+        <v>83</v>
+      </c>
+      <c r="H259" t="s">
+        <v>82</v>
+      </c>
+      <c r="I259">
+        <v>0</v>
+      </c>
+      <c r="J259">
+        <v>1</v>
+      </c>
+      <c r="K259">
+        <v>1</v>
+      </c>
+      <c r="L259">
+        <v>0</v>
+      </c>
+      <c r="M259">
+        <v>2</v>
+      </c>
+      <c r="N259">
+        <v>2</v>
+      </c>
+      <c r="O259" t="s">
+        <v>91</v>
+      </c>
+      <c r="P259" t="s">
+        <v>396</v>
+      </c>
+      <c r="Q259">
+        <v>2.75</v>
+      </c>
+      <c r="R259">
+        <v>2.1</v>
+      </c>
+      <c r="S259">
+        <v>4</v>
+      </c>
+      <c r="T259">
+        <v>1.4</v>
+      </c>
+      <c r="U259">
+        <v>2.75</v>
+      </c>
+      <c r="V259">
+        <v>3</v>
+      </c>
+      <c r="W259">
+        <v>1.36</v>
+      </c>
+      <c r="X259">
+        <v>8</v>
+      </c>
+      <c r="Y259">
+        <v>1.08</v>
+      </c>
+      <c r="Z259">
+        <v>2</v>
+      </c>
+      <c r="AA259">
+        <v>3.4</v>
+      </c>
+      <c r="AB259">
+        <v>3.7</v>
+      </c>
+      <c r="AC259">
+        <v>1.06</v>
+      </c>
+      <c r="AD259">
+        <v>10</v>
+      </c>
+      <c r="AE259">
+        <v>1.34</v>
+      </c>
+      <c r="AF259">
+        <v>3.4</v>
+      </c>
+      <c r="AG259">
+        <v>1.91</v>
+      </c>
+      <c r="AH259">
+        <v>1.83</v>
+      </c>
+      <c r="AI259">
+        <v>1.75</v>
+      </c>
+      <c r="AJ259">
+        <v>2</v>
+      </c>
+      <c r="AK259">
+        <v>1.29</v>
+      </c>
+      <c r="AL259">
+        <v>1.3</v>
+      </c>
+      <c r="AM259">
+        <v>1.72</v>
+      </c>
+      <c r="AN259">
+        <v>1.54</v>
+      </c>
+      <c r="AO259">
+        <v>1.58</v>
+      </c>
+      <c r="AP259">
+        <v>1.43</v>
+      </c>
+      <c r="AQ259">
+        <v>1.69</v>
+      </c>
+      <c r="AR259">
+        <v>1.64</v>
+      </c>
+      <c r="AS259">
+        <v>1.39</v>
+      </c>
+      <c r="AT259">
+        <v>3.03</v>
+      </c>
+      <c r="AU259">
+        <v>0</v>
+      </c>
+      <c r="AV259">
+        <v>6</v>
+      </c>
+      <c r="AW259">
+        <v>11</v>
+      </c>
+      <c r="AX259">
+        <v>5</v>
+      </c>
+      <c r="AY259">
+        <v>12</v>
+      </c>
+      <c r="AZ259">
+        <v>13</v>
+      </c>
+      <c r="BA259">
+        <v>7</v>
+      </c>
+      <c r="BB259">
+        <v>7</v>
+      </c>
+      <c r="BC259">
+        <v>14</v>
+      </c>
+      <c r="BD259">
+        <v>1.5</v>
+      </c>
+      <c r="BE259">
+        <v>6.75</v>
+      </c>
+      <c r="BF259">
+        <v>2.8</v>
+      </c>
+      <c r="BG259">
+        <v>1.2</v>
+      </c>
+      <c r="BH259">
+        <v>3.95</v>
+      </c>
+      <c r="BI259">
+        <v>1.35</v>
+      </c>
+      <c r="BJ259">
+        <v>2.9</v>
+      </c>
+      <c r="BK259">
+        <v>1.58</v>
+      </c>
+      <c r="BL259">
+        <v>2.18</v>
+      </c>
+      <c r="BM259">
+        <v>1.95</v>
+      </c>
+      <c r="BN259">
+        <v>1.75</v>
+      </c>
+      <c r="BO259">
+        <v>2.43</v>
+      </c>
+      <c r="BP259">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="260" spans="1:68">
+      <c r="A260" s="1">
+        <v>259</v>
+      </c>
+      <c r="B260">
+        <v>7466931</v>
+      </c>
+      <c r="C260" t="s">
+        <v>68</v>
+      </c>
+      <c r="D260" t="s">
+        <v>69</v>
+      </c>
+      <c r="E260" s="2">
+        <v>45710.60416666666</v>
+      </c>
+      <c r="F260">
+        <v>26</v>
+      </c>
+      <c r="G260" t="s">
+        <v>86</v>
+      </c>
+      <c r="H260" t="s">
+        <v>78</v>
+      </c>
+      <c r="I260">
+        <v>0</v>
+      </c>
+      <c r="J260">
+        <v>1</v>
+      </c>
+      <c r="K260">
+        <v>1</v>
+      </c>
+      <c r="L260">
+        <v>2</v>
+      </c>
+      <c r="M260">
+        <v>1</v>
+      </c>
+      <c r="N260">
+        <v>3</v>
+      </c>
+      <c r="O260" t="s">
+        <v>258</v>
+      </c>
+      <c r="P260" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q260">
+        <v>3.1</v>
+      </c>
+      <c r="R260">
+        <v>2.38</v>
+      </c>
+      <c r="S260">
+        <v>2.88</v>
+      </c>
+      <c r="T260">
+        <v>1.29</v>
+      </c>
+      <c r="U260">
+        <v>3.5</v>
+      </c>
+      <c r="V260">
+        <v>2.25</v>
+      </c>
+      <c r="W260">
+        <v>1.57</v>
+      </c>
+      <c r="X260">
+        <v>5.5</v>
+      </c>
+      <c r="Y260">
+        <v>1.14</v>
+      </c>
+      <c r="Z260">
+        <v>2.62</v>
+      </c>
+      <c r="AA260">
+        <v>3.6</v>
+      </c>
+      <c r="AB260">
+        <v>2.45</v>
+      </c>
+      <c r="AC260">
+        <v>1.03</v>
+      </c>
+      <c r="AD260">
+        <v>18</v>
+      </c>
+      <c r="AE260">
+        <v>1.17</v>
+      </c>
+      <c r="AF260">
+        <v>5.3</v>
+      </c>
+      <c r="AG260">
+        <v>1.5</v>
+      </c>
+      <c r="AH260">
+        <v>2.48</v>
+      </c>
+      <c r="AI260">
+        <v>1.44</v>
+      </c>
+      <c r="AJ260">
+        <v>2.63</v>
+      </c>
+      <c r="AK260">
+        <v>1.55</v>
+      </c>
+      <c r="AL260">
+        <v>1.27</v>
+      </c>
+      <c r="AM260">
+        <v>1.44</v>
+      </c>
+      <c r="AN260">
+        <v>1.79</v>
+      </c>
+      <c r="AO260">
+        <v>1.62</v>
+      </c>
+      <c r="AP260">
+        <v>1.87</v>
+      </c>
+      <c r="AQ260">
+        <v>1.5</v>
+      </c>
+      <c r="AR260">
+        <v>1.6</v>
+      </c>
+      <c r="AS260">
+        <v>1.53</v>
+      </c>
+      <c r="AT260">
+        <v>3.13</v>
+      </c>
+      <c r="AU260">
+        <v>7</v>
+      </c>
+      <c r="AV260">
+        <v>8</v>
+      </c>
+      <c r="AW260">
+        <v>6</v>
+      </c>
+      <c r="AX260">
+        <v>8</v>
+      </c>
+      <c r="AY260">
+        <v>16</v>
+      </c>
+      <c r="AZ260">
+        <v>19</v>
+      </c>
+      <c r="BA260">
+        <v>2</v>
+      </c>
+      <c r="BB260">
+        <v>3</v>
+      </c>
+      <c r="BC260">
+        <v>5</v>
+      </c>
+      <c r="BD260">
+        <v>1.91</v>
+      </c>
+      <c r="BE260">
+        <v>7</v>
+      </c>
+      <c r="BF260">
+        <v>2.05</v>
+      </c>
+      <c r="BG260">
+        <v>1.18</v>
+      </c>
+      <c r="BH260">
+        <v>4.1</v>
+      </c>
+      <c r="BI260">
+        <v>1.3</v>
+      </c>
+      <c r="BJ260">
+        <v>3.05</v>
+      </c>
+      <c r="BK260">
+        <v>1.53</v>
+      </c>
+      <c r="BL260">
+        <v>2.32</v>
+      </c>
+      <c r="BM260">
+        <v>1.85</v>
+      </c>
+      <c r="BN260">
+        <v>1.83</v>
+      </c>
+      <c r="BO260">
+        <v>2.3</v>
+      </c>
+      <c r="BP260">
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="400">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -793,6 +793,9 @@
     <t>['57', '89']</t>
   </si>
   <si>
+    <t>['23', '25', '33', '34']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1206,6 +1209,12 @@
   <si>
     <t>['37', '66']</t>
   </si>
+  <si>
+    <t>['6', '63', '90']</t>
+  </si>
+  <si>
+    <t>['14', '37']</t>
+  </si>
 </sst>
 </file>
 
@@ -1566,7 +1575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP260"/>
+  <dimension ref="A1:BP262"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2028,7 +2037,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2109,7 +2118,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ3">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2440,7 +2449,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2724,7 +2733,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ6">
         <v>0.38</v>
@@ -2852,7 +2861,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -3058,7 +3067,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3470,7 +3479,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3882,7 +3891,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4787,7 +4796,7 @@
         <v>0.31</v>
       </c>
       <c r="AQ16">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4990,7 +4999,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ17">
         <v>0.83</v>
@@ -5118,7 +5127,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5324,7 +5333,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -6148,7 +6157,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6354,7 +6363,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6972,7 +6981,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7178,7 +7187,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7384,7 +7393,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7668,7 +7677,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ30">
         <v>1.23</v>
@@ -7796,7 +7805,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7877,7 +7886,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ31">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR31">
         <v>1.62</v>
@@ -8002,7 +8011,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8414,7 +8423,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -8907,7 +8916,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ36">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR36">
         <v>1.93</v>
@@ -9110,7 +9119,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ37">
         <v>1.08</v>
@@ -9238,7 +9247,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9444,7 +9453,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9650,7 +9659,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9856,7 +9865,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -10062,7 +10071,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10268,7 +10277,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -11791,7 +11800,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ50">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR50">
         <v>1.67</v>
@@ -11916,7 +11925,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -11994,7 +12003,7 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ51">
         <v>1.92</v>
@@ -12122,7 +12131,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12200,7 +12209,7 @@
         <v>3</v>
       </c>
       <c r="AP52">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ52">
         <v>1.38</v>
@@ -12328,7 +12337,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12740,7 +12749,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -13152,7 +13161,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13358,7 +13367,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13439,7 +13448,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ58">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR58">
         <v>1.42</v>
@@ -13564,7 +13573,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13770,7 +13779,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13976,7 +13985,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14182,7 +14191,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14263,7 +14272,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ62">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR62">
         <v>1.29</v>
@@ -14594,7 +14603,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14672,7 +14681,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ64">
         <v>1.58</v>
@@ -14800,7 +14809,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -15006,7 +15015,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -15705,7 +15714,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ69">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR69">
         <v>1.45</v>
@@ -16036,7 +16045,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16242,7 +16251,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q72">
         <v>1.95</v>
@@ -16448,7 +16457,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16654,7 +16663,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16860,7 +16869,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -16938,7 +16947,7 @@
         <v>1.33</v>
       </c>
       <c r="AP75">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ75">
         <v>1.57</v>
@@ -17066,7 +17075,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17272,7 +17281,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17684,7 +17693,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17890,7 +17899,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18302,7 +18311,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18383,7 +18392,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ82">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR82">
         <v>1.04</v>
@@ -18586,7 +18595,7 @@
         <v>0</v>
       </c>
       <c r="AP83">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ83">
         <v>0.38</v>
@@ -18714,7 +18723,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18920,7 +18929,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -19126,7 +19135,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19538,7 +19547,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19950,7 +19959,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20156,7 +20165,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20237,7 +20246,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ91">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR91">
         <v>2.46</v>
@@ -20440,7 +20449,7 @@
         <v>1.75</v>
       </c>
       <c r="AP92">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ92">
         <v>1.92</v>
@@ -21598,7 +21607,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21804,7 +21813,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -22010,7 +22019,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22422,7 +22431,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22628,7 +22637,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23864,7 +23873,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -24070,7 +24079,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24276,7 +24285,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q111">
         <v>3.25</v>
@@ -24482,7 +24491,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24688,7 +24697,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -25181,7 +25190,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ115">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR115">
         <v>2.22</v>
@@ -25306,7 +25315,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25512,7 +25521,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25718,7 +25727,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25796,7 +25805,7 @@
         <v>0.8</v>
       </c>
       <c r="AP118">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ118">
         <v>1.23</v>
@@ -25924,7 +25933,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -26005,7 +26014,7 @@
         <v>0.31</v>
       </c>
       <c r="AQ119">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR119">
         <v>1.07</v>
@@ -26130,7 +26139,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26336,7 +26345,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26414,7 +26423,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ121">
         <v>1.23</v>
@@ -26542,7 +26551,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26748,7 +26757,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -27366,7 +27375,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27572,7 +27581,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -28190,7 +28199,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28602,7 +28611,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -29014,7 +29023,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29220,7 +29229,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -29298,10 +29307,10 @@
         <v>2.67</v>
       </c>
       <c r="AP135">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ135">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR135">
         <v>1.25</v>
@@ -29504,10 +29513,10 @@
         <v>1.83</v>
       </c>
       <c r="AP136">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ136">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR136">
         <v>2.3</v>
@@ -30662,7 +30671,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30868,7 +30877,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -31280,7 +31289,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31361,7 +31370,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ145">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR145">
         <v>1.4</v>
@@ -31486,7 +31495,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31692,7 +31701,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31898,7 +31907,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -32104,7 +32113,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32516,7 +32525,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -33006,7 +33015,7 @@
         <v>0.71</v>
       </c>
       <c r="AP153">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ153">
         <v>0.67</v>
@@ -33134,7 +33143,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33340,7 +33349,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33546,7 +33555,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33752,7 +33761,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33830,7 +33839,7 @@
         <v>0.86</v>
       </c>
       <c r="AP157">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ157">
         <v>1.08</v>
@@ -33958,7 +33967,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34782,7 +34791,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -34863,7 +34872,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ162">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR162">
         <v>1.71</v>
@@ -34988,7 +34997,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35194,7 +35203,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35400,7 +35409,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35812,7 +35821,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36018,7 +36027,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36430,7 +36439,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36511,7 +36520,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ170">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR170">
         <v>1.79</v>
@@ -36714,7 +36723,7 @@
         <v>0.75</v>
       </c>
       <c r="AP171">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ171">
         <v>1.08</v>
@@ -36842,7 +36851,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37332,7 +37341,7 @@
         <v>1.25</v>
       </c>
       <c r="AP174">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ174">
         <v>1.17</v>
@@ -37460,7 +37469,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -38078,7 +38087,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38696,7 +38705,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38902,7 +38911,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39314,7 +39323,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39520,7 +39529,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39601,7 +39610,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ185">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR185">
         <v>1.32</v>
@@ -39726,7 +39735,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -39807,7 +39816,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ186">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR186">
         <v>1.43</v>
@@ -40138,7 +40147,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40344,7 +40353,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40550,7 +40559,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40756,7 +40765,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -41168,7 +41177,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41580,7 +41589,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41786,7 +41795,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -41864,7 +41873,7 @@
         <v>1.33</v>
       </c>
       <c r="AP196">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ196">
         <v>1.23</v>
@@ -42198,7 +42207,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42404,7 +42413,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42610,7 +42619,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42691,7 +42700,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ200">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR200">
         <v>1.18</v>
@@ -42816,7 +42825,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -43022,7 +43031,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43228,7 +43237,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43434,7 +43443,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43515,7 +43524,7 @@
         <v>2</v>
       </c>
       <c r="AQ204">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR204">
         <v>1.5</v>
@@ -43640,7 +43649,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -43924,7 +43933,7 @@
         <v>0.9</v>
       </c>
       <c r="AP206">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ206">
         <v>0.86</v>
@@ -44052,7 +44061,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44464,7 +44473,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44876,7 +44885,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -44954,7 +44963,7 @@
         <v>1.45</v>
       </c>
       <c r="AP211">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ211">
         <v>1.69</v>
@@ -45082,7 +45091,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45288,7 +45297,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45369,7 +45378,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ213">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR213">
         <v>1.61</v>
@@ -45494,7 +45503,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45700,7 +45709,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -45906,7 +45915,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -46112,7 +46121,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46318,7 +46327,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46524,7 +46533,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46730,7 +46739,7 @@
         <v>240</v>
       </c>
       <c r="P220" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q220">
         <v>1.73</v>
@@ -47017,7 +47026,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ221">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR221">
         <v>1.77</v>
@@ -47142,7 +47151,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -47554,7 +47563,7 @@
         <v>107</v>
       </c>
       <c r="P224" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q224">
         <v>6</v>
@@ -47760,7 +47769,7 @@
         <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q225">
         <v>6.5</v>
@@ -47966,7 +47975,7 @@
         <v>243</v>
       </c>
       <c r="P226" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q226">
         <v>2.38</v>
@@ -48044,7 +48053,7 @@
         <v>1.91</v>
       </c>
       <c r="AP226">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ226">
         <v>1.5</v>
@@ -48172,7 +48181,7 @@
         <v>155</v>
       </c>
       <c r="P227" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48378,7 +48387,7 @@
         <v>244</v>
       </c>
       <c r="P228" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q228">
         <v>1.91</v>
@@ -48790,7 +48799,7 @@
         <v>91</v>
       </c>
       <c r="P230" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q230">
         <v>2.88</v>
@@ -49202,7 +49211,7 @@
         <v>95</v>
       </c>
       <c r="P232" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q232">
         <v>2.2</v>
@@ -49280,7 +49289,7 @@
         <v>1.45</v>
       </c>
       <c r="AP232">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ232">
         <v>1.58</v>
@@ -49614,7 +49623,7 @@
         <v>151</v>
       </c>
       <c r="P234" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q234">
         <v>2.6</v>
@@ -49820,7 +49829,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q235">
         <v>4.5</v>
@@ -49901,7 +49910,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ235">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR235">
         <v>1.81</v>
@@ -50232,7 +50241,7 @@
         <v>91</v>
       </c>
       <c r="P237" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50438,7 +50447,7 @@
         <v>91</v>
       </c>
       <c r="P238" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q238">
         <v>2.75</v>
@@ -50850,7 +50859,7 @@
         <v>249</v>
       </c>
       <c r="P240" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q240">
         <v>1.8</v>
@@ -51056,7 +51065,7 @@
         <v>250</v>
       </c>
       <c r="P241" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q241">
         <v>6</v>
@@ -51137,7 +51146,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ241">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR241">
         <v>1.39</v>
@@ -51468,7 +51477,7 @@
         <v>91</v>
       </c>
       <c r="P243" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q243">
         <v>9</v>
@@ -51674,7 +51683,7 @@
         <v>203</v>
       </c>
       <c r="P244" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q244">
         <v>5</v>
@@ -51958,7 +51967,7 @@
         <v>1.75</v>
       </c>
       <c r="AP245">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ245">
         <v>1.62</v>
@@ -52373,7 +52382,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ247">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR247">
         <v>1.54</v>
@@ -52704,7 +52713,7 @@
         <v>254</v>
       </c>
       <c r="P249" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q249">
         <v>2.63</v>
@@ -52910,7 +52919,7 @@
         <v>255</v>
       </c>
       <c r="P250" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q250">
         <v>1.57</v>
@@ -53322,7 +53331,7 @@
         <v>256</v>
       </c>
       <c r="P252" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q252">
         <v>4</v>
@@ -53403,7 +53412,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ252">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AR252">
         <v>1.61</v>
@@ -53528,7 +53537,7 @@
         <v>91</v>
       </c>
       <c r="P253" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q253">
         <v>3.6</v>
@@ -53734,7 +53743,7 @@
         <v>257</v>
       </c>
       <c r="P254" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q254">
         <v>3.25</v>
@@ -53940,7 +53949,7 @@
         <v>91</v>
       </c>
       <c r="P255" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q255">
         <v>5</v>
@@ -54146,7 +54155,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q256">
         <v>3.75</v>
@@ -54352,7 +54361,7 @@
         <v>91</v>
       </c>
       <c r="P257" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q257">
         <v>1.73</v>
@@ -54764,7 +54773,7 @@
         <v>91</v>
       </c>
       <c r="P259" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q259">
         <v>2.75</v>
@@ -54970,7 +54979,7 @@
         <v>258</v>
       </c>
       <c r="P260" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q260">
         <v>3.1</v>
@@ -55127,6 +55136,418 @@
       </c>
       <c r="BP260">
         <v>1.54</v>
+      </c>
+    </row>
+    <row r="261" spans="1:68">
+      <c r="A261" s="1">
+        <v>260</v>
+      </c>
+      <c r="B261">
+        <v>7466937</v>
+      </c>
+      <c r="C261" t="s">
+        <v>68</v>
+      </c>
+      <c r="D261" t="s">
+        <v>69</v>
+      </c>
+      <c r="E261" s="2">
+        <v>45711.45833333334</v>
+      </c>
+      <c r="F261">
+        <v>26</v>
+      </c>
+      <c r="G261" t="s">
+        <v>74</v>
+      </c>
+      <c r="H261" t="s">
+        <v>75</v>
+      </c>
+      <c r="I261">
+        <v>4</v>
+      </c>
+      <c r="J261">
+        <v>1</v>
+      </c>
+      <c r="K261">
+        <v>5</v>
+      </c>
+      <c r="L261">
+        <v>4</v>
+      </c>
+      <c r="M261">
+        <v>3</v>
+      </c>
+      <c r="N261">
+        <v>7</v>
+      </c>
+      <c r="O261" t="s">
+        <v>259</v>
+      </c>
+      <c r="P261" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q261">
+        <v>2.38</v>
+      </c>
+      <c r="R261">
+        <v>2.38</v>
+      </c>
+      <c r="S261">
+        <v>4.33</v>
+      </c>
+      <c r="T261">
+        <v>1.3</v>
+      </c>
+      <c r="U261">
+        <v>3.4</v>
+      </c>
+      <c r="V261">
+        <v>2.5</v>
+      </c>
+      <c r="W261">
+        <v>1.5</v>
+      </c>
+      <c r="X261">
+        <v>6</v>
+      </c>
+      <c r="Y261">
+        <v>1.13</v>
+      </c>
+      <c r="Z261">
+        <v>1.73</v>
+      </c>
+      <c r="AA261">
+        <v>4</v>
+      </c>
+      <c r="AB261">
+        <v>4.33</v>
+      </c>
+      <c r="AC261">
+        <v>1.03</v>
+      </c>
+      <c r="AD261">
+        <v>16</v>
+      </c>
+      <c r="AE261">
+        <v>1.22</v>
+      </c>
+      <c r="AF261">
+        <v>4.5</v>
+      </c>
+      <c r="AG261">
+        <v>1.65</v>
+      </c>
+      <c r="AH261">
+        <v>2.15</v>
+      </c>
+      <c r="AI261">
+        <v>1.62</v>
+      </c>
+      <c r="AJ261">
+        <v>2.2</v>
+      </c>
+      <c r="AK261">
+        <v>1.23</v>
+      </c>
+      <c r="AL261">
+        <v>1.25</v>
+      </c>
+      <c r="AM261">
+        <v>1.95</v>
+      </c>
+      <c r="AN261">
+        <v>1.67</v>
+      </c>
+      <c r="AO261">
+        <v>1.77</v>
+      </c>
+      <c r="AP261">
+        <v>1.77</v>
+      </c>
+      <c r="AQ261">
+        <v>1.64</v>
+      </c>
+      <c r="AR261">
+        <v>1.6</v>
+      </c>
+      <c r="AS261">
+        <v>1.32</v>
+      </c>
+      <c r="AT261">
+        <v>2.92</v>
+      </c>
+      <c r="AU261">
+        <v>6</v>
+      </c>
+      <c r="AV261">
+        <v>6</v>
+      </c>
+      <c r="AW261">
+        <v>8</v>
+      </c>
+      <c r="AX261">
+        <v>12</v>
+      </c>
+      <c r="AY261">
+        <v>19</v>
+      </c>
+      <c r="AZ261">
+        <v>24</v>
+      </c>
+      <c r="BA261">
+        <v>7</v>
+      </c>
+      <c r="BB261">
+        <v>6</v>
+      </c>
+      <c r="BC261">
+        <v>13</v>
+      </c>
+      <c r="BD261">
+        <v>1.43</v>
+      </c>
+      <c r="BE261">
+        <v>7.5</v>
+      </c>
+      <c r="BF261">
+        <v>3.15</v>
+      </c>
+      <c r="BG261">
+        <v>1.14</v>
+      </c>
+      <c r="BH261">
+        <v>4.6</v>
+      </c>
+      <c r="BI261">
+        <v>1.28</v>
+      </c>
+      <c r="BJ261">
+        <v>3.3</v>
+      </c>
+      <c r="BK261">
+        <v>1.47</v>
+      </c>
+      <c r="BL261">
+        <v>2.48</v>
+      </c>
+      <c r="BM261">
+        <v>1.73</v>
+      </c>
+      <c r="BN261">
+        <v>1.96</v>
+      </c>
+      <c r="BO261">
+        <v>2.12</v>
+      </c>
+      <c r="BP261">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="262" spans="1:68">
+      <c r="A262" s="1">
+        <v>261</v>
+      </c>
+      <c r="B262">
+        <v>7466936</v>
+      </c>
+      <c r="C262" t="s">
+        <v>68</v>
+      </c>
+      <c r="D262" t="s">
+        <v>69</v>
+      </c>
+      <c r="E262" s="2">
+        <v>45711.5625</v>
+      </c>
+      <c r="F262">
+        <v>26</v>
+      </c>
+      <c r="G262" t="s">
+        <v>85</v>
+      </c>
+      <c r="H262" t="s">
+        <v>89</v>
+      </c>
+      <c r="I262">
+        <v>0</v>
+      </c>
+      <c r="J262">
+        <v>2</v>
+      </c>
+      <c r="K262">
+        <v>2</v>
+      </c>
+      <c r="L262">
+        <v>0</v>
+      </c>
+      <c r="M262">
+        <v>2</v>
+      </c>
+      <c r="N262">
+        <v>2</v>
+      </c>
+      <c r="O262" t="s">
+        <v>91</v>
+      </c>
+      <c r="P262" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q262">
+        <v>3.1</v>
+      </c>
+      <c r="R262">
+        <v>2.5</v>
+      </c>
+      <c r="S262">
+        <v>2.75</v>
+      </c>
+      <c r="T262">
+        <v>1.22</v>
+      </c>
+      <c r="U262">
+        <v>4</v>
+      </c>
+      <c r="V262">
+        <v>2.1</v>
+      </c>
+      <c r="W262">
+        <v>1.67</v>
+      </c>
+      <c r="X262">
+        <v>4.5</v>
+      </c>
+      <c r="Y262">
+        <v>1.18</v>
+      </c>
+      <c r="Z262">
+        <v>2.75</v>
+      </c>
+      <c r="AA262">
+        <v>3.7</v>
+      </c>
+      <c r="AB262">
+        <v>2.3</v>
+      </c>
+      <c r="AC262">
+        <v>1.01</v>
+      </c>
+      <c r="AD262">
+        <v>23</v>
+      </c>
+      <c r="AE262">
+        <v>1.13</v>
+      </c>
+      <c r="AF262">
+        <v>6.4</v>
+      </c>
+      <c r="AG262">
+        <v>1.63</v>
+      </c>
+      <c r="AH262">
+        <v>2.28</v>
+      </c>
+      <c r="AI262">
+        <v>1.36</v>
+      </c>
+      <c r="AJ262">
+        <v>3</v>
+      </c>
+      <c r="AK262">
+        <v>1.61</v>
+      </c>
+      <c r="AL262">
+        <v>1.25</v>
+      </c>
+      <c r="AM262">
+        <v>1.43</v>
+      </c>
+      <c r="AN262">
+        <v>2.17</v>
+      </c>
+      <c r="AO262">
+        <v>2.29</v>
+      </c>
+      <c r="AP262">
+        <v>2</v>
+      </c>
+      <c r="AQ262">
+        <v>2.33</v>
+      </c>
+      <c r="AR262">
+        <v>1.96</v>
+      </c>
+      <c r="AS262">
+        <v>2.02</v>
+      </c>
+      <c r="AT262">
+        <v>3.98</v>
+      </c>
+      <c r="AU262">
+        <v>6</v>
+      </c>
+      <c r="AV262">
+        <v>5</v>
+      </c>
+      <c r="AW262">
+        <v>11</v>
+      </c>
+      <c r="AX262">
+        <v>4</v>
+      </c>
+      <c r="AY262">
+        <v>25</v>
+      </c>
+      <c r="AZ262">
+        <v>11</v>
+      </c>
+      <c r="BA262">
+        <v>7</v>
+      </c>
+      <c r="BB262">
+        <v>5</v>
+      </c>
+      <c r="BC262">
+        <v>12</v>
+      </c>
+      <c r="BD262">
+        <v>1.75</v>
+      </c>
+      <c r="BE262">
+        <v>6.5</v>
+      </c>
+      <c r="BF262">
+        <v>2.3</v>
+      </c>
+      <c r="BG262">
+        <v>1.21</v>
+      </c>
+      <c r="BH262">
+        <v>3.8</v>
+      </c>
+      <c r="BI262">
+        <v>1.37</v>
+      </c>
+      <c r="BJ262">
+        <v>2.8</v>
+      </c>
+      <c r="BK262">
+        <v>1.62</v>
+      </c>
+      <c r="BL262">
+        <v>2.14</v>
+      </c>
+      <c r="BM262">
+        <v>1.98</v>
+      </c>
+      <c r="BN262">
+        <v>1.72</v>
+      </c>
+      <c r="BO262">
+        <v>2.48</v>
+      </c>
+      <c r="BP262">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="404">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -796,6 +796,18 @@
     <t>['23', '25', '33', '34']</t>
   </si>
   <si>
+    <t>['29', '59', '71', '90+1']</t>
+  </si>
+  <si>
+    <t>['18']</t>
+  </si>
+  <si>
+    <t>['12', '75']</t>
+  </si>
+  <si>
+    <t>['24', '36', '44', '78']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -896,9 +908,6 @@
   </si>
   <si>
     <t>['23', '37']</t>
-  </si>
-  <si>
-    <t>['18']</t>
   </si>
   <si>
     <t>['9', '59', '69']</t>
@@ -1214,6 +1223,9 @@
   </si>
   <si>
     <t>['14', '37']</t>
+  </si>
+  <si>
+    <t>['1', '47']</t>
   </si>
 </sst>
 </file>
@@ -1575,7 +1587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP262"/>
+  <dimension ref="A1:BP266"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1912,7 +1924,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ2">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2037,7 +2049,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2449,7 +2461,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2736,7 +2748,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ6">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2861,7 +2873,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2942,7 +2954,7 @@
         <v>2</v>
       </c>
       <c r="AQ7">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3067,7 +3079,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3148,7 +3160,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ8">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3479,7 +3491,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3557,7 +3569,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ10">
         <v>1.38</v>
@@ -3891,7 +3903,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -3969,7 +3981,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ12">
         <v>1.08</v>
@@ -4381,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ14">
         <v>1.23</v>
@@ -5127,7 +5139,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5333,7 +5345,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5411,7 +5423,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ19">
         <v>1.5</v>
@@ -6157,7 +6169,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6238,7 +6250,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ23">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR23">
         <v>0.86</v>
@@ -6363,7 +6375,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6444,7 +6456,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ24">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR24">
         <v>0.77</v>
@@ -6856,7 +6868,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ26">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR26">
         <v>1.29</v>
@@ -6981,7 +6993,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7062,7 +7074,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ27">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR27">
         <v>0.83</v>
@@ -7187,7 +7199,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7393,7 +7405,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7471,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ29">
         <v>1.69</v>
@@ -7805,7 +7817,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8011,7 +8023,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8295,7 +8307,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ33">
         <v>0.83</v>
@@ -8423,7 +8435,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -8501,7 +8513,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ34">
         <v>0.67</v>
@@ -9247,7 +9259,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9453,7 +9465,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9659,7 +9671,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9865,7 +9877,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9943,7 +9955,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ41">
         <v>1.62</v>
@@ -10071,7 +10083,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10277,7 +10289,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10770,7 +10782,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ45">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR45">
         <v>1.78</v>
@@ -11591,7 +11603,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ49">
         <v>1.08</v>
@@ -11797,7 +11809,7 @@
         <v>3</v>
       </c>
       <c r="AP50">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ50">
         <v>1.64</v>
@@ -11925,7 +11937,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -12131,7 +12143,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12337,7 +12349,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12418,7 +12430,7 @@
         <v>2</v>
       </c>
       <c r="AQ53">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR53">
         <v>1.65</v>
@@ -12749,7 +12761,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -13161,7 +13173,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13239,7 +13251,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ57">
         <v>1.57</v>
@@ -13367,7 +13379,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13445,7 +13457,7 @@
         <v>3</v>
       </c>
       <c r="AP58">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ58">
         <v>2.33</v>
@@ -13573,7 +13585,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13654,7 +13666,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ59">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR59">
         <v>0.95</v>
@@ -13779,7 +13791,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13985,7 +13997,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14066,7 +14078,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ61">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR61">
         <v>1.76</v>
@@ -14191,7 +14203,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14269,7 +14281,7 @@
         <v>3</v>
       </c>
       <c r="AP62">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ62">
         <v>2.33</v>
@@ -14478,7 +14490,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ63">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR63">
         <v>1.12</v>
@@ -14603,7 +14615,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14684,7 +14696,7 @@
         <v>2</v>
       </c>
       <c r="AQ64">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR64">
         <v>2.4</v>
@@ -14809,7 +14821,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -15015,7 +15027,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -15302,7 +15314,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ67">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR67">
         <v>2.4</v>
@@ -15711,7 +15723,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ69">
         <v>1.64</v>
@@ -16045,7 +16057,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16123,7 +16135,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ71">
         <v>1.23</v>
@@ -16251,7 +16263,7 @@
         <v>139</v>
       </c>
       <c r="P72" t="s">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="Q72">
         <v>1.95</v>
@@ -16457,7 +16469,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16538,7 +16550,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ73">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR73">
         <v>2.01</v>
@@ -16663,7 +16675,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16869,7 +16881,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -17075,7 +17087,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17281,7 +17293,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17693,7 +17705,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17771,7 +17783,7 @@
         <v>2.33</v>
       </c>
       <c r="AP79">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ79">
         <v>1.38</v>
@@ -17899,7 +17911,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18311,7 +18323,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18598,7 +18610,7 @@
         <v>2</v>
       </c>
       <c r="AQ83">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR83">
         <v>2.31</v>
@@ -18723,7 +18735,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18801,7 +18813,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ84">
         <v>0.86</v>
@@ -18929,7 +18941,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -19010,7 +19022,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ85">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR85">
         <v>1.28</v>
@@ -19135,7 +19147,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19422,7 +19434,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ87">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR87">
         <v>1.26</v>
@@ -19547,7 +19559,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19625,7 +19637,7 @@
         <v>1.25</v>
       </c>
       <c r="AP88">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ88">
         <v>1.62</v>
@@ -19831,7 +19843,7 @@
         <v>1</v>
       </c>
       <c r="AP89">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ89">
         <v>1.23</v>
@@ -19959,7 +19971,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20165,7 +20177,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -21607,7 +21619,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21685,7 +21697,7 @@
         <v>0.25</v>
       </c>
       <c r="AP98">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ98">
         <v>1.69</v>
@@ -21813,7 +21825,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -21894,7 +21906,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ99">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR99">
         <v>1.99</v>
@@ -22019,7 +22031,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22431,7 +22443,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22512,7 +22524,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ102">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR102">
         <v>1.76</v>
@@ -22637,7 +22649,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22715,10 +22727,10 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ103">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR103">
         <v>1.37</v>
@@ -23127,10 +23139,10 @@
         <v>0</v>
       </c>
       <c r="AP105">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ105">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR105">
         <v>1.17</v>
@@ -23333,7 +23345,7 @@
         <v>2</v>
       </c>
       <c r="AP106">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ106">
         <v>1.38</v>
@@ -23542,7 +23554,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ107">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR107">
         <v>1.75</v>
@@ -23873,7 +23885,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -24079,7 +24091,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24285,7 +24297,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q111">
         <v>3.25</v>
@@ -24363,7 +24375,7 @@
         <v>1.4</v>
       </c>
       <c r="AP111">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ111">
         <v>1.92</v>
@@ -24491,7 +24503,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24697,7 +24709,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -25315,7 +25327,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25521,7 +25533,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25727,7 +25739,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25933,7 +25945,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -26139,7 +26151,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26345,7 +26357,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26551,7 +26563,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26629,10 +26641,10 @@
         <v>0</v>
       </c>
       <c r="AP122">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ122">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR122">
         <v>1.46</v>
@@ -26757,7 +26769,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -26835,10 +26847,10 @@
         <v>0.83</v>
       </c>
       <c r="AP123">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ123">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR123">
         <v>1.13</v>
@@ -27375,7 +27387,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27453,7 +27465,7 @@
         <v>1.33</v>
       </c>
       <c r="AP126">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ126">
         <v>1.62</v>
@@ -27581,7 +27593,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -28071,10 +28083,10 @@
         <v>1.67</v>
       </c>
       <c r="AP129">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ129">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR129">
         <v>1.64</v>
@@ -28199,7 +28211,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28280,7 +28292,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ130">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR130">
         <v>1.95</v>
@@ -28611,7 +28623,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -29023,7 +29035,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29229,7 +29241,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -30671,7 +30683,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30749,7 +30761,7 @@
         <v>1.43</v>
       </c>
       <c r="AP142">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ142">
         <v>1.38</v>
@@ -30877,7 +30889,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -31164,7 +31176,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ144">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR144">
         <v>1.54</v>
@@ -31289,7 +31301,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31495,7 +31507,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31701,7 +31713,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31782,7 +31794,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ147">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR147">
         <v>1.16</v>
@@ -31907,7 +31919,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -32113,7 +32125,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32525,7 +32537,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -32603,7 +32615,7 @@
         <v>0.71</v>
       </c>
       <c r="AP151">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ151">
         <v>0.83</v>
@@ -33143,7 +33155,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33224,7 +33236,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ154">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR154">
         <v>1.76</v>
@@ -33349,7 +33361,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33430,7 +33442,7 @@
         <v>2</v>
       </c>
       <c r="AQ155">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR155">
         <v>1.52</v>
@@ -33555,7 +33567,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33633,7 +33645,7 @@
         <v>0.86</v>
       </c>
       <c r="AP156">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ156">
         <v>1.69</v>
@@ -33761,7 +33773,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33967,7 +33979,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34251,7 +34263,7 @@
         <v>0.14</v>
       </c>
       <c r="AP159">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ159">
         <v>1.08</v>
@@ -34791,7 +34803,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -34997,7 +35009,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35203,7 +35215,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35409,7 +35421,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35487,7 +35499,7 @@
         <v>1.5</v>
       </c>
       <c r="AP165">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ165">
         <v>1.92</v>
@@ -35696,7 +35708,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ166">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR166">
         <v>1.59</v>
@@ -35821,7 +35833,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36027,7 +36039,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36108,7 +36120,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ168">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR168">
         <v>1.46</v>
@@ -36439,7 +36451,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36851,7 +36863,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37344,7 +37356,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ174">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR174">
         <v>1.48</v>
@@ -37469,7 +37481,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -37547,10 +37559,10 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ175">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR175">
         <v>1.78</v>
@@ -37959,7 +37971,7 @@
         <v>1.13</v>
       </c>
       <c r="AP177">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ177">
         <v>1.08</v>
@@ -38087,7 +38099,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38371,7 +38383,7 @@
         <v>0.13</v>
       </c>
       <c r="AP179">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ179">
         <v>1.08</v>
@@ -38705,7 +38717,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38911,7 +38923,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39195,10 +39207,10 @@
         <v>0.22</v>
       </c>
       <c r="AP183">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ183">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR183">
         <v>1.34</v>
@@ -39323,7 +39335,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39404,7 +39416,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ184">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR184">
         <v>1.59</v>
@@ -39529,7 +39541,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39735,7 +39747,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -40147,7 +40159,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40353,7 +40365,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40559,7 +40571,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40765,7 +40777,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -41177,7 +41189,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41461,7 +41473,7 @@
         <v>2</v>
       </c>
       <c r="AP194">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ194">
         <v>1.5</v>
@@ -41589,7 +41601,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41795,7 +41807,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -42079,7 +42091,7 @@
         <v>1.8</v>
       </c>
       <c r="AP197">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ197">
         <v>1.92</v>
@@ -42207,7 +42219,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42413,7 +42425,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42619,7 +42631,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42697,7 +42709,7 @@
         <v>2</v>
       </c>
       <c r="AP200">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ200">
         <v>1.64</v>
@@ -42825,7 +42837,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -42903,10 +42915,10 @@
         <v>1.5</v>
       </c>
       <c r="AP201">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ201">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR201">
         <v>1.75</v>
@@ -43031,7 +43043,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43112,7 +43124,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ202">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR202">
         <v>1.35</v>
@@ -43237,7 +43249,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43443,7 +43455,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43649,7 +43661,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -44061,7 +44073,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44142,7 +44154,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ207">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR207">
         <v>1.34</v>
@@ -44473,7 +44485,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44760,7 +44772,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ210">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR210">
         <v>1.48</v>
@@ -44885,7 +44897,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -44966,7 +44978,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ211">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR211">
         <v>1.61</v>
@@ -45091,7 +45103,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45297,7 +45309,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45503,7 +45515,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45584,7 +45596,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ214">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR214">
         <v>1.2</v>
@@ -45709,7 +45721,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -45790,7 +45802,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ215">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR215">
         <v>1.97</v>
@@ -45915,7 +45927,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -46121,7 +46133,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46202,7 +46214,7 @@
         <v>2</v>
       </c>
       <c r="AQ217">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR217">
         <v>1.44</v>
@@ -46327,7 +46339,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46533,7 +46545,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46739,7 +46751,7 @@
         <v>240</v>
       </c>
       <c r="P220" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q220">
         <v>1.73</v>
@@ -46817,7 +46829,7 @@
         <v>0.82</v>
       </c>
       <c r="AP220">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ220">
         <v>0.86</v>
@@ -47151,7 +47163,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -47229,7 +47241,7 @@
         <v>0.7</v>
       </c>
       <c r="AP222">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ222">
         <v>1.08</v>
@@ -47563,7 +47575,7 @@
         <v>107</v>
       </c>
       <c r="P224" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Q224">
         <v>6</v>
@@ -47769,7 +47781,7 @@
         <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q225">
         <v>6.5</v>
@@ -47847,7 +47859,7 @@
         <v>1.73</v>
       </c>
       <c r="AP225">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ225">
         <v>1.92</v>
@@ -47975,7 +47987,7 @@
         <v>243</v>
       </c>
       <c r="P226" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q226">
         <v>2.38</v>
@@ -48181,7 +48193,7 @@
         <v>155</v>
       </c>
       <c r="P227" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48259,7 +48271,7 @@
         <v>0.5</v>
       </c>
       <c r="AP227">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ227">
         <v>1.08</v>
@@ -48387,7 +48399,7 @@
         <v>244</v>
       </c>
       <c r="P228" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="Q228">
         <v>1.91</v>
@@ -48799,7 +48811,7 @@
         <v>91</v>
       </c>
       <c r="P230" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="Q230">
         <v>2.88</v>
@@ -49211,7 +49223,7 @@
         <v>95</v>
       </c>
       <c r="P232" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q232">
         <v>2.2</v>
@@ -49292,7 +49304,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ232">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR232">
         <v>1.61</v>
@@ -49623,7 +49635,7 @@
         <v>151</v>
       </c>
       <c r="P234" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q234">
         <v>2.6</v>
@@ -49704,7 +49716,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ234">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR234">
         <v>1.13</v>
@@ -49829,7 +49841,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="Q235">
         <v>4.5</v>
@@ -50113,10 +50125,10 @@
         <v>1.27</v>
       </c>
       <c r="AP236">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ236">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR236">
         <v>1.21</v>
@@ -50241,7 +50253,7 @@
         <v>91</v>
       </c>
       <c r="P237" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50447,7 +50459,7 @@
         <v>91</v>
       </c>
       <c r="P238" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Q238">
         <v>2.75</v>
@@ -50859,7 +50871,7 @@
         <v>249</v>
       </c>
       <c r="P240" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q240">
         <v>1.8</v>
@@ -50937,7 +50949,7 @@
         <v>1.18</v>
       </c>
       <c r="AP240">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ240">
         <v>1.23</v>
@@ -51065,7 +51077,7 @@
         <v>250</v>
       </c>
       <c r="P241" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Q241">
         <v>6</v>
@@ -51349,7 +51361,7 @@
         <v>1.75</v>
       </c>
       <c r="AP242">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ242">
         <v>1.5</v>
@@ -51477,7 +51489,7 @@
         <v>91</v>
       </c>
       <c r="P243" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="Q243">
         <v>9</v>
@@ -51683,7 +51695,7 @@
         <v>203</v>
       </c>
       <c r="P244" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Q244">
         <v>5</v>
@@ -51764,7 +51776,7 @@
         <v>0.31</v>
       </c>
       <c r="AQ244">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR244">
         <v>1.15</v>
@@ -52713,7 +52725,7 @@
         <v>254</v>
       </c>
       <c r="P249" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="Q249">
         <v>2.63</v>
@@ -52791,7 +52803,7 @@
         <v>0.91</v>
       </c>
       <c r="AP249">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ249">
         <v>1.08</v>
@@ -52919,7 +52931,7 @@
         <v>255</v>
       </c>
       <c r="P250" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q250">
         <v>1.57</v>
@@ -53331,7 +53343,7 @@
         <v>256</v>
       </c>
       <c r="P252" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Q252">
         <v>4</v>
@@ -53537,7 +53549,7 @@
         <v>91</v>
       </c>
       <c r="P253" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="Q253">
         <v>3.6</v>
@@ -53743,7 +53755,7 @@
         <v>257</v>
       </c>
       <c r="P254" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="Q254">
         <v>3.25</v>
@@ -53949,7 +53961,7 @@
         <v>91</v>
       </c>
       <c r="P255" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Q255">
         <v>5</v>
@@ -54155,7 +54167,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="Q256">
         <v>3.75</v>
@@ -54361,7 +54373,7 @@
         <v>91</v>
       </c>
       <c r="P257" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="Q257">
         <v>1.73</v>
@@ -54773,7 +54785,7 @@
         <v>91</v>
       </c>
       <c r="P259" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="Q259">
         <v>2.75</v>
@@ -54979,7 +54991,7 @@
         <v>258</v>
       </c>
       <c r="P260" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q260">
         <v>3.1</v>
@@ -55185,7 +55197,7 @@
         <v>259</v>
       </c>
       <c r="P261" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="Q261">
         <v>2.38</v>
@@ -55391,7 +55403,7 @@
         <v>91</v>
       </c>
       <c r="P262" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="Q262">
         <v>3.1</v>
@@ -55548,6 +55560,830 @@
       </c>
       <c r="BP262">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="263" spans="1:68">
+      <c r="A263" s="1">
+        <v>262</v>
+      </c>
+      <c r="B263">
+        <v>7466945</v>
+      </c>
+      <c r="C263" t="s">
+        <v>68</v>
+      </c>
+      <c r="D263" t="s">
+        <v>69</v>
+      </c>
+      <c r="E263" s="2">
+        <v>45713.6875</v>
+      </c>
+      <c r="F263">
+        <v>27</v>
+      </c>
+      <c r="G263" t="s">
+        <v>82</v>
+      </c>
+      <c r="H263" t="s">
+        <v>86</v>
+      </c>
+      <c r="I263">
+        <v>1</v>
+      </c>
+      <c r="J263">
+        <v>0</v>
+      </c>
+      <c r="K263">
+        <v>1</v>
+      </c>
+      <c r="L263">
+        <v>4</v>
+      </c>
+      <c r="M263">
+        <v>1</v>
+      </c>
+      <c r="N263">
+        <v>5</v>
+      </c>
+      <c r="O263" t="s">
+        <v>260</v>
+      </c>
+      <c r="P263" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q263">
+        <v>3.2</v>
+      </c>
+      <c r="R263">
+        <v>2.2</v>
+      </c>
+      <c r="S263">
+        <v>3.25</v>
+      </c>
+      <c r="T263">
+        <v>1.4</v>
+      </c>
+      <c r="U263">
+        <v>2.75</v>
+      </c>
+      <c r="V263">
+        <v>2.75</v>
+      </c>
+      <c r="W263">
+        <v>1.4</v>
+      </c>
+      <c r="X263">
+        <v>8</v>
+      </c>
+      <c r="Y263">
+        <v>1.08</v>
+      </c>
+      <c r="Z263">
+        <v>2.7</v>
+      </c>
+      <c r="AA263">
+        <v>3.5</v>
+      </c>
+      <c r="AB263">
+        <v>2.45</v>
+      </c>
+      <c r="AC263">
+        <v>1.06</v>
+      </c>
+      <c r="AD263">
+        <v>11</v>
+      </c>
+      <c r="AE263">
+        <v>1.31</v>
+      </c>
+      <c r="AF263">
+        <v>3.6</v>
+      </c>
+      <c r="AG263">
+        <v>2</v>
+      </c>
+      <c r="AH263">
+        <v>1.75</v>
+      </c>
+      <c r="AI263">
+        <v>1.75</v>
+      </c>
+      <c r="AJ263">
+        <v>2</v>
+      </c>
+      <c r="AK263">
+        <v>1.44</v>
+      </c>
+      <c r="AL263">
+        <v>1.31</v>
+      </c>
+      <c r="AM263">
+        <v>1.5</v>
+      </c>
+      <c r="AN263">
+        <v>0.85</v>
+      </c>
+      <c r="AO263">
+        <v>1.17</v>
+      </c>
+      <c r="AP263">
+        <v>1</v>
+      </c>
+      <c r="AQ263">
+        <v>1.08</v>
+      </c>
+      <c r="AR263">
+        <v>1.48</v>
+      </c>
+      <c r="AS263">
+        <v>1.14</v>
+      </c>
+      <c r="AT263">
+        <v>2.62</v>
+      </c>
+      <c r="AU263">
+        <v>7</v>
+      </c>
+      <c r="AV263">
+        <v>3</v>
+      </c>
+      <c r="AW263">
+        <v>13</v>
+      </c>
+      <c r="AX263">
+        <v>4</v>
+      </c>
+      <c r="AY263">
+        <v>25</v>
+      </c>
+      <c r="AZ263">
+        <v>8</v>
+      </c>
+      <c r="BA263">
+        <v>3</v>
+      </c>
+      <c r="BB263">
+        <v>8</v>
+      </c>
+      <c r="BC263">
+        <v>11</v>
+      </c>
+      <c r="BD263">
+        <v>2.08</v>
+      </c>
+      <c r="BE263">
+        <v>6.75</v>
+      </c>
+      <c r="BF263">
+        <v>1.89</v>
+      </c>
+      <c r="BG263">
+        <v>1.2</v>
+      </c>
+      <c r="BH263">
+        <v>3.95</v>
+      </c>
+      <c r="BI263">
+        <v>1.35</v>
+      </c>
+      <c r="BJ263">
+        <v>2.9</v>
+      </c>
+      <c r="BK263">
+        <v>1.58</v>
+      </c>
+      <c r="BL263">
+        <v>2.18</v>
+      </c>
+      <c r="BM263">
+        <v>1.93</v>
+      </c>
+      <c r="BN263">
+        <v>1.76</v>
+      </c>
+      <c r="BO263">
+        <v>2.43</v>
+      </c>
+      <c r="BP263">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="264" spans="1:68">
+      <c r="A264" s="1">
+        <v>263</v>
+      </c>
+      <c r="B264">
+        <v>7466944</v>
+      </c>
+      <c r="C264" t="s">
+        <v>68</v>
+      </c>
+      <c r="D264" t="s">
+        <v>69</v>
+      </c>
+      <c r="E264" s="2">
+        <v>45713.6875</v>
+      </c>
+      <c r="F264">
+        <v>27</v>
+      </c>
+      <c r="G264" t="s">
+        <v>87</v>
+      </c>
+      <c r="H264" t="s">
+        <v>83</v>
+      </c>
+      <c r="I264">
+        <v>1</v>
+      </c>
+      <c r="J264">
+        <v>1</v>
+      </c>
+      <c r="K264">
+        <v>2</v>
+      </c>
+      <c r="L264">
+        <v>1</v>
+      </c>
+      <c r="M264">
+        <v>2</v>
+      </c>
+      <c r="N264">
+        <v>3</v>
+      </c>
+      <c r="O264" t="s">
+        <v>261</v>
+      </c>
+      <c r="P264" t="s">
+        <v>403</v>
+      </c>
+      <c r="Q264">
+        <v>3.5</v>
+      </c>
+      <c r="R264">
+        <v>2.1</v>
+      </c>
+      <c r="S264">
+        <v>3.1</v>
+      </c>
+      <c r="T264">
+        <v>1.4</v>
+      </c>
+      <c r="U264">
+        <v>2.75</v>
+      </c>
+      <c r="V264">
+        <v>3</v>
+      </c>
+      <c r="W264">
+        <v>1.36</v>
+      </c>
+      <c r="X264">
+        <v>8</v>
+      </c>
+      <c r="Y264">
+        <v>1.08</v>
+      </c>
+      <c r="Z264">
+        <v>2.75</v>
+      </c>
+      <c r="AA264">
+        <v>3.5</v>
+      </c>
+      <c r="AB264">
+        <v>2.4</v>
+      </c>
+      <c r="AC264">
+        <v>1.06</v>
+      </c>
+      <c r="AD264">
+        <v>8.5</v>
+      </c>
+      <c r="AE264">
+        <v>1.3</v>
+      </c>
+      <c r="AF264">
+        <v>3.4</v>
+      </c>
+      <c r="AG264">
+        <v>1.85</v>
+      </c>
+      <c r="AH264">
+        <v>1.85</v>
+      </c>
+      <c r="AI264">
+        <v>1.75</v>
+      </c>
+      <c r="AJ264">
+        <v>2</v>
+      </c>
+      <c r="AK264">
+        <v>1.55</v>
+      </c>
+      <c r="AL264">
+        <v>1.31</v>
+      </c>
+      <c r="AM264">
+        <v>1.38</v>
+      </c>
+      <c r="AN264">
+        <v>0.83</v>
+      </c>
+      <c r="AO264">
+        <v>1.58</v>
+      </c>
+      <c r="AP264">
+        <v>0.77</v>
+      </c>
+      <c r="AQ264">
+        <v>1.69</v>
+      </c>
+      <c r="AR264">
+        <v>1.21</v>
+      </c>
+      <c r="AS264">
+        <v>1.5</v>
+      </c>
+      <c r="AT264">
+        <v>2.71</v>
+      </c>
+      <c r="AU264">
+        <v>6</v>
+      </c>
+      <c r="AV264">
+        <v>6</v>
+      </c>
+      <c r="AW264">
+        <v>13</v>
+      </c>
+      <c r="AX264">
+        <v>6</v>
+      </c>
+      <c r="AY264">
+        <v>25</v>
+      </c>
+      <c r="AZ264">
+        <v>15</v>
+      </c>
+      <c r="BA264">
+        <v>7</v>
+      </c>
+      <c r="BB264">
+        <v>4</v>
+      </c>
+      <c r="BC264">
+        <v>11</v>
+      </c>
+      <c r="BD264">
+        <v>2.33</v>
+      </c>
+      <c r="BE264">
+        <v>6.75</v>
+      </c>
+      <c r="BF264">
+        <v>1.72</v>
+      </c>
+      <c r="BG264">
+        <v>1.22</v>
+      </c>
+      <c r="BH264">
+        <v>3.7</v>
+      </c>
+      <c r="BI264">
+        <v>1.4</v>
+      </c>
+      <c r="BJ264">
+        <v>2.7</v>
+      </c>
+      <c r="BK264">
+        <v>1.65</v>
+      </c>
+      <c r="BL264">
+        <v>2.08</v>
+      </c>
+      <c r="BM264">
+        <v>2.02</v>
+      </c>
+      <c r="BN264">
+        <v>1.68</v>
+      </c>
+      <c r="BO264">
+        <v>2.55</v>
+      </c>
+      <c r="BP264">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="265" spans="1:68">
+      <c r="A265" s="1">
+        <v>264</v>
+      </c>
+      <c r="B265">
+        <v>7466940</v>
+      </c>
+      <c r="C265" t="s">
+        <v>68</v>
+      </c>
+      <c r="D265" t="s">
+        <v>69</v>
+      </c>
+      <c r="E265" s="2">
+        <v>45713.6875</v>
+      </c>
+      <c r="F265">
+        <v>27</v>
+      </c>
+      <c r="G265" t="s">
+        <v>80</v>
+      </c>
+      <c r="H265" t="s">
+        <v>88</v>
+      </c>
+      <c r="I265">
+        <v>1</v>
+      </c>
+      <c r="J265">
+        <v>0</v>
+      </c>
+      <c r="K265">
+        <v>1</v>
+      </c>
+      <c r="L265">
+        <v>2</v>
+      </c>
+      <c r="M265">
+        <v>1</v>
+      </c>
+      <c r="N265">
+        <v>3</v>
+      </c>
+      <c r="O265" t="s">
+        <v>262</v>
+      </c>
+      <c r="P265" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q265">
+        <v>2.88</v>
+      </c>
+      <c r="R265">
+        <v>2.38</v>
+      </c>
+      <c r="S265">
+        <v>3.25</v>
+      </c>
+      <c r="T265">
+        <v>1.3</v>
+      </c>
+      <c r="U265">
+        <v>3.4</v>
+      </c>
+      <c r="V265">
+        <v>2.38</v>
+      </c>
+      <c r="W265">
+        <v>1.53</v>
+      </c>
+      <c r="X265">
+        <v>6</v>
+      </c>
+      <c r="Y265">
+        <v>1.13</v>
+      </c>
+      <c r="Z265">
+        <v>2.1</v>
+      </c>
+      <c r="AA265">
+        <v>3.75</v>
+      </c>
+      <c r="AB265">
+        <v>3.1</v>
+      </c>
+      <c r="AC265">
+        <v>1.03</v>
+      </c>
+      <c r="AD265">
+        <v>16</v>
+      </c>
+      <c r="AE265">
+        <v>1.2</v>
+      </c>
+      <c r="AF265">
+        <v>4.85</v>
+      </c>
+      <c r="AG265">
+        <v>1.75</v>
+      </c>
+      <c r="AH265">
+        <v>1.95</v>
+      </c>
+      <c r="AI265">
+        <v>1.53</v>
+      </c>
+      <c r="AJ265">
+        <v>2.38</v>
+      </c>
+      <c r="AK265">
+        <v>1.38</v>
+      </c>
+      <c r="AL265">
+        <v>1.27</v>
+      </c>
+      <c r="AM265">
+        <v>1.63</v>
+      </c>
+      <c r="AN265">
+        <v>1.5</v>
+      </c>
+      <c r="AO265">
+        <v>1.69</v>
+      </c>
+      <c r="AP265">
+        <v>1.62</v>
+      </c>
+      <c r="AQ265">
+        <v>1.57</v>
+      </c>
+      <c r="AR265">
+        <v>1.6</v>
+      </c>
+      <c r="AS265">
+        <v>1.65</v>
+      </c>
+      <c r="AT265">
+        <v>3.25</v>
+      </c>
+      <c r="AU265">
+        <v>5</v>
+      </c>
+      <c r="AV265">
+        <v>6</v>
+      </c>
+      <c r="AW265">
+        <v>7</v>
+      </c>
+      <c r="AX265">
+        <v>14</v>
+      </c>
+      <c r="AY265">
+        <v>16</v>
+      </c>
+      <c r="AZ265">
+        <v>25</v>
+      </c>
+      <c r="BA265">
+        <v>1</v>
+      </c>
+      <c r="BB265">
+        <v>9</v>
+      </c>
+      <c r="BC265">
+        <v>10</v>
+      </c>
+      <c r="BD265">
+        <v>1.83</v>
+      </c>
+      <c r="BE265">
+        <v>6.75</v>
+      </c>
+      <c r="BF265">
+        <v>2.15</v>
+      </c>
+      <c r="BG265">
+        <v>1.19</v>
+      </c>
+      <c r="BH265">
+        <v>4.1</v>
+      </c>
+      <c r="BI265">
+        <v>1.34</v>
+      </c>
+      <c r="BJ265">
+        <v>2.9</v>
+      </c>
+      <c r="BK265">
+        <v>1.55</v>
+      </c>
+      <c r="BL265">
+        <v>2.25</v>
+      </c>
+      <c r="BM265">
+        <v>1.89</v>
+      </c>
+      <c r="BN265">
+        <v>1.8</v>
+      </c>
+      <c r="BO265">
+        <v>2.33</v>
+      </c>
+      <c r="BP265">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="266" spans="1:68">
+      <c r="A266" s="1">
+        <v>265</v>
+      </c>
+      <c r="B266">
+        <v>7466946</v>
+      </c>
+      <c r="C266" t="s">
+        <v>68</v>
+      </c>
+      <c r="D266" t="s">
+        <v>69</v>
+      </c>
+      <c r="E266" s="2">
+        <v>45713.71875</v>
+      </c>
+      <c r="F266">
+        <v>27</v>
+      </c>
+      <c r="G266" t="s">
+        <v>78</v>
+      </c>
+      <c r="H266" t="s">
+        <v>84</v>
+      </c>
+      <c r="I266">
+        <v>3</v>
+      </c>
+      <c r="J266">
+        <v>0</v>
+      </c>
+      <c r="K266">
+        <v>3</v>
+      </c>
+      <c r="L266">
+        <v>4</v>
+      </c>
+      <c r="M266">
+        <v>0</v>
+      </c>
+      <c r="N266">
+        <v>4</v>
+      </c>
+      <c r="O266" t="s">
+        <v>263</v>
+      </c>
+      <c r="P266" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q266">
+        <v>1.62</v>
+      </c>
+      <c r="R266">
+        <v>3</v>
+      </c>
+      <c r="S266">
+        <v>8</v>
+      </c>
+      <c r="T266">
+        <v>1.18</v>
+      </c>
+      <c r="U266">
+        <v>4.5</v>
+      </c>
+      <c r="V266">
+        <v>1.83</v>
+      </c>
+      <c r="W266">
+        <v>1.83</v>
+      </c>
+      <c r="X266">
+        <v>3.75</v>
+      </c>
+      <c r="Y266">
+        <v>1.25</v>
+      </c>
+      <c r="Z266">
+        <v>1.2</v>
+      </c>
+      <c r="AA266">
+        <v>6.5</v>
+      </c>
+      <c r="AB266">
+        <v>12</v>
+      </c>
+      <c r="AC266">
+        <v>1.01</v>
+      </c>
+      <c r="AD266">
+        <v>39</v>
+      </c>
+      <c r="AE266">
+        <v>1.09</v>
+      </c>
+      <c r="AF266">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG266">
+        <v>1.3</v>
+      </c>
+      <c r="AH266">
+        <v>3.33</v>
+      </c>
+      <c r="AI266">
+        <v>1.7</v>
+      </c>
+      <c r="AJ266">
+        <v>2.05</v>
+      </c>
+      <c r="AK266">
+        <v>1.05</v>
+      </c>
+      <c r="AL266">
+        <v>1.1</v>
+      </c>
+      <c r="AM266">
+        <v>4.1</v>
+      </c>
+      <c r="AN266">
+        <v>1.83</v>
+      </c>
+      <c r="AO266">
+        <v>0.38</v>
+      </c>
+      <c r="AP266">
+        <v>1.92</v>
+      </c>
+      <c r="AQ266">
+        <v>0.36</v>
+      </c>
+      <c r="AR266">
+        <v>1.91</v>
+      </c>
+      <c r="AS266">
+        <v>1.07</v>
+      </c>
+      <c r="AT266">
+        <v>2.98</v>
+      </c>
+      <c r="AU266">
+        <v>11</v>
+      </c>
+      <c r="AV266">
+        <v>3</v>
+      </c>
+      <c r="AW266">
+        <v>9</v>
+      </c>
+      <c r="AX266">
+        <v>5</v>
+      </c>
+      <c r="AY266">
+        <v>22</v>
+      </c>
+      <c r="AZ266">
+        <v>11</v>
+      </c>
+      <c r="BA266">
+        <v>4</v>
+      </c>
+      <c r="BB266">
+        <v>2</v>
+      </c>
+      <c r="BC266">
+        <v>6</v>
+      </c>
+      <c r="BD266">
+        <v>1.15</v>
+      </c>
+      <c r="BE266">
+        <v>10</v>
+      </c>
+      <c r="BF266">
+        <v>5.6</v>
+      </c>
+      <c r="BG266">
+        <v>1.19</v>
+      </c>
+      <c r="BH266">
+        <v>3.9</v>
+      </c>
+      <c r="BI266">
+        <v>1.36</v>
+      </c>
+      <c r="BJ266">
+        <v>2.85</v>
+      </c>
+      <c r="BK266">
+        <v>1.58</v>
+      </c>
+      <c r="BL266">
+        <v>2.18</v>
+      </c>
+      <c r="BM266">
+        <v>1.91</v>
+      </c>
+      <c r="BN266">
+        <v>1.77</v>
+      </c>
+      <c r="BO266">
+        <v>2.35</v>
+      </c>
+      <c r="BP266">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="408">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -808,6 +808,15 @@
     <t>['24', '36', '44', '78']</t>
   </si>
   <si>
+    <t>['22', '26', '47']</t>
+  </si>
+  <si>
+    <t>['45+4']</t>
+  </si>
+  <si>
+    <t>['11', '63']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1227,6 +1236,9 @@
   <si>
     <t>['1', '47']</t>
   </si>
+  <si>
+    <t>['4', '45+2']</t>
+  </si>
 </sst>
 </file>
 
@@ -1587,7 +1599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP266"/>
+  <dimension ref="A1:BP271"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1921,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ2">
         <v>1.69</v>
@@ -2049,7 +2061,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2461,7 +2473,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2873,7 +2885,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2951,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ7">
         <v>1.57</v>
@@ -3079,7 +3091,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3363,7 +3375,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ9">
         <v>1.69</v>
@@ -3491,7 +3503,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3572,7 +3584,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ10">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3903,7 +3915,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4187,7 +4199,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ13">
         <v>1.08</v>
@@ -5014,7 +5026,7 @@
         <v>2</v>
       </c>
       <c r="AQ17">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5139,7 +5151,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5220,7 +5232,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ18">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5345,7 +5357,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5632,7 +5644,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ20">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5835,7 +5847,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ21">
         <v>1.08</v>
@@ -6169,7 +6181,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6375,7 +6387,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6659,7 +6671,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ25">
         <v>0.86</v>
@@ -6865,7 +6877,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ26">
         <v>0.36</v>
@@ -6993,7 +7005,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7199,7 +7211,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7280,7 +7292,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ28">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR28">
         <v>1.25</v>
@@ -7405,7 +7417,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7817,7 +7829,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7895,7 +7907,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ31">
         <v>2.33</v>
@@ -8023,7 +8035,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8310,7 +8322,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ33">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR33">
         <v>1.6</v>
@@ -8435,7 +8447,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -8925,7 +8937,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ36">
         <v>1.64</v>
@@ -9259,7 +9271,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9465,7 +9477,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9671,7 +9683,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9749,10 +9761,10 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ40">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR40">
         <v>1.93</v>
@@ -9877,7 +9889,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9958,7 +9970,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ41">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR41">
         <v>1.34</v>
@@ -10083,7 +10095,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10289,7 +10301,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10370,7 +10382,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ43">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR43">
         <v>1.79</v>
@@ -10779,7 +10791,7 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ45">
         <v>1.57</v>
@@ -10988,7 +11000,7 @@
         <v>0.31</v>
       </c>
       <c r="AQ46">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR46">
         <v>0.83</v>
@@ -11191,7 +11203,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ47">
         <v>1.08</v>
@@ -11937,7 +11949,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -12018,7 +12030,7 @@
         <v>2</v>
       </c>
       <c r="AQ51">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR51">
         <v>2.05</v>
@@ -12143,7 +12155,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12224,7 +12236,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ52">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR52">
         <v>0.75</v>
@@ -12349,7 +12361,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12427,7 +12439,7 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ53">
         <v>1.69</v>
@@ -12761,7 +12773,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -13045,7 +13057,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ56">
         <v>1.23</v>
@@ -13173,7 +13185,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13379,7 +13391,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13585,7 +13597,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13791,7 +13803,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13869,7 +13881,7 @@
         <v>0.5</v>
       </c>
       <c r="AP60">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ60">
         <v>1.23</v>
@@ -13997,7 +14009,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14203,7 +14215,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14615,7 +14627,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14821,7 +14833,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14902,7 +14914,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ65">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR65">
         <v>1.33</v>
@@ -15027,7 +15039,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -15105,7 +15117,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ66">
         <v>0.86</v>
@@ -15520,7 +15532,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ68">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR68">
         <v>1.37</v>
@@ -16057,7 +16069,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16341,7 +16353,7 @@
         <v>1.67</v>
       </c>
       <c r="AP72">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ72">
         <v>1.23</v>
@@ -16469,7 +16481,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16675,7 +16687,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16753,7 +16765,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ74">
         <v>1.08</v>
@@ -16881,7 +16893,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -17087,7 +17099,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17293,7 +17305,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17580,7 +17592,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ78">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR78">
         <v>1.65</v>
@@ -17705,7 +17717,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17786,7 +17798,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ79">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR79">
         <v>1.27</v>
@@ -17911,7 +17923,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -17989,7 +18001,7 @@
         <v>3</v>
       </c>
       <c r="AP80">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ80">
         <v>1.5</v>
@@ -18195,7 +18207,7 @@
         <v>0.33</v>
       </c>
       <c r="AP81">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ81">
         <v>1.69</v>
@@ -18323,7 +18335,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18735,7 +18747,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18941,7 +18953,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -19147,7 +19159,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19225,10 +19237,10 @@
         <v>0.5</v>
       </c>
       <c r="AP86">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ86">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR86">
         <v>1.7</v>
@@ -19559,7 +19571,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19640,7 +19652,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ88">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR88">
         <v>1.67</v>
@@ -19971,7 +19983,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20177,7 +20189,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20464,7 +20476,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ92">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR92">
         <v>1.13</v>
@@ -20876,7 +20888,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ94">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR94">
         <v>1.6</v>
@@ -21285,7 +21297,7 @@
         <v>1.75</v>
       </c>
       <c r="AP96">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ96">
         <v>1.57</v>
@@ -21491,7 +21503,7 @@
         <v>1.25</v>
       </c>
       <c r="AP97">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ97">
         <v>1.23</v>
@@ -21619,7 +21631,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21825,7 +21837,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -21903,7 +21915,7 @@
         <v>2.5</v>
       </c>
       <c r="AP99">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ99">
         <v>1.08</v>
@@ -22031,7 +22043,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22109,7 +22121,7 @@
         <v>2.25</v>
       </c>
       <c r="AP100">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ100">
         <v>1.5</v>
@@ -22443,7 +22455,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22521,7 +22533,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ102">
         <v>1.57</v>
@@ -22649,7 +22661,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23348,7 +23360,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ106">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR106">
         <v>1.54</v>
@@ -23551,7 +23563,7 @@
         <v>2</v>
       </c>
       <c r="AP107">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ107">
         <v>1.08</v>
@@ -23757,7 +23769,7 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ108">
         <v>0.67</v>
@@ -23885,7 +23897,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -23963,10 +23975,10 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ109">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR109">
         <v>1.61</v>
@@ -24091,7 +24103,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24169,10 +24181,10 @@
         <v>0.4</v>
       </c>
       <c r="AP110">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ110">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR110">
         <v>1.96</v>
@@ -24297,7 +24309,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q111">
         <v>3.25</v>
@@ -24378,7 +24390,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ111">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR111">
         <v>1.72</v>
@@ -24503,7 +24515,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24709,7 +24721,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -25327,7 +25339,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25533,7 +25545,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25739,7 +25751,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25945,7 +25957,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -26151,7 +26163,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26357,7 +26369,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26563,7 +26575,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26769,7 +26781,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -27053,10 +27065,10 @@
         <v>0.83</v>
       </c>
       <c r="AP124">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ124">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR124">
         <v>1.52</v>
@@ -27259,7 +27271,7 @@
         <v>0.83</v>
       </c>
       <c r="AP125">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ125">
         <v>0.67</v>
@@ -27387,7 +27399,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27468,7 +27480,7 @@
         <v>1</v>
       </c>
       <c r="AQ126">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR126">
         <v>1.38</v>
@@ -27593,7 +27605,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -27674,7 +27686,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ127">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR127">
         <v>1.54</v>
@@ -27877,7 +27889,7 @@
         <v>0.83</v>
       </c>
       <c r="AP128">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ128">
         <v>1.08</v>
@@ -28211,7 +28223,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28289,7 +28301,7 @@
         <v>1.33</v>
       </c>
       <c r="AP130">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ130">
         <v>1.69</v>
@@ -28495,10 +28507,10 @@
         <v>1.67</v>
       </c>
       <c r="AP131">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ131">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR131">
         <v>1.72</v>
@@ -28623,7 +28635,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -29035,7 +29047,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29241,7 +29253,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -30683,7 +30695,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30764,7 +30776,7 @@
         <v>1</v>
       </c>
       <c r="AQ142">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR142">
         <v>1.38</v>
@@ -30889,7 +30901,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30967,10 +30979,10 @@
         <v>1.29</v>
       </c>
       <c r="AP143">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ143">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR143">
         <v>1.7</v>
@@ -31301,7 +31313,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31379,7 +31391,7 @@
         <v>1.57</v>
       </c>
       <c r="AP145">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ145">
         <v>1.64</v>
@@ -31507,7 +31519,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31588,7 +31600,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ146">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR146">
         <v>1.74</v>
@@ -31713,7 +31725,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31919,7 +31931,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -32125,7 +32137,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32203,7 +32215,7 @@
         <v>2.29</v>
       </c>
       <c r="AP149">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ149">
         <v>1.5</v>
@@ -32537,7 +32549,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -32618,7 +32630,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ151">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR151">
         <v>1.14</v>
@@ -33155,7 +33167,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33233,7 +33245,7 @@
         <v>1.29</v>
       </c>
       <c r="AP154">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ154">
         <v>1.69</v>
@@ -33361,7 +33373,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33439,7 +33451,7 @@
         <v>1.43</v>
       </c>
       <c r="AP155">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ155">
         <v>1.08</v>
@@ -33567,7 +33579,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33773,7 +33785,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33979,7 +33991,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34678,7 +34690,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ161">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR161">
         <v>1.54</v>
@@ -34803,7 +34815,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -34881,7 +34893,7 @@
         <v>1.75</v>
       </c>
       <c r="AP162">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ162">
         <v>1.64</v>
@@ -35009,7 +35021,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35215,7 +35227,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35296,7 +35308,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ164">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR164">
         <v>1.2</v>
@@ -35421,7 +35433,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35502,7 +35514,7 @@
         <v>1</v>
       </c>
       <c r="AQ165">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR165">
         <v>1.31</v>
@@ -35833,7 +35845,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36039,7 +36051,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36117,7 +36129,7 @@
         <v>1.38</v>
       </c>
       <c r="AP168">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ168">
         <v>1.57</v>
@@ -36451,7 +36463,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36529,7 +36541,7 @@
         <v>2.43</v>
       </c>
       <c r="AP170">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ170">
         <v>2.33</v>
@@ -36863,7 +36875,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37147,7 +37159,7 @@
         <v>1.25</v>
       </c>
       <c r="AP173">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ173">
         <v>1.23</v>
@@ -37481,7 +37493,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -38099,7 +38111,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38177,7 +38189,7 @@
         <v>0.63</v>
       </c>
       <c r="AP178">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ178">
         <v>0.67</v>
@@ -38592,7 +38604,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ180">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR180">
         <v>2.03</v>
@@ -38717,7 +38729,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38798,7 +38810,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ181">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR181">
         <v>1.08</v>
@@ -38923,7 +38935,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39001,7 +39013,7 @@
         <v>0.89</v>
       </c>
       <c r="AP182">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ182">
         <v>0.86</v>
@@ -39335,7 +39347,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39541,7 +39553,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39747,7 +39759,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -40159,7 +40171,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40365,7 +40377,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40443,10 +40455,10 @@
         <v>1.33</v>
       </c>
       <c r="AP189">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ189">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR189">
         <v>1.54</v>
@@ -40571,7 +40583,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40649,10 +40661,10 @@
         <v>1.67</v>
       </c>
       <c r="AP190">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ190">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR190">
         <v>1.66</v>
@@ -40777,7 +40789,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -40855,10 +40867,10 @@
         <v>1.5</v>
       </c>
       <c r="AP191">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ191">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR191">
         <v>1.71</v>
@@ -41189,7 +41201,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41601,7 +41613,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41807,7 +41819,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -42094,7 +42106,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ197">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR197">
         <v>1.62</v>
@@ -42219,7 +42231,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42300,7 +42312,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ198">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR198">
         <v>1.57</v>
@@ -42425,7 +42437,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42503,7 +42515,7 @@
         <v>1</v>
       </c>
       <c r="AP199">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ199">
         <v>1.08</v>
@@ -42631,7 +42643,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42837,7 +42849,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -43043,7 +43055,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43249,7 +43261,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43327,10 +43339,10 @@
         <v>1.4</v>
       </c>
       <c r="AP203">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ203">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR203">
         <v>1.57</v>
@@ -43455,7 +43467,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43533,7 +43545,7 @@
         <v>2.56</v>
       </c>
       <c r="AP204">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ204">
         <v>2.33</v>
@@ -43661,7 +43673,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -44073,7 +44085,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44485,7 +44497,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44769,7 +44781,7 @@
         <v>0.2</v>
       </c>
       <c r="AP210">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ210">
         <v>0.36</v>
@@ -44897,7 +44909,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45103,7 +45115,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45309,7 +45321,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45387,7 +45399,7 @@
         <v>2.4</v>
       </c>
       <c r="AP213">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ213">
         <v>2.33</v>
@@ -45515,7 +45527,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45721,7 +45733,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -45927,7 +45939,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -46005,7 +46017,7 @@
         <v>1.45</v>
       </c>
       <c r="AP216">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ216">
         <v>1.57</v>
@@ -46133,7 +46145,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46211,7 +46223,7 @@
         <v>0.18</v>
       </c>
       <c r="AP217">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ217">
         <v>0.36</v>
@@ -46339,7 +46351,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46545,7 +46557,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46626,7 +46638,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ219">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR219">
         <v>1.13</v>
@@ -46751,7 +46763,7 @@
         <v>240</v>
       </c>
       <c r="P220" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q220">
         <v>1.73</v>
@@ -47163,7 +47175,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -47447,10 +47459,10 @@
         <v>0.9</v>
       </c>
       <c r="AP223">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ223">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR223">
         <v>1.79</v>
@@ -47575,7 +47587,7 @@
         <v>107</v>
       </c>
       <c r="P224" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="Q224">
         <v>6</v>
@@ -47656,7 +47668,7 @@
         <v>0.31</v>
       </c>
       <c r="AQ224">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR224">
         <v>1.11</v>
@@ -47781,7 +47793,7 @@
         <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q225">
         <v>6.5</v>
@@ -47862,7 +47874,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ225">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR225">
         <v>1.21</v>
@@ -47987,7 +47999,7 @@
         <v>243</v>
       </c>
       <c r="P226" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="Q226">
         <v>2.38</v>
@@ -48193,7 +48205,7 @@
         <v>155</v>
       </c>
       <c r="P227" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48399,7 +48411,7 @@
         <v>244</v>
       </c>
       <c r="P228" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q228">
         <v>1.91</v>
@@ -48477,7 +48489,7 @@
         <v>0.5</v>
       </c>
       <c r="AP228">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ228">
         <v>0.67</v>
@@ -48811,7 +48823,7 @@
         <v>91</v>
       </c>
       <c r="P230" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="Q230">
         <v>2.88</v>
@@ -49095,7 +49107,7 @@
         <v>1.58</v>
       </c>
       <c r="AP231">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ231">
         <v>1.57</v>
@@ -49223,7 +49235,7 @@
         <v>95</v>
       </c>
       <c r="P232" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="Q232">
         <v>2.2</v>
@@ -49635,7 +49647,7 @@
         <v>151</v>
       </c>
       <c r="P234" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Q234">
         <v>2.6</v>
@@ -49841,7 +49853,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Q235">
         <v>4.5</v>
@@ -50253,7 +50265,7 @@
         <v>91</v>
       </c>
       <c r="P237" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50331,7 +50343,7 @@
         <v>0.91</v>
       </c>
       <c r="AP237">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ237">
         <v>1.23</v>
@@ -50459,7 +50471,7 @@
         <v>91</v>
       </c>
       <c r="P238" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Q238">
         <v>2.75</v>
@@ -50537,7 +50549,7 @@
         <v>1.45</v>
       </c>
       <c r="AP238">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ238">
         <v>1.69</v>
@@ -50746,7 +50758,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ239">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR239">
         <v>2</v>
@@ -50871,7 +50883,7 @@
         <v>249</v>
       </c>
       <c r="P240" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Q240">
         <v>1.8</v>
@@ -51077,7 +51089,7 @@
         <v>250</v>
       </c>
       <c r="P241" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="Q241">
         <v>6</v>
@@ -51489,7 +51501,7 @@
         <v>91</v>
       </c>
       <c r="P243" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Q243">
         <v>9</v>
@@ -51570,7 +51582,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ243">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AR243">
         <v>1.2</v>
@@ -51695,7 +51707,7 @@
         <v>203</v>
       </c>
       <c r="P244" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="Q244">
         <v>5</v>
@@ -51982,7 +51994,7 @@
         <v>2</v>
       </c>
       <c r="AQ245">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR245">
         <v>1.98</v>
@@ -52600,7 +52612,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ248">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR248">
         <v>1.52</v>
@@ -52725,7 +52737,7 @@
         <v>254</v>
       </c>
       <c r="P249" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="Q249">
         <v>2.63</v>
@@ -52931,7 +52943,7 @@
         <v>255</v>
       </c>
       <c r="P250" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q250">
         <v>1.57</v>
@@ -53009,7 +53021,7 @@
         <v>0.75</v>
       </c>
       <c r="AP250">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ250">
         <v>0.86</v>
@@ -53215,7 +53227,7 @@
         <v>1.18</v>
       </c>
       <c r="AP251">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ251">
         <v>1.08</v>
@@ -53343,7 +53355,7 @@
         <v>256</v>
       </c>
       <c r="P252" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Q252">
         <v>4</v>
@@ -53549,7 +53561,7 @@
         <v>91</v>
       </c>
       <c r="P253" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="Q253">
         <v>3.6</v>
@@ -53755,7 +53767,7 @@
         <v>257</v>
       </c>
       <c r="P254" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="Q254">
         <v>3.25</v>
@@ -53961,7 +53973,7 @@
         <v>91</v>
       </c>
       <c r="P255" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="Q255">
         <v>5</v>
@@ -54167,7 +54179,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="Q256">
         <v>3.75</v>
@@ -54373,7 +54385,7 @@
         <v>91</v>
       </c>
       <c r="P257" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="Q257">
         <v>1.73</v>
@@ -54785,7 +54797,7 @@
         <v>91</v>
       </c>
       <c r="P259" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="Q259">
         <v>2.75</v>
@@ -54991,7 +55003,7 @@
         <v>258</v>
       </c>
       <c r="P260" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q260">
         <v>3.1</v>
@@ -55197,7 +55209,7 @@
         <v>259</v>
       </c>
       <c r="P261" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="Q261">
         <v>2.38</v>
@@ -55403,7 +55415,7 @@
         <v>91</v>
       </c>
       <c r="P262" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="Q262">
         <v>3.1</v>
@@ -55609,7 +55621,7 @@
         <v>260</v>
       </c>
       <c r="P263" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q263">
         <v>3.2</v>
@@ -55815,7 +55827,7 @@
         <v>261</v>
       </c>
       <c r="P264" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="Q264">
         <v>3.5</v>
@@ -56384,6 +56396,1036 @@
       </c>
       <c r="BP266">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="267" spans="1:68">
+      <c r="A267" s="1">
+        <v>266</v>
+      </c>
+      <c r="B267">
+        <v>7466942</v>
+      </c>
+      <c r="C267" t="s">
+        <v>68</v>
+      </c>
+      <c r="D267" t="s">
+        <v>69</v>
+      </c>
+      <c r="E267" s="2">
+        <v>45714.6875</v>
+      </c>
+      <c r="F267">
+        <v>27</v>
+      </c>
+      <c r="G267" t="s">
+        <v>81</v>
+      </c>
+      <c r="H267" t="s">
+        <v>85</v>
+      </c>
+      <c r="I267">
+        <v>0</v>
+      </c>
+      <c r="J267">
+        <v>1</v>
+      </c>
+      <c r="K267">
+        <v>1</v>
+      </c>
+      <c r="L267">
+        <v>0</v>
+      </c>
+      <c r="M267">
+        <v>1</v>
+      </c>
+      <c r="N267">
+        <v>1</v>
+      </c>
+      <c r="O267" t="s">
+        <v>91</v>
+      </c>
+      <c r="P267" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q267">
+        <v>3.75</v>
+      </c>
+      <c r="R267">
+        <v>2.63</v>
+      </c>
+      <c r="S267">
+        <v>2.25</v>
+      </c>
+      <c r="T267">
+        <v>1.2</v>
+      </c>
+      <c r="U267">
+        <v>4.33</v>
+      </c>
+      <c r="V267">
+        <v>1.91</v>
+      </c>
+      <c r="W267">
+        <v>1.8</v>
+      </c>
+      <c r="X267">
+        <v>4</v>
+      </c>
+      <c r="Y267">
+        <v>1.22</v>
+      </c>
+      <c r="Z267">
+        <v>4.33</v>
+      </c>
+      <c r="AA267">
+        <v>4.33</v>
+      </c>
+      <c r="AB267">
+        <v>1.67</v>
+      </c>
+      <c r="AC267">
+        <v>1.01</v>
+      </c>
+      <c r="AD267">
+        <v>32</v>
+      </c>
+      <c r="AE267">
+        <v>1.1</v>
+      </c>
+      <c r="AF267">
+        <v>7.6</v>
+      </c>
+      <c r="AG267">
+        <v>1.32</v>
+      </c>
+      <c r="AH267">
+        <v>3.21</v>
+      </c>
+      <c r="AI267">
+        <v>1.36</v>
+      </c>
+      <c r="AJ267">
+        <v>3</v>
+      </c>
+      <c r="AK267">
+        <v>2</v>
+      </c>
+      <c r="AL267">
+        <v>1.21</v>
+      </c>
+      <c r="AM267">
+        <v>1.25</v>
+      </c>
+      <c r="AN267">
+        <v>1.31</v>
+      </c>
+      <c r="AO267">
+        <v>1.38</v>
+      </c>
+      <c r="AP267">
+        <v>1.21</v>
+      </c>
+      <c r="AQ267">
+        <v>1.5</v>
+      </c>
+      <c r="AR267">
+        <v>1.78</v>
+      </c>
+      <c r="AS267">
+        <v>1.84</v>
+      </c>
+      <c r="AT267">
+        <v>3.62</v>
+      </c>
+      <c r="AU267">
+        <v>7</v>
+      </c>
+      <c r="AV267">
+        <v>6</v>
+      </c>
+      <c r="AW267">
+        <v>3</v>
+      </c>
+      <c r="AX267">
+        <v>2</v>
+      </c>
+      <c r="AY267">
+        <v>12</v>
+      </c>
+      <c r="AZ267">
+        <v>13</v>
+      </c>
+      <c r="BA267">
+        <v>8</v>
+      </c>
+      <c r="BB267">
+        <v>3</v>
+      </c>
+      <c r="BC267">
+        <v>11</v>
+      </c>
+      <c r="BD267">
+        <v>2.75</v>
+      </c>
+      <c r="BE267">
+        <v>7</v>
+      </c>
+      <c r="BF267">
+        <v>1.52</v>
+      </c>
+      <c r="BG267">
+        <v>1.12</v>
+      </c>
+      <c r="BH267">
+        <v>5.1</v>
+      </c>
+      <c r="BI267">
+        <v>1.23</v>
+      </c>
+      <c r="BJ267">
+        <v>3.65</v>
+      </c>
+      <c r="BK267">
+        <v>1.38</v>
+      </c>
+      <c r="BL267">
+        <v>2.75</v>
+      </c>
+      <c r="BM267">
+        <v>1.61</v>
+      </c>
+      <c r="BN267">
+        <v>2.15</v>
+      </c>
+      <c r="BO267">
+        <v>1.93</v>
+      </c>
+      <c r="BP267">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="268" spans="1:68">
+      <c r="A268" s="1">
+        <v>267</v>
+      </c>
+      <c r="B268">
+        <v>7466948</v>
+      </c>
+      <c r="C268" t="s">
+        <v>68</v>
+      </c>
+      <c r="D268" t="s">
+        <v>69</v>
+      </c>
+      <c r="E268" s="2">
+        <v>45714.6875</v>
+      </c>
+      <c r="F268">
+        <v>27</v>
+      </c>
+      <c r="G268" t="s">
+        <v>70</v>
+      </c>
+      <c r="H268" t="s">
+        <v>71</v>
+      </c>
+      <c r="I268">
+        <v>2</v>
+      </c>
+      <c r="J268">
+        <v>2</v>
+      </c>
+      <c r="K268">
+        <v>4</v>
+      </c>
+      <c r="L268">
+        <v>3</v>
+      </c>
+      <c r="M268">
+        <v>2</v>
+      </c>
+      <c r="N268">
+        <v>5</v>
+      </c>
+      <c r="O268" t="s">
+        <v>264</v>
+      </c>
+      <c r="P268" t="s">
+        <v>407</v>
+      </c>
+      <c r="Q268">
+        <v>2.05</v>
+      </c>
+      <c r="R268">
+        <v>2.4</v>
+      </c>
+      <c r="S268">
+        <v>5.5</v>
+      </c>
+      <c r="T268">
+        <v>1.33</v>
+      </c>
+      <c r="U268">
+        <v>3.25</v>
+      </c>
+      <c r="V268">
+        <v>2.5</v>
+      </c>
+      <c r="W268">
+        <v>1.5</v>
+      </c>
+      <c r="X268">
+        <v>6</v>
+      </c>
+      <c r="Y268">
+        <v>1.13</v>
+      </c>
+      <c r="Z268">
+        <v>1.53</v>
+      </c>
+      <c r="AA268">
+        <v>4.33</v>
+      </c>
+      <c r="AB268">
+        <v>5.75</v>
+      </c>
+      <c r="AC268">
+        <v>1.03</v>
+      </c>
+      <c r="AD268">
+        <v>16</v>
+      </c>
+      <c r="AE268">
+        <v>1.22</v>
+      </c>
+      <c r="AF268">
+        <v>4.5</v>
+      </c>
+      <c r="AG268">
+        <v>1.67</v>
+      </c>
+      <c r="AH268">
+        <v>2.2</v>
+      </c>
+      <c r="AI268">
+        <v>1.8</v>
+      </c>
+      <c r="AJ268">
+        <v>1.95</v>
+      </c>
+      <c r="AK268">
+        <v>1.13</v>
+      </c>
+      <c r="AL268">
+        <v>1.2</v>
+      </c>
+      <c r="AM268">
+        <v>2.55</v>
+      </c>
+      <c r="AN268">
+        <v>1.23</v>
+      </c>
+      <c r="AO268">
+        <v>0.83</v>
+      </c>
+      <c r="AP268">
+        <v>1.36</v>
+      </c>
+      <c r="AQ268">
+        <v>0.77</v>
+      </c>
+      <c r="AR268">
+        <v>1.55</v>
+      </c>
+      <c r="AS268">
+        <v>0.89</v>
+      </c>
+      <c r="AT268">
+        <v>2.44</v>
+      </c>
+      <c r="AU268">
+        <v>7</v>
+      </c>
+      <c r="AV268">
+        <v>4</v>
+      </c>
+      <c r="AW268">
+        <v>1</v>
+      </c>
+      <c r="AX268">
+        <v>4</v>
+      </c>
+      <c r="AY268">
+        <v>11</v>
+      </c>
+      <c r="AZ268">
+        <v>13</v>
+      </c>
+      <c r="BA268">
+        <v>5</v>
+      </c>
+      <c r="BB268">
+        <v>6</v>
+      </c>
+      <c r="BC268">
+        <v>11</v>
+      </c>
+      <c r="BD268">
+        <v>1.36</v>
+      </c>
+      <c r="BE268">
+        <v>7.5</v>
+      </c>
+      <c r="BF268">
+        <v>3.4</v>
+      </c>
+      <c r="BG268">
+        <v>1.21</v>
+      </c>
+      <c r="BH268">
+        <v>3.7</v>
+      </c>
+      <c r="BI268">
+        <v>1.4</v>
+      </c>
+      <c r="BJ268">
+        <v>2.7</v>
+      </c>
+      <c r="BK268">
+        <v>1.66</v>
+      </c>
+      <c r="BL268">
+        <v>2.07</v>
+      </c>
+      <c r="BM268">
+        <v>2.02</v>
+      </c>
+      <c r="BN268">
+        <v>1.68</v>
+      </c>
+      <c r="BO268">
+        <v>2.55</v>
+      </c>
+      <c r="BP268">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="269" spans="1:68">
+      <c r="A269" s="1">
+        <v>268</v>
+      </c>
+      <c r="B269">
+        <v>7466939</v>
+      </c>
+      <c r="C269" t="s">
+        <v>68</v>
+      </c>
+      <c r="D269" t="s">
+        <v>69</v>
+      </c>
+      <c r="E269" s="2">
+        <v>45714.6875</v>
+      </c>
+      <c r="F269">
+        <v>27</v>
+      </c>
+      <c r="G269" t="s">
+        <v>77</v>
+      </c>
+      <c r="H269" t="s">
+        <v>73</v>
+      </c>
+      <c r="I269">
+        <v>1</v>
+      </c>
+      <c r="J269">
+        <v>0</v>
+      </c>
+      <c r="K269">
+        <v>1</v>
+      </c>
+      <c r="L269">
+        <v>1</v>
+      </c>
+      <c r="M269">
+        <v>1</v>
+      </c>
+      <c r="N269">
+        <v>2</v>
+      </c>
+      <c r="O269" t="s">
+        <v>265</v>
+      </c>
+      <c r="P269" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q269">
+        <v>2.63</v>
+      </c>
+      <c r="R269">
+        <v>2.2</v>
+      </c>
+      <c r="S269">
+        <v>4</v>
+      </c>
+      <c r="T269">
+        <v>1.4</v>
+      </c>
+      <c r="U269">
+        <v>2.75</v>
+      </c>
+      <c r="V269">
+        <v>2.75</v>
+      </c>
+      <c r="W269">
+        <v>1.4</v>
+      </c>
+      <c r="X269">
+        <v>8</v>
+      </c>
+      <c r="Y269">
+        <v>1.08</v>
+      </c>
+      <c r="Z269">
+        <v>2.2</v>
+      </c>
+      <c r="AA269">
+        <v>3.6</v>
+      </c>
+      <c r="AB269">
+        <v>3</v>
+      </c>
+      <c r="AC269">
+        <v>1.05</v>
+      </c>
+      <c r="AD269">
+        <v>9.5</v>
+      </c>
+      <c r="AE269">
+        <v>1.28</v>
+      </c>
+      <c r="AF269">
+        <v>3.55</v>
+      </c>
+      <c r="AG269">
+        <v>1.95</v>
+      </c>
+      <c r="AH269">
+        <v>1.75</v>
+      </c>
+      <c r="AI269">
+        <v>1.8</v>
+      </c>
+      <c r="AJ269">
+        <v>1.95</v>
+      </c>
+      <c r="AK269">
+        <v>1.27</v>
+      </c>
+      <c r="AL269">
+        <v>1.3</v>
+      </c>
+      <c r="AM269">
+        <v>1.77</v>
+      </c>
+      <c r="AN269">
+        <v>1.77</v>
+      </c>
+      <c r="AO269">
+        <v>1.08</v>
+      </c>
+      <c r="AP269">
+        <v>1.71</v>
+      </c>
+      <c r="AQ269">
+        <v>1.08</v>
+      </c>
+      <c r="AR269">
+        <v>1.65</v>
+      </c>
+      <c r="AS269">
+        <v>1.09</v>
+      </c>
+      <c r="AT269">
+        <v>2.74</v>
+      </c>
+      <c r="AU269">
+        <v>4</v>
+      </c>
+      <c r="AV269">
+        <v>5</v>
+      </c>
+      <c r="AW269">
+        <v>9</v>
+      </c>
+      <c r="AX269">
+        <v>10</v>
+      </c>
+      <c r="AY269">
+        <v>16</v>
+      </c>
+      <c r="AZ269">
+        <v>16</v>
+      </c>
+      <c r="BA269">
+        <v>2</v>
+      </c>
+      <c r="BB269">
+        <v>5</v>
+      </c>
+      <c r="BC269">
+        <v>7</v>
+      </c>
+      <c r="BD269">
+        <v>1.74</v>
+      </c>
+      <c r="BE269">
+        <v>6.75</v>
+      </c>
+      <c r="BF269">
+        <v>2.28</v>
+      </c>
+      <c r="BG269">
+        <v>1.19</v>
+      </c>
+      <c r="BH269">
+        <v>4.1</v>
+      </c>
+      <c r="BI269">
+        <v>1.34</v>
+      </c>
+      <c r="BJ269">
+        <v>2.9</v>
+      </c>
+      <c r="BK269">
+        <v>1.56</v>
+      </c>
+      <c r="BL269">
+        <v>2.23</v>
+      </c>
+      <c r="BM269">
+        <v>1.9</v>
+      </c>
+      <c r="BN269">
+        <v>1.79</v>
+      </c>
+      <c r="BO269">
+        <v>2.38</v>
+      </c>
+      <c r="BP269">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="270" spans="1:68">
+      <c r="A270" s="1">
+        <v>269</v>
+      </c>
+      <c r="B270">
+        <v>7466941</v>
+      </c>
+      <c r="C270" t="s">
+        <v>68</v>
+      </c>
+      <c r="D270" t="s">
+        <v>69</v>
+      </c>
+      <c r="E270" s="2">
+        <v>45714.6875</v>
+      </c>
+      <c r="F270">
+        <v>27</v>
+      </c>
+      <c r="G270" t="s">
+        <v>75</v>
+      </c>
+      <c r="H270" t="s">
+        <v>72</v>
+      </c>
+      <c r="I270">
+        <v>0</v>
+      </c>
+      <c r="J270">
+        <v>0</v>
+      </c>
+      <c r="K270">
+        <v>0</v>
+      </c>
+      <c r="L270">
+        <v>0</v>
+      </c>
+      <c r="M270">
+        <v>0</v>
+      </c>
+      <c r="N270">
+        <v>0</v>
+      </c>
+      <c r="O270" t="s">
+        <v>91</v>
+      </c>
+      <c r="P270" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q270">
+        <v>4.5</v>
+      </c>
+      <c r="R270">
+        <v>2.1</v>
+      </c>
+      <c r="S270">
+        <v>2.6</v>
+      </c>
+      <c r="T270">
+        <v>1.44</v>
+      </c>
+      <c r="U270">
+        <v>2.63</v>
+      </c>
+      <c r="V270">
+        <v>3.25</v>
+      </c>
+      <c r="W270">
+        <v>1.33</v>
+      </c>
+      <c r="X270">
+        <v>9</v>
+      </c>
+      <c r="Y270">
+        <v>1.07</v>
+      </c>
+      <c r="Z270">
+        <v>4.4</v>
+      </c>
+      <c r="AA270">
+        <v>4</v>
+      </c>
+      <c r="AB270">
+        <v>1.7</v>
+      </c>
+      <c r="AC270">
+        <v>1.07</v>
+      </c>
+      <c r="AD270">
+        <v>9.6</v>
+      </c>
+      <c r="AE270">
+        <v>1.38</v>
+      </c>
+      <c r="AF270">
+        <v>3.15</v>
+      </c>
+      <c r="AG270">
+        <v>1.95</v>
+      </c>
+      <c r="AH270">
+        <v>1.75</v>
+      </c>
+      <c r="AI270">
+        <v>1.95</v>
+      </c>
+      <c r="AJ270">
+        <v>1.8</v>
+      </c>
+      <c r="AK270">
+        <v>1.8</v>
+      </c>
+      <c r="AL270">
+        <v>1.31</v>
+      </c>
+      <c r="AM270">
+        <v>1.25</v>
+      </c>
+      <c r="AN270">
+        <v>2</v>
+      </c>
+      <c r="AO270">
+        <v>1.92</v>
+      </c>
+      <c r="AP270">
+        <v>1.92</v>
+      </c>
+      <c r="AQ270">
+        <v>1.86</v>
+      </c>
+      <c r="AR270">
+        <v>1.5</v>
+      </c>
+      <c r="AS270">
+        <v>1.32</v>
+      </c>
+      <c r="AT270">
+        <v>2.82</v>
+      </c>
+      <c r="AU270">
+        <v>3</v>
+      </c>
+      <c r="AV270">
+        <v>2</v>
+      </c>
+      <c r="AW270">
+        <v>4</v>
+      </c>
+      <c r="AX270">
+        <v>12</v>
+      </c>
+      <c r="AY270">
+        <v>9</v>
+      </c>
+      <c r="AZ270">
+        <v>21</v>
+      </c>
+      <c r="BA270">
+        <v>3</v>
+      </c>
+      <c r="BB270">
+        <v>11</v>
+      </c>
+      <c r="BC270">
+        <v>14</v>
+      </c>
+      <c r="BD270">
+        <v>2.9</v>
+      </c>
+      <c r="BE270">
+        <v>7</v>
+      </c>
+      <c r="BF270">
+        <v>1.49</v>
+      </c>
+      <c r="BG270">
+        <v>1.24</v>
+      </c>
+      <c r="BH270">
+        <v>3.55</v>
+      </c>
+      <c r="BI270">
+        <v>1.41</v>
+      </c>
+      <c r="BJ270">
+        <v>2.65</v>
+      </c>
+      <c r="BK270">
+        <v>1.67</v>
+      </c>
+      <c r="BL270">
+        <v>2.05</v>
+      </c>
+      <c r="BM270">
+        <v>2.08</v>
+      </c>
+      <c r="BN270">
+        <v>1.65</v>
+      </c>
+      <c r="BO270">
+        <v>2.65</v>
+      </c>
+      <c r="BP270">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="271" spans="1:68">
+      <c r="A271" s="1">
+        <v>270</v>
+      </c>
+      <c r="B271">
+        <v>7466947</v>
+      </c>
+      <c r="C271" t="s">
+        <v>68</v>
+      </c>
+      <c r="D271" t="s">
+        <v>69</v>
+      </c>
+      <c r="E271" s="2">
+        <v>45714.71875</v>
+      </c>
+      <c r="F271">
+        <v>27</v>
+      </c>
+      <c r="G271" t="s">
+        <v>89</v>
+      </c>
+      <c r="H271" t="s">
+        <v>74</v>
+      </c>
+      <c r="I271">
+        <v>1</v>
+      </c>
+      <c r="J271">
+        <v>0</v>
+      </c>
+      <c r="K271">
+        <v>1</v>
+      </c>
+      <c r="L271">
+        <v>2</v>
+      </c>
+      <c r="M271">
+        <v>0</v>
+      </c>
+      <c r="N271">
+        <v>2</v>
+      </c>
+      <c r="O271" t="s">
+        <v>266</v>
+      </c>
+      <c r="P271" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q271">
+        <v>1.95</v>
+      </c>
+      <c r="R271">
+        <v>2.63</v>
+      </c>
+      <c r="S271">
+        <v>5</v>
+      </c>
+      <c r="T271">
+        <v>1.22</v>
+      </c>
+      <c r="U271">
+        <v>4</v>
+      </c>
+      <c r="V271">
+        <v>2.1</v>
+      </c>
+      <c r="W271">
+        <v>1.67</v>
+      </c>
+      <c r="X271">
+        <v>4.5</v>
+      </c>
+      <c r="Y271">
+        <v>1.18</v>
+      </c>
+      <c r="Z271">
+        <v>1.5</v>
+      </c>
+      <c r="AA271">
+        <v>4.4</v>
+      </c>
+      <c r="AB271">
+        <v>6</v>
+      </c>
+      <c r="AC271">
+        <v>1.01</v>
+      </c>
+      <c r="AD271">
+        <v>28</v>
+      </c>
+      <c r="AE271">
+        <v>1.13</v>
+      </c>
+      <c r="AF271">
+        <v>6.4</v>
+      </c>
+      <c r="AG271">
+        <v>1.42</v>
+      </c>
+      <c r="AH271">
+        <v>2.74</v>
+      </c>
+      <c r="AI271">
+        <v>1.53</v>
+      </c>
+      <c r="AJ271">
+        <v>2.38</v>
+      </c>
+      <c r="AK271">
+        <v>1.15</v>
+      </c>
+      <c r="AL271">
+        <v>1.19</v>
+      </c>
+      <c r="AM271">
+        <v>2.45</v>
+      </c>
+      <c r="AN271">
+        <v>2.42</v>
+      </c>
+      <c r="AO271">
+        <v>1.62</v>
+      </c>
+      <c r="AP271">
+        <v>2.46</v>
+      </c>
+      <c r="AQ271">
+        <v>1.5</v>
+      </c>
+      <c r="AR271">
+        <v>1.81</v>
+      </c>
+      <c r="AS271">
+        <v>1.41</v>
+      </c>
+      <c r="AT271">
+        <v>3.22</v>
+      </c>
+      <c r="AU271">
+        <v>4</v>
+      </c>
+      <c r="AV271">
+        <v>0</v>
+      </c>
+      <c r="AW271">
+        <v>9</v>
+      </c>
+      <c r="AX271">
+        <v>4</v>
+      </c>
+      <c r="AY271">
+        <v>16</v>
+      </c>
+      <c r="AZ271">
+        <v>5</v>
+      </c>
+      <c r="BA271">
+        <v>4</v>
+      </c>
+      <c r="BB271">
+        <v>2</v>
+      </c>
+      <c r="BC271">
+        <v>6</v>
+      </c>
+      <c r="BD271">
+        <v>1.3</v>
+      </c>
+      <c r="BE271">
+        <v>8</v>
+      </c>
+      <c r="BF271">
+        <v>3.65</v>
+      </c>
+      <c r="BG271">
+        <v>1.14</v>
+      </c>
+      <c r="BH271">
+        <v>4.8</v>
+      </c>
+      <c r="BI271">
+        <v>1.26</v>
+      </c>
+      <c r="BJ271">
+        <v>3.4</v>
+      </c>
+      <c r="BK271">
+        <v>1.44</v>
+      </c>
+      <c r="BL271">
+        <v>2.55</v>
+      </c>
+      <c r="BM271">
+        <v>1.68</v>
+      </c>
+      <c r="BN271">
+        <v>2.02</v>
+      </c>
+      <c r="BO271">
+        <v>2.06</v>
+      </c>
+      <c r="BP271">
+        <v>1.66</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1694" uniqueCount="409">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -817,6 +817,9 @@
     <t>['11', '63']</t>
   </si>
   <si>
+    <t>['21', '43']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1599,7 +1602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP271"/>
+  <dimension ref="A1:BP272"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2061,7 +2064,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2473,7 +2476,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2885,7 +2888,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -3091,7 +3094,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3169,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ8">
         <v>1.08</v>
@@ -3503,7 +3506,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3915,7 +3918,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4614,7 +4617,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ15">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -5151,7 +5154,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5357,7 +5360,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -6181,7 +6184,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6387,7 +6390,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -7005,7 +7008,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7211,7 +7214,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7289,7 +7292,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ28">
         <v>1.5</v>
@@ -7417,7 +7420,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7829,7 +7832,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8035,7 +8038,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8447,7 +8450,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -8528,7 +8531,7 @@
         <v>1</v>
       </c>
       <c r="AQ34">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR34">
         <v>1.29</v>
@@ -9271,7 +9274,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9477,7 +9480,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9683,7 +9686,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9889,7 +9892,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -10095,7 +10098,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10173,7 +10176,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ42">
         <v>1.5</v>
@@ -10301,7 +10304,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -11949,7 +11952,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -12155,7 +12158,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12361,7 +12364,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12773,7 +12776,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -12854,7 +12857,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ55">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR55">
         <v>1.6</v>
@@ -13185,7 +13188,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13391,7 +13394,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13597,7 +13600,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13803,7 +13806,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -14009,7 +14012,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14215,7 +14218,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14627,7 +14630,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14833,7 +14836,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14911,7 +14914,7 @@
         <v>0.67</v>
       </c>
       <c r="AP65">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ65">
         <v>0.77</v>
@@ -15039,7 +15042,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -16069,7 +16072,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16481,7 +16484,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16687,7 +16690,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16893,7 +16896,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -17099,7 +17102,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17180,7 +17183,7 @@
         <v>0.31</v>
       </c>
       <c r="AQ76">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR76">
         <v>0.91</v>
@@ -17305,7 +17308,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17717,7 +17720,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17923,7 +17926,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18335,7 +18338,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18747,7 +18750,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18953,7 +18956,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -19159,7 +19162,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19571,7 +19574,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19983,7 +19986,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20061,7 +20064,7 @@
         <v>1.25</v>
       </c>
       <c r="AP90">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ90">
         <v>1.08</v>
@@ -20189,7 +20192,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -21094,7 +21097,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ95">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR95">
         <v>1.12</v>
@@ -21631,7 +21634,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21837,7 +21840,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -22043,7 +22046,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22455,7 +22458,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22661,7 +22664,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22945,7 +22948,7 @@
         <v>0.8</v>
       </c>
       <c r="AP104">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ104">
         <v>1.08</v>
@@ -23772,7 +23775,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ108">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR108">
         <v>1.48</v>
@@ -23897,7 +23900,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -24103,7 +24106,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24309,7 +24312,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q111">
         <v>3.25</v>
@@ -24515,7 +24518,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24721,7 +24724,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -25339,7 +25342,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25545,7 +25548,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25751,7 +25754,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25957,7 +25960,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -26163,7 +26166,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26369,7 +26372,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26575,7 +26578,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26781,7 +26784,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -27274,7 +27277,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ125">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR125">
         <v>1.7</v>
@@ -27399,7 +27402,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27605,7 +27608,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -27683,7 +27686,7 @@
         <v>1.33</v>
       </c>
       <c r="AP127">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ127">
         <v>1.86</v>
@@ -28223,7 +28226,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28635,7 +28638,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -29047,7 +29050,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29253,7 +29256,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -30695,7 +30698,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30901,7 +30904,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -31313,7 +31316,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31519,7 +31522,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31725,7 +31728,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31931,7 +31934,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -32137,7 +32140,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32421,7 +32424,7 @@
         <v>0.71</v>
       </c>
       <c r="AP150">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ150">
         <v>0.86</v>
@@ -32549,7 +32552,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -33042,7 +33045,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ153">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR153">
         <v>1.32</v>
@@ -33167,7 +33170,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33373,7 +33376,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33579,7 +33582,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33785,7 +33788,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33991,7 +33994,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34815,7 +34818,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -35021,7 +35024,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35099,7 +35102,7 @@
         <v>1.38</v>
       </c>
       <c r="AP163">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ163">
         <v>1.57</v>
@@ -35227,7 +35230,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35433,7 +35436,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35845,7 +35848,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36051,7 +36054,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36463,7 +36466,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36875,7 +36878,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37493,7 +37496,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -38111,7 +38114,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38192,7 +38195,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ178">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR178">
         <v>1.73</v>
@@ -38729,7 +38732,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38935,7 +38938,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39347,7 +39350,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39553,7 +39556,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39759,7 +39762,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -39837,7 +39840,7 @@
         <v>2.5</v>
       </c>
       <c r="AP186">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ186">
         <v>2.33</v>
@@ -40171,7 +40174,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40377,7 +40380,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40583,7 +40586,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40789,7 +40792,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -41201,7 +41204,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41282,7 +41285,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ193">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR193">
         <v>1.51</v>
@@ -41613,7 +41616,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41819,7 +41822,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -42231,7 +42234,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42437,7 +42440,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42643,7 +42646,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42849,7 +42852,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -43055,7 +43058,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43133,7 +43136,7 @@
         <v>1.44</v>
       </c>
       <c r="AP202">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ202">
         <v>1.69</v>
@@ -43261,7 +43264,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43467,7 +43470,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43673,7 +43676,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -44085,7 +44088,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44497,7 +44500,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44909,7 +44912,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45115,7 +45118,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45193,7 +45196,7 @@
         <v>1.3</v>
       </c>
       <c r="AP212">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ212">
         <v>1.69</v>
@@ -45321,7 +45324,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45527,7 +45530,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45733,7 +45736,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -45939,7 +45942,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -46145,7 +46148,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46351,7 +46354,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46557,7 +46560,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46763,7 +46766,7 @@
         <v>240</v>
       </c>
       <c r="P220" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q220">
         <v>1.73</v>
@@ -47175,7 +47178,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -47587,7 +47590,7 @@
         <v>107</v>
       </c>
       <c r="P224" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q224">
         <v>6</v>
@@ -47793,7 +47796,7 @@
         <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q225">
         <v>6.5</v>
@@ -47999,7 +48002,7 @@
         <v>243</v>
       </c>
       <c r="P226" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q226">
         <v>2.38</v>
@@ -48205,7 +48208,7 @@
         <v>155</v>
       </c>
       <c r="P227" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48411,7 +48414,7 @@
         <v>244</v>
       </c>
       <c r="P228" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q228">
         <v>1.91</v>
@@ -48492,7 +48495,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ228">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR228">
         <v>1.71</v>
@@ -48823,7 +48826,7 @@
         <v>91</v>
       </c>
       <c r="P230" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q230">
         <v>2.88</v>
@@ -49235,7 +49238,7 @@
         <v>95</v>
       </c>
       <c r="P232" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q232">
         <v>2.2</v>
@@ -49522,7 +49525,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ233">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR233">
         <v>1.37</v>
@@ -49647,7 +49650,7 @@
         <v>151</v>
       </c>
       <c r="P234" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q234">
         <v>2.6</v>
@@ -49853,7 +49856,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q235">
         <v>4.5</v>
@@ -50265,7 +50268,7 @@
         <v>91</v>
       </c>
       <c r="P237" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50471,7 +50474,7 @@
         <v>91</v>
       </c>
       <c r="P238" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q238">
         <v>2.75</v>
@@ -50883,7 +50886,7 @@
         <v>249</v>
       </c>
       <c r="P240" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q240">
         <v>1.8</v>
@@ -51089,7 +51092,7 @@
         <v>250</v>
       </c>
       <c r="P241" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q241">
         <v>6</v>
@@ -51501,7 +51504,7 @@
         <v>91</v>
       </c>
       <c r="P243" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q243">
         <v>9</v>
@@ -51707,7 +51710,7 @@
         <v>203</v>
       </c>
       <c r="P244" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q244">
         <v>5</v>
@@ -52197,7 +52200,7 @@
         <v>0.73</v>
       </c>
       <c r="AP246">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ246">
         <v>1.08</v>
@@ -52737,7 +52740,7 @@
         <v>254</v>
       </c>
       <c r="P249" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q249">
         <v>2.63</v>
@@ -52943,7 +52946,7 @@
         <v>255</v>
       </c>
       <c r="P250" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q250">
         <v>1.57</v>
@@ -53355,7 +53358,7 @@
         <v>256</v>
       </c>
       <c r="P252" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q252">
         <v>4</v>
@@ -53561,7 +53564,7 @@
         <v>91</v>
       </c>
       <c r="P253" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q253">
         <v>3.6</v>
@@ -53767,7 +53770,7 @@
         <v>257</v>
       </c>
       <c r="P254" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q254">
         <v>3.25</v>
@@ -53973,7 +53976,7 @@
         <v>91</v>
       </c>
       <c r="P255" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q255">
         <v>5</v>
@@ -54179,7 +54182,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q256">
         <v>3.75</v>
@@ -54385,7 +54388,7 @@
         <v>91</v>
       </c>
       <c r="P257" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q257">
         <v>1.73</v>
@@ -54797,7 +54800,7 @@
         <v>91</v>
       </c>
       <c r="P259" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q259">
         <v>2.75</v>
@@ -55003,7 +55006,7 @@
         <v>258</v>
       </c>
       <c r="P260" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q260">
         <v>3.1</v>
@@ -55209,7 +55212,7 @@
         <v>259</v>
       </c>
       <c r="P261" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q261">
         <v>2.38</v>
@@ -55415,7 +55418,7 @@
         <v>91</v>
       </c>
       <c r="P262" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q262">
         <v>3.1</v>
@@ -55621,7 +55624,7 @@
         <v>260</v>
       </c>
       <c r="P263" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q263">
         <v>3.2</v>
@@ -55827,7 +55830,7 @@
         <v>261</v>
       </c>
       <c r="P264" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q264">
         <v>3.5</v>
@@ -56651,7 +56654,7 @@
         <v>264</v>
       </c>
       <c r="P268" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q268">
         <v>2.05</v>
@@ -57426,6 +57429,212 @@
       </c>
       <c r="BP271">
         <v>1.66</v>
+      </c>
+    </row>
+    <row r="272" spans="1:68">
+      <c r="A272" s="1">
+        <v>271</v>
+      </c>
+      <c r="B272">
+        <v>7466943</v>
+      </c>
+      <c r="C272" t="s">
+        <v>68</v>
+      </c>
+      <c r="D272" t="s">
+        <v>69</v>
+      </c>
+      <c r="E272" s="2">
+        <v>45715.70833333334</v>
+      </c>
+      <c r="F272">
+        <v>27</v>
+      </c>
+      <c r="G272" t="s">
+        <v>76</v>
+      </c>
+      <c r="H272" t="s">
+        <v>79</v>
+      </c>
+      <c r="I272">
+        <v>2</v>
+      </c>
+      <c r="J272">
+        <v>0</v>
+      </c>
+      <c r="K272">
+        <v>2</v>
+      </c>
+      <c r="L272">
+        <v>2</v>
+      </c>
+      <c r="M272">
+        <v>0</v>
+      </c>
+      <c r="N272">
+        <v>2</v>
+      </c>
+      <c r="O272" t="s">
+        <v>267</v>
+      </c>
+      <c r="P272" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q272">
+        <v>2.2</v>
+      </c>
+      <c r="R272">
+        <v>2.38</v>
+      </c>
+      <c r="S272">
+        <v>5</v>
+      </c>
+      <c r="T272">
+        <v>1.3</v>
+      </c>
+      <c r="U272">
+        <v>3.4</v>
+      </c>
+      <c r="V272">
+        <v>2.5</v>
+      </c>
+      <c r="W272">
+        <v>1.5</v>
+      </c>
+      <c r="X272">
+        <v>6</v>
+      </c>
+      <c r="Y272">
+        <v>1.13</v>
+      </c>
+      <c r="Z272">
+        <v>1.73</v>
+      </c>
+      <c r="AA272">
+        <v>4</v>
+      </c>
+      <c r="AB272">
+        <v>4.2</v>
+      </c>
+      <c r="AC272">
+        <v>1.03</v>
+      </c>
+      <c r="AD272">
+        <v>12</v>
+      </c>
+      <c r="AE272">
+        <v>1.2</v>
+      </c>
+      <c r="AF272">
+        <v>4.2</v>
+      </c>
+      <c r="AG272">
+        <v>1.7</v>
+      </c>
+      <c r="AH272">
+        <v>2.05</v>
+      </c>
+      <c r="AI272">
+        <v>1.7</v>
+      </c>
+      <c r="AJ272">
+        <v>2.05</v>
+      </c>
+      <c r="AK272">
+        <v>1.17</v>
+      </c>
+      <c r="AL272">
+        <v>1.23</v>
+      </c>
+      <c r="AM272">
+        <v>2.2</v>
+      </c>
+      <c r="AN272">
+        <v>1.08</v>
+      </c>
+      <c r="AO272">
+        <v>0.67</v>
+      </c>
+      <c r="AP272">
+        <v>1.21</v>
+      </c>
+      <c r="AQ272">
+        <v>0.62</v>
+      </c>
+      <c r="AR272">
+        <v>1.27</v>
+      </c>
+      <c r="AS272">
+        <v>1.03</v>
+      </c>
+      <c r="AT272">
+        <v>2.3</v>
+      </c>
+      <c r="AU272">
+        <v>3</v>
+      </c>
+      <c r="AV272">
+        <v>3</v>
+      </c>
+      <c r="AW272">
+        <v>6</v>
+      </c>
+      <c r="AX272">
+        <v>8</v>
+      </c>
+      <c r="AY272">
+        <v>11</v>
+      </c>
+      <c r="AZ272">
+        <v>16</v>
+      </c>
+      <c r="BA272">
+        <v>3</v>
+      </c>
+      <c r="BB272">
+        <v>3</v>
+      </c>
+      <c r="BC272">
+        <v>6</v>
+      </c>
+      <c r="BD272">
+        <v>1.38</v>
+      </c>
+      <c r="BE272">
+        <v>7</v>
+      </c>
+      <c r="BF272">
+        <v>3.4</v>
+      </c>
+      <c r="BG272">
+        <v>1.2</v>
+      </c>
+      <c r="BH272">
+        <v>3.9</v>
+      </c>
+      <c r="BI272">
+        <v>1.37</v>
+      </c>
+      <c r="BJ272">
+        <v>2.8</v>
+      </c>
+      <c r="BK272">
+        <v>1.61</v>
+      </c>
+      <c r="BL272">
+        <v>2.15</v>
+      </c>
+      <c r="BM272">
+        <v>1.97</v>
+      </c>
+      <c r="BN272">
+        <v>1.72</v>
+      </c>
+      <c r="BO272">
+        <v>2.48</v>
+      </c>
+      <c r="BP272">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1694" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="414">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -820,6 +820,18 @@
     <t>['21', '43']</t>
   </si>
   <si>
+    <t>['83']</t>
+  </si>
+  <si>
+    <t>['51', '54', '88']</t>
+  </si>
+  <si>
+    <t>['41', '90+8']</t>
+  </si>
+  <si>
+    <t>['40']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1242,6 +1254,9 @@
   <si>
     <t>['4', '45+2']</t>
   </si>
+  <si>
+    <t>['45+1']</t>
+  </si>
 </sst>
 </file>
 
@@ -1602,7 +1617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP272"/>
+  <dimension ref="A1:BP278"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1939,7 +1954,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ2">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2064,7 +2079,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2476,7 +2491,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2763,7 +2778,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ6">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2888,7 +2903,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2966,7 +2981,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ7">
         <v>1.57</v>
@@ -3094,7 +3109,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3175,7 +3190,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ8">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3378,7 +3393,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ9">
         <v>1.69</v>
@@ -3506,7 +3521,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3587,7 +3602,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ10">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3918,7 +3933,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -3996,7 +4011,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ12">
         <v>1.08</v>
@@ -4205,7 +4220,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ13">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4408,7 +4423,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ14">
         <v>1.23</v>
@@ -5029,7 +5044,7 @@
         <v>2</v>
       </c>
       <c r="AQ17">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5154,7 +5169,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5360,7 +5375,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5438,7 +5453,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ19">
         <v>1.5</v>
@@ -5850,7 +5865,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ21">
         <v>1.08</v>
@@ -6184,7 +6199,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6265,7 +6280,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ23">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR23">
         <v>0.86</v>
@@ -6390,7 +6405,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6471,7 +6486,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ24">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR24">
         <v>0.77</v>
@@ -6674,7 +6689,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ25">
         <v>0.86</v>
@@ -6880,10 +6895,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ26">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR26">
         <v>1.29</v>
@@ -7008,7 +7023,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7214,7 +7229,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7295,7 +7310,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ28">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR28">
         <v>1.25</v>
@@ -7420,7 +7435,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7832,7 +7847,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8038,7 +8053,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8322,10 +8337,10 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ33">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR33">
         <v>1.6</v>
@@ -8450,7 +8465,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -8528,7 +8543,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ34">
         <v>0.62</v>
@@ -8940,7 +8955,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ36">
         <v>1.64</v>
@@ -9274,7 +9289,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9355,7 +9370,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ38">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR38">
         <v>0.92</v>
@@ -9480,7 +9495,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9686,7 +9701,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9892,7 +9907,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9970,7 +9985,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ41">
         <v>1.5</v>
@@ -10098,7 +10113,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10304,7 +10319,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10591,7 +10606,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ44">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR44">
         <v>1</v>
@@ -10794,7 +10809,7 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ45">
         <v>1.57</v>
@@ -11003,7 +11018,7 @@
         <v>0.31</v>
       </c>
       <c r="AQ46">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR46">
         <v>0.83</v>
@@ -11618,7 +11633,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ49">
         <v>1.08</v>
@@ -11824,7 +11839,7 @@
         <v>3</v>
       </c>
       <c r="AP50">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ50">
         <v>1.64</v>
@@ -11952,7 +11967,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -12158,7 +12173,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12239,7 +12254,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ52">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR52">
         <v>0.75</v>
@@ -12364,7 +12379,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12442,10 +12457,10 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ53">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR53">
         <v>1.65</v>
@@ -12776,7 +12791,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -13060,7 +13075,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ56">
         <v>1.23</v>
@@ -13188,7 +13203,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13394,7 +13409,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13472,7 +13487,7 @@
         <v>3</v>
       </c>
       <c r="AP58">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ58">
         <v>2.33</v>
@@ -13600,7 +13615,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13681,7 +13696,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ59">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR59">
         <v>0.95</v>
@@ -13806,7 +13821,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -14012,7 +14027,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14093,7 +14108,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ61">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR61">
         <v>1.76</v>
@@ -14218,7 +14233,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14296,7 +14311,7 @@
         <v>3</v>
       </c>
       <c r="AP62">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ62">
         <v>2.33</v>
@@ -14630,7 +14645,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14711,7 +14726,7 @@
         <v>2</v>
       </c>
       <c r="AQ64">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR64">
         <v>2.4</v>
@@ -14836,7 +14851,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14917,7 +14932,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ65">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR65">
         <v>1.33</v>
@@ -15042,7 +15057,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -15120,7 +15135,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ66">
         <v>0.86</v>
@@ -15329,7 +15344,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ67">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR67">
         <v>2.4</v>
@@ -16072,7 +16087,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16150,7 +16165,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ71">
         <v>1.23</v>
@@ -16484,7 +16499,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16565,7 +16580,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ73">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR73">
         <v>2.01</v>
@@ -16690,7 +16705,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16896,7 +16911,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -17102,7 +17117,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17308,7 +17323,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17389,7 +17404,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ77">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR77">
         <v>1.11</v>
@@ -17720,7 +17735,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17798,10 +17813,10 @@
         <v>2.33</v>
       </c>
       <c r="AP79">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ79">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR79">
         <v>1.27</v>
@@ -17926,7 +17941,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18004,7 +18019,7 @@
         <v>3</v>
       </c>
       <c r="AP80">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ80">
         <v>1.5</v>
@@ -18210,7 +18225,7 @@
         <v>0.33</v>
       </c>
       <c r="AP81">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ81">
         <v>1.69</v>
@@ -18338,7 +18353,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18625,7 +18640,7 @@
         <v>2</v>
       </c>
       <c r="AQ83">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR83">
         <v>2.31</v>
@@ -18750,7 +18765,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18828,7 +18843,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ84">
         <v>0.86</v>
@@ -18956,7 +18971,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -19162,7 +19177,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19240,10 +19255,10 @@
         <v>0.5</v>
       </c>
       <c r="AP86">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ86">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR86">
         <v>1.7</v>
@@ -19449,7 +19464,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ87">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR87">
         <v>1.26</v>
@@ -19574,7 +19589,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19858,7 +19873,7 @@
         <v>1</v>
       </c>
       <c r="AP89">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ89">
         <v>1.23</v>
@@ -19986,7 +20001,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20192,7 +20207,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20685,7 +20700,7 @@
         <v>0.31</v>
       </c>
       <c r="AQ93">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR93">
         <v>1.09</v>
@@ -20891,7 +20906,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ94">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR94">
         <v>1.6</v>
@@ -21300,7 +21315,7 @@
         <v>1.75</v>
       </c>
       <c r="AP96">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ96">
         <v>1.57</v>
@@ -21506,7 +21521,7 @@
         <v>1.25</v>
       </c>
       <c r="AP97">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ97">
         <v>1.23</v>
@@ -21634,7 +21649,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21712,7 +21727,7 @@
         <v>0.25</v>
       </c>
       <c r="AP98">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ98">
         <v>1.69</v>
@@ -21840,7 +21855,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -21921,7 +21936,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ99">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR99">
         <v>1.99</v>
@@ -22046,7 +22061,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22458,7 +22473,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22536,7 +22551,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ102">
         <v>1.57</v>
@@ -22664,7 +22679,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22742,10 +22757,10 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ103">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR103">
         <v>1.37</v>
@@ -22951,7 +22966,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ104">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR104">
         <v>1.57</v>
@@ -23154,10 +23169,10 @@
         <v>0</v>
       </c>
       <c r="AP105">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ105">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR105">
         <v>1.17</v>
@@ -23360,10 +23375,10 @@
         <v>2</v>
       </c>
       <c r="AP106">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ106">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR106">
         <v>1.54</v>
@@ -23566,10 +23581,10 @@
         <v>2</v>
       </c>
       <c r="AP107">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ107">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR107">
         <v>1.75</v>
@@ -23900,7 +23915,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -23978,7 +23993,7 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ109">
         <v>1.5</v>
@@ -24106,7 +24121,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24187,7 +24202,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ110">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR110">
         <v>1.96</v>
@@ -24312,7 +24327,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q111">
         <v>3.25</v>
@@ -24518,7 +24533,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24724,7 +24739,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -25342,7 +25357,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25548,7 +25563,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25754,7 +25769,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25960,7 +25975,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -26166,7 +26181,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26372,7 +26387,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26578,7 +26593,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26656,10 +26671,10 @@
         <v>0</v>
       </c>
       <c r="AP122">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ122">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR122">
         <v>1.46</v>
@@ -26784,7 +26799,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -26862,7 +26877,7 @@
         <v>0.83</v>
       </c>
       <c r="AP123">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ123">
         <v>1.57</v>
@@ -27068,10 +27083,10 @@
         <v>0.83</v>
       </c>
       <c r="AP124">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ124">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR124">
         <v>1.52</v>
@@ -27274,7 +27289,7 @@
         <v>0.83</v>
       </c>
       <c r="AP125">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ125">
         <v>0.62</v>
@@ -27402,7 +27417,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27480,7 +27495,7 @@
         <v>1.33</v>
       </c>
       <c r="AP126">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ126">
         <v>1.5</v>
@@ -27608,7 +27623,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -27895,7 +27910,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ128">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR128">
         <v>1.43</v>
@@ -28101,7 +28116,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ129">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR129">
         <v>1.64</v>
@@ -28226,7 +28241,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28307,7 +28322,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ130">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR130">
         <v>1.95</v>
@@ -28510,10 +28525,10 @@
         <v>1.67</v>
       </c>
       <c r="AP131">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ131">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR131">
         <v>1.72</v>
@@ -28638,7 +28653,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -29050,7 +29065,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29256,7 +29271,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -30698,7 +30713,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30776,10 +30791,10 @@
         <v>1.43</v>
       </c>
       <c r="AP142">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ142">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR142">
         <v>1.38</v>
@@ -30904,7 +30919,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -30982,7 +30997,7 @@
         <v>1.29</v>
       </c>
       <c r="AP143">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ143">
         <v>1.5</v>
@@ -31191,7 +31206,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ144">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR144">
         <v>1.54</v>
@@ -31316,7 +31331,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31522,7 +31537,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31728,7 +31743,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31934,7 +31949,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -32140,7 +32155,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32552,7 +32567,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -32630,10 +32645,10 @@
         <v>0.71</v>
       </c>
       <c r="AP151">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ151">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR151">
         <v>1.14</v>
@@ -32839,7 +32854,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ152">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR152">
         <v>2.08</v>
@@ -33170,7 +33185,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33248,10 +33263,10 @@
         <v>1.29</v>
       </c>
       <c r="AP154">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ154">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR154">
         <v>1.76</v>
@@ -33376,7 +33391,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33454,10 +33469,10 @@
         <v>1.43</v>
       </c>
       <c r="AP155">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ155">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR155">
         <v>1.52</v>
@@ -33582,7 +33597,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33660,7 +33675,7 @@
         <v>0.86</v>
       </c>
       <c r="AP156">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ156">
         <v>1.69</v>
@@ -33788,7 +33803,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33994,7 +34009,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34693,7 +34708,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ161">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR161">
         <v>1.54</v>
@@ -34818,7 +34833,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -34896,7 +34911,7 @@
         <v>1.75</v>
       </c>
       <c r="AP162">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ162">
         <v>1.64</v>
@@ -35024,7 +35039,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35230,7 +35245,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35436,7 +35451,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35514,7 +35529,7 @@
         <v>1.5</v>
       </c>
       <c r="AP165">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ165">
         <v>1.86</v>
@@ -35723,7 +35738,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ166">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR166">
         <v>1.59</v>
@@ -35848,7 +35863,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36054,7 +36069,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36466,7 +36481,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36753,7 +36768,7 @@
         <v>2</v>
       </c>
       <c r="AQ171">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR171">
         <v>2.11</v>
@@ -36878,7 +36893,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37162,7 +37177,7 @@
         <v>1.25</v>
       </c>
       <c r="AP173">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ173">
         <v>1.23</v>
@@ -37371,7 +37386,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ174">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR174">
         <v>1.48</v>
@@ -37496,7 +37511,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -37577,7 +37592,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ175">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR175">
         <v>1.78</v>
@@ -37986,7 +38001,7 @@
         <v>1.13</v>
       </c>
       <c r="AP177">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ177">
         <v>1.08</v>
@@ -38114,7 +38129,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38192,7 +38207,7 @@
         <v>0.63</v>
       </c>
       <c r="AP178">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ178">
         <v>0.62</v>
@@ -38398,7 +38413,7 @@
         <v>0.13</v>
       </c>
       <c r="AP179">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ179">
         <v>1.08</v>
@@ -38607,7 +38622,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ180">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR180">
         <v>2.03</v>
@@ -38732,7 +38747,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38813,7 +38828,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ181">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR181">
         <v>1.08</v>
@@ -38938,7 +38953,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39222,10 +39237,10 @@
         <v>0.22</v>
       </c>
       <c r="AP183">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ183">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR183">
         <v>1.34</v>
@@ -39350,7 +39365,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39556,7 +39571,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39762,7 +39777,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -40174,7 +40189,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40380,7 +40395,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40586,7 +40601,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40664,7 +40679,7 @@
         <v>1.67</v>
       </c>
       <c r="AP190">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ190">
         <v>1.86</v>
@@ -40792,7 +40807,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -41079,7 +41094,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ192">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR192">
         <v>1.73</v>
@@ -41204,7 +41219,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41488,7 +41503,7 @@
         <v>2</v>
       </c>
       <c r="AP194">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ194">
         <v>1.5</v>
@@ -41616,7 +41631,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41822,7 +41837,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -42106,7 +42121,7 @@
         <v>1.8</v>
       </c>
       <c r="AP197">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ197">
         <v>1.86</v>
@@ -42234,7 +42249,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42315,7 +42330,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ198">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR198">
         <v>1.57</v>
@@ -42440,7 +42455,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42518,7 +42533,7 @@
         <v>1</v>
       </c>
       <c r="AP199">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ199">
         <v>1.08</v>
@@ -42646,7 +42661,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42724,7 +42739,7 @@
         <v>2</v>
       </c>
       <c r="AP200">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ200">
         <v>1.64</v>
@@ -42852,7 +42867,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -43058,7 +43073,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43139,7 +43154,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ202">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR202">
         <v>1.35</v>
@@ -43264,7 +43279,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43342,10 +43357,10 @@
         <v>1.4</v>
       </c>
       <c r="AP203">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ203">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR203">
         <v>1.57</v>
@@ -43470,7 +43485,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43548,7 +43563,7 @@
         <v>2.56</v>
       </c>
       <c r="AP204">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ204">
         <v>2.33</v>
@@ -43676,7 +43691,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -44088,7 +44103,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44169,7 +44184,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ207">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR207">
         <v>1.34</v>
@@ -44500,7 +44515,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44787,7 +44802,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ210">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR210">
         <v>1.48</v>
@@ -44912,7 +44927,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45118,7 +45133,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45324,7 +45339,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45402,7 +45417,7 @@
         <v>2.4</v>
       </c>
       <c r="AP213">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ213">
         <v>2.33</v>
@@ -45530,7 +45545,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45611,7 +45626,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ214">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR214">
         <v>1.2</v>
@@ -45736,7 +45751,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -45817,7 +45832,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ215">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR215">
         <v>1.97</v>
@@ -45942,7 +45957,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -46148,7 +46163,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46226,10 +46241,10 @@
         <v>0.18</v>
       </c>
       <c r="AP217">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ217">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR217">
         <v>1.44</v>
@@ -46354,7 +46369,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46560,7 +46575,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46641,7 +46656,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ219">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR219">
         <v>1.13</v>
@@ -46766,7 +46781,7 @@
         <v>240</v>
       </c>
       <c r="P220" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q220">
         <v>1.73</v>
@@ -47178,7 +47193,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -47256,10 +47271,10 @@
         <v>0.7</v>
       </c>
       <c r="AP222">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ222">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR222">
         <v>1.58</v>
@@ -47462,10 +47477,10 @@
         <v>0.9</v>
       </c>
       <c r="AP223">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ223">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR223">
         <v>1.79</v>
@@ -47590,7 +47605,7 @@
         <v>107</v>
       </c>
       <c r="P224" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="Q224">
         <v>6</v>
@@ -47796,7 +47811,7 @@
         <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q225">
         <v>6.5</v>
@@ -47874,7 +47889,7 @@
         <v>1.73</v>
       </c>
       <c r="AP225">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ225">
         <v>1.86</v>
@@ -48002,7 +48017,7 @@
         <v>243</v>
       </c>
       <c r="P226" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="Q226">
         <v>2.38</v>
@@ -48208,7 +48223,7 @@
         <v>155</v>
       </c>
       <c r="P227" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48286,7 +48301,7 @@
         <v>0.5</v>
       </c>
       <c r="AP227">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ227">
         <v>1.08</v>
@@ -48414,7 +48429,7 @@
         <v>244</v>
       </c>
       <c r="P228" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="Q228">
         <v>1.91</v>
@@ -48826,7 +48841,7 @@
         <v>91</v>
       </c>
       <c r="P230" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="Q230">
         <v>2.88</v>
@@ -49110,7 +49125,7 @@
         <v>1.58</v>
       </c>
       <c r="AP231">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ231">
         <v>1.57</v>
@@ -49238,7 +49253,7 @@
         <v>95</v>
       </c>
       <c r="P232" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="Q232">
         <v>2.2</v>
@@ -49319,7 +49334,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ232">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR232">
         <v>1.61</v>
@@ -49650,7 +49665,7 @@
         <v>151</v>
       </c>
       <c r="P234" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="Q234">
         <v>2.6</v>
@@ -49731,7 +49746,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ234">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR234">
         <v>1.13</v>
@@ -49856,7 +49871,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="Q235">
         <v>4.5</v>
@@ -50140,10 +50155,10 @@
         <v>1.27</v>
       </c>
       <c r="AP236">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ236">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR236">
         <v>1.21</v>
@@ -50268,7 +50283,7 @@
         <v>91</v>
       </c>
       <c r="P237" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50346,7 +50361,7 @@
         <v>0.91</v>
       </c>
       <c r="AP237">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ237">
         <v>1.23</v>
@@ -50474,7 +50489,7 @@
         <v>91</v>
       </c>
       <c r="P238" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="Q238">
         <v>2.75</v>
@@ -50761,7 +50776,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ239">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR239">
         <v>2</v>
@@ -50886,7 +50901,7 @@
         <v>249</v>
       </c>
       <c r="P240" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="Q240">
         <v>1.8</v>
@@ -51092,7 +51107,7 @@
         <v>250</v>
       </c>
       <c r="P241" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="Q241">
         <v>6</v>
@@ -51376,7 +51391,7 @@
         <v>1.75</v>
       </c>
       <c r="AP242">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ242">
         <v>1.5</v>
@@ -51504,7 +51519,7 @@
         <v>91</v>
       </c>
       <c r="P243" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="Q243">
         <v>9</v>
@@ -51710,7 +51725,7 @@
         <v>203</v>
       </c>
       <c r="P244" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q244">
         <v>5</v>
@@ -52615,7 +52630,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ248">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR248">
         <v>1.52</v>
@@ -52740,7 +52755,7 @@
         <v>254</v>
       </c>
       <c r="P249" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="Q249">
         <v>2.63</v>
@@ -52818,10 +52833,10 @@
         <v>0.91</v>
       </c>
       <c r="AP249">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ249">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR249">
         <v>1.43</v>
@@ -52946,7 +52961,7 @@
         <v>255</v>
       </c>
       <c r="P250" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="Q250">
         <v>1.57</v>
@@ -53024,7 +53039,7 @@
         <v>0.75</v>
       </c>
       <c r="AP250">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ250">
         <v>0.86</v>
@@ -53358,7 +53373,7 @@
         <v>256</v>
       </c>
       <c r="P252" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="Q252">
         <v>4</v>
@@ -53564,7 +53579,7 @@
         <v>91</v>
       </c>
       <c r="P253" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="Q253">
         <v>3.6</v>
@@ -53770,7 +53785,7 @@
         <v>257</v>
       </c>
       <c r="P254" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="Q254">
         <v>3.25</v>
@@ -53976,7 +53991,7 @@
         <v>91</v>
       </c>
       <c r="P255" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="Q255">
         <v>5</v>
@@ -54182,7 +54197,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="Q256">
         <v>3.75</v>
@@ -54388,7 +54403,7 @@
         <v>91</v>
       </c>
       <c r="P257" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="Q257">
         <v>1.73</v>
@@ -54800,7 +54815,7 @@
         <v>91</v>
       </c>
       <c r="P259" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="Q259">
         <v>2.75</v>
@@ -55006,7 +55021,7 @@
         <v>258</v>
       </c>
       <c r="P260" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q260">
         <v>3.1</v>
@@ -55212,7 +55227,7 @@
         <v>259</v>
       </c>
       <c r="P261" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="Q261">
         <v>2.38</v>
@@ -55418,7 +55433,7 @@
         <v>91</v>
       </c>
       <c r="P262" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="Q262">
         <v>3.1</v>
@@ -55624,7 +55639,7 @@
         <v>260</v>
       </c>
       <c r="P263" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q263">
         <v>3.2</v>
@@ -55702,10 +55717,10 @@
         <v>1.17</v>
       </c>
       <c r="AP263">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ263">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR263">
         <v>1.48</v>
@@ -55830,7 +55845,7 @@
         <v>261</v>
       </c>
       <c r="P264" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="Q264">
         <v>3.5</v>
@@ -55908,10 +55923,10 @@
         <v>1.58</v>
       </c>
       <c r="AP264">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AQ264">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR264">
         <v>1.21</v>
@@ -56114,7 +56129,7 @@
         <v>1.69</v>
       </c>
       <c r="AP265">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ265">
         <v>1.57</v>
@@ -56323,7 +56338,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ266">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR266">
         <v>1.91</v>
@@ -56529,7 +56544,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ267">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR267">
         <v>1.78</v>
@@ -56654,7 +56669,7 @@
         <v>264</v>
       </c>
       <c r="P268" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="Q268">
         <v>2.05</v>
@@ -56735,7 +56750,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ268">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR268">
         <v>1.55</v>
@@ -56938,10 +56953,10 @@
         <v>1.08</v>
       </c>
       <c r="AP269">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ269">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR269">
         <v>1.65</v>
@@ -57144,7 +57159,7 @@
         <v>1.92</v>
       </c>
       <c r="AP270">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ270">
         <v>1.86</v>
@@ -57350,7 +57365,7 @@
         <v>1.62</v>
       </c>
       <c r="AP271">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ271">
         <v>1.5</v>
@@ -57635,6 +57650,1242 @@
       </c>
       <c r="BP272">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="273" spans="1:68">
+      <c r="A273" s="1">
+        <v>272</v>
+      </c>
+      <c r="B273">
+        <v>7466955</v>
+      </c>
+      <c r="C273" t="s">
+        <v>68</v>
+      </c>
+      <c r="D273" t="s">
+        <v>69</v>
+      </c>
+      <c r="E273" s="2">
+        <v>45724.39583333334</v>
+      </c>
+      <c r="F273">
+        <v>28</v>
+      </c>
+      <c r="G273" t="s">
+        <v>75</v>
+      </c>
+      <c r="H273" t="s">
+        <v>85</v>
+      </c>
+      <c r="I273">
+        <v>0</v>
+      </c>
+      <c r="J273">
+        <v>0</v>
+      </c>
+      <c r="K273">
+        <v>0</v>
+      </c>
+      <c r="L273">
+        <v>1</v>
+      </c>
+      <c r="M273">
+        <v>0</v>
+      </c>
+      <c r="N273">
+        <v>1</v>
+      </c>
+      <c r="O273" t="s">
+        <v>268</v>
+      </c>
+      <c r="P273" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q273">
+        <v>4</v>
+      </c>
+      <c r="R273">
+        <v>2.38</v>
+      </c>
+      <c r="S273">
+        <v>2.5</v>
+      </c>
+      <c r="T273">
+        <v>1.3</v>
+      </c>
+      <c r="U273">
+        <v>3.4</v>
+      </c>
+      <c r="V273">
+        <v>2.5</v>
+      </c>
+      <c r="W273">
+        <v>1.5</v>
+      </c>
+      <c r="X273">
+        <v>6</v>
+      </c>
+      <c r="Y273">
+        <v>1.13</v>
+      </c>
+      <c r="Z273">
+        <v>3.6</v>
+      </c>
+      <c r="AA273">
+        <v>3.7</v>
+      </c>
+      <c r="AB273">
+        <v>1.95</v>
+      </c>
+      <c r="AC273">
+        <v>1.03</v>
+      </c>
+      <c r="AD273">
+        <v>16</v>
+      </c>
+      <c r="AE273">
+        <v>1.2</v>
+      </c>
+      <c r="AF273">
+        <v>4.85</v>
+      </c>
+      <c r="AG273">
+        <v>1.57</v>
+      </c>
+      <c r="AH273">
+        <v>2.31</v>
+      </c>
+      <c r="AI273">
+        <v>1.57</v>
+      </c>
+      <c r="AJ273">
+        <v>2.25</v>
+      </c>
+      <c r="AK273">
+        <v>1.85</v>
+      </c>
+      <c r="AL273">
+        <v>1.26</v>
+      </c>
+      <c r="AM273">
+        <v>1.27</v>
+      </c>
+      <c r="AN273">
+        <v>1.92</v>
+      </c>
+      <c r="AO273">
+        <v>1.5</v>
+      </c>
+      <c r="AP273">
+        <v>2</v>
+      </c>
+      <c r="AQ273">
+        <v>1.4</v>
+      </c>
+      <c r="AR273">
+        <v>1.46</v>
+      </c>
+      <c r="AS273">
+        <v>1.8</v>
+      </c>
+      <c r="AT273">
+        <v>3.26</v>
+      </c>
+      <c r="AU273">
+        <v>5</v>
+      </c>
+      <c r="AV273">
+        <v>4</v>
+      </c>
+      <c r="AW273">
+        <v>5</v>
+      </c>
+      <c r="AX273">
+        <v>11</v>
+      </c>
+      <c r="AY273">
+        <v>12</v>
+      </c>
+      <c r="AZ273">
+        <v>19</v>
+      </c>
+      <c r="BA273">
+        <v>3</v>
+      </c>
+      <c r="BB273">
+        <v>2</v>
+      </c>
+      <c r="BC273">
+        <v>5</v>
+      </c>
+      <c r="BD273">
+        <v>2.9</v>
+      </c>
+      <c r="BE273">
+        <v>7</v>
+      </c>
+      <c r="BF273">
+        <v>1.47</v>
+      </c>
+      <c r="BG273">
+        <v>1.16</v>
+      </c>
+      <c r="BH273">
+        <v>4.5</v>
+      </c>
+      <c r="BI273">
+        <v>1.28</v>
+      </c>
+      <c r="BJ273">
+        <v>3.2</v>
+      </c>
+      <c r="BK273">
+        <v>1.48</v>
+      </c>
+      <c r="BL273">
+        <v>2.45</v>
+      </c>
+      <c r="BM273">
+        <v>1.73</v>
+      </c>
+      <c r="BN273">
+        <v>1.96</v>
+      </c>
+      <c r="BO273">
+        <v>2.12</v>
+      </c>
+      <c r="BP273">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="274" spans="1:68">
+      <c r="A274" s="1">
+        <v>273</v>
+      </c>
+      <c r="B274">
+        <v>7466953</v>
+      </c>
+      <c r="C274" t="s">
+        <v>68</v>
+      </c>
+      <c r="D274" t="s">
+        <v>69</v>
+      </c>
+      <c r="E274" s="2">
+        <v>45724.5</v>
+      </c>
+      <c r="F274">
+        <v>28</v>
+      </c>
+      <c r="G274" t="s">
+        <v>89</v>
+      </c>
+      <c r="H274" t="s">
+        <v>84</v>
+      </c>
+      <c r="I274">
+        <v>0</v>
+      </c>
+      <c r="J274">
+        <v>1</v>
+      </c>
+      <c r="K274">
+        <v>1</v>
+      </c>
+      <c r="L274">
+        <v>3</v>
+      </c>
+      <c r="M274">
+        <v>1</v>
+      </c>
+      <c r="N274">
+        <v>4</v>
+      </c>
+      <c r="O274" t="s">
+        <v>269</v>
+      </c>
+      <c r="P274" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q274">
+        <v>1.4</v>
+      </c>
+      <c r="R274">
+        <v>3.6</v>
+      </c>
+      <c r="S274">
+        <v>12</v>
+      </c>
+      <c r="T274">
+        <v>1.14</v>
+      </c>
+      <c r="U274">
+        <v>5.5</v>
+      </c>
+      <c r="V274">
+        <v>1.73</v>
+      </c>
+      <c r="W274">
+        <v>2</v>
+      </c>
+      <c r="X274">
+        <v>3.25</v>
+      </c>
+      <c r="Y274">
+        <v>1.33</v>
+      </c>
+      <c r="Z274">
+        <v>1.1</v>
+      </c>
+      <c r="AA274">
+        <v>12</v>
+      </c>
+      <c r="AB274">
+        <v>16</v>
+      </c>
+      <c r="AC274">
+        <v>1.01</v>
+      </c>
+      <c r="AD274">
+        <v>41</v>
+      </c>
+      <c r="AE274">
+        <v>1.05</v>
+      </c>
+      <c r="AF274">
+        <v>11</v>
+      </c>
+      <c r="AG274">
+        <v>1.23</v>
+      </c>
+      <c r="AH274">
+        <v>3.9</v>
+      </c>
+      <c r="AI274">
+        <v>1.91</v>
+      </c>
+      <c r="AJ274">
+        <v>1.91</v>
+      </c>
+      <c r="AK274">
+        <v>1.01</v>
+      </c>
+      <c r="AL274">
+        <v>1.06</v>
+      </c>
+      <c r="AM274">
+        <v>6.5</v>
+      </c>
+      <c r="AN274">
+        <v>2.46</v>
+      </c>
+      <c r="AO274">
+        <v>0.36</v>
+      </c>
+      <c r="AP274">
+        <v>2.5</v>
+      </c>
+      <c r="AQ274">
+        <v>0.33</v>
+      </c>
+      <c r="AR274">
+        <v>1.79</v>
+      </c>
+      <c r="AS274">
+        <v>1.05</v>
+      </c>
+      <c r="AT274">
+        <v>2.84</v>
+      </c>
+      <c r="AU274">
+        <v>8</v>
+      </c>
+      <c r="AV274">
+        <v>5</v>
+      </c>
+      <c r="AW274">
+        <v>21</v>
+      </c>
+      <c r="AX274">
+        <v>2</v>
+      </c>
+      <c r="AY274">
+        <v>30</v>
+      </c>
+      <c r="AZ274">
+        <v>7</v>
+      </c>
+      <c r="BA274">
+        <v>6</v>
+      </c>
+      <c r="BB274">
+        <v>4</v>
+      </c>
+      <c r="BC274">
+        <v>10</v>
+      </c>
+      <c r="BD274">
+        <v>1.09</v>
+      </c>
+      <c r="BE274">
+        <v>12</v>
+      </c>
+      <c r="BF274">
+        <v>7</v>
+      </c>
+      <c r="BG274">
+        <v>1.13</v>
+      </c>
+      <c r="BH274">
+        <v>4.9</v>
+      </c>
+      <c r="BI274">
+        <v>1.24</v>
+      </c>
+      <c r="BJ274">
+        <v>3.55</v>
+      </c>
+      <c r="BK274">
+        <v>1.41</v>
+      </c>
+      <c r="BL274">
+        <v>2.65</v>
+      </c>
+      <c r="BM274">
+        <v>1.65</v>
+      </c>
+      <c r="BN274">
+        <v>2.08</v>
+      </c>
+      <c r="BO274">
+        <v>1.97</v>
+      </c>
+      <c r="BP274">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="275" spans="1:68">
+      <c r="A275" s="1">
+        <v>274</v>
+      </c>
+      <c r="B275">
+        <v>7466950</v>
+      </c>
+      <c r="C275" t="s">
+        <v>68</v>
+      </c>
+      <c r="D275" t="s">
+        <v>69</v>
+      </c>
+      <c r="E275" s="2">
+        <v>45724.5</v>
+      </c>
+      <c r="F275">
+        <v>28</v>
+      </c>
+      <c r="G275" t="s">
+        <v>80</v>
+      </c>
+      <c r="H275" t="s">
+        <v>83</v>
+      </c>
+      <c r="I275">
+        <v>1</v>
+      </c>
+      <c r="J275">
+        <v>1</v>
+      </c>
+      <c r="K275">
+        <v>2</v>
+      </c>
+      <c r="L275">
+        <v>2</v>
+      </c>
+      <c r="M275">
+        <v>1</v>
+      </c>
+      <c r="N275">
+        <v>3</v>
+      </c>
+      <c r="O275" t="s">
+        <v>270</v>
+      </c>
+      <c r="P275" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q275">
+        <v>2.5</v>
+      </c>
+      <c r="R275">
+        <v>2.25</v>
+      </c>
+      <c r="S275">
+        <v>4</v>
+      </c>
+      <c r="T275">
+        <v>1.33</v>
+      </c>
+      <c r="U275">
+        <v>3.25</v>
+      </c>
+      <c r="V275">
+        <v>2.63</v>
+      </c>
+      <c r="W275">
+        <v>1.44</v>
+      </c>
+      <c r="X275">
+        <v>6.5</v>
+      </c>
+      <c r="Y275">
+        <v>1.11</v>
+      </c>
+      <c r="Z275">
+        <v>2.05</v>
+      </c>
+      <c r="AA275">
+        <v>3.5</v>
+      </c>
+      <c r="AB275">
+        <v>3.5</v>
+      </c>
+      <c r="AC275">
+        <v>1.05</v>
+      </c>
+      <c r="AD275">
+        <v>13</v>
+      </c>
+      <c r="AE275">
+        <v>1.27</v>
+      </c>
+      <c r="AF275">
+        <v>4</v>
+      </c>
+      <c r="AG275">
+        <v>1.67</v>
+      </c>
+      <c r="AH275">
+        <v>2.1</v>
+      </c>
+      <c r="AI275">
+        <v>1.67</v>
+      </c>
+      <c r="AJ275">
+        <v>2.1</v>
+      </c>
+      <c r="AK275">
+        <v>1.29</v>
+      </c>
+      <c r="AL275">
+        <v>1.29</v>
+      </c>
+      <c r="AM275">
+        <v>1.75</v>
+      </c>
+      <c r="AN275">
+        <v>1.62</v>
+      </c>
+      <c r="AO275">
+        <v>1.69</v>
+      </c>
+      <c r="AP275">
+        <v>1.71</v>
+      </c>
+      <c r="AQ275">
+        <v>1.57</v>
+      </c>
+      <c r="AR275">
+        <v>1.59</v>
+      </c>
+      <c r="AS275">
+        <v>1.49</v>
+      </c>
+      <c r="AT275">
+        <v>3.08</v>
+      </c>
+      <c r="AU275">
+        <v>5</v>
+      </c>
+      <c r="AV275">
+        <v>2</v>
+      </c>
+      <c r="AW275">
+        <v>5</v>
+      </c>
+      <c r="AX275">
+        <v>5</v>
+      </c>
+      <c r="AY275">
+        <v>11</v>
+      </c>
+      <c r="AZ275">
+        <v>8</v>
+      </c>
+      <c r="BA275">
+        <v>3</v>
+      </c>
+      <c r="BB275">
+        <v>7</v>
+      </c>
+      <c r="BC275">
+        <v>10</v>
+      </c>
+      <c r="BD275">
+        <v>1.68</v>
+      </c>
+      <c r="BE275">
+        <v>6.75</v>
+      </c>
+      <c r="BF275">
+        <v>2.4</v>
+      </c>
+      <c r="BG275">
+        <v>1.21</v>
+      </c>
+      <c r="BH275">
+        <v>3.8</v>
+      </c>
+      <c r="BI275">
+        <v>1.38</v>
+      </c>
+      <c r="BJ275">
+        <v>2.7</v>
+      </c>
+      <c r="BK275">
+        <v>1.63</v>
+      </c>
+      <c r="BL275">
+        <v>2.1</v>
+      </c>
+      <c r="BM275">
+        <v>1.98</v>
+      </c>
+      <c r="BN275">
+        <v>1.72</v>
+      </c>
+      <c r="BO275">
+        <v>2.5</v>
+      </c>
+      <c r="BP275">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="276" spans="1:68">
+      <c r="A276" s="1">
+        <v>275</v>
+      </c>
+      <c r="B276">
+        <v>7466952</v>
+      </c>
+      <c r="C276" t="s">
+        <v>68</v>
+      </c>
+      <c r="D276" t="s">
+        <v>69</v>
+      </c>
+      <c r="E276" s="2">
+        <v>45724.5</v>
+      </c>
+      <c r="F276">
+        <v>28</v>
+      </c>
+      <c r="G276" t="s">
+        <v>82</v>
+      </c>
+      <c r="H276" t="s">
+        <v>71</v>
+      </c>
+      <c r="I276">
+        <v>0</v>
+      </c>
+      <c r="J276">
+        <v>0</v>
+      </c>
+      <c r="K276">
+        <v>0</v>
+      </c>
+      <c r="L276">
+        <v>1</v>
+      </c>
+      <c r="M276">
+        <v>0</v>
+      </c>
+      <c r="N276">
+        <v>1</v>
+      </c>
+      <c r="O276" t="s">
+        <v>225</v>
+      </c>
+      <c r="P276" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q276">
+        <v>1.95</v>
+      </c>
+      <c r="R276">
+        <v>2.4</v>
+      </c>
+      <c r="S276">
+        <v>6.5</v>
+      </c>
+      <c r="T276">
+        <v>1.33</v>
+      </c>
+      <c r="U276">
+        <v>3.25</v>
+      </c>
+      <c r="V276">
+        <v>2.63</v>
+      </c>
+      <c r="W276">
+        <v>1.44</v>
+      </c>
+      <c r="X276">
+        <v>6.5</v>
+      </c>
+      <c r="Y276">
+        <v>1.11</v>
+      </c>
+      <c r="Z276">
+        <v>1.45</v>
+      </c>
+      <c r="AA276">
+        <v>4.5</v>
+      </c>
+      <c r="AB276">
+        <v>6.5</v>
+      </c>
+      <c r="AC276">
+        <v>1.04</v>
+      </c>
+      <c r="AD276">
+        <v>13</v>
+      </c>
+      <c r="AE276">
+        <v>1.28</v>
+      </c>
+      <c r="AF276">
+        <v>3.9</v>
+      </c>
+      <c r="AG276">
+        <v>1.8</v>
+      </c>
+      <c r="AH276">
+        <v>1.91</v>
+      </c>
+      <c r="AI276">
+        <v>1.95</v>
+      </c>
+      <c r="AJ276">
+        <v>1.8</v>
+      </c>
+      <c r="AK276">
+        <v>1.11</v>
+      </c>
+      <c r="AL276">
+        <v>1.2</v>
+      </c>
+      <c r="AM276">
+        <v>2.6</v>
+      </c>
+      <c r="AN276">
+        <v>1</v>
+      </c>
+      <c r="AO276">
+        <v>0.77</v>
+      </c>
+      <c r="AP276">
+        <v>1.13</v>
+      </c>
+      <c r="AQ276">
+        <v>0.71</v>
+      </c>
+      <c r="AR276">
+        <v>1.51</v>
+      </c>
+      <c r="AS276">
+        <v>0.91</v>
+      </c>
+      <c r="AT276">
+        <v>2.42</v>
+      </c>
+      <c r="AU276">
+        <v>5</v>
+      </c>
+      <c r="AV276">
+        <v>9</v>
+      </c>
+      <c r="AW276">
+        <v>15</v>
+      </c>
+      <c r="AX276">
+        <v>7</v>
+      </c>
+      <c r="AY276">
+        <v>26</v>
+      </c>
+      <c r="AZ276">
+        <v>19</v>
+      </c>
+      <c r="BA276">
+        <v>5</v>
+      </c>
+      <c r="BB276">
+        <v>4</v>
+      </c>
+      <c r="BC276">
+        <v>9</v>
+      </c>
+      <c r="BD276">
+        <v>1.38</v>
+      </c>
+      <c r="BE276">
+        <v>7.5</v>
+      </c>
+      <c r="BF276">
+        <v>3.3</v>
+      </c>
+      <c r="BG276">
+        <v>1.21</v>
+      </c>
+      <c r="BH276">
+        <v>3.8</v>
+      </c>
+      <c r="BI276">
+        <v>1.36</v>
+      </c>
+      <c r="BJ276">
+        <v>2.8</v>
+      </c>
+      <c r="BK276">
+        <v>1.61</v>
+      </c>
+      <c r="BL276">
+        <v>2.15</v>
+      </c>
+      <c r="BM276">
+        <v>1.96</v>
+      </c>
+      <c r="BN276">
+        <v>1.74</v>
+      </c>
+      <c r="BO276">
+        <v>2.43</v>
+      </c>
+      <c r="BP276">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="277" spans="1:68">
+      <c r="A277" s="1">
+        <v>276</v>
+      </c>
+      <c r="B277">
+        <v>7466949</v>
+      </c>
+      <c r="C277" t="s">
+        <v>68</v>
+      </c>
+      <c r="D277" t="s">
+        <v>69</v>
+      </c>
+      <c r="E277" s="2">
+        <v>45724.60416666666</v>
+      </c>
+      <c r="F277">
+        <v>28</v>
+      </c>
+      <c r="G277" t="s">
+        <v>77</v>
+      </c>
+      <c r="H277" t="s">
+        <v>86</v>
+      </c>
+      <c r="I277">
+        <v>0</v>
+      </c>
+      <c r="J277">
+        <v>0</v>
+      </c>
+      <c r="K277">
+        <v>0</v>
+      </c>
+      <c r="L277">
+        <v>0</v>
+      </c>
+      <c r="M277">
+        <v>1</v>
+      </c>
+      <c r="N277">
+        <v>1</v>
+      </c>
+      <c r="O277" t="s">
+        <v>91</v>
+      </c>
+      <c r="P277" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q277">
+        <v>2.75</v>
+      </c>
+      <c r="R277">
+        <v>2.4</v>
+      </c>
+      <c r="S277">
+        <v>3.25</v>
+      </c>
+      <c r="T277">
+        <v>1.25</v>
+      </c>
+      <c r="U277">
+        <v>3.75</v>
+      </c>
+      <c r="V277">
+        <v>2.2</v>
+      </c>
+      <c r="W277">
+        <v>1.62</v>
+      </c>
+      <c r="X277">
+        <v>5</v>
+      </c>
+      <c r="Y277">
+        <v>1.17</v>
+      </c>
+      <c r="Z277">
+        <v>2.35</v>
+      </c>
+      <c r="AA277">
+        <v>3.75</v>
+      </c>
+      <c r="AB277">
+        <v>2.75</v>
+      </c>
+      <c r="AC277">
+        <v>1.02</v>
+      </c>
+      <c r="AD277">
+        <v>20</v>
+      </c>
+      <c r="AE277">
+        <v>1.17</v>
+      </c>
+      <c r="AF277">
+        <v>5.4</v>
+      </c>
+      <c r="AG277">
+        <v>1.57</v>
+      </c>
+      <c r="AH277">
+        <v>2.3</v>
+      </c>
+      <c r="AI277">
+        <v>1.44</v>
+      </c>
+      <c r="AJ277">
+        <v>2.63</v>
+      </c>
+      <c r="AK277">
+        <v>1.42</v>
+      </c>
+      <c r="AL277">
+        <v>1.27</v>
+      </c>
+      <c r="AM277">
+        <v>1.58</v>
+      </c>
+      <c r="AN277">
+        <v>1.71</v>
+      </c>
+      <c r="AO277">
+        <v>1.08</v>
+      </c>
+      <c r="AP277">
+        <v>1.6</v>
+      </c>
+      <c r="AQ277">
+        <v>1.21</v>
+      </c>
+      <c r="AR277">
+        <v>1.64</v>
+      </c>
+      <c r="AS277">
+        <v>1.14</v>
+      </c>
+      <c r="AT277">
+        <v>2.78</v>
+      </c>
+      <c r="AU277">
+        <v>4</v>
+      </c>
+      <c r="AV277">
+        <v>5</v>
+      </c>
+      <c r="AW277">
+        <v>10</v>
+      </c>
+      <c r="AX277">
+        <v>8</v>
+      </c>
+      <c r="AY277">
+        <v>19</v>
+      </c>
+      <c r="AZ277">
+        <v>19</v>
+      </c>
+      <c r="BA277">
+        <v>6</v>
+      </c>
+      <c r="BB277">
+        <v>5</v>
+      </c>
+      <c r="BC277">
+        <v>11</v>
+      </c>
+      <c r="BD277">
+        <v>2.15</v>
+      </c>
+      <c r="BE277">
+        <v>6.75</v>
+      </c>
+      <c r="BF277">
+        <v>1.84</v>
+      </c>
+      <c r="BG277">
+        <v>1.16</v>
+      </c>
+      <c r="BH277">
+        <v>4.3</v>
+      </c>
+      <c r="BI277">
+        <v>1.3</v>
+      </c>
+      <c r="BJ277">
+        <v>3.05</v>
+      </c>
+      <c r="BK277">
+        <v>1.53</v>
+      </c>
+      <c r="BL277">
+        <v>2.32</v>
+      </c>
+      <c r="BM277">
+        <v>1.84</v>
+      </c>
+      <c r="BN277">
+        <v>1.84</v>
+      </c>
+      <c r="BO277">
+        <v>2.3</v>
+      </c>
+      <c r="BP277">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="278" spans="1:68">
+      <c r="A278" s="1">
+        <v>277</v>
+      </c>
+      <c r="B278">
+        <v>7466958</v>
+      </c>
+      <c r="C278" t="s">
+        <v>68</v>
+      </c>
+      <c r="D278" t="s">
+        <v>69</v>
+      </c>
+      <c r="E278" s="2">
+        <v>45724.70833333334</v>
+      </c>
+      <c r="F278">
+        <v>28</v>
+      </c>
+      <c r="G278" t="s">
+        <v>87</v>
+      </c>
+      <c r="H278" t="s">
+        <v>73</v>
+      </c>
+      <c r="I278">
+        <v>1</v>
+      </c>
+      <c r="J278">
+        <v>1</v>
+      </c>
+      <c r="K278">
+        <v>2</v>
+      </c>
+      <c r="L278">
+        <v>1</v>
+      </c>
+      <c r="M278">
+        <v>1</v>
+      </c>
+      <c r="N278">
+        <v>2</v>
+      </c>
+      <c r="O278" t="s">
+        <v>271</v>
+      </c>
+      <c r="P278" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q278">
+        <v>3.25</v>
+      </c>
+      <c r="R278">
+        <v>2</v>
+      </c>
+      <c r="S278">
+        <v>3.6</v>
+      </c>
+      <c r="T278">
+        <v>1.5</v>
+      </c>
+      <c r="U278">
+        <v>2.5</v>
+      </c>
+      <c r="V278">
+        <v>3.4</v>
+      </c>
+      <c r="W278">
+        <v>1.3</v>
+      </c>
+      <c r="X278">
+        <v>10</v>
+      </c>
+      <c r="Y278">
+        <v>1.06</v>
+      </c>
+      <c r="Z278">
+        <v>2.4</v>
+      </c>
+      <c r="AA278">
+        <v>3.15</v>
+      </c>
+      <c r="AB278">
+        <v>3</v>
+      </c>
+      <c r="AC278">
+        <v>1.09</v>
+      </c>
+      <c r="AD278">
+        <v>8.6</v>
+      </c>
+      <c r="AE278">
+        <v>1.43</v>
+      </c>
+      <c r="AF278">
+        <v>2.94</v>
+      </c>
+      <c r="AG278">
+        <v>1.7</v>
+      </c>
+      <c r="AH278">
+        <v>2.05</v>
+      </c>
+      <c r="AI278">
+        <v>1.95</v>
+      </c>
+      <c r="AJ278">
+        <v>1.8</v>
+      </c>
+      <c r="AK278">
+        <v>1.41</v>
+      </c>
+      <c r="AL278">
+        <v>1.34</v>
+      </c>
+      <c r="AM278">
+        <v>1.49</v>
+      </c>
+      <c r="AN278">
+        <v>0.77</v>
+      </c>
+      <c r="AO278">
+        <v>1.08</v>
+      </c>
+      <c r="AP278">
+        <v>0.79</v>
+      </c>
+      <c r="AQ278">
+        <v>1.07</v>
+      </c>
+      <c r="AR278">
+        <v>1.27</v>
+      </c>
+      <c r="AS278">
+        <v>1.12</v>
+      </c>
+      <c r="AT278">
+        <v>2.39</v>
+      </c>
+      <c r="AU278">
+        <v>4</v>
+      </c>
+      <c r="AV278">
+        <v>5</v>
+      </c>
+      <c r="AW278">
+        <v>8</v>
+      </c>
+      <c r="AX278">
+        <v>8</v>
+      </c>
+      <c r="AY278">
+        <v>15</v>
+      </c>
+      <c r="AZ278">
+        <v>19</v>
+      </c>
+      <c r="BA278">
+        <v>5</v>
+      </c>
+      <c r="BB278">
+        <v>5</v>
+      </c>
+      <c r="BC278">
+        <v>10</v>
+      </c>
+      <c r="BD278">
+        <v>1.98</v>
+      </c>
+      <c r="BE278">
+        <v>6.4</v>
+      </c>
+      <c r="BF278">
+        <v>2</v>
+      </c>
+      <c r="BG278">
+        <v>1.25</v>
+      </c>
+      <c r="BH278">
+        <v>3.45</v>
+      </c>
+      <c r="BI278">
+        <v>1.44</v>
+      </c>
+      <c r="BJ278">
+        <v>2.55</v>
+      </c>
+      <c r="BK278">
+        <v>1.72</v>
+      </c>
+      <c r="BL278">
+        <v>1.98</v>
+      </c>
+      <c r="BM278">
+        <v>2.15</v>
+      </c>
+      <c r="BN278">
+        <v>1.61</v>
+      </c>
+      <c r="BO278">
+        <v>2.7</v>
+      </c>
+      <c r="BP278">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="417">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -823,13 +823,22 @@
     <t>['83']</t>
   </si>
   <si>
-    <t>['51', '54', '88']</t>
+    <t>['51', '55', '88']</t>
   </si>
   <si>
     <t>['41', '90+8']</t>
   </si>
   <si>
     <t>['40']</t>
+  </si>
+  <si>
+    <t>['60']</t>
+  </si>
+  <si>
+    <t>['67', '84']</t>
+  </si>
+  <si>
+    <t>['45+2']</t>
   </si>
   <si>
     <t>['60', '65']</t>
@@ -845,9 +854,6 @@
   </si>
   <si>
     <t>['18', '84']</t>
-  </si>
-  <si>
-    <t>['60']</t>
   </si>
   <si>
     <t>['67', '77']</t>
@@ -1257,6 +1263,9 @@
   <si>
     <t>['45+1']</t>
   </si>
+  <si>
+    <t>['42', '65']</t>
+  </si>
 </sst>
 </file>
 
@@ -1617,7 +1626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP278"/>
+  <dimension ref="A1:BP281"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1951,7 +1960,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ2">
         <v>1.57</v>
@@ -2079,7 +2088,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2491,7 +2500,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2903,7 +2912,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -2984,7 +2993,7 @@
         <v>2</v>
       </c>
       <c r="AQ7">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3109,7 +3118,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3521,7 +3530,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3599,7 +3608,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ10">
         <v>1.4</v>
@@ -3933,7 +3942,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -4217,7 +4226,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ13">
         <v>1.07</v>
@@ -4632,7 +4641,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ15">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -5169,7 +5178,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5250,7 +5259,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ18">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5375,7 +5384,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -6199,7 +6208,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6405,7 +6414,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -7023,7 +7032,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7104,7 +7113,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ27">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR27">
         <v>0.83</v>
@@ -7229,7 +7238,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7435,7 +7444,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7513,7 +7522,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ29">
         <v>1.69</v>
@@ -7847,7 +7856,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7925,7 +7934,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ31">
         <v>2.33</v>
@@ -8053,7 +8062,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8465,7 +8474,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -8546,7 +8555,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ34">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR34">
         <v>1.29</v>
@@ -9289,7 +9298,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9495,7 +9504,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9701,7 +9710,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9779,10 +9788,10 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ40">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR40">
         <v>1.93</v>
@@ -9907,7 +9916,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -10113,7 +10122,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10319,7 +10328,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10812,7 +10821,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ45">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR45">
         <v>1.78</v>
@@ -11221,7 +11230,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ47">
         <v>1.08</v>
@@ -11967,7 +11976,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -12048,7 +12057,7 @@
         <v>2</v>
       </c>
       <c r="AQ51">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR51">
         <v>2.05</v>
@@ -12173,7 +12182,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12379,7 +12388,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12791,7 +12800,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -12872,7 +12881,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ55">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR55">
         <v>1.6</v>
@@ -13203,7 +13212,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13281,7 +13290,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ57">
         <v>1.57</v>
@@ -13409,7 +13418,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13615,7 +13624,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13821,7 +13830,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13899,7 +13908,7 @@
         <v>0.5</v>
       </c>
       <c r="AP60">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ60">
         <v>1.23</v>
@@ -14027,7 +14036,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14233,7 +14242,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14520,7 +14529,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ63">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR63">
         <v>1.12</v>
@@ -14645,7 +14654,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14851,7 +14860,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -15057,7 +15066,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -15753,7 +15762,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ69">
         <v>1.64</v>
@@ -16087,7 +16096,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16371,7 +16380,7 @@
         <v>1.67</v>
       </c>
       <c r="AP72">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ72">
         <v>1.23</v>
@@ -16499,7 +16508,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16705,7 +16714,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16783,7 +16792,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ74">
         <v>1.08</v>
@@ -16911,7 +16920,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -17117,7 +17126,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17198,7 +17207,7 @@
         <v>0.31</v>
       </c>
       <c r="AQ76">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR76">
         <v>0.91</v>
@@ -17323,7 +17332,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17610,7 +17619,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ78">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR78">
         <v>1.65</v>
@@ -17735,7 +17744,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17941,7 +17950,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18353,7 +18362,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18765,7 +18774,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18971,7 +18980,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -19052,7 +19061,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ85">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR85">
         <v>1.28</v>
@@ -19177,7 +19186,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19589,7 +19598,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19667,7 +19676,7 @@
         <v>1.25</v>
       </c>
       <c r="AP88">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ88">
         <v>1.5</v>
@@ -20001,7 +20010,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20207,7 +20216,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20494,7 +20503,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ92">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR92">
         <v>1.13</v>
@@ -21112,7 +21121,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ95">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR95">
         <v>1.12</v>
@@ -21649,7 +21658,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21855,7 +21864,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -21933,7 +21942,7 @@
         <v>2.5</v>
       </c>
       <c r="AP99">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ99">
         <v>1.21</v>
@@ -22061,7 +22070,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22139,7 +22148,7 @@
         <v>2.25</v>
       </c>
       <c r="AP100">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ100">
         <v>1.5</v>
@@ -22473,7 +22482,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22554,7 +22563,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ102">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR102">
         <v>1.76</v>
@@ -22679,7 +22688,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23787,10 +23796,10 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ108">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR108">
         <v>1.48</v>
@@ -23915,7 +23924,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -24121,7 +24130,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24199,7 +24208,7 @@
         <v>0.4</v>
       </c>
       <c r="AP110">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ110">
         <v>0.71</v>
@@ -24327,7 +24336,7 @@
         <v>162</v>
       </c>
       <c r="P111" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="Q111">
         <v>3.25</v>
@@ -24405,10 +24414,10 @@
         <v>1.4</v>
       </c>
       <c r="AP111">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ111">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR111">
         <v>1.72</v>
@@ -24533,7 +24542,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24739,7 +24748,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -25357,7 +25366,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25563,7 +25572,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25769,7 +25778,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25975,7 +25984,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -26181,7 +26190,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26387,7 +26396,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26593,7 +26602,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26799,7 +26808,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -26880,7 +26889,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ123">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR123">
         <v>1.13</v>
@@ -27292,7 +27301,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ125">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR125">
         <v>1.7</v>
@@ -27417,7 +27426,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27623,7 +27632,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -27704,7 +27713,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ127">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR127">
         <v>1.54</v>
@@ -27907,7 +27916,7 @@
         <v>0.83</v>
       </c>
       <c r="AP128">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ128">
         <v>1.07</v>
@@ -28113,7 +28122,7 @@
         <v>1.67</v>
       </c>
       <c r="AP129">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ129">
         <v>1.21</v>
@@ -28241,7 +28250,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28319,7 +28328,7 @@
         <v>1.33</v>
       </c>
       <c r="AP130">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ130">
         <v>1.57</v>
@@ -28653,7 +28662,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -29065,7 +29074,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29271,7 +29280,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -30713,7 +30722,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30919,7 +30928,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -31331,7 +31340,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31409,7 +31418,7 @@
         <v>1.57</v>
       </c>
       <c r="AP145">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ145">
         <v>1.64</v>
@@ -31537,7 +31546,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31618,7 +31627,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ146">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR146">
         <v>1.74</v>
@@ -31743,7 +31752,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31824,7 +31833,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ147">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR147">
         <v>1.16</v>
@@ -31949,7 +31958,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -32155,7 +32164,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32233,7 +32242,7 @@
         <v>2.29</v>
       </c>
       <c r="AP149">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ149">
         <v>1.5</v>
@@ -32567,7 +32576,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -33060,7 +33069,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ153">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR153">
         <v>1.32</v>
@@ -33185,7 +33194,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33391,7 +33400,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33597,7 +33606,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33803,7 +33812,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -34009,7 +34018,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34293,7 +34302,7 @@
         <v>0.14</v>
       </c>
       <c r="AP159">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ159">
         <v>1.08</v>
@@ -34833,7 +34842,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -35039,7 +35048,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35245,7 +35254,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35451,7 +35460,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35532,7 +35541,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ165">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR165">
         <v>1.31</v>
@@ -35863,7 +35872,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36069,7 +36078,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36147,10 +36156,10 @@
         <v>1.38</v>
       </c>
       <c r="AP168">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ168">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR168">
         <v>1.46</v>
@@ -36481,7 +36490,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36559,7 +36568,7 @@
         <v>2.43</v>
       </c>
       <c r="AP170">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ170">
         <v>2.33</v>
@@ -36893,7 +36902,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37511,7 +37520,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -37589,7 +37598,7 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ175">
         <v>1.57</v>
@@ -38129,7 +38138,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38210,7 +38219,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ178">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR178">
         <v>1.73</v>
@@ -38747,7 +38756,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38953,7 +38962,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39031,7 +39040,7 @@
         <v>0.89</v>
       </c>
       <c r="AP182">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ182">
         <v>0.86</v>
@@ -39365,7 +39374,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39446,7 +39455,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ184">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR184">
         <v>1.59</v>
@@ -39571,7 +39580,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39777,7 +39786,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -40189,7 +40198,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40395,7 +40404,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40473,7 +40482,7 @@
         <v>1.33</v>
       </c>
       <c r="AP189">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ189">
         <v>1.5</v>
@@ -40601,7 +40610,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40682,7 +40691,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ190">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR190">
         <v>1.66</v>
@@ -40807,7 +40816,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -40885,7 +40894,7 @@
         <v>1.5</v>
       </c>
       <c r="AP191">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ191">
         <v>1.5</v>
@@ -41219,7 +41228,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41300,7 +41309,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ193">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR193">
         <v>1.51</v>
@@ -41631,7 +41640,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41837,7 +41846,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -42124,7 +42133,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ197">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR197">
         <v>1.62</v>
@@ -42249,7 +42258,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42455,7 +42464,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42661,7 +42670,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42867,7 +42876,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -42945,10 +42954,10 @@
         <v>1.5</v>
       </c>
       <c r="AP201">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ201">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR201">
         <v>1.75</v>
@@ -43073,7 +43082,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43279,7 +43288,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43485,7 +43494,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43691,7 +43700,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -44103,7 +44112,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44515,7 +44524,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44799,7 +44808,7 @@
         <v>0.2</v>
       </c>
       <c r="AP210">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ210">
         <v>0.33</v>
@@ -44927,7 +44936,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45008,7 +45017,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ211">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR211">
         <v>1.61</v>
@@ -45133,7 +45142,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45339,7 +45348,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45545,7 +45554,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45751,7 +45760,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -45957,7 +45966,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -46035,7 +46044,7 @@
         <v>1.45</v>
       </c>
       <c r="AP216">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ216">
         <v>1.57</v>
@@ -46163,7 +46172,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46369,7 +46378,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46575,7 +46584,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46781,7 +46790,7 @@
         <v>240</v>
       </c>
       <c r="P220" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q220">
         <v>1.73</v>
@@ -46859,7 +46868,7 @@
         <v>0.82</v>
       </c>
       <c r="AP220">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ220">
         <v>0.86</v>
@@ -47193,7 +47202,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -47605,7 +47614,7 @@
         <v>107</v>
       </c>
       <c r="P224" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q224">
         <v>6</v>
@@ -47811,7 +47820,7 @@
         <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q225">
         <v>6.5</v>
@@ -47892,7 +47901,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ225">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR225">
         <v>1.21</v>
@@ -48017,7 +48026,7 @@
         <v>243</v>
       </c>
       <c r="P226" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q226">
         <v>2.38</v>
@@ -48223,7 +48232,7 @@
         <v>155</v>
       </c>
       <c r="P227" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48429,7 +48438,7 @@
         <v>244</v>
       </c>
       <c r="P228" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Q228">
         <v>1.91</v>
@@ -48507,10 +48516,10 @@
         <v>0.5</v>
       </c>
       <c r="AP228">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ228">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR228">
         <v>1.71</v>
@@ -48841,7 +48850,7 @@
         <v>91</v>
       </c>
       <c r="P230" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q230">
         <v>2.88</v>
@@ -49253,7 +49262,7 @@
         <v>95</v>
       </c>
       <c r="P232" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q232">
         <v>2.2</v>
@@ -49540,7 +49549,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ233">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR233">
         <v>1.37</v>
@@ -49665,7 +49674,7 @@
         <v>151</v>
       </c>
       <c r="P234" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q234">
         <v>2.6</v>
@@ -49871,7 +49880,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Q235">
         <v>4.5</v>
@@ -50283,7 +50292,7 @@
         <v>91</v>
       </c>
       <c r="P237" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50489,7 +50498,7 @@
         <v>91</v>
       </c>
       <c r="P238" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Q238">
         <v>2.75</v>
@@ -50567,7 +50576,7 @@
         <v>1.45</v>
       </c>
       <c r="AP238">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ238">
         <v>1.69</v>
@@ -50901,7 +50910,7 @@
         <v>249</v>
       </c>
       <c r="P240" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q240">
         <v>1.8</v>
@@ -50979,7 +50988,7 @@
         <v>1.18</v>
       </c>
       <c r="AP240">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ240">
         <v>1.23</v>
@@ -51107,7 +51116,7 @@
         <v>250</v>
       </c>
       <c r="P241" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Q241">
         <v>6</v>
@@ -51519,7 +51528,7 @@
         <v>91</v>
       </c>
       <c r="P243" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Q243">
         <v>9</v>
@@ -51600,7 +51609,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ243">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR243">
         <v>1.2</v>
@@ -51725,7 +51734,7 @@
         <v>203</v>
       </c>
       <c r="P244" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="Q244">
         <v>5</v>
@@ -51806,7 +51815,7 @@
         <v>0.31</v>
       </c>
       <c r="AQ244">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR244">
         <v>1.15</v>
@@ -52755,7 +52764,7 @@
         <v>254</v>
       </c>
       <c r="P249" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Q249">
         <v>2.63</v>
@@ -52961,7 +52970,7 @@
         <v>255</v>
       </c>
       <c r="P250" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q250">
         <v>1.57</v>
@@ -53245,7 +53254,7 @@
         <v>1.18</v>
       </c>
       <c r="AP251">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ251">
         <v>1.08</v>
@@ -53373,7 +53382,7 @@
         <v>256</v>
       </c>
       <c r="P252" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q252">
         <v>4</v>
@@ -53579,7 +53588,7 @@
         <v>91</v>
       </c>
       <c r="P253" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Q253">
         <v>3.6</v>
@@ -53785,7 +53794,7 @@
         <v>257</v>
       </c>
       <c r="P254" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Q254">
         <v>3.25</v>
@@ -53991,7 +54000,7 @@
         <v>91</v>
       </c>
       <c r="P255" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Q255">
         <v>5</v>
@@ -54197,7 +54206,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Q256">
         <v>3.75</v>
@@ -54403,7 +54412,7 @@
         <v>91</v>
       </c>
       <c r="P257" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Q257">
         <v>1.73</v>
@@ -54815,7 +54824,7 @@
         <v>91</v>
       </c>
       <c r="P259" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Q259">
         <v>2.75</v>
@@ -55021,7 +55030,7 @@
         <v>258</v>
       </c>
       <c r="P260" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q260">
         <v>3.1</v>
@@ -55227,7 +55236,7 @@
         <v>259</v>
       </c>
       <c r="P261" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Q261">
         <v>2.38</v>
@@ -55433,7 +55442,7 @@
         <v>91</v>
       </c>
       <c r="P262" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Q262">
         <v>3.1</v>
@@ -55639,7 +55648,7 @@
         <v>260</v>
       </c>
       <c r="P263" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q263">
         <v>3.2</v>
@@ -55845,7 +55854,7 @@
         <v>261</v>
       </c>
       <c r="P264" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q264">
         <v>3.5</v>
@@ -56132,7 +56141,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ265">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR265">
         <v>1.6</v>
@@ -56335,7 +56344,7 @@
         <v>0.38</v>
       </c>
       <c r="AP266">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ266">
         <v>0.33</v>
@@ -56541,7 +56550,7 @@
         <v>1.38</v>
       </c>
       <c r="AP267">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ267">
         <v>1.4</v>
@@ -56669,7 +56678,7 @@
         <v>264</v>
       </c>
       <c r="P268" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Q268">
         <v>2.05</v>
@@ -56747,7 +56756,7 @@
         <v>0.83</v>
       </c>
       <c r="AP268">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ268">
         <v>0.71</v>
@@ -57162,7 +57171,7 @@
         <v>2</v>
       </c>
       <c r="AQ270">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR270">
         <v>1.5</v>
@@ -57574,7 +57583,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ272">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR272">
         <v>1.27</v>
@@ -57905,7 +57914,7 @@
         <v>269</v>
       </c>
       <c r="P274" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Q274">
         <v>1.4</v>
@@ -58111,7 +58120,7 @@
         <v>270</v>
       </c>
       <c r="P275" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q275">
         <v>2.5</v>
@@ -58886,6 +58895,624 @@
       </c>
       <c r="BP278">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="279" spans="1:68">
+      <c r="A279" s="1">
+        <v>278</v>
+      </c>
+      <c r="B279">
+        <v>7466951</v>
+      </c>
+      <c r="C279" t="s">
+        <v>68</v>
+      </c>
+      <c r="D279" t="s">
+        <v>69</v>
+      </c>
+      <c r="E279" s="2">
+        <v>45725.45833333334</v>
+      </c>
+      <c r="F279">
+        <v>28</v>
+      </c>
+      <c r="G279" t="s">
+        <v>78</v>
+      </c>
+      <c r="H279" t="s">
+        <v>79</v>
+      </c>
+      <c r="I279">
+        <v>0</v>
+      </c>
+      <c r="J279">
+        <v>0</v>
+      </c>
+      <c r="K279">
+        <v>0</v>
+      </c>
+      <c r="L279">
+        <v>1</v>
+      </c>
+      <c r="M279">
+        <v>0</v>
+      </c>
+      <c r="N279">
+        <v>1</v>
+      </c>
+      <c r="O279" t="s">
+        <v>272</v>
+      </c>
+      <c r="P279" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q279">
+        <v>1.57</v>
+      </c>
+      <c r="R279">
+        <v>3</v>
+      </c>
+      <c r="S279">
+        <v>9</v>
+      </c>
+      <c r="T279">
+        <v>1.2</v>
+      </c>
+      <c r="U279">
+        <v>4.33</v>
+      </c>
+      <c r="V279">
+        <v>1.91</v>
+      </c>
+      <c r="W279">
+        <v>1.8</v>
+      </c>
+      <c r="X279">
+        <v>4</v>
+      </c>
+      <c r="Y279">
+        <v>1.22</v>
+      </c>
+      <c r="Z279">
+        <v>1.19</v>
+      </c>
+      <c r="AA279">
+        <v>7.5</v>
+      </c>
+      <c r="AB279">
+        <v>10.5</v>
+      </c>
+      <c r="AC279">
+        <v>1.01</v>
+      </c>
+      <c r="AD279">
+        <v>39</v>
+      </c>
+      <c r="AE279">
+        <v>1.11</v>
+      </c>
+      <c r="AF279">
+        <v>7.4</v>
+      </c>
+      <c r="AG279">
+        <v>1.35</v>
+      </c>
+      <c r="AH279">
+        <v>3.04</v>
+      </c>
+      <c r="AI279">
+        <v>1.8</v>
+      </c>
+      <c r="AJ279">
+        <v>1.95</v>
+      </c>
+      <c r="AK279">
+        <v>1.04</v>
+      </c>
+      <c r="AL279">
+        <v>1.09</v>
+      </c>
+      <c r="AM279">
+        <v>4.33</v>
+      </c>
+      <c r="AN279">
+        <v>1.92</v>
+      </c>
+      <c r="AO279">
+        <v>0.62</v>
+      </c>
+      <c r="AP279">
+        <v>2</v>
+      </c>
+      <c r="AQ279">
+        <v>0.57</v>
+      </c>
+      <c r="AR279">
+        <v>1.96</v>
+      </c>
+      <c r="AS279">
+        <v>1.04</v>
+      </c>
+      <c r="AT279">
+        <v>3</v>
+      </c>
+      <c r="AU279">
+        <v>8</v>
+      </c>
+      <c r="AV279">
+        <v>4</v>
+      </c>
+      <c r="AW279">
+        <v>14</v>
+      </c>
+      <c r="AX279">
+        <v>0</v>
+      </c>
+      <c r="AY279">
+        <v>30</v>
+      </c>
+      <c r="AZ279">
+        <v>4</v>
+      </c>
+      <c r="BA279">
+        <v>12</v>
+      </c>
+      <c r="BB279">
+        <v>2</v>
+      </c>
+      <c r="BC279">
+        <v>14</v>
+      </c>
+      <c r="BD279">
+        <v>1.13</v>
+      </c>
+      <c r="BE279">
+        <v>10</v>
+      </c>
+      <c r="BF279">
+        <v>6.25</v>
+      </c>
+      <c r="BG279">
+        <v>1.18</v>
+      </c>
+      <c r="BH279">
+        <v>4.2</v>
+      </c>
+      <c r="BI279">
+        <v>1.32</v>
+      </c>
+      <c r="BJ279">
+        <v>3.05</v>
+      </c>
+      <c r="BK279">
+        <v>1.53</v>
+      </c>
+      <c r="BL279">
+        <v>2.32</v>
+      </c>
+      <c r="BM279">
+        <v>1.82</v>
+      </c>
+      <c r="BN279">
+        <v>1.86</v>
+      </c>
+      <c r="BO279">
+        <v>2.23</v>
+      </c>
+      <c r="BP279">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="280" spans="1:68">
+      <c r="A280" s="1">
+        <v>279</v>
+      </c>
+      <c r="B280">
+        <v>7466956</v>
+      </c>
+      <c r="C280" t="s">
+        <v>68</v>
+      </c>
+      <c r="D280" t="s">
+        <v>69</v>
+      </c>
+      <c r="E280" s="2">
+        <v>45725.45833333334</v>
+      </c>
+      <c r="F280">
+        <v>28</v>
+      </c>
+      <c r="G280" t="s">
+        <v>81</v>
+      </c>
+      <c r="H280" t="s">
+        <v>88</v>
+      </c>
+      <c r="I280">
+        <v>0</v>
+      </c>
+      <c r="J280">
+        <v>1</v>
+      </c>
+      <c r="K280">
+        <v>1</v>
+      </c>
+      <c r="L280">
+        <v>2</v>
+      </c>
+      <c r="M280">
+        <v>2</v>
+      </c>
+      <c r="N280">
+        <v>4</v>
+      </c>
+      <c r="O280" t="s">
+        <v>273</v>
+      </c>
+      <c r="P280" t="s">
+        <v>416</v>
+      </c>
+      <c r="Q280">
+        <v>2.88</v>
+      </c>
+      <c r="R280">
+        <v>2.5</v>
+      </c>
+      <c r="S280">
+        <v>2.88</v>
+      </c>
+      <c r="T280">
+        <v>1.22</v>
+      </c>
+      <c r="U280">
+        <v>4</v>
+      </c>
+      <c r="V280">
+        <v>2.1</v>
+      </c>
+      <c r="W280">
+        <v>1.67</v>
+      </c>
+      <c r="X280">
+        <v>4.5</v>
+      </c>
+      <c r="Y280">
+        <v>1.18</v>
+      </c>
+      <c r="Z280">
+        <v>2.4</v>
+      </c>
+      <c r="AA280">
+        <v>3.75</v>
+      </c>
+      <c r="AB280">
+        <v>2.55</v>
+      </c>
+      <c r="AC280">
+        <v>1.01</v>
+      </c>
+      <c r="AD280">
+        <v>24</v>
+      </c>
+      <c r="AE280">
+        <v>1.12</v>
+      </c>
+      <c r="AF280">
+        <v>6.8</v>
+      </c>
+      <c r="AG280">
+        <v>1.38</v>
+      </c>
+      <c r="AH280">
+        <v>2.9</v>
+      </c>
+      <c r="AI280">
+        <v>1.36</v>
+      </c>
+      <c r="AJ280">
+        <v>3</v>
+      </c>
+      <c r="AK280">
+        <v>1.46</v>
+      </c>
+      <c r="AL280">
+        <v>1.24</v>
+      </c>
+      <c r="AM280">
+        <v>1.58</v>
+      </c>
+      <c r="AN280">
+        <v>1.21</v>
+      </c>
+      <c r="AO280">
+        <v>1.57</v>
+      </c>
+      <c r="AP280">
+        <v>1.2</v>
+      </c>
+      <c r="AQ280">
+        <v>1.53</v>
+      </c>
+      <c r="AR280">
+        <v>1.76</v>
+      </c>
+      <c r="AS280">
+        <v>1.68</v>
+      </c>
+      <c r="AT280">
+        <v>3.44</v>
+      </c>
+      <c r="AU280">
+        <v>5</v>
+      </c>
+      <c r="AV280">
+        <v>9</v>
+      </c>
+      <c r="AW280">
+        <v>8</v>
+      </c>
+      <c r="AX280">
+        <v>9</v>
+      </c>
+      <c r="AY280">
+        <v>17</v>
+      </c>
+      <c r="AZ280">
+        <v>20</v>
+      </c>
+      <c r="BA280">
+        <v>3</v>
+      </c>
+      <c r="BB280">
+        <v>6</v>
+      </c>
+      <c r="BC280">
+        <v>9</v>
+      </c>
+      <c r="BD280">
+        <v>1.73</v>
+      </c>
+      <c r="BE280">
+        <v>7</v>
+      </c>
+      <c r="BF280">
+        <v>2.3</v>
+      </c>
+      <c r="BG280">
+        <v>1.09</v>
+      </c>
+      <c r="BH280">
+        <v>5.8</v>
+      </c>
+      <c r="BI280">
+        <v>1.17</v>
+      </c>
+      <c r="BJ280">
+        <v>4.3</v>
+      </c>
+      <c r="BK280">
+        <v>1.3</v>
+      </c>
+      <c r="BL280">
+        <v>3.15</v>
+      </c>
+      <c r="BM280">
+        <v>1.49</v>
+      </c>
+      <c r="BN280">
+        <v>2.4</v>
+      </c>
+      <c r="BO280">
+        <v>1.77</v>
+      </c>
+      <c r="BP280">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="281" spans="1:68">
+      <c r="A281" s="1">
+        <v>280</v>
+      </c>
+      <c r="B281">
+        <v>7466954</v>
+      </c>
+      <c r="C281" t="s">
+        <v>68</v>
+      </c>
+      <c r="D281" t="s">
+        <v>69</v>
+      </c>
+      <c r="E281" s="2">
+        <v>45725.5625</v>
+      </c>
+      <c r="F281">
+        <v>28</v>
+      </c>
+      <c r="G281" t="s">
+        <v>70</v>
+      </c>
+      <c r="H281" t="s">
+        <v>72</v>
+      </c>
+      <c r="I281">
+        <v>1</v>
+      </c>
+      <c r="J281">
+        <v>0</v>
+      </c>
+      <c r="K281">
+        <v>1</v>
+      </c>
+      <c r="L281">
+        <v>1</v>
+      </c>
+      <c r="M281">
+        <v>1</v>
+      </c>
+      <c r="N281">
+        <v>2</v>
+      </c>
+      <c r="O281" t="s">
+        <v>274</v>
+      </c>
+      <c r="P281" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q281">
+        <v>5.5</v>
+      </c>
+      <c r="R281">
+        <v>2.1</v>
+      </c>
+      <c r="S281">
+        <v>2.4</v>
+      </c>
+      <c r="T281">
+        <v>1.44</v>
+      </c>
+      <c r="U281">
+        <v>2.63</v>
+      </c>
+      <c r="V281">
+        <v>3.25</v>
+      </c>
+      <c r="W281">
+        <v>1.33</v>
+      </c>
+      <c r="X281">
+        <v>10</v>
+      </c>
+      <c r="Y281">
+        <v>1.06</v>
+      </c>
+      <c r="Z281">
+        <v>4.3</v>
+      </c>
+      <c r="AA281">
+        <v>3.35</v>
+      </c>
+      <c r="AB281">
+        <v>1.86</v>
+      </c>
+      <c r="AC281">
+        <v>1.06</v>
+      </c>
+      <c r="AD281">
+        <v>10</v>
+      </c>
+      <c r="AE281">
+        <v>1.34</v>
+      </c>
+      <c r="AF281">
+        <v>3.4</v>
+      </c>
+      <c r="AG281">
+        <v>1.7</v>
+      </c>
+      <c r="AH281">
+        <v>2.05</v>
+      </c>
+      <c r="AI281">
+        <v>2</v>
+      </c>
+      <c r="AJ281">
+        <v>1.75</v>
+      </c>
+      <c r="AK281">
+        <v>1.93</v>
+      </c>
+      <c r="AL281">
+        <v>1.29</v>
+      </c>
+      <c r="AM281">
+        <v>1.2</v>
+      </c>
+      <c r="AN281">
+        <v>1.36</v>
+      </c>
+      <c r="AO281">
+        <v>1.86</v>
+      </c>
+      <c r="AP281">
+        <v>1.33</v>
+      </c>
+      <c r="AQ281">
+        <v>1.8</v>
+      </c>
+      <c r="AR281">
+        <v>1.53</v>
+      </c>
+      <c r="AS281">
+        <v>1.34</v>
+      </c>
+      <c r="AT281">
+        <v>2.87</v>
+      </c>
+      <c r="AU281">
+        <v>7</v>
+      </c>
+      <c r="AV281">
+        <v>7</v>
+      </c>
+      <c r="AW281">
+        <v>4</v>
+      </c>
+      <c r="AX281">
+        <v>11</v>
+      </c>
+      <c r="AY281">
+        <v>12</v>
+      </c>
+      <c r="AZ281">
+        <v>23</v>
+      </c>
+      <c r="BA281">
+        <v>2</v>
+      </c>
+      <c r="BB281">
+        <v>9</v>
+      </c>
+      <c r="BC281">
+        <v>11</v>
+      </c>
+      <c r="BD281">
+        <v>2.8</v>
+      </c>
+      <c r="BE281">
+        <v>6.75</v>
+      </c>
+      <c r="BF281">
+        <v>1.5</v>
+      </c>
+      <c r="BG281">
+        <v>1.28</v>
+      </c>
+      <c r="BH281">
+        <v>3.2</v>
+      </c>
+      <c r="BI281">
+        <v>1.49</v>
+      </c>
+      <c r="BJ281">
+        <v>2.4</v>
+      </c>
+      <c r="BK281">
+        <v>1.8</v>
+      </c>
+      <c r="BL281">
+        <v>1.89</v>
+      </c>
+      <c r="BM281">
+        <v>2.25</v>
+      </c>
+      <c r="BN281">
+        <v>1.55</v>
+      </c>
+      <c r="BO281">
+        <v>2.9</v>
+      </c>
+      <c r="BP281">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1754" uniqueCount="417">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1626,7 +1626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP281"/>
+  <dimension ref="A1:BP282"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3196,7 +3196,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ8">
         <v>1.21</v>
@@ -5671,7 +5671,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ20">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -7316,7 +7316,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ28">
         <v>1.4</v>
@@ -9997,7 +9997,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ41">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR41">
         <v>1.34</v>
@@ -10200,7 +10200,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ42">
         <v>1.5</v>
@@ -10409,7 +10409,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ43">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR43">
         <v>1.79</v>
@@ -14938,7 +14938,7 @@
         <v>0.67</v>
       </c>
       <c r="AP65">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ65">
         <v>0.71</v>
@@ -15559,7 +15559,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ68">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR68">
         <v>1.37</v>
@@ -19679,7 +19679,7 @@
         <v>2</v>
       </c>
       <c r="AQ88">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR88">
         <v>1.67</v>
@@ -20088,7 +20088,7 @@
         <v>1.25</v>
       </c>
       <c r="AP90">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ90">
         <v>1.08</v>
@@ -22972,7 +22972,7 @@
         <v>0.8</v>
       </c>
       <c r="AP104">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ104">
         <v>1.07</v>
@@ -24005,7 +24005,7 @@
         <v>2</v>
       </c>
       <c r="AQ109">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR109">
         <v>1.61</v>
@@ -27507,7 +27507,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ126">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR126">
         <v>1.38</v>
@@ -27710,7 +27710,7 @@
         <v>1.33</v>
       </c>
       <c r="AP127">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ127">
         <v>1.8</v>
@@ -31009,7 +31009,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ143">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR143">
         <v>1.7</v>
@@ -32448,7 +32448,7 @@
         <v>0.71</v>
       </c>
       <c r="AP150">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ150">
         <v>0.86</v>
@@ -35126,7 +35126,7 @@
         <v>1.38</v>
       </c>
       <c r="AP163">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ163">
         <v>1.57</v>
@@ -35335,7 +35335,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ164">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR164">
         <v>1.2</v>
@@ -39864,7 +39864,7 @@
         <v>2.5</v>
       </c>
       <c r="AP186">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ186">
         <v>2.33</v>
@@ -40485,7 +40485,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ189">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR189">
         <v>1.54</v>
@@ -40897,7 +40897,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ191">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR191">
         <v>1.71</v>
@@ -43160,7 +43160,7 @@
         <v>1.44</v>
       </c>
       <c r="AP202">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ202">
         <v>1.57</v>
@@ -45220,7 +45220,7 @@
         <v>1.3</v>
       </c>
       <c r="AP212">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ212">
         <v>1.69</v>
@@ -47695,7 +47695,7 @@
         <v>0.31</v>
       </c>
       <c r="AQ224">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR224">
         <v>1.11</v>
@@ -52021,7 +52021,7 @@
         <v>2</v>
       </c>
       <c r="AQ245">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR245">
         <v>1.98</v>
@@ -52224,7 +52224,7 @@
         <v>0.73</v>
       </c>
       <c r="AP246">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ246">
         <v>1.08</v>
@@ -57377,7 +57377,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ271">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR271">
         <v>1.81</v>
@@ -57580,7 +57580,7 @@
         <v>0.67</v>
       </c>
       <c r="AP272">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ272">
         <v>0.57</v>
@@ -59513,6 +59513,212 @@
       </c>
       <c r="BP281">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="282" spans="1:68">
+      <c r="A282" s="1">
+        <v>281</v>
+      </c>
+      <c r="B282">
+        <v>7466957</v>
+      </c>
+      <c r="C282" t="s">
+        <v>68</v>
+      </c>
+      <c r="D282" t="s">
+        <v>69</v>
+      </c>
+      <c r="E282" s="2">
+        <v>45726.70833333334</v>
+      </c>
+      <c r="F282">
+        <v>28</v>
+      </c>
+      <c r="G282" t="s">
+        <v>76</v>
+      </c>
+      <c r="H282" t="s">
+        <v>74</v>
+      </c>
+      <c r="I282">
+        <v>0</v>
+      </c>
+      <c r="J282">
+        <v>0</v>
+      </c>
+      <c r="K282">
+        <v>0</v>
+      </c>
+      <c r="L282">
+        <v>0</v>
+      </c>
+      <c r="M282">
+        <v>1</v>
+      </c>
+      <c r="N282">
+        <v>1</v>
+      </c>
+      <c r="O282" t="s">
+        <v>91</v>
+      </c>
+      <c r="P282" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q282">
+        <v>3.5</v>
+      </c>
+      <c r="R282">
+        <v>2.25</v>
+      </c>
+      <c r="S282">
+        <v>2.88</v>
+      </c>
+      <c r="T282">
+        <v>1.33</v>
+      </c>
+      <c r="U282">
+        <v>3.25</v>
+      </c>
+      <c r="V282">
+        <v>2.63</v>
+      </c>
+      <c r="W282">
+        <v>1.44</v>
+      </c>
+      <c r="X282">
+        <v>6.5</v>
+      </c>
+      <c r="Y282">
+        <v>1.11</v>
+      </c>
+      <c r="Z282">
+        <v>3.3</v>
+      </c>
+      <c r="AA282">
+        <v>3.65</v>
+      </c>
+      <c r="AB282">
+        <v>2</v>
+      </c>
+      <c r="AC282">
+        <v>1.03</v>
+      </c>
+      <c r="AD282">
+        <v>17</v>
+      </c>
+      <c r="AE282">
+        <v>1.19</v>
+      </c>
+      <c r="AF282">
+        <v>5</v>
+      </c>
+      <c r="AG282">
+        <v>1.57</v>
+      </c>
+      <c r="AH282">
+        <v>2.25</v>
+      </c>
+      <c r="AI282">
+        <v>1.57</v>
+      </c>
+      <c r="AJ282">
+        <v>2.25</v>
+      </c>
+      <c r="AK282">
+        <v>1.65</v>
+      </c>
+      <c r="AL282">
+        <v>1.28</v>
+      </c>
+      <c r="AM282">
+        <v>1.36</v>
+      </c>
+      <c r="AN282">
+        <v>1.21</v>
+      </c>
+      <c r="AO282">
+        <v>1.5</v>
+      </c>
+      <c r="AP282">
+        <v>1.13</v>
+      </c>
+      <c r="AQ282">
+        <v>1.6</v>
+      </c>
+      <c r="AR282">
+        <v>1.26</v>
+      </c>
+      <c r="AS282">
+        <v>1.35</v>
+      </c>
+      <c r="AT282">
+        <v>2.61</v>
+      </c>
+      <c r="AU282">
+        <v>3</v>
+      </c>
+      <c r="AV282">
+        <v>4</v>
+      </c>
+      <c r="AW282">
+        <v>7</v>
+      </c>
+      <c r="AX282">
+        <v>6</v>
+      </c>
+      <c r="AY282">
+        <v>16</v>
+      </c>
+      <c r="AZ282">
+        <v>11</v>
+      </c>
+      <c r="BA282">
+        <v>3</v>
+      </c>
+      <c r="BB282">
+        <v>4</v>
+      </c>
+      <c r="BC282">
+        <v>7</v>
+      </c>
+      <c r="BD282">
+        <v>2.2</v>
+      </c>
+      <c r="BE282">
+        <v>6.75</v>
+      </c>
+      <c r="BF282">
+        <v>1.79</v>
+      </c>
+      <c r="BG282">
+        <v>1.19</v>
+      </c>
+      <c r="BH282">
+        <v>4.1</v>
+      </c>
+      <c r="BI282">
+        <v>1.33</v>
+      </c>
+      <c r="BJ282">
+        <v>2.95</v>
+      </c>
+      <c r="BK282">
+        <v>1.55</v>
+      </c>
+      <c r="BL282">
+        <v>2.28</v>
+      </c>
+      <c r="BM282">
+        <v>1.88</v>
+      </c>
+      <c r="BN282">
+        <v>1.81</v>
+      </c>
+      <c r="BO282">
+        <v>2.33</v>
+      </c>
+      <c r="BP282">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1754" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="425">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -841,6 +841,18 @@
     <t>['45+2']</t>
   </si>
   <si>
+    <t>['75']</t>
+  </si>
+  <si>
+    <t>['90+1']</t>
+  </si>
+  <si>
+    <t>['82', '90+3']</t>
+  </si>
+  <si>
+    <t>['11', '39']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1266,6 +1278,18 @@
   <si>
     <t>['42', '65']</t>
   </si>
+  <si>
+    <t>['19', '47']</t>
+  </si>
+  <si>
+    <t>['35', '37', '41', '87']</t>
+  </si>
+  <si>
+    <t>['21', '48']</t>
+  </si>
+  <si>
+    <t>['30', '71']</t>
+  </si>
 </sst>
 </file>
 
@@ -1626,7 +1650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP282"/>
+  <dimension ref="A1:BP287"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2088,7 +2112,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2166,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AQ3">
         <v>2.33</v>
@@ -2375,7 +2399,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ4">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2500,7 +2524,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2578,10 +2602,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ5">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2912,7 +2936,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -3118,7 +3142,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3530,7 +3554,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -4435,7 +4459,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ14">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4844,10 +4868,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AQ16">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5050,7 +5074,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ17">
         <v>0.71</v>
@@ -5178,7 +5202,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5384,7 +5408,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5668,7 +5692,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ20">
         <v>1.6</v>
@@ -5877,7 +5901,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ21">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -6083,7 +6107,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ22">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR22">
         <v>1.72</v>
@@ -6208,7 +6232,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6414,7 +6438,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6492,7 +6516,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AQ24">
         <v>1.57</v>
@@ -6701,7 +6725,7 @@
         <v>2</v>
       </c>
       <c r="AQ25">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR25">
         <v>1.78</v>
@@ -7032,7 +7056,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7110,7 +7134,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ27">
         <v>1.53</v>
@@ -7238,7 +7262,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7444,7 +7468,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7856,7 +7880,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8062,7 +8086,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8140,7 +8164,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AQ32">
         <v>1.08</v>
@@ -8474,7 +8498,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -8761,7 +8785,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ35">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR35">
         <v>1.87</v>
@@ -8967,7 +8991,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ36">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR36">
         <v>1.93</v>
@@ -9170,10 +9194,10 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ37">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR37">
         <v>1.98</v>
@@ -9298,7 +9322,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9504,7 +9528,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9582,7 +9606,7 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ39">
         <v>1.5</v>
@@ -9710,7 +9734,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9916,7 +9940,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -10122,7 +10146,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10328,7 +10352,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -11024,7 +11048,7 @@
         <v>0.5</v>
       </c>
       <c r="AP46">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AQ46">
         <v>0.71</v>
@@ -11233,7 +11257,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ47">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR47">
         <v>1.75</v>
@@ -11439,7 +11463,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ48">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR48">
         <v>1.44</v>
@@ -11851,7 +11875,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ50">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR50">
         <v>1.67</v>
@@ -11976,7 +12000,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -12054,7 +12078,7 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ51">
         <v>1.8</v>
@@ -12182,7 +12206,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12388,7 +12412,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12672,7 +12696,7 @@
         <v>0.5</v>
       </c>
       <c r="AP54">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ54">
         <v>1.69</v>
@@ -12800,7 +12824,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -13087,7 +13111,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ56">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR56">
         <v>1.59</v>
@@ -13212,7 +13236,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13293,7 +13317,7 @@
         <v>2</v>
       </c>
       <c r="AQ57">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR57">
         <v>1.39</v>
@@ -13418,7 +13442,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13624,7 +13648,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13702,7 +13726,7 @@
         <v>3</v>
       </c>
       <c r="AP59">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AQ59">
         <v>1.21</v>
@@ -13830,7 +13854,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -14036,7 +14060,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14114,7 +14138,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ61">
         <v>0.33</v>
@@ -14242,7 +14266,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14654,7 +14678,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14732,7 +14756,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ64">
         <v>1.57</v>
@@ -14860,7 +14884,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -15066,7 +15090,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -15147,7 +15171,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ66">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR66">
         <v>1.43</v>
@@ -15556,7 +15580,7 @@
         <v>1.33</v>
       </c>
       <c r="AP68">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ68">
         <v>1.6</v>
@@ -15765,7 +15789,7 @@
         <v>2</v>
       </c>
       <c r="AQ69">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR69">
         <v>1.45</v>
@@ -16096,7 +16120,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16383,7 +16407,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ72">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR72">
         <v>1.91</v>
@@ -16508,7 +16532,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16714,7 +16738,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16795,7 +16819,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ74">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR74">
         <v>1.31</v>
@@ -16920,7 +16944,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -17001,7 +17025,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ75">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR75">
         <v>0.91</v>
@@ -17126,7 +17150,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17204,7 +17228,7 @@
         <v>0.33</v>
       </c>
       <c r="AP76">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AQ76">
         <v>0.57</v>
@@ -17332,7 +17356,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17410,7 +17434,7 @@
         <v>0.33</v>
       </c>
       <c r="AP77">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AQ77">
         <v>1.07</v>
@@ -17616,7 +17640,7 @@
         <v>2.33</v>
       </c>
       <c r="AP78">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ78">
         <v>1.8</v>
@@ -17744,7 +17768,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17950,7 +17974,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18362,7 +18386,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18443,7 +18467,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ82">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR82">
         <v>1.04</v>
@@ -18646,7 +18670,7 @@
         <v>0</v>
       </c>
       <c r="AP83">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ83">
         <v>0.33</v>
@@ -18774,7 +18798,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18855,7 +18879,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ84">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR84">
         <v>1.51</v>
@@ -18980,7 +19004,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -19186,7 +19210,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19470,7 +19494,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ87">
         <v>1.57</v>
@@ -19598,7 +19622,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -20010,7 +20034,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20216,7 +20240,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20706,7 +20730,7 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AQ93">
         <v>1.07</v>
@@ -20912,7 +20936,7 @@
         <v>2.5</v>
       </c>
       <c r="AP94">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ94">
         <v>1.4</v>
@@ -21118,7 +21142,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AQ95">
         <v>0.57</v>
@@ -21327,7 +21351,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ96">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR96">
         <v>1.78</v>
@@ -21533,7 +21557,7 @@
         <v>2</v>
       </c>
       <c r="AQ97">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR97">
         <v>1.51</v>
@@ -21658,7 +21682,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21864,7 +21888,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -22070,7 +22094,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22357,7 +22381,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ101">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR101">
         <v>1.81</v>
@@ -22482,7 +22506,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22688,7 +22712,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23924,7 +23948,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -24130,7 +24154,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24542,7 +24566,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24748,7 +24772,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -24829,7 +24853,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ113">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR113">
         <v>1.98</v>
@@ -25032,10 +25056,10 @@
         <v>0</v>
       </c>
       <c r="AP114">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ114">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR114">
         <v>1.26</v>
@@ -25241,7 +25265,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ115">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR115">
         <v>2.22</v>
@@ -25366,7 +25390,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25444,10 +25468,10 @@
         <v>1.4</v>
       </c>
       <c r="AP116">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ116">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR116">
         <v>1.57</v>
@@ -25572,7 +25596,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25778,7 +25802,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25856,7 +25880,7 @@
         <v>0.8</v>
       </c>
       <c r="AP118">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ118">
         <v>1.23</v>
@@ -25984,7 +26008,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -26062,7 +26086,7 @@
         <v>2.6</v>
       </c>
       <c r="AP119">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AQ119">
         <v>2.33</v>
@@ -26190,7 +26214,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26268,7 +26292,7 @@
         <v>1</v>
       </c>
       <c r="AP120">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AQ120">
         <v>1.08</v>
@@ -26396,7 +26420,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26477,7 +26501,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ121">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR121">
         <v>1.12</v>
@@ -26602,7 +26626,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26808,7 +26832,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -27426,7 +27450,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27632,7 +27656,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -28250,7 +28274,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28662,7 +28686,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28740,7 +28764,7 @@
         <v>0.5</v>
       </c>
       <c r="AP132">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AQ132">
         <v>1.69</v>
@@ -28949,7 +28973,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ133">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR133">
         <v>1.02</v>
@@ -29074,7 +29098,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29152,7 +29176,7 @@
         <v>2.17</v>
       </c>
       <c r="AP134">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AQ134">
         <v>1.5</v>
@@ -29280,7 +29304,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -29564,10 +29588,10 @@
         <v>1.83</v>
       </c>
       <c r="AP136">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ136">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR136">
         <v>2.3</v>
@@ -29770,10 +29794,10 @@
         <v>0.83</v>
       </c>
       <c r="AP137">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ137">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR137">
         <v>1.42</v>
@@ -29979,7 +30003,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ138">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR138">
         <v>1.44</v>
@@ -30391,7 +30415,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ140">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR140">
         <v>1.88</v>
@@ -30594,7 +30618,7 @@
         <v>1.17</v>
       </c>
       <c r="AP141">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ141">
         <v>1.23</v>
@@ -30722,7 +30746,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30928,7 +30952,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -31340,7 +31364,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31421,7 +31445,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ145">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR145">
         <v>1.4</v>
@@ -31546,7 +31570,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31752,7 +31776,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31830,7 +31854,7 @@
         <v>1.14</v>
       </c>
       <c r="AP147">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AQ147">
         <v>1.53</v>
@@ -31958,7 +31982,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -32039,7 +32063,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ148">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR148">
         <v>1.08</v>
@@ -32164,7 +32188,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32451,7 +32475,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ150">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR150">
         <v>1.48</v>
@@ -32576,7 +32600,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -33194,7 +33218,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33400,7 +33424,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33606,7 +33630,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33812,7 +33836,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33890,7 +33914,7 @@
         <v>0.86</v>
       </c>
       <c r="AP157">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ157">
         <v>1.08</v>
@@ -34018,7 +34042,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34096,7 +34120,7 @@
         <v>1</v>
       </c>
       <c r="AP158">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AQ158">
         <v>1.23</v>
@@ -34305,7 +34329,7 @@
         <v>2</v>
       </c>
       <c r="AQ159">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR159">
         <v>1.69</v>
@@ -34508,10 +34532,10 @@
         <v>1.14</v>
       </c>
       <c r="AP160">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ160">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR160">
         <v>1.69</v>
@@ -34842,7 +34866,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -34923,7 +34947,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ162">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR162">
         <v>1.71</v>
@@ -35048,7 +35072,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35129,7 +35153,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ163">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR163">
         <v>1.48</v>
@@ -35254,7 +35278,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35332,7 +35356,7 @@
         <v>1.13</v>
       </c>
       <c r="AP164">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AQ164">
         <v>1.6</v>
@@ -35460,7 +35484,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35872,7 +35896,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35953,7 +35977,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ167">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR167">
         <v>1.06</v>
@@ -36078,7 +36102,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36362,7 +36386,7 @@
         <v>2.38</v>
       </c>
       <c r="AP169">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ169">
         <v>1.5</v>
@@ -36490,7 +36514,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36774,7 +36798,7 @@
         <v>0.75</v>
       </c>
       <c r="AP171">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ171">
         <v>1.07</v>
@@ -36902,7 +36926,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -36980,10 +37004,10 @@
         <v>1.13</v>
       </c>
       <c r="AP172">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AQ172">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR172">
         <v>1.06</v>
@@ -37520,7 +37544,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -37804,7 +37828,7 @@
         <v>1.13</v>
       </c>
       <c r="AP176">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ176">
         <v>1.69</v>
@@ -38138,7 +38162,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38425,7 +38449,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ179">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR179">
         <v>1.54</v>
@@ -38756,7 +38780,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38962,7 +38986,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39043,7 +39067,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ182">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR182">
         <v>1.74</v>
@@ -39374,7 +39398,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39580,7 +39604,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39658,10 +39682,10 @@
         <v>1.89</v>
       </c>
       <c r="AP185">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ185">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR185">
         <v>1.32</v>
@@ -39786,7 +39810,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -40070,7 +40094,7 @@
         <v>2.22</v>
       </c>
       <c r="AP187">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AQ187">
         <v>1.5</v>
@@ -40198,7 +40222,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40279,7 +40303,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ188">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR188">
         <v>1.51</v>
@@ -40404,7 +40428,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40610,7 +40634,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40816,7 +40840,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -41100,7 +41124,7 @@
         <v>0.78</v>
       </c>
       <c r="AP192">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ192">
         <v>1.07</v>
@@ -41228,7 +41252,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41640,7 +41664,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41718,10 +41742,10 @@
         <v>0.22</v>
       </c>
       <c r="AP195">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AQ195">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR195">
         <v>1.14</v>
@@ -41846,7 +41870,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -41924,10 +41948,10 @@
         <v>1.33</v>
       </c>
       <c r="AP196">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ196">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR196">
         <v>2.09</v>
@@ -42258,7 +42282,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42464,7 +42488,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42670,7 +42694,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42751,7 +42775,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ200">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR200">
         <v>1.18</v>
@@ -42876,7 +42900,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -43082,7 +43106,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43288,7 +43312,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43494,7 +43518,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43700,7 +43724,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -43987,7 +44011,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ206">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR206">
         <v>1.56</v>
@@ -44112,7 +44136,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44190,7 +44214,7 @@
         <v>1.11</v>
       </c>
       <c r="AP207">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ207">
         <v>1.21</v>
@@ -44524,7 +44548,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44602,10 +44626,10 @@
         <v>1.3</v>
       </c>
       <c r="AP209">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AQ209">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR209">
         <v>1.16</v>
@@ -44936,7 +44960,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45142,7 +45166,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45348,7 +45372,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45554,7 +45578,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45760,7 +45784,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -45966,7 +45990,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -46047,7 +46071,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ216">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR216">
         <v>1.58</v>
@@ -46172,7 +46196,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46378,7 +46402,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46456,7 +46480,7 @@
         <v>1</v>
       </c>
       <c r="AP218">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ218">
         <v>1.23</v>
@@ -46584,7 +46608,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46662,7 +46686,7 @@
         <v>1.36</v>
       </c>
       <c r="AP219">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AQ219">
         <v>1.4</v>
@@ -46790,7 +46814,7 @@
         <v>240</v>
       </c>
       <c r="P220" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q220">
         <v>1.73</v>
@@ -46871,7 +46895,7 @@
         <v>2</v>
       </c>
       <c r="AQ220">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR220">
         <v>1.85</v>
@@ -47074,10 +47098,10 @@
         <v>2.09</v>
       </c>
       <c r="AP221">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ221">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR221">
         <v>1.77</v>
@@ -47202,7 +47226,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -47614,7 +47638,7 @@
         <v>107</v>
       </c>
       <c r="P224" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="Q224">
         <v>6</v>
@@ -47692,7 +47716,7 @@
         <v>1.64</v>
       </c>
       <c r="AP224">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AQ224">
         <v>1.6</v>
@@ -47820,7 +47844,7 @@
         <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q225">
         <v>6.5</v>
@@ -48026,7 +48050,7 @@
         <v>243</v>
       </c>
       <c r="P226" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="Q226">
         <v>2.38</v>
@@ -48104,7 +48128,7 @@
         <v>1.91</v>
       </c>
       <c r="AP226">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ226">
         <v>1.5</v>
@@ -48232,7 +48256,7 @@
         <v>155</v>
       </c>
       <c r="P227" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48313,7 +48337,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ227">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR227">
         <v>1.4</v>
@@ -48438,7 +48462,7 @@
         <v>244</v>
       </c>
       <c r="P228" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="Q228">
         <v>1.91</v>
@@ -48725,7 +48749,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ229">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR229">
         <v>1.51</v>
@@ -48850,7 +48874,7 @@
         <v>91</v>
       </c>
       <c r="P230" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="Q230">
         <v>2.88</v>
@@ -49137,7 +49161,7 @@
         <v>2</v>
       </c>
       <c r="AQ231">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR231">
         <v>1.47</v>
@@ -49262,7 +49286,7 @@
         <v>95</v>
       </c>
       <c r="P232" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="Q232">
         <v>2.2</v>
@@ -49546,7 +49570,7 @@
         <v>0.73</v>
       </c>
       <c r="AP233">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ233">
         <v>0.57</v>
@@ -49674,7 +49698,7 @@
         <v>151</v>
       </c>
       <c r="P234" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q234">
         <v>2.6</v>
@@ -49752,7 +49776,7 @@
         <v>0.17</v>
       </c>
       <c r="AP234">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AQ234">
         <v>0.33</v>
@@ -49880,7 +49904,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="Q235">
         <v>4.5</v>
@@ -49958,7 +49982,7 @@
         <v>2.45</v>
       </c>
       <c r="AP235">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ235">
         <v>2.33</v>
@@ -50292,7 +50316,7 @@
         <v>91</v>
       </c>
       <c r="P237" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50498,7 +50522,7 @@
         <v>91</v>
       </c>
       <c r="P238" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="Q238">
         <v>2.75</v>
@@ -50910,7 +50934,7 @@
         <v>249</v>
       </c>
       <c r="P240" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="Q240">
         <v>1.8</v>
@@ -50991,7 +51015,7 @@
         <v>2</v>
       </c>
       <c r="AQ240">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR240">
         <v>1.89</v>
@@ -51116,7 +51140,7 @@
         <v>250</v>
       </c>
       <c r="P241" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="Q241">
         <v>6</v>
@@ -51194,7 +51218,7 @@
         <v>2.5</v>
       </c>
       <c r="AP241">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ241">
         <v>2.33</v>
@@ -51528,7 +51552,7 @@
         <v>91</v>
       </c>
       <c r="P243" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="Q243">
         <v>9</v>
@@ -51734,7 +51758,7 @@
         <v>203</v>
       </c>
       <c r="P244" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="Q244">
         <v>5</v>
@@ -51812,7 +51836,7 @@
         <v>1.58</v>
       </c>
       <c r="AP244">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AQ244">
         <v>1.53</v>
@@ -52018,7 +52042,7 @@
         <v>1.75</v>
       </c>
       <c r="AP245">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ245">
         <v>1.6</v>
@@ -52227,7 +52251,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ246">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR246">
         <v>1.24</v>
@@ -52433,7 +52457,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ247">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR247">
         <v>1.54</v>
@@ -52764,7 +52788,7 @@
         <v>254</v>
       </c>
       <c r="P249" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="Q249">
         <v>2.63</v>
@@ -52970,7 +52994,7 @@
         <v>255</v>
       </c>
       <c r="P250" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q250">
         <v>1.57</v>
@@ -53051,7 +53075,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ250">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR250">
         <v>1.85</v>
@@ -53382,7 +53406,7 @@
         <v>256</v>
       </c>
       <c r="P252" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="Q252">
         <v>4</v>
@@ -53588,7 +53612,7 @@
         <v>91</v>
       </c>
       <c r="P253" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="Q253">
         <v>3.6</v>
@@ -53669,7 +53693,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ253">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR253">
         <v>1.19</v>
@@ -53794,7 +53818,7 @@
         <v>257</v>
       </c>
       <c r="P254" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="Q254">
         <v>3.25</v>
@@ -53872,7 +53896,7 @@
         <v>1.08</v>
       </c>
       <c r="AP254">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ254">
         <v>1.08</v>
@@ -54000,7 +54024,7 @@
         <v>91</v>
       </c>
       <c r="P255" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="Q255">
         <v>5</v>
@@ -54078,10 +54102,10 @@
         <v>1.46</v>
       </c>
       <c r="AP255">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AQ255">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR255">
         <v>1.18</v>
@@ -54206,7 +54230,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="Q256">
         <v>3.75</v>
@@ -54284,7 +54308,7 @@
         <v>1.08</v>
       </c>
       <c r="AP256">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AQ256">
         <v>1.23</v>
@@ -54412,7 +54436,7 @@
         <v>91</v>
       </c>
       <c r="P257" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="Q257">
         <v>1.73</v>
@@ -54493,7 +54517,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ257">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR257">
         <v>1.97</v>
@@ -54696,10 +54720,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP258">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ258">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR258">
         <v>1.79</v>
@@ -54824,7 +54848,7 @@
         <v>91</v>
       </c>
       <c r="P259" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="Q259">
         <v>2.75</v>
@@ -55030,7 +55054,7 @@
         <v>258</v>
       </c>
       <c r="P260" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q260">
         <v>3.1</v>
@@ -55236,7 +55260,7 @@
         <v>259</v>
       </c>
       <c r="P261" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="Q261">
         <v>2.38</v>
@@ -55317,7 +55341,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ261">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR261">
         <v>1.6</v>
@@ -55442,7 +55466,7 @@
         <v>91</v>
       </c>
       <c r="P262" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="Q262">
         <v>3.1</v>
@@ -55520,7 +55544,7 @@
         <v>2.29</v>
       </c>
       <c r="AP262">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ262">
         <v>2.33</v>
@@ -55648,7 +55672,7 @@
         <v>260</v>
       </c>
       <c r="P263" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Q263">
         <v>3.2</v>
@@ -55854,7 +55878,7 @@
         <v>261</v>
       </c>
       <c r="P264" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="Q264">
         <v>3.5</v>
@@ -56678,7 +56702,7 @@
         <v>264</v>
       </c>
       <c r="P268" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="Q268">
         <v>2.05</v>
@@ -57914,7 +57938,7 @@
         <v>269</v>
       </c>
       <c r="P274" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="Q274">
         <v>1.4</v>
@@ -58120,7 +58144,7 @@
         <v>270</v>
       </c>
       <c r="P275" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q275">
         <v>2.5</v>
@@ -59150,7 +59174,7 @@
         <v>273</v>
       </c>
       <c r="P280" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="Q280">
         <v>2.88</v>
@@ -59356,7 +59380,7 @@
         <v>274</v>
       </c>
       <c r="P281" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q281">
         <v>5.5</v>
@@ -59562,7 +59586,7 @@
         <v>91</v>
       </c>
       <c r="P282" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="Q282">
         <v>3.5</v>
@@ -59719,6 +59743,1036 @@
       </c>
       <c r="BP282">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="283" spans="1:68">
+      <c r="A283" s="1">
+        <v>282</v>
+      </c>
+      <c r="B283">
+        <v>7466968</v>
+      </c>
+      <c r="C283" t="s">
+        <v>68</v>
+      </c>
+      <c r="D283" t="s">
+        <v>69</v>
+      </c>
+      <c r="E283" s="2">
+        <v>45731.5</v>
+      </c>
+      <c r="F283">
+        <v>29</v>
+      </c>
+      <c r="G283" t="s">
+        <v>84</v>
+      </c>
+      <c r="H283" t="s">
+        <v>87</v>
+      </c>
+      <c r="I283">
+        <v>0</v>
+      </c>
+      <c r="J283">
+        <v>1</v>
+      </c>
+      <c r="K283">
+        <v>1</v>
+      </c>
+      <c r="L283">
+        <v>1</v>
+      </c>
+      <c r="M283">
+        <v>2</v>
+      </c>
+      <c r="N283">
+        <v>3</v>
+      </c>
+      <c r="O283" t="s">
+        <v>275</v>
+      </c>
+      <c r="P283" t="s">
+        <v>421</v>
+      </c>
+      <c r="Q283">
+        <v>4</v>
+      </c>
+      <c r="R283">
+        <v>2.2</v>
+      </c>
+      <c r="S283">
+        <v>2.75</v>
+      </c>
+      <c r="T283">
+        <v>1.36</v>
+      </c>
+      <c r="U283">
+        <v>3</v>
+      </c>
+      <c r="V283">
+        <v>2.75</v>
+      </c>
+      <c r="W283">
+        <v>1.4</v>
+      </c>
+      <c r="X283">
+        <v>7</v>
+      </c>
+      <c r="Y283">
+        <v>1.1</v>
+      </c>
+      <c r="Z283">
+        <v>3.4</v>
+      </c>
+      <c r="AA283">
+        <v>3.5</v>
+      </c>
+      <c r="AB283">
+        <v>2.05</v>
+      </c>
+      <c r="AC283">
+        <v>1.05</v>
+      </c>
+      <c r="AD283">
+        <v>9</v>
+      </c>
+      <c r="AE283">
+        <v>1.28</v>
+      </c>
+      <c r="AF283">
+        <v>3.6</v>
+      </c>
+      <c r="AG283">
+        <v>1.75</v>
+      </c>
+      <c r="AH283">
+        <v>2.01</v>
+      </c>
+      <c r="AI283">
+        <v>1.67</v>
+      </c>
+      <c r="AJ283">
+        <v>2.1</v>
+      </c>
+      <c r="AK283">
+        <v>1.73</v>
+      </c>
+      <c r="AL283">
+        <v>1.29</v>
+      </c>
+      <c r="AM283">
+        <v>1.3</v>
+      </c>
+      <c r="AN283">
+        <v>0.31</v>
+      </c>
+      <c r="AO283">
+        <v>0.86</v>
+      </c>
+      <c r="AP283">
+        <v>0.29</v>
+      </c>
+      <c r="AQ283">
+        <v>1</v>
+      </c>
+      <c r="AR283">
+        <v>1.16</v>
+      </c>
+      <c r="AS283">
+        <v>1.32</v>
+      </c>
+      <c r="AT283">
+        <v>2.48</v>
+      </c>
+      <c r="AU283">
+        <v>4</v>
+      </c>
+      <c r="AV283">
+        <v>4</v>
+      </c>
+      <c r="AW283">
+        <v>7</v>
+      </c>
+      <c r="AX283">
+        <v>2</v>
+      </c>
+      <c r="AY283">
+        <v>12</v>
+      </c>
+      <c r="AZ283">
+        <v>6</v>
+      </c>
+      <c r="BA283">
+        <v>5</v>
+      </c>
+      <c r="BB283">
+        <v>1</v>
+      </c>
+      <c r="BC283">
+        <v>6</v>
+      </c>
+      <c r="BD283">
+        <v>2.53</v>
+      </c>
+      <c r="BE283">
+        <v>6.7</v>
+      </c>
+      <c r="BF283">
+        <v>1.84</v>
+      </c>
+      <c r="BG283">
+        <v>1.18</v>
+      </c>
+      <c r="BH283">
+        <v>3.84</v>
+      </c>
+      <c r="BI283">
+        <v>1.38</v>
+      </c>
+      <c r="BJ283">
+        <v>2.71</v>
+      </c>
+      <c r="BK283">
+        <v>1.7</v>
+      </c>
+      <c r="BL283">
+        <v>2.03</v>
+      </c>
+      <c r="BM283">
+        <v>2.05</v>
+      </c>
+      <c r="BN283">
+        <v>1.7</v>
+      </c>
+      <c r="BO283">
+        <v>2.78</v>
+      </c>
+      <c r="BP283">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="284" spans="1:68">
+      <c r="A284" s="1">
+        <v>283</v>
+      </c>
+      <c r="B284">
+        <v>7466962</v>
+      </c>
+      <c r="C284" t="s">
+        <v>68</v>
+      </c>
+      <c r="D284" t="s">
+        <v>69</v>
+      </c>
+      <c r="E284" s="2">
+        <v>45731.5</v>
+      </c>
+      <c r="F284">
+        <v>29</v>
+      </c>
+      <c r="G284" t="s">
+        <v>73</v>
+      </c>
+      <c r="H284" t="s">
+        <v>76</v>
+      </c>
+      <c r="I284">
+        <v>0</v>
+      </c>
+      <c r="J284">
+        <v>0</v>
+      </c>
+      <c r="K284">
+        <v>0</v>
+      </c>
+      <c r="L284">
+        <v>1</v>
+      </c>
+      <c r="M284">
+        <v>1</v>
+      </c>
+      <c r="N284">
+        <v>2</v>
+      </c>
+      <c r="O284" t="s">
+        <v>276</v>
+      </c>
+      <c r="P284" t="s">
+        <v>341</v>
+      </c>
+      <c r="Q284">
+        <v>2.88</v>
+      </c>
+      <c r="R284">
+        <v>2.05</v>
+      </c>
+      <c r="S284">
+        <v>4.33</v>
+      </c>
+      <c r="T284">
+        <v>1.5</v>
+      </c>
+      <c r="U284">
+        <v>2.5</v>
+      </c>
+      <c r="V284">
+        <v>3.4</v>
+      </c>
+      <c r="W284">
+        <v>1.3</v>
+      </c>
+      <c r="X284">
+        <v>10</v>
+      </c>
+      <c r="Y284">
+        <v>1.06</v>
+      </c>
+      <c r="Z284">
+        <v>2.1</v>
+      </c>
+      <c r="AA284">
+        <v>3.35</v>
+      </c>
+      <c r="AB284">
+        <v>3.45</v>
+      </c>
+      <c r="AC284">
+        <v>1.08</v>
+      </c>
+      <c r="AD284">
+        <v>7.5</v>
+      </c>
+      <c r="AE284">
+        <v>1.42</v>
+      </c>
+      <c r="AF284">
+        <v>2.8</v>
+      </c>
+      <c r="AG284">
+        <v>1.7</v>
+      </c>
+      <c r="AH284">
+        <v>2.05</v>
+      </c>
+      <c r="AI284">
+        <v>1.95</v>
+      </c>
+      <c r="AJ284">
+        <v>1.8</v>
+      </c>
+      <c r="AK284">
+        <v>1.29</v>
+      </c>
+      <c r="AL284">
+        <v>1.33</v>
+      </c>
+      <c r="AM284">
+        <v>1.68</v>
+      </c>
+      <c r="AN284">
+        <v>1.29</v>
+      </c>
+      <c r="AO284">
+        <v>1.23</v>
+      </c>
+      <c r="AP284">
+        <v>1.27</v>
+      </c>
+      <c r="AQ284">
+        <v>1.21</v>
+      </c>
+      <c r="AR284">
+        <v>1.4</v>
+      </c>
+      <c r="AS284">
+        <v>1.41</v>
+      </c>
+      <c r="AT284">
+        <v>2.81</v>
+      </c>
+      <c r="AU284">
+        <v>6</v>
+      </c>
+      <c r="AV284">
+        <v>5</v>
+      </c>
+      <c r="AW284">
+        <v>8</v>
+      </c>
+      <c r="AX284">
+        <v>5</v>
+      </c>
+      <c r="AY284">
+        <v>17</v>
+      </c>
+      <c r="AZ284">
+        <v>11</v>
+      </c>
+      <c r="BA284">
+        <v>6</v>
+      </c>
+      <c r="BB284">
+        <v>5</v>
+      </c>
+      <c r="BC284">
+        <v>11</v>
+      </c>
+      <c r="BD284">
+        <v>1.73</v>
+      </c>
+      <c r="BE284">
+        <v>8</v>
+      </c>
+      <c r="BF284">
+        <v>2.38</v>
+      </c>
+      <c r="BG284">
+        <v>1.2</v>
+      </c>
+      <c r="BH284">
+        <v>3.7</v>
+      </c>
+      <c r="BI284">
+        <v>1.41</v>
+      </c>
+      <c r="BJ284">
+        <v>2.6</v>
+      </c>
+      <c r="BK284">
+        <v>1.73</v>
+      </c>
+      <c r="BL284">
+        <v>2</v>
+      </c>
+      <c r="BM284">
+        <v>2.19</v>
+      </c>
+      <c r="BN284">
+        <v>1.57</v>
+      </c>
+      <c r="BO284">
+        <v>2.88</v>
+      </c>
+      <c r="BP284">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="285" spans="1:68">
+      <c r="A285" s="1">
+        <v>284</v>
+      </c>
+      <c r="B285">
+        <v>7466964</v>
+      </c>
+      <c r="C285" t="s">
+        <v>68</v>
+      </c>
+      <c r="D285" t="s">
+        <v>69</v>
+      </c>
+      <c r="E285" s="2">
+        <v>45731.5</v>
+      </c>
+      <c r="F285">
+        <v>29</v>
+      </c>
+      <c r="G285" t="s">
+        <v>71</v>
+      </c>
+      <c r="H285" t="s">
+        <v>75</v>
+      </c>
+      <c r="I285">
+        <v>0</v>
+      </c>
+      <c r="J285">
+        <v>3</v>
+      </c>
+      <c r="K285">
+        <v>3</v>
+      </c>
+      <c r="L285">
+        <v>2</v>
+      </c>
+      <c r="M285">
+        <v>4</v>
+      </c>
+      <c r="N285">
+        <v>6</v>
+      </c>
+      <c r="O285" t="s">
+        <v>277</v>
+      </c>
+      <c r="P285" t="s">
+        <v>422</v>
+      </c>
+      <c r="Q285">
+        <v>4</v>
+      </c>
+      <c r="R285">
+        <v>2.2</v>
+      </c>
+      <c r="S285">
+        <v>2.63</v>
+      </c>
+      <c r="T285">
+        <v>1.36</v>
+      </c>
+      <c r="U285">
+        <v>3</v>
+      </c>
+      <c r="V285">
+        <v>2.75</v>
+      </c>
+      <c r="W285">
+        <v>1.4</v>
+      </c>
+      <c r="X285">
+        <v>8</v>
+      </c>
+      <c r="Y285">
+        <v>1.08</v>
+      </c>
+      <c r="Z285">
+        <v>3.55</v>
+      </c>
+      <c r="AA285">
+        <v>3.35</v>
+      </c>
+      <c r="AB285">
+        <v>2.05</v>
+      </c>
+      <c r="AC285">
+        <v>1.05</v>
+      </c>
+      <c r="AD285">
+        <v>9</v>
+      </c>
+      <c r="AE285">
+        <v>1.28</v>
+      </c>
+      <c r="AF285">
+        <v>3.55</v>
+      </c>
+      <c r="AG285">
+        <v>1.7</v>
+      </c>
+      <c r="AH285">
+        <v>2.05</v>
+      </c>
+      <c r="AI285">
+        <v>1.7</v>
+      </c>
+      <c r="AJ285">
+        <v>2.05</v>
+      </c>
+      <c r="AK285">
+        <v>1.72</v>
+      </c>
+      <c r="AL285">
+        <v>1.29</v>
+      </c>
+      <c r="AM285">
+        <v>1.3</v>
+      </c>
+      <c r="AN285">
+        <v>0.5</v>
+      </c>
+      <c r="AO285">
+        <v>1.64</v>
+      </c>
+      <c r="AP285">
+        <v>0.47</v>
+      </c>
+      <c r="AQ285">
+        <v>1.73</v>
+      </c>
+      <c r="AR285">
+        <v>1.24</v>
+      </c>
+      <c r="AS285">
+        <v>1.36</v>
+      </c>
+      <c r="AT285">
+        <v>2.6</v>
+      </c>
+      <c r="AU285">
+        <v>5</v>
+      </c>
+      <c r="AV285">
+        <v>7</v>
+      </c>
+      <c r="AW285">
+        <v>7</v>
+      </c>
+      <c r="AX285">
+        <v>5</v>
+      </c>
+      <c r="AY285">
+        <v>15</v>
+      </c>
+      <c r="AZ285">
+        <v>12</v>
+      </c>
+      <c r="BA285">
+        <v>6</v>
+      </c>
+      <c r="BB285">
+        <v>3</v>
+      </c>
+      <c r="BC285">
+        <v>9</v>
+      </c>
+      <c r="BD285">
+        <v>2.1</v>
+      </c>
+      <c r="BE285">
+        <v>8.5</v>
+      </c>
+      <c r="BF285">
+        <v>1.85</v>
+      </c>
+      <c r="BG285">
+        <v>1.13</v>
+      </c>
+      <c r="BH285">
+        <v>4.5</v>
+      </c>
+      <c r="BI285">
+        <v>1.28</v>
+      </c>
+      <c r="BJ285">
+        <v>3.05</v>
+      </c>
+      <c r="BK285">
+        <v>1.53</v>
+      </c>
+      <c r="BL285">
+        <v>2.28</v>
+      </c>
+      <c r="BM285">
+        <v>1.9</v>
+      </c>
+      <c r="BN285">
+        <v>1.8</v>
+      </c>
+      <c r="BO285">
+        <v>2.45</v>
+      </c>
+      <c r="BP285">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="286" spans="1:68">
+      <c r="A286" s="1">
+        <v>285</v>
+      </c>
+      <c r="B286">
+        <v>7466966</v>
+      </c>
+      <c r="C286" t="s">
+        <v>68</v>
+      </c>
+      <c r="D286" t="s">
+        <v>69</v>
+      </c>
+      <c r="E286" s="2">
+        <v>45731.5</v>
+      </c>
+      <c r="F286">
+        <v>29</v>
+      </c>
+      <c r="G286" t="s">
+        <v>85</v>
+      </c>
+      <c r="H286" t="s">
+        <v>80</v>
+      </c>
+      <c r="I286">
+        <v>2</v>
+      </c>
+      <c r="J286">
+        <v>1</v>
+      </c>
+      <c r="K286">
+        <v>3</v>
+      </c>
+      <c r="L286">
+        <v>2</v>
+      </c>
+      <c r="M286">
+        <v>2</v>
+      </c>
+      <c r="N286">
+        <v>4</v>
+      </c>
+      <c r="O286" t="s">
+        <v>278</v>
+      </c>
+      <c r="P286" t="s">
+        <v>423</v>
+      </c>
+      <c r="Q286">
+        <v>2.2</v>
+      </c>
+      <c r="R286">
+        <v>2.5</v>
+      </c>
+      <c r="S286">
+        <v>4.5</v>
+      </c>
+      <c r="T286">
+        <v>1.25</v>
+      </c>
+      <c r="U286">
+        <v>3.75</v>
+      </c>
+      <c r="V286">
+        <v>2.2</v>
+      </c>
+      <c r="W286">
+        <v>1.62</v>
+      </c>
+      <c r="X286">
+        <v>5</v>
+      </c>
+      <c r="Y286">
+        <v>1.17</v>
+      </c>
+      <c r="Z286">
+        <v>1.67</v>
+      </c>
+      <c r="AA286">
+        <v>4.33</v>
+      </c>
+      <c r="AB286">
+        <v>4.33</v>
+      </c>
+      <c r="AC286">
+        <v>1.01</v>
+      </c>
+      <c r="AD286">
+        <v>13</v>
+      </c>
+      <c r="AE286">
+        <v>1.14</v>
+      </c>
+      <c r="AF286">
+        <v>5.5</v>
+      </c>
+      <c r="AG286">
+        <v>1.44</v>
+      </c>
+      <c r="AH286">
+        <v>2.75</v>
+      </c>
+      <c r="AI286">
+        <v>1.5</v>
+      </c>
+      <c r="AJ286">
+        <v>2.5</v>
+      </c>
+      <c r="AK286">
+        <v>1.2</v>
+      </c>
+      <c r="AL286">
+        <v>1.21</v>
+      </c>
+      <c r="AM286">
+        <v>2.15</v>
+      </c>
+      <c r="AN286">
+        <v>2</v>
+      </c>
+      <c r="AO286">
+        <v>1.57</v>
+      </c>
+      <c r="AP286">
+        <v>1.93</v>
+      </c>
+      <c r="AQ286">
+        <v>1.53</v>
+      </c>
+      <c r="AR286">
+        <v>1.99</v>
+      </c>
+      <c r="AS286">
+        <v>1.47</v>
+      </c>
+      <c r="AT286">
+        <v>3.46</v>
+      </c>
+      <c r="AU286">
+        <v>5</v>
+      </c>
+      <c r="AV286">
+        <v>4</v>
+      </c>
+      <c r="AW286">
+        <v>8</v>
+      </c>
+      <c r="AX286">
+        <v>12</v>
+      </c>
+      <c r="AY286">
+        <v>14</v>
+      </c>
+      <c r="AZ286">
+        <v>17</v>
+      </c>
+      <c r="BA286">
+        <v>4</v>
+      </c>
+      <c r="BB286">
+        <v>5</v>
+      </c>
+      <c r="BC286">
+        <v>9</v>
+      </c>
+      <c r="BD286">
+        <v>1.39</v>
+      </c>
+      <c r="BE286">
+        <v>10.25</v>
+      </c>
+      <c r="BF286">
+        <v>3.7</v>
+      </c>
+      <c r="BG286">
+        <v>1.13</v>
+      </c>
+      <c r="BH286">
+        <v>4.6</v>
+      </c>
+      <c r="BI286">
+        <v>1.27</v>
+      </c>
+      <c r="BJ286">
+        <v>3.14</v>
+      </c>
+      <c r="BK286">
+        <v>1.51</v>
+      </c>
+      <c r="BL286">
+        <v>2.32</v>
+      </c>
+      <c r="BM286">
+        <v>1.85</v>
+      </c>
+      <c r="BN286">
+        <v>1.85</v>
+      </c>
+      <c r="BO286">
+        <v>2.4</v>
+      </c>
+      <c r="BP286">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="287" spans="1:68">
+      <c r="A287" s="1">
+        <v>286</v>
+      </c>
+      <c r="B287">
+        <v>7466959</v>
+      </c>
+      <c r="C287" t="s">
+        <v>68</v>
+      </c>
+      <c r="D287" t="s">
+        <v>69</v>
+      </c>
+      <c r="E287" s="2">
+        <v>45731.60416666666</v>
+      </c>
+      <c r="F287">
+        <v>29</v>
+      </c>
+      <c r="G287" t="s">
+        <v>88</v>
+      </c>
+      <c r="H287" t="s">
+        <v>77</v>
+      </c>
+      <c r="I287">
+        <v>1</v>
+      </c>
+      <c r="J287">
+        <v>1</v>
+      </c>
+      <c r="K287">
+        <v>2</v>
+      </c>
+      <c r="L287">
+        <v>1</v>
+      </c>
+      <c r="M287">
+        <v>2</v>
+      </c>
+      <c r="N287">
+        <v>3</v>
+      </c>
+      <c r="O287" t="s">
+        <v>195</v>
+      </c>
+      <c r="P287" t="s">
+        <v>424</v>
+      </c>
+      <c r="Q287">
+        <v>2.25</v>
+      </c>
+      <c r="R287">
+        <v>2.5</v>
+      </c>
+      <c r="S287">
+        <v>4.33</v>
+      </c>
+      <c r="T287">
+        <v>1.25</v>
+      </c>
+      <c r="U287">
+        <v>3.75</v>
+      </c>
+      <c r="V287">
+        <v>2.1</v>
+      </c>
+      <c r="W287">
+        <v>1.67</v>
+      </c>
+      <c r="X287">
+        <v>4.5</v>
+      </c>
+      <c r="Y287">
+        <v>1.18</v>
+      </c>
+      <c r="Z287">
+        <v>1.86</v>
+      </c>
+      <c r="AA287">
+        <v>3.95</v>
+      </c>
+      <c r="AB287">
+        <v>3.65</v>
+      </c>
+      <c r="AC287">
+        <v>1.01</v>
+      </c>
+      <c r="AD287">
+        <v>17</v>
+      </c>
+      <c r="AE287">
+        <v>1.15</v>
+      </c>
+      <c r="AF287">
+        <v>5.25</v>
+      </c>
+      <c r="AG287">
+        <v>1.6</v>
+      </c>
+      <c r="AH287">
+        <v>2.25</v>
+      </c>
+      <c r="AI287">
+        <v>1.44</v>
+      </c>
+      <c r="AJ287">
+        <v>2.63</v>
+      </c>
+      <c r="AK287">
+        <v>1.23</v>
+      </c>
+      <c r="AL287">
+        <v>1.23</v>
+      </c>
+      <c r="AM287">
+        <v>2.05</v>
+      </c>
+      <c r="AN287">
+        <v>1.62</v>
+      </c>
+      <c r="AO287">
+        <v>1.08</v>
+      </c>
+      <c r="AP287">
+        <v>1.5</v>
+      </c>
+      <c r="AQ287">
+        <v>1.21</v>
+      </c>
+      <c r="AR287">
+        <v>1.74</v>
+      </c>
+      <c r="AS287">
+        <v>1.24</v>
+      </c>
+      <c r="AT287">
+        <v>2.98</v>
+      </c>
+      <c r="AU287">
+        <v>6</v>
+      </c>
+      <c r="AV287">
+        <v>5</v>
+      </c>
+      <c r="AW287">
+        <v>12</v>
+      </c>
+      <c r="AX287">
+        <v>6</v>
+      </c>
+      <c r="AY287">
+        <v>22</v>
+      </c>
+      <c r="AZ287">
+        <v>13</v>
+      </c>
+      <c r="BA287">
+        <v>4</v>
+      </c>
+      <c r="BB287">
+        <v>3</v>
+      </c>
+      <c r="BC287">
+        <v>7</v>
+      </c>
+      <c r="BD287">
+        <v>1.36</v>
+      </c>
+      <c r="BE287">
+        <v>10</v>
+      </c>
+      <c r="BF287">
+        <v>3.4</v>
+      </c>
+      <c r="BG287">
+        <v>1.06</v>
+      </c>
+      <c r="BH287">
+        <v>6.25</v>
+      </c>
+      <c r="BI287">
+        <v>1.16</v>
+      </c>
+      <c r="BJ287">
+        <v>4.2</v>
+      </c>
+      <c r="BK287">
+        <v>1.31</v>
+      </c>
+      <c r="BL287">
+        <v>2.92</v>
+      </c>
+      <c r="BM287">
+        <v>1.56</v>
+      </c>
+      <c r="BN287">
+        <v>2.21</v>
+      </c>
+      <c r="BO287">
+        <v>1.85</v>
+      </c>
+      <c r="BP287">
+        <v>1.85</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="427">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -853,6 +853,9 @@
     <t>['11', '39']</t>
   </si>
   <si>
+    <t>['78', '88']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1290,6 +1293,9 @@
   <si>
     <t>['30', '71']</t>
   </si>
+  <si>
+    <t>['28', '67', '90']</t>
+  </si>
 </sst>
 </file>
 
@@ -1650,7 +1656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP287"/>
+  <dimension ref="A1:BP290"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2112,7 +2118,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2396,7 +2402,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ4">
         <v>1</v>
@@ -2524,7 +2530,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2936,7 +2942,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -3142,7 +3148,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3554,7 +3560,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3838,10 +3844,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ11">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4047,7 +4053,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ12">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4662,7 +4668,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ15">
         <v>0.57</v>
@@ -5202,7 +5208,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5408,7 +5414,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5489,7 +5495,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ19">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -6104,7 +6110,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ22">
         <v>1.53</v>
@@ -6232,7 +6238,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6310,7 +6316,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ23">
         <v>1.21</v>
@@ -6438,7 +6444,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -7056,7 +7062,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7262,7 +7268,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7468,7 +7474,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7755,7 +7761,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ30">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR30">
         <v>0.47</v>
@@ -7880,7 +7886,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8086,7 +8092,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8167,7 +8173,7 @@
         <v>0.29</v>
       </c>
       <c r="AQ32">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR32">
         <v>0.65</v>
@@ -8498,7 +8504,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -8782,7 +8788,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ35">
         <v>1.21</v>
@@ -9322,7 +9328,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9528,7 +9534,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9609,7 +9615,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ39">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR39">
         <v>1.56</v>
@@ -9734,7 +9740,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9940,7 +9946,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -10146,7 +10152,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10227,7 +10233,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ42">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR42">
         <v>1.11</v>
@@ -10352,7 +10358,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10430,7 +10436,7 @@
         <v>2</v>
       </c>
       <c r="AP43">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ43">
         <v>1.6</v>
@@ -10636,7 +10642,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ44">
         <v>1.07</v>
@@ -11669,7 +11675,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ49">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR49">
         <v>1.39</v>
@@ -12000,7 +12006,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -12206,7 +12212,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12412,7 +12418,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12824,7 +12830,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -12902,7 +12908,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ55">
         <v>0.57</v>
@@ -13236,7 +13242,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13442,7 +13448,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13648,7 +13654,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13854,7 +13860,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13935,7 +13941,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ60">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR60">
         <v>1.43</v>
@@ -14060,7 +14066,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14266,7 +14272,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14550,7 +14556,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ63">
         <v>1.53</v>
@@ -14678,7 +14684,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14884,7 +14890,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -15090,7 +15096,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -15374,7 +15380,7 @@
         <v>0</v>
       </c>
       <c r="AP67">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ67">
         <v>0.33</v>
@@ -15995,7 +16001,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ70">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR70">
         <v>1.35</v>
@@ -16120,7 +16126,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16201,7 +16207,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ71">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR71">
         <v>1.59</v>
@@ -16532,7 +16538,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16610,7 +16616,7 @@
         <v>2.33</v>
       </c>
       <c r="AP73">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ73">
         <v>1.21</v>
@@ -16738,7 +16744,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16944,7 +16950,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -17150,7 +17156,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17356,7 +17362,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17768,7 +17774,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17974,7 +17980,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18055,7 +18061,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ80">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR80">
         <v>1.97</v>
@@ -18386,7 +18392,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18464,7 +18470,7 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ82">
         <v>1.73</v>
@@ -18798,7 +18804,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -19004,7 +19010,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -19210,7 +19216,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19622,7 +19628,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19909,7 +19915,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ89">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR89">
         <v>1.28</v>
@@ -20034,7 +20040,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20115,7 +20121,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ90">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR90">
         <v>1.61</v>
@@ -20240,7 +20246,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20318,7 +20324,7 @@
         <v>3</v>
       </c>
       <c r="AP91">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ91">
         <v>2.33</v>
@@ -21682,7 +21688,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21888,7 +21894,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -22094,7 +22100,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22175,7 +22181,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ100">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR100">
         <v>1.55</v>
@@ -22378,7 +22384,7 @@
         <v>0</v>
       </c>
       <c r="AP101">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ101">
         <v>1.21</v>
@@ -22506,7 +22512,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22712,7 +22718,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23948,7 +23954,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -24154,7 +24160,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24566,7 +24572,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24644,10 +24650,10 @@
         <v>2</v>
       </c>
       <c r="AP112">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ112">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR112">
         <v>1.12</v>
@@ -24772,7 +24778,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -24850,7 +24856,7 @@
         <v>0.4</v>
       </c>
       <c r="AP113">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ113">
         <v>1</v>
@@ -25262,7 +25268,7 @@
         <v>2.2</v>
       </c>
       <c r="AP115">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ115">
         <v>1.73</v>
@@ -25390,7 +25396,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25596,7 +25602,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25802,7 +25808,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25883,7 +25889,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ118">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR118">
         <v>2.34</v>
@@ -26008,7 +26014,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -26214,7 +26220,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26295,7 +26301,7 @@
         <v>0.47</v>
       </c>
       <c r="AQ120">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR120">
         <v>1.13</v>
@@ -26420,7 +26426,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26626,7 +26632,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26832,7 +26838,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -27450,7 +27456,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27656,7 +27662,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -28274,7 +28280,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28686,7 +28692,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28970,7 +28976,7 @@
         <v>1.33</v>
       </c>
       <c r="AP133">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ133">
         <v>1.21</v>
@@ -29098,7 +29104,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29179,7 +29185,7 @@
         <v>0.29</v>
       </c>
       <c r="AQ134">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR134">
         <v>1.08</v>
@@ -29304,7 +29310,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -30206,10 +30212,10 @@
         <v>1</v>
       </c>
       <c r="AP139">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ139">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR139">
         <v>2.18</v>
@@ -30412,7 +30418,7 @@
         <v>1.67</v>
       </c>
       <c r="AP140">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ140">
         <v>1.53</v>
@@ -30621,7 +30627,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ141">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR141">
         <v>1.64</v>
@@ -30746,7 +30752,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30952,7 +30958,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -31364,7 +31370,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31570,7 +31576,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31648,7 +31654,7 @@
         <v>1.57</v>
       </c>
       <c r="AP146">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ146">
         <v>1.8</v>
@@ -31776,7 +31782,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31982,7 +31988,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -32060,7 +32066,7 @@
         <v>1.43</v>
       </c>
       <c r="AP148">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ148">
         <v>1.53</v>
@@ -32188,7 +32194,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32269,7 +32275,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ149">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR149">
         <v>1.84</v>
@@ -32600,7 +32606,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -32884,7 +32890,7 @@
         <v>0.71</v>
       </c>
       <c r="AP152">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ152">
         <v>1.07</v>
@@ -33218,7 +33224,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33424,7 +33430,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33630,7 +33636,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33836,7 +33842,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33917,7 +33923,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ157">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR157">
         <v>2.25</v>
@@ -34042,7 +34048,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34123,7 +34129,7 @@
         <v>0.29</v>
       </c>
       <c r="AQ158">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR158">
         <v>1.06</v>
@@ -34866,7 +34872,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -35072,7 +35078,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35278,7 +35284,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35484,7 +35490,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35768,7 +35774,7 @@
         <v>0.13</v>
       </c>
       <c r="AP166">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ166">
         <v>0.33</v>
@@ -35896,7 +35902,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35974,7 +35980,7 @@
         <v>0.63</v>
       </c>
       <c r="AP167">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ167">
         <v>1</v>
@@ -36102,7 +36108,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36389,7 +36395,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ169">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR169">
         <v>1.39</v>
@@ -36514,7 +36520,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36926,7 +36932,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37213,7 +37219,7 @@
         <v>2</v>
       </c>
       <c r="AQ173">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR173">
         <v>1.56</v>
@@ -37544,7 +37550,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -38037,7 +38043,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ177">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR177">
         <v>1.19</v>
@@ -38162,7 +38168,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38652,7 +38658,7 @@
         <v>1</v>
       </c>
       <c r="AP180">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ180">
         <v>0.71</v>
@@ -38780,7 +38786,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38858,7 +38864,7 @@
         <v>1.22</v>
       </c>
       <c r="AP181">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ181">
         <v>1.4</v>
@@ -38986,7 +38992,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39398,7 +39404,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39476,7 +39482,7 @@
         <v>1.56</v>
       </c>
       <c r="AP184">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ184">
         <v>1.53</v>
@@ -39604,7 +39610,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39810,7 +39816,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -40097,7 +40103,7 @@
         <v>0.47</v>
       </c>
       <c r="AQ187">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR187">
         <v>1.17</v>
@@ -40222,7 +40228,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40428,7 +40434,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40634,7 +40640,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40840,7 +40846,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -41252,7 +41258,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41539,7 +41545,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ194">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR194">
         <v>1.41</v>
@@ -41664,7 +41670,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41870,7 +41876,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -42282,7 +42288,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42360,7 +42366,7 @@
         <v>0.89</v>
       </c>
       <c r="AP198">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ198">
         <v>0.71</v>
@@ -42488,7 +42494,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42569,7 +42575,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ199">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR199">
         <v>1.79</v>
@@ -42694,7 +42700,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42900,7 +42906,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -43106,7 +43112,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43312,7 +43318,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43518,7 +43524,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43724,7 +43730,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -43802,7 +43808,7 @@
         <v>1.11</v>
       </c>
       <c r="AP205">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ205">
         <v>1.69</v>
@@ -44136,7 +44142,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44420,10 +44426,10 @@
         <v>1.11</v>
       </c>
       <c r="AP208">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ208">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR208">
         <v>1.98</v>
@@ -44548,7 +44554,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44960,7 +44966,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45166,7 +45172,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45372,7 +45378,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45578,7 +45584,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45656,7 +45662,7 @@
         <v>1.3</v>
       </c>
       <c r="AP214">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ214">
         <v>1.57</v>
@@ -45784,7 +45790,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -45862,7 +45868,7 @@
         <v>1.3</v>
       </c>
       <c r="AP215">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ215">
         <v>1.21</v>
@@ -45990,7 +45996,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -46196,7 +46202,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46402,7 +46408,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46483,7 +46489,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ218">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR218">
         <v>1.33</v>
@@ -46608,7 +46614,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46814,7 +46820,7 @@
         <v>240</v>
       </c>
       <c r="P220" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q220">
         <v>1.73</v>
@@ -47226,7 +47232,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -47638,7 +47644,7 @@
         <v>107</v>
       </c>
       <c r="P224" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q224">
         <v>6</v>
@@ -47844,7 +47850,7 @@
         <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q225">
         <v>6.5</v>
@@ -48050,7 +48056,7 @@
         <v>243</v>
       </c>
       <c r="P226" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q226">
         <v>2.38</v>
@@ -48131,7 +48137,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ226">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR226">
         <v>2.02</v>
@@ -48256,7 +48262,7 @@
         <v>155</v>
       </c>
       <c r="P227" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48462,7 +48468,7 @@
         <v>244</v>
       </c>
       <c r="P228" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q228">
         <v>1.91</v>
@@ -48874,7 +48880,7 @@
         <v>91</v>
       </c>
       <c r="P230" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q230">
         <v>2.88</v>
@@ -48952,10 +48958,10 @@
         <v>1</v>
       </c>
       <c r="AP230">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ230">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR230">
         <v>1.57</v>
@@ -49286,7 +49292,7 @@
         <v>95</v>
       </c>
       <c r="P232" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q232">
         <v>2.2</v>
@@ -49698,7 +49704,7 @@
         <v>151</v>
       </c>
       <c r="P234" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q234">
         <v>2.6</v>
@@ -49904,7 +49910,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q235">
         <v>4.5</v>
@@ -50316,7 +50322,7 @@
         <v>91</v>
       </c>
       <c r="P237" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50397,7 +50403,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ237">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR237">
         <v>1.59</v>
@@ -50522,7 +50528,7 @@
         <v>91</v>
       </c>
       <c r="P238" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q238">
         <v>2.75</v>
@@ -50806,7 +50812,7 @@
         <v>1.5</v>
       </c>
       <c r="AP239">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ239">
         <v>1.4</v>
@@ -50934,7 +50940,7 @@
         <v>249</v>
       </c>
       <c r="P240" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q240">
         <v>1.8</v>
@@ -51140,7 +51146,7 @@
         <v>250</v>
       </c>
       <c r="P241" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q241">
         <v>6</v>
@@ -51427,7 +51433,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ242">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR242">
         <v>1.61</v>
@@ -51552,7 +51558,7 @@
         <v>91</v>
       </c>
       <c r="P243" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q243">
         <v>9</v>
@@ -51630,7 +51636,7 @@
         <v>1.83</v>
       </c>
       <c r="AP243">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ243">
         <v>1.8</v>
@@ -51758,7 +51764,7 @@
         <v>203</v>
       </c>
       <c r="P244" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q244">
         <v>5</v>
@@ -52454,7 +52460,7 @@
         <v>1.92</v>
       </c>
       <c r="AP247">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ247">
         <v>1.73</v>
@@ -52788,7 +52794,7 @@
         <v>254</v>
       </c>
       <c r="P249" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q249">
         <v>2.63</v>
@@ -52994,7 +53000,7 @@
         <v>255</v>
       </c>
       <c r="P250" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q250">
         <v>1.57</v>
@@ -53281,7 +53287,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ251">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR251">
         <v>1.71</v>
@@ -53406,7 +53412,7 @@
         <v>256</v>
       </c>
       <c r="P252" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q252">
         <v>4</v>
@@ -53612,7 +53618,7 @@
         <v>91</v>
       </c>
       <c r="P253" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q253">
         <v>3.6</v>
@@ -53690,7 +53696,7 @@
         <v>0.92</v>
       </c>
       <c r="AP253">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AQ253">
         <v>1.21</v>
@@ -53818,7 +53824,7 @@
         <v>257</v>
       </c>
       <c r="P254" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q254">
         <v>3.25</v>
@@ -53899,7 +53905,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ254">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR254">
         <v>1.39</v>
@@ -54024,7 +54030,7 @@
         <v>91</v>
       </c>
       <c r="P255" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q255">
         <v>5</v>
@@ -54230,7 +54236,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q256">
         <v>3.75</v>
@@ -54311,7 +54317,7 @@
         <v>0.47</v>
       </c>
       <c r="AQ256">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR256">
         <v>1.19</v>
@@ -54436,7 +54442,7 @@
         <v>91</v>
       </c>
       <c r="P257" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q257">
         <v>1.73</v>
@@ -54514,7 +54520,7 @@
         <v>1.08</v>
       </c>
       <c r="AP257">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ257">
         <v>1.21</v>
@@ -54848,7 +54854,7 @@
         <v>91</v>
       </c>
       <c r="P259" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q259">
         <v>2.75</v>
@@ -54926,7 +54932,7 @@
         <v>1.58</v>
       </c>
       <c r="AP259">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ259">
         <v>1.69</v>
@@ -55054,7 +55060,7 @@
         <v>258</v>
       </c>
       <c r="P260" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q260">
         <v>3.1</v>
@@ -55135,7 +55141,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ260">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR260">
         <v>1.6</v>
@@ -55260,7 +55266,7 @@
         <v>259</v>
       </c>
       <c r="P261" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q261">
         <v>2.38</v>
@@ -55466,7 +55472,7 @@
         <v>91</v>
       </c>
       <c r="P262" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q262">
         <v>3.1</v>
@@ -55672,7 +55678,7 @@
         <v>260</v>
       </c>
       <c r="P263" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q263">
         <v>3.2</v>
@@ -55878,7 +55884,7 @@
         <v>261</v>
       </c>
       <c r="P264" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q264">
         <v>3.5</v>
@@ -56702,7 +56708,7 @@
         <v>264</v>
       </c>
       <c r="P268" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q268">
         <v>2.05</v>
@@ -57938,7 +57944,7 @@
         <v>269</v>
       </c>
       <c r="P274" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q274">
         <v>1.4</v>
@@ -58144,7 +58150,7 @@
         <v>270</v>
       </c>
       <c r="P275" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q275">
         <v>2.5</v>
@@ -59174,7 +59180,7 @@
         <v>273</v>
       </c>
       <c r="P280" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q280">
         <v>2.88</v>
@@ -59380,7 +59386,7 @@
         <v>274</v>
       </c>
       <c r="P281" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q281">
         <v>5.5</v>
@@ -59586,7 +59592,7 @@
         <v>91</v>
       </c>
       <c r="P282" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q282">
         <v>3.5</v>
@@ -59792,7 +59798,7 @@
         <v>275</v>
       </c>
       <c r="P283" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q283">
         <v>4</v>
@@ -59998,7 +60004,7 @@
         <v>276</v>
       </c>
       <c r="P284" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q284">
         <v>2.88</v>
@@ -60204,7 +60210,7 @@
         <v>277</v>
       </c>
       <c r="P285" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q285">
         <v>4</v>
@@ -60410,7 +60416,7 @@
         <v>278</v>
       </c>
       <c r="P286" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q286">
         <v>2.2</v>
@@ -60616,7 +60622,7 @@
         <v>195</v>
       </c>
       <c r="P287" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q287">
         <v>2.25</v>
@@ -60773,6 +60779,624 @@
       </c>
       <c r="BP287">
         <v>1.85</v>
+      </c>
+    </row>
+    <row r="288" spans="1:68">
+      <c r="A288" s="1">
+        <v>287</v>
+      </c>
+      <c r="B288">
+        <v>7466963</v>
+      </c>
+      <c r="C288" t="s">
+        <v>68</v>
+      </c>
+      <c r="D288" t="s">
+        <v>69</v>
+      </c>
+      <c r="E288" s="2">
+        <v>45732.4375</v>
+      </c>
+      <c r="F288">
+        <v>29</v>
+      </c>
+      <c r="G288" t="s">
+        <v>83</v>
+      </c>
+      <c r="H288" t="s">
+        <v>81</v>
+      </c>
+      <c r="I288">
+        <v>0</v>
+      </c>
+      <c r="J288">
+        <v>0</v>
+      </c>
+      <c r="K288">
+        <v>0</v>
+      </c>
+      <c r="L288">
+        <v>2</v>
+      </c>
+      <c r="M288">
+        <v>0</v>
+      </c>
+      <c r="N288">
+        <v>2</v>
+      </c>
+      <c r="O288" t="s">
+        <v>279</v>
+      </c>
+      <c r="P288" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q288">
+        <v>2.5</v>
+      </c>
+      <c r="R288">
+        <v>2.4</v>
+      </c>
+      <c r="S288">
+        <v>3.75</v>
+      </c>
+      <c r="T288">
+        <v>1.29</v>
+      </c>
+      <c r="U288">
+        <v>3.5</v>
+      </c>
+      <c r="V288">
+        <v>2.25</v>
+      </c>
+      <c r="W288">
+        <v>1.57</v>
+      </c>
+      <c r="X288">
+        <v>5.5</v>
+      </c>
+      <c r="Y288">
+        <v>1.14</v>
+      </c>
+      <c r="Z288">
+        <v>2</v>
+      </c>
+      <c r="AA288">
+        <v>3.85</v>
+      </c>
+      <c r="AB288">
+        <v>3.25</v>
+      </c>
+      <c r="AC288">
+        <v>1.01</v>
+      </c>
+      <c r="AD288">
+        <v>13</v>
+      </c>
+      <c r="AE288">
+        <v>1.18</v>
+      </c>
+      <c r="AF288">
+        <v>4.75</v>
+      </c>
+      <c r="AG288">
+        <v>1.6</v>
+      </c>
+      <c r="AH288">
+        <v>2.2</v>
+      </c>
+      <c r="AI288">
+        <v>1.5</v>
+      </c>
+      <c r="AJ288">
+        <v>2.5</v>
+      </c>
+      <c r="AK288">
+        <v>1.32</v>
+      </c>
+      <c r="AL288">
+        <v>1.25</v>
+      </c>
+      <c r="AM288">
+        <v>1.77</v>
+      </c>
+      <c r="AN288">
+        <v>1.43</v>
+      </c>
+      <c r="AO288">
+        <v>1.23</v>
+      </c>
+      <c r="AP288">
+        <v>1.53</v>
+      </c>
+      <c r="AQ288">
+        <v>1.14</v>
+      </c>
+      <c r="AR288">
+        <v>1.6</v>
+      </c>
+      <c r="AS288">
+        <v>1.59</v>
+      </c>
+      <c r="AT288">
+        <v>3.19</v>
+      </c>
+      <c r="AU288">
+        <v>5</v>
+      </c>
+      <c r="AV288">
+        <v>5</v>
+      </c>
+      <c r="AW288">
+        <v>9</v>
+      </c>
+      <c r="AX288">
+        <v>8</v>
+      </c>
+      <c r="AY288">
+        <v>19</v>
+      </c>
+      <c r="AZ288">
+        <v>15</v>
+      </c>
+      <c r="BA288">
+        <v>6</v>
+      </c>
+      <c r="BB288">
+        <v>5</v>
+      </c>
+      <c r="BC288">
+        <v>11</v>
+      </c>
+      <c r="BD288">
+        <v>1.68</v>
+      </c>
+      <c r="BE288">
+        <v>7.3</v>
+      </c>
+      <c r="BF288">
+        <v>2.82</v>
+      </c>
+      <c r="BG288">
+        <v>1.06</v>
+      </c>
+      <c r="BH288">
+        <v>6.1</v>
+      </c>
+      <c r="BI288">
+        <v>1.16</v>
+      </c>
+      <c r="BJ288">
+        <v>4.05</v>
+      </c>
+      <c r="BK288">
+        <v>1.33</v>
+      </c>
+      <c r="BL288">
+        <v>2.83</v>
+      </c>
+      <c r="BM288">
+        <v>1.59</v>
+      </c>
+      <c r="BN288">
+        <v>2.16</v>
+      </c>
+      <c r="BO288">
+        <v>2</v>
+      </c>
+      <c r="BP288">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="289" spans="1:68">
+      <c r="A289" s="1">
+        <v>288</v>
+      </c>
+      <c r="B289">
+        <v>7466960</v>
+      </c>
+      <c r="C289" t="s">
+        <v>68</v>
+      </c>
+      <c r="D289" t="s">
+        <v>69</v>
+      </c>
+      <c r="E289" s="2">
+        <v>45732.4375</v>
+      </c>
+      <c r="F289">
+        <v>29</v>
+      </c>
+      <c r="G289" t="s">
+        <v>72</v>
+      </c>
+      <c r="H289" t="s">
+        <v>78</v>
+      </c>
+      <c r="I289">
+        <v>1</v>
+      </c>
+      <c r="J289">
+        <v>0</v>
+      </c>
+      <c r="K289">
+        <v>1</v>
+      </c>
+      <c r="L289">
+        <v>1</v>
+      </c>
+      <c r="M289">
+        <v>0</v>
+      </c>
+      <c r="N289">
+        <v>1</v>
+      </c>
+      <c r="O289" t="s">
+        <v>172</v>
+      </c>
+      <c r="P289" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q289">
+        <v>2.4</v>
+      </c>
+      <c r="R289">
+        <v>2.2</v>
+      </c>
+      <c r="S289">
+        <v>4.75</v>
+      </c>
+      <c r="T289">
+        <v>1.4</v>
+      </c>
+      <c r="U289">
+        <v>2.75</v>
+      </c>
+      <c r="V289">
+        <v>2.75</v>
+      </c>
+      <c r="W289">
+        <v>1.4</v>
+      </c>
+      <c r="X289">
+        <v>8</v>
+      </c>
+      <c r="Y289">
+        <v>1.08</v>
+      </c>
+      <c r="Z289">
+        <v>1.76</v>
+      </c>
+      <c r="AA289">
+        <v>3.7</v>
+      </c>
+      <c r="AB289">
+        <v>4.2</v>
+      </c>
+      <c r="AC289">
+        <v>1.05</v>
+      </c>
+      <c r="AD289">
+        <v>9.5</v>
+      </c>
+      <c r="AE289">
+        <v>1.28</v>
+      </c>
+      <c r="AF289">
+        <v>3.55</v>
+      </c>
+      <c r="AG289">
+        <v>1.75</v>
+      </c>
+      <c r="AH289">
+        <v>2</v>
+      </c>
+      <c r="AI289">
+        <v>1.8</v>
+      </c>
+      <c r="AJ289">
+        <v>1.95</v>
+      </c>
+      <c r="AK289">
+        <v>1.21</v>
+      </c>
+      <c r="AL289">
+        <v>1.27</v>
+      </c>
+      <c r="AM289">
+        <v>1.98</v>
+      </c>
+      <c r="AN289">
+        <v>2.15</v>
+      </c>
+      <c r="AO289">
+        <v>1.5</v>
+      </c>
+      <c r="AP289">
+        <v>2.21</v>
+      </c>
+      <c r="AQ289">
+        <v>1.4</v>
+      </c>
+      <c r="AR289">
+        <v>1.99</v>
+      </c>
+      <c r="AS289">
+        <v>1.55</v>
+      </c>
+      <c r="AT289">
+        <v>3.54</v>
+      </c>
+      <c r="AU289">
+        <v>5</v>
+      </c>
+      <c r="AV289">
+        <v>3</v>
+      </c>
+      <c r="AW289">
+        <v>8</v>
+      </c>
+      <c r="AX289">
+        <v>6</v>
+      </c>
+      <c r="AY289">
+        <v>15</v>
+      </c>
+      <c r="AZ289">
+        <v>10</v>
+      </c>
+      <c r="BA289">
+        <v>5</v>
+      </c>
+      <c r="BB289">
+        <v>4</v>
+      </c>
+      <c r="BC289">
+        <v>9</v>
+      </c>
+      <c r="BD289">
+        <v>1.44</v>
+      </c>
+      <c r="BE289">
+        <v>9.5</v>
+      </c>
+      <c r="BF289">
+        <v>3.48</v>
+      </c>
+      <c r="BG289">
+        <v>1.22</v>
+      </c>
+      <c r="BH289">
+        <v>3.5</v>
+      </c>
+      <c r="BI289">
+        <v>1.43</v>
+      </c>
+      <c r="BJ289">
+        <v>2.54</v>
+      </c>
+      <c r="BK289">
+        <v>1.73</v>
+      </c>
+      <c r="BL289">
+        <v>2</v>
+      </c>
+      <c r="BM289">
+        <v>2.23</v>
+      </c>
+      <c r="BN289">
+        <v>1.55</v>
+      </c>
+      <c r="BO289">
+        <v>2.92</v>
+      </c>
+      <c r="BP289">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="290" spans="1:68">
+      <c r="A290" s="1">
+        <v>289</v>
+      </c>
+      <c r="B290">
+        <v>7466965</v>
+      </c>
+      <c r="C290" t="s">
+        <v>68</v>
+      </c>
+      <c r="D290" t="s">
+        <v>69</v>
+      </c>
+      <c r="E290" s="2">
+        <v>45732.66666666666</v>
+      </c>
+      <c r="F290">
+        <v>29</v>
+      </c>
+      <c r="G290" t="s">
+        <v>79</v>
+      </c>
+      <c r="H290" t="s">
+        <v>70</v>
+      </c>
+      <c r="I290">
+        <v>0</v>
+      </c>
+      <c r="J290">
+        <v>1</v>
+      </c>
+      <c r="K290">
+        <v>1</v>
+      </c>
+      <c r="L290">
+        <v>0</v>
+      </c>
+      <c r="M290">
+        <v>3</v>
+      </c>
+      <c r="N290">
+        <v>3</v>
+      </c>
+      <c r="O290" t="s">
+        <v>91</v>
+      </c>
+      <c r="P290" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q290">
+        <v>4.33</v>
+      </c>
+      <c r="R290">
+        <v>2.25</v>
+      </c>
+      <c r="S290">
+        <v>2.4</v>
+      </c>
+      <c r="T290">
+        <v>1.36</v>
+      </c>
+      <c r="U290">
+        <v>3</v>
+      </c>
+      <c r="V290">
+        <v>2.63</v>
+      </c>
+      <c r="W290">
+        <v>1.44</v>
+      </c>
+      <c r="X290">
+        <v>7</v>
+      </c>
+      <c r="Y290">
+        <v>1.1</v>
+      </c>
+      <c r="Z290">
+        <v>4.2</v>
+      </c>
+      <c r="AA290">
+        <v>3.9</v>
+      </c>
+      <c r="AB290">
+        <v>1.74</v>
+      </c>
+      <c r="AC290">
+        <v>1.05</v>
+      </c>
+      <c r="AD290">
+        <v>9.5</v>
+      </c>
+      <c r="AE290">
+        <v>1.25</v>
+      </c>
+      <c r="AF290">
+        <v>3.85</v>
+      </c>
+      <c r="AG290">
+        <v>1.7</v>
+      </c>
+      <c r="AH290">
+        <v>2.05</v>
+      </c>
+      <c r="AI290">
+        <v>1.67</v>
+      </c>
+      <c r="AJ290">
+        <v>2.1</v>
+      </c>
+      <c r="AK290">
+        <v>1.93</v>
+      </c>
+      <c r="AL290">
+        <v>1.27</v>
+      </c>
+      <c r="AM290">
+        <v>1.23</v>
+      </c>
+      <c r="AN290">
+        <v>0.64</v>
+      </c>
+      <c r="AO290">
+        <v>1.08</v>
+      </c>
+      <c r="AP290">
+        <v>0.6</v>
+      </c>
+      <c r="AQ290">
+        <v>1.21</v>
+      </c>
+      <c r="AR290">
+        <v>1.19</v>
+      </c>
+      <c r="AS290">
+        <v>1.36</v>
+      </c>
+      <c r="AT290">
+        <v>2.55</v>
+      </c>
+      <c r="AU290">
+        <v>4</v>
+      </c>
+      <c r="AV290">
+        <v>6</v>
+      </c>
+      <c r="AW290">
+        <v>8</v>
+      </c>
+      <c r="AX290">
+        <v>13</v>
+      </c>
+      <c r="AY290">
+        <v>17</v>
+      </c>
+      <c r="AZ290">
+        <v>23</v>
+      </c>
+      <c r="BA290">
+        <v>6</v>
+      </c>
+      <c r="BB290">
+        <v>4</v>
+      </c>
+      <c r="BC290">
+        <v>10</v>
+      </c>
+      <c r="BD290">
+        <v>2.76</v>
+      </c>
+      <c r="BE290">
+        <v>9</v>
+      </c>
+      <c r="BF290">
+        <v>1.63</v>
+      </c>
+      <c r="BG290">
+        <v>1.17</v>
+      </c>
+      <c r="BH290">
+        <v>4</v>
+      </c>
+      <c r="BI290">
+        <v>1.35</v>
+      </c>
+      <c r="BJ290">
+        <v>2.74</v>
+      </c>
+      <c r="BK290">
+        <v>1.73</v>
+      </c>
+      <c r="BL290">
+        <v>2</v>
+      </c>
+      <c r="BM290">
+        <v>2.08</v>
+      </c>
+      <c r="BN290">
+        <v>1.67</v>
+      </c>
+      <c r="BO290">
+        <v>2.71</v>
+      </c>
+      <c r="BP290">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="428">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -856,6 +856,9 @@
     <t>['78', '88']</t>
   </si>
   <si>
+    <t>['37', '73']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1656,7 +1659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP290"/>
+  <dimension ref="A1:BP293"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1993,7 +1996,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ2">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2118,7 +2121,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2402,7 +2405,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ4">
         <v>1</v>
@@ -2530,7 +2533,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2942,7 +2945,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -3020,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ7">
         <v>1.53</v>
@@ -3148,7 +3151,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3560,7 +3563,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -4053,7 +4056,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ12">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4465,7 +4468,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ14">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -5208,7 +5211,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5414,7 +5417,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5492,7 +5495,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AQ19">
         <v>1.4</v>
@@ -6110,7 +6113,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ22">
         <v>1.53</v>
@@ -6238,7 +6241,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6444,7 +6447,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6525,7 +6528,7 @@
         <v>0.47</v>
       </c>
       <c r="AQ24">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR24">
         <v>0.77</v>
@@ -6728,7 +6731,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -7062,7 +7065,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7268,7 +7271,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7474,7 +7477,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7886,7 +7889,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8092,7 +8095,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8173,7 +8176,7 @@
         <v>0.29</v>
       </c>
       <c r="AQ32">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR32">
         <v>0.65</v>
@@ -8504,7 +8507,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -8791,7 +8794,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ35">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR35">
         <v>1.87</v>
@@ -9328,7 +9331,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9534,7 +9537,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9740,7 +9743,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9946,7 +9949,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -10024,7 +10027,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AQ41">
         <v>1.6</v>
@@ -10152,7 +10155,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10358,7 +10361,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -11675,7 +11678,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ49">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR49">
         <v>1.39</v>
@@ -12006,7 +12009,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -12212,7 +12215,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12418,7 +12421,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12496,10 +12499,10 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ53">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR53">
         <v>1.65</v>
@@ -12830,7 +12833,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -12908,7 +12911,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ55">
         <v>0.57</v>
@@ -13117,7 +13120,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ56">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR56">
         <v>1.59</v>
@@ -13242,7 +13245,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13448,7 +13451,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13526,7 +13529,7 @@
         <v>3</v>
       </c>
       <c r="AP58">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AQ58">
         <v>2.33</v>
@@ -13654,7 +13657,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13860,7 +13863,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -14066,7 +14069,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14272,7 +14275,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14684,7 +14687,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14765,7 +14768,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ64">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR64">
         <v>2.4</v>
@@ -14890,7 +14893,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -15096,7 +15099,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -15380,7 +15383,7 @@
         <v>0</v>
       </c>
       <c r="AP67">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ67">
         <v>0.33</v>
@@ -16001,7 +16004,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ70">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR70">
         <v>1.35</v>
@@ -16126,7 +16129,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16413,7 +16416,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ72">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR72">
         <v>1.91</v>
@@ -16538,7 +16541,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16744,7 +16747,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16950,7 +16953,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -17156,7 +17159,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17362,7 +17365,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17774,7 +17777,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17852,7 +17855,7 @@
         <v>2.33</v>
       </c>
       <c r="AP79">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AQ79">
         <v>1.4</v>
@@ -17980,7 +17983,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18264,7 +18267,7 @@
         <v>0.33</v>
       </c>
       <c r="AP81">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ81">
         <v>1.69</v>
@@ -18392,7 +18395,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18804,7 +18807,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -19010,7 +19013,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -19216,7 +19219,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19503,7 +19506,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ87">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR87">
         <v>1.26</v>
@@ -19628,7 +19631,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -20040,7 +20043,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20121,7 +20124,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ90">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR90">
         <v>1.61</v>
@@ -20246,7 +20249,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20324,7 +20327,7 @@
         <v>3</v>
       </c>
       <c r="AP91">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ91">
         <v>2.33</v>
@@ -21560,10 +21563,10 @@
         <v>1.25</v>
       </c>
       <c r="AP97">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ97">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR97">
         <v>1.51</v>
@@ -21688,7 +21691,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21766,7 +21769,7 @@
         <v>0.25</v>
       </c>
       <c r="AP98">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AQ98">
         <v>1.69</v>
@@ -21894,7 +21897,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -22100,7 +22103,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22512,7 +22515,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22718,7 +22721,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22799,7 +22802,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ103">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR103">
         <v>1.37</v>
@@ -23208,7 +23211,7 @@
         <v>0</v>
       </c>
       <c r="AP105">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AQ105">
         <v>0.33</v>
@@ -23954,7 +23957,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -24032,7 +24035,7 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ109">
         <v>1.6</v>
@@ -24160,7 +24163,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24572,7 +24575,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24778,7 +24781,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -25268,7 +25271,7 @@
         <v>2.2</v>
       </c>
       <c r="AP115">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ115">
         <v>1.73</v>
@@ -25396,7 +25399,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25602,7 +25605,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25808,7 +25811,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -26014,7 +26017,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -26220,7 +26223,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26301,7 +26304,7 @@
         <v>0.47</v>
       </c>
       <c r="AQ120">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR120">
         <v>1.13</v>
@@ -26426,7 +26429,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26507,7 +26510,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ121">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR121">
         <v>1.12</v>
@@ -26632,7 +26635,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26838,7 +26841,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -26916,7 +26919,7 @@
         <v>0.83</v>
       </c>
       <c r="AP123">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AQ123">
         <v>1.53</v>
@@ -27122,7 +27125,7 @@
         <v>0.83</v>
       </c>
       <c r="AP124">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ124">
         <v>0.71</v>
@@ -27456,7 +27459,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27662,7 +27665,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -28280,7 +28283,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28361,7 +28364,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ130">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR130">
         <v>1.95</v>
@@ -28692,7 +28695,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28979,7 +28982,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ133">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR133">
         <v>1.02</v>
@@ -29104,7 +29107,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29310,7 +29313,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -30212,10 +30215,10 @@
         <v>1</v>
       </c>
       <c r="AP139">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ139">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR139">
         <v>2.18</v>
@@ -30752,7 +30755,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30958,7 +30961,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -31370,7 +31373,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31576,7 +31579,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31782,7 +31785,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31988,7 +31991,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -32194,7 +32197,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32606,7 +32609,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -32684,7 +32687,7 @@
         <v>0.71</v>
       </c>
       <c r="AP151">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AQ151">
         <v>0.71</v>
@@ -32890,7 +32893,7 @@
         <v>0.71</v>
       </c>
       <c r="AP152">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ152">
         <v>1.07</v>
@@ -33224,7 +33227,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33305,7 +33308,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ154">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR154">
         <v>1.76</v>
@@ -33430,7 +33433,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33508,7 +33511,7 @@
         <v>1.43</v>
       </c>
       <c r="AP155">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ155">
         <v>1.21</v>
@@ -33636,7 +33639,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33842,7 +33845,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33923,7 +33926,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ157">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR157">
         <v>2.25</v>
@@ -34048,7 +34051,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34541,7 +34544,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ160">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR160">
         <v>1.69</v>
@@ -34872,7 +34875,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -35078,7 +35081,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35284,7 +35287,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35490,7 +35493,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35902,7 +35905,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36108,7 +36111,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36520,7 +36523,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36932,7 +36935,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37013,7 +37016,7 @@
         <v>0.29</v>
       </c>
       <c r="AQ172">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR172">
         <v>1.06</v>
@@ -37216,7 +37219,7 @@
         <v>1.25</v>
       </c>
       <c r="AP173">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ173">
         <v>1.14</v>
@@ -37550,7 +37553,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -37631,7 +37634,7 @@
         <v>2</v>
       </c>
       <c r="AQ175">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR175">
         <v>1.78</v>
@@ -38040,10 +38043,10 @@
         <v>1.13</v>
       </c>
       <c r="AP177">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AQ177">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR177">
         <v>1.19</v>
@@ -38168,7 +38171,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38658,7 +38661,7 @@
         <v>1</v>
       </c>
       <c r="AP180">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ180">
         <v>0.71</v>
@@ -38786,7 +38789,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38992,7 +38995,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39404,7 +39407,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39610,7 +39613,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39816,7 +39819,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -40228,7 +40231,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40434,7 +40437,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40640,7 +40643,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40846,7 +40849,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -41258,7 +41261,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41670,7 +41673,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41876,7 +41879,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -41957,7 +41960,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ196">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR196">
         <v>2.09</v>
@@ -42288,7 +42291,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42494,7 +42497,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42575,7 +42578,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ199">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR199">
         <v>1.79</v>
@@ -42700,7 +42703,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42778,7 +42781,7 @@
         <v>2</v>
       </c>
       <c r="AP200">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AQ200">
         <v>1.73</v>
@@ -42906,7 +42909,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -43112,7 +43115,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43193,7 +43196,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ202">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR202">
         <v>1.35</v>
@@ -43318,7 +43321,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43524,7 +43527,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43602,7 +43605,7 @@
         <v>2.56</v>
       </c>
       <c r="AP204">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ204">
         <v>2.33</v>
@@ -43730,7 +43733,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -44142,7 +44145,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44426,7 +44429,7 @@
         <v>1.11</v>
       </c>
       <c r="AP208">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ208">
         <v>1.14</v>
@@ -44554,7 +44557,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44966,7 +44969,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45172,7 +45175,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45378,7 +45381,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45584,7 +45587,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45665,7 +45668,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ214">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR214">
         <v>1.2</v>
@@ -45790,7 +45793,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -45868,7 +45871,7 @@
         <v>1.3</v>
       </c>
       <c r="AP215">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ215">
         <v>1.21</v>
@@ -45996,7 +45999,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -46202,7 +46205,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46280,7 +46283,7 @@
         <v>0.18</v>
       </c>
       <c r="AP217">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ217">
         <v>0.33</v>
@@ -46408,7 +46411,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46614,7 +46617,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46820,7 +46823,7 @@
         <v>240</v>
       </c>
       <c r="P220" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q220">
         <v>1.73</v>
@@ -47232,7 +47235,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -47644,7 +47647,7 @@
         <v>107</v>
       </c>
       <c r="P224" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q224">
         <v>6</v>
@@ -47850,7 +47853,7 @@
         <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q225">
         <v>6.5</v>
@@ -47928,7 +47931,7 @@
         <v>1.73</v>
       </c>
       <c r="AP225">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AQ225">
         <v>1.8</v>
@@ -48056,7 +48059,7 @@
         <v>243</v>
       </c>
       <c r="P226" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q226">
         <v>2.38</v>
@@ -48262,7 +48265,7 @@
         <v>155</v>
       </c>
       <c r="P227" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48468,7 +48471,7 @@
         <v>244</v>
       </c>
       <c r="P228" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q228">
         <v>1.91</v>
@@ -48755,7 +48758,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ229">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR229">
         <v>1.51</v>
@@ -48880,7 +48883,7 @@
         <v>91</v>
       </c>
       <c r="P230" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q230">
         <v>2.88</v>
@@ -48961,7 +48964,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ230">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR230">
         <v>1.57</v>
@@ -49164,7 +49167,7 @@
         <v>1.58</v>
       </c>
       <c r="AP231">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ231">
         <v>1.53</v>
@@ -49292,7 +49295,7 @@
         <v>95</v>
       </c>
       <c r="P232" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q232">
         <v>2.2</v>
@@ -49373,7 +49376,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ232">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR232">
         <v>1.61</v>
@@ -49704,7 +49707,7 @@
         <v>151</v>
       </c>
       <c r="P234" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q234">
         <v>2.6</v>
@@ -49910,7 +49913,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q235">
         <v>4.5</v>
@@ -50194,7 +50197,7 @@
         <v>1.27</v>
       </c>
       <c r="AP236">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AQ236">
         <v>1.21</v>
@@ -50322,7 +50325,7 @@
         <v>91</v>
       </c>
       <c r="P237" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50528,7 +50531,7 @@
         <v>91</v>
       </c>
       <c r="P238" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q238">
         <v>2.75</v>
@@ -50812,7 +50815,7 @@
         <v>1.5</v>
       </c>
       <c r="AP239">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ239">
         <v>1.4</v>
@@ -50940,7 +50943,7 @@
         <v>249</v>
       </c>
       <c r="P240" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q240">
         <v>1.8</v>
@@ -51021,7 +51024,7 @@
         <v>2</v>
       </c>
       <c r="AQ240">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR240">
         <v>1.89</v>
@@ -51146,7 +51149,7 @@
         <v>250</v>
       </c>
       <c r="P241" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q241">
         <v>6</v>
@@ -51558,7 +51561,7 @@
         <v>91</v>
       </c>
       <c r="P243" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q243">
         <v>9</v>
@@ -51764,7 +51767,7 @@
         <v>203</v>
       </c>
       <c r="P244" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q244">
         <v>5</v>
@@ -52794,7 +52797,7 @@
         <v>254</v>
       </c>
       <c r="P249" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q249">
         <v>2.63</v>
@@ -53000,7 +53003,7 @@
         <v>255</v>
       </c>
       <c r="P250" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q250">
         <v>1.57</v>
@@ -53287,7 +53290,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ251">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR251">
         <v>1.71</v>
@@ -53412,7 +53415,7 @@
         <v>256</v>
       </c>
       <c r="P252" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q252">
         <v>4</v>
@@ -53618,7 +53621,7 @@
         <v>91</v>
       </c>
       <c r="P253" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q253">
         <v>3.6</v>
@@ -53824,7 +53827,7 @@
         <v>257</v>
       </c>
       <c r="P254" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q254">
         <v>3.25</v>
@@ -53905,7 +53908,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ254">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR254">
         <v>1.39</v>
@@ -54030,7 +54033,7 @@
         <v>91</v>
       </c>
       <c r="P255" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q255">
         <v>5</v>
@@ -54236,7 +54239,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q256">
         <v>3.75</v>
@@ -54442,7 +54445,7 @@
         <v>91</v>
       </c>
       <c r="P257" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q257">
         <v>1.73</v>
@@ -54520,10 +54523,10 @@
         <v>1.08</v>
       </c>
       <c r="AP257">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ257">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR257">
         <v>1.97</v>
@@ -54854,7 +54857,7 @@
         <v>91</v>
       </c>
       <c r="P259" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q259">
         <v>2.75</v>
@@ -55060,7 +55063,7 @@
         <v>258</v>
       </c>
       <c r="P260" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q260">
         <v>3.1</v>
@@ -55266,7 +55269,7 @@
         <v>259</v>
       </c>
       <c r="P261" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q261">
         <v>2.38</v>
@@ -55472,7 +55475,7 @@
         <v>91</v>
       </c>
       <c r="P262" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q262">
         <v>3.1</v>
@@ -55678,7 +55681,7 @@
         <v>260</v>
       </c>
       <c r="P263" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q263">
         <v>3.2</v>
@@ -55884,7 +55887,7 @@
         <v>261</v>
       </c>
       <c r="P264" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q264">
         <v>3.5</v>
@@ -55962,10 +55965,10 @@
         <v>1.58</v>
       </c>
       <c r="AP264">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AQ264">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR264">
         <v>1.21</v>
@@ -56708,7 +56711,7 @@
         <v>264</v>
       </c>
       <c r="P268" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q268">
         <v>2.05</v>
@@ -57198,7 +57201,7 @@
         <v>1.92</v>
       </c>
       <c r="AP270">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ270">
         <v>1.8</v>
@@ -57816,7 +57819,7 @@
         <v>1.5</v>
       </c>
       <c r="AP273">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ273">
         <v>1.4</v>
@@ -57944,7 +57947,7 @@
         <v>269</v>
       </c>
       <c r="P274" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q274">
         <v>1.4</v>
@@ -58150,7 +58153,7 @@
         <v>270</v>
       </c>
       <c r="P275" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q275">
         <v>2.5</v>
@@ -58231,7 +58234,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ275">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR275">
         <v>1.59</v>
@@ -58846,7 +58849,7 @@
         <v>1.08</v>
       </c>
       <c r="AP278">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AQ278">
         <v>1.07</v>
@@ -59180,7 +59183,7 @@
         <v>273</v>
       </c>
       <c r="P280" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q280">
         <v>2.88</v>
@@ -59386,7 +59389,7 @@
         <v>274</v>
       </c>
       <c r="P281" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q281">
         <v>5.5</v>
@@ -59592,7 +59595,7 @@
         <v>91</v>
       </c>
       <c r="P282" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q282">
         <v>3.5</v>
@@ -59798,7 +59801,7 @@
         <v>275</v>
       </c>
       <c r="P283" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q283">
         <v>4</v>
@@ -60004,7 +60007,7 @@
         <v>276</v>
       </c>
       <c r="P284" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q284">
         <v>2.88</v>
@@ -60085,7 +60088,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ284">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR284">
         <v>1.4</v>
@@ -60210,7 +60213,7 @@
         <v>277</v>
       </c>
       <c r="P285" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q285">
         <v>4</v>
@@ -60416,7 +60419,7 @@
         <v>278</v>
       </c>
       <c r="P286" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q286">
         <v>2.2</v>
@@ -60622,7 +60625,7 @@
         <v>195</v>
       </c>
       <c r="P287" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q287">
         <v>2.25</v>
@@ -61112,7 +61115,7 @@
         <v>1.5</v>
       </c>
       <c r="AP289">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ289">
         <v>1.4</v>
@@ -61240,7 +61243,7 @@
         <v>91</v>
       </c>
       <c r="P290" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q290">
         <v>4.33</v>
@@ -61321,7 +61324,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ290">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR290">
         <v>1.19</v>
@@ -61397,6 +61400,624 @@
       </c>
       <c r="BP290">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="291" spans="1:68">
+      <c r="A291" s="1">
+        <v>290</v>
+      </c>
+      <c r="B291">
+        <v>7466970</v>
+      </c>
+      <c r="C291" t="s">
+        <v>68</v>
+      </c>
+      <c r="D291" t="s">
+        <v>69</v>
+      </c>
+      <c r="E291" s="2">
+        <v>45748.65625</v>
+      </c>
+      <c r="F291">
+        <v>30</v>
+      </c>
+      <c r="G291" t="s">
+        <v>72</v>
+      </c>
+      <c r="H291" t="s">
+        <v>83</v>
+      </c>
+      <c r="I291">
+        <v>1</v>
+      </c>
+      <c r="J291">
+        <v>0</v>
+      </c>
+      <c r="K291">
+        <v>1</v>
+      </c>
+      <c r="L291">
+        <v>2</v>
+      </c>
+      <c r="M291">
+        <v>1</v>
+      </c>
+      <c r="N291">
+        <v>3</v>
+      </c>
+      <c r="O291" t="s">
+        <v>280</v>
+      </c>
+      <c r="P291" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q291">
+        <v>2</v>
+      </c>
+      <c r="R291">
+        <v>2.2</v>
+      </c>
+      <c r="S291">
+        <v>7.5</v>
+      </c>
+      <c r="T291">
+        <v>1.44</v>
+      </c>
+      <c r="U291">
+        <v>2.63</v>
+      </c>
+      <c r="V291">
+        <v>3</v>
+      </c>
+      <c r="W291">
+        <v>1.36</v>
+      </c>
+      <c r="X291">
+        <v>9</v>
+      </c>
+      <c r="Y291">
+        <v>1.07</v>
+      </c>
+      <c r="Z291">
+        <v>1.42</v>
+      </c>
+      <c r="AA291">
+        <v>4.4</v>
+      </c>
+      <c r="AB291">
+        <v>8</v>
+      </c>
+      <c r="AC291">
+        <v>1.05</v>
+      </c>
+      <c r="AD291">
+        <v>9</v>
+      </c>
+      <c r="AE291">
+        <v>1.33</v>
+      </c>
+      <c r="AF291">
+        <v>3.25</v>
+      </c>
+      <c r="AG291">
+        <v>1.91</v>
+      </c>
+      <c r="AH291">
+        <v>1.8</v>
+      </c>
+      <c r="AI291">
+        <v>2.2</v>
+      </c>
+      <c r="AJ291">
+        <v>1.62</v>
+      </c>
+      <c r="AK291">
+        <v>1.09</v>
+      </c>
+      <c r="AL291">
+        <v>1.2</v>
+      </c>
+      <c r="AM291">
+        <v>2.75</v>
+      </c>
+      <c r="AN291">
+        <v>2.21</v>
+      </c>
+      <c r="AO291">
+        <v>1.57</v>
+      </c>
+      <c r="AP291">
+        <v>2.27</v>
+      </c>
+      <c r="AQ291">
+        <v>1.47</v>
+      </c>
+      <c r="AR291">
+        <v>1.96</v>
+      </c>
+      <c r="AS291">
+        <v>1.45</v>
+      </c>
+      <c r="AT291">
+        <v>3.41</v>
+      </c>
+      <c r="AU291">
+        <v>5</v>
+      </c>
+      <c r="AV291">
+        <v>4</v>
+      </c>
+      <c r="AW291">
+        <v>13</v>
+      </c>
+      <c r="AX291">
+        <v>6</v>
+      </c>
+      <c r="AY291">
+        <v>25</v>
+      </c>
+      <c r="AZ291">
+        <v>12</v>
+      </c>
+      <c r="BA291">
+        <v>5</v>
+      </c>
+      <c r="BB291">
+        <v>4</v>
+      </c>
+      <c r="BC291">
+        <v>9</v>
+      </c>
+      <c r="BD291">
+        <v>1.24</v>
+      </c>
+      <c r="BE291">
+        <v>8</v>
+      </c>
+      <c r="BF291">
+        <v>4.35</v>
+      </c>
+      <c r="BG291">
+        <v>1.26</v>
+      </c>
+      <c r="BH291">
+        <v>3.4</v>
+      </c>
+      <c r="BI291">
+        <v>1.46</v>
+      </c>
+      <c r="BJ291">
+        <v>2.5</v>
+      </c>
+      <c r="BK291">
+        <v>1.72</v>
+      </c>
+      <c r="BL291">
+        <v>1.98</v>
+      </c>
+      <c r="BM291">
+        <v>2.12</v>
+      </c>
+      <c r="BN291">
+        <v>1.63</v>
+      </c>
+      <c r="BO291">
+        <v>2.65</v>
+      </c>
+      <c r="BP291">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="292" spans="1:68">
+      <c r="A292" s="1">
+        <v>291</v>
+      </c>
+      <c r="B292">
+        <v>7466973</v>
+      </c>
+      <c r="C292" t="s">
+        <v>68</v>
+      </c>
+      <c r="D292" t="s">
+        <v>69</v>
+      </c>
+      <c r="E292" s="2">
+        <v>45748.65625</v>
+      </c>
+      <c r="F292">
+        <v>30</v>
+      </c>
+      <c r="G292" t="s">
+        <v>87</v>
+      </c>
+      <c r="H292" t="s">
+        <v>76</v>
+      </c>
+      <c r="I292">
+        <v>1</v>
+      </c>
+      <c r="J292">
+        <v>0</v>
+      </c>
+      <c r="K292">
+        <v>1</v>
+      </c>
+      <c r="L292">
+        <v>1</v>
+      </c>
+      <c r="M292">
+        <v>0</v>
+      </c>
+      <c r="N292">
+        <v>1</v>
+      </c>
+      <c r="O292" t="s">
+        <v>199</v>
+      </c>
+      <c r="P292" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q292">
+        <v>3.1</v>
+      </c>
+      <c r="R292">
+        <v>2.05</v>
+      </c>
+      <c r="S292">
+        <v>3.75</v>
+      </c>
+      <c r="T292">
+        <v>1.44</v>
+      </c>
+      <c r="U292">
+        <v>2.63</v>
+      </c>
+      <c r="V292">
+        <v>3.25</v>
+      </c>
+      <c r="W292">
+        <v>1.33</v>
+      </c>
+      <c r="X292">
+        <v>10</v>
+      </c>
+      <c r="Y292">
+        <v>1.06</v>
+      </c>
+      <c r="Z292">
+        <v>2.35</v>
+      </c>
+      <c r="AA292">
+        <v>3.3</v>
+      </c>
+      <c r="AB292">
+        <v>3.1</v>
+      </c>
+      <c r="AC292">
+        <v>1.07</v>
+      </c>
+      <c r="AD292">
+        <v>8</v>
+      </c>
+      <c r="AE292">
+        <v>1.38</v>
+      </c>
+      <c r="AF292">
+        <v>3</v>
+      </c>
+      <c r="AG292">
+        <v>1.95</v>
+      </c>
+      <c r="AH292">
+        <v>1.8</v>
+      </c>
+      <c r="AI292">
+        <v>1.91</v>
+      </c>
+      <c r="AJ292">
+        <v>1.91</v>
+      </c>
+      <c r="AK292">
+        <v>1.39</v>
+      </c>
+      <c r="AL292">
+        <v>1.33</v>
+      </c>
+      <c r="AM292">
+        <v>1.53</v>
+      </c>
+      <c r="AN292">
+        <v>0.79</v>
+      </c>
+      <c r="AO292">
+        <v>1.21</v>
+      </c>
+      <c r="AP292">
+        <v>0.93</v>
+      </c>
+      <c r="AQ292">
+        <v>1.13</v>
+      </c>
+      <c r="AR292">
+        <v>1.28</v>
+      </c>
+      <c r="AS292">
+        <v>1.4</v>
+      </c>
+      <c r="AT292">
+        <v>2.68</v>
+      </c>
+      <c r="AU292">
+        <v>3</v>
+      </c>
+      <c r="AV292">
+        <v>2</v>
+      </c>
+      <c r="AW292">
+        <v>7</v>
+      </c>
+      <c r="AX292">
+        <v>8</v>
+      </c>
+      <c r="AY292">
+        <v>11</v>
+      </c>
+      <c r="AZ292">
+        <v>15</v>
+      </c>
+      <c r="BA292">
+        <v>1</v>
+      </c>
+      <c r="BB292">
+        <v>2</v>
+      </c>
+      <c r="BC292">
+        <v>3</v>
+      </c>
+      <c r="BD292">
+        <v>1.81</v>
+      </c>
+      <c r="BE292">
+        <v>6.5</v>
+      </c>
+      <c r="BF292">
+        <v>2.18</v>
+      </c>
+      <c r="BG292">
+        <v>1.25</v>
+      </c>
+      <c r="BH292">
+        <v>3.45</v>
+      </c>
+      <c r="BI292">
+        <v>1.44</v>
+      </c>
+      <c r="BJ292">
+        <v>2.55</v>
+      </c>
+      <c r="BK292">
+        <v>1.73</v>
+      </c>
+      <c r="BL292">
+        <v>1.96</v>
+      </c>
+      <c r="BM292">
+        <v>2.15</v>
+      </c>
+      <c r="BN292">
+        <v>1.61</v>
+      </c>
+      <c r="BO292">
+        <v>2.7</v>
+      </c>
+      <c r="BP292">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="293" spans="1:68">
+      <c r="A293" s="1">
+        <v>292</v>
+      </c>
+      <c r="B293">
+        <v>7466972</v>
+      </c>
+      <c r="C293" t="s">
+        <v>68</v>
+      </c>
+      <c r="D293" t="s">
+        <v>69</v>
+      </c>
+      <c r="E293" s="2">
+        <v>45748.66666666666</v>
+      </c>
+      <c r="F293">
+        <v>30</v>
+      </c>
+      <c r="G293" t="s">
+        <v>75</v>
+      </c>
+      <c r="H293" t="s">
+        <v>70</v>
+      </c>
+      <c r="I293">
+        <v>1</v>
+      </c>
+      <c r="J293">
+        <v>0</v>
+      </c>
+      <c r="K293">
+        <v>1</v>
+      </c>
+      <c r="L293">
+        <v>1</v>
+      </c>
+      <c r="M293">
+        <v>0</v>
+      </c>
+      <c r="N293">
+        <v>1</v>
+      </c>
+      <c r="O293" t="s">
+        <v>120</v>
+      </c>
+      <c r="P293" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q293">
+        <v>2.88</v>
+      </c>
+      <c r="R293">
+        <v>2.1</v>
+      </c>
+      <c r="S293">
+        <v>3.75</v>
+      </c>
+      <c r="T293">
+        <v>1.4</v>
+      </c>
+      <c r="U293">
+        <v>2.75</v>
+      </c>
+      <c r="V293">
+        <v>3</v>
+      </c>
+      <c r="W293">
+        <v>1.36</v>
+      </c>
+      <c r="X293">
+        <v>8</v>
+      </c>
+      <c r="Y293">
+        <v>1.08</v>
+      </c>
+      <c r="Z293">
+        <v>2.15</v>
+      </c>
+      <c r="AA293">
+        <v>3.4</v>
+      </c>
+      <c r="AB293">
+        <v>3.4</v>
+      </c>
+      <c r="AC293">
+        <v>1.05</v>
+      </c>
+      <c r="AD293">
+        <v>9</v>
+      </c>
+      <c r="AE293">
+        <v>1.3</v>
+      </c>
+      <c r="AF293">
+        <v>3.45</v>
+      </c>
+      <c r="AG293">
+        <v>1.85</v>
+      </c>
+      <c r="AH293">
+        <v>1.85</v>
+      </c>
+      <c r="AI293">
+        <v>1.8</v>
+      </c>
+      <c r="AJ293">
+        <v>1.95</v>
+      </c>
+      <c r="AK293">
+        <v>1.34</v>
+      </c>
+      <c r="AL293">
+        <v>1.3</v>
+      </c>
+      <c r="AM293">
+        <v>1.65</v>
+      </c>
+      <c r="AN293">
+        <v>2</v>
+      </c>
+      <c r="AO293">
+        <v>1.21</v>
+      </c>
+      <c r="AP293">
+        <v>2.07</v>
+      </c>
+      <c r="AQ293">
+        <v>1.13</v>
+      </c>
+      <c r="AR293">
+        <v>1.45</v>
+      </c>
+      <c r="AS293">
+        <v>1.4</v>
+      </c>
+      <c r="AT293">
+        <v>2.85</v>
+      </c>
+      <c r="AU293">
+        <v>3</v>
+      </c>
+      <c r="AV293">
+        <v>7</v>
+      </c>
+      <c r="AW293">
+        <v>6</v>
+      </c>
+      <c r="AX293">
+        <v>18</v>
+      </c>
+      <c r="AY293">
+        <v>11</v>
+      </c>
+      <c r="AZ293">
+        <v>31</v>
+      </c>
+      <c r="BA293">
+        <v>3</v>
+      </c>
+      <c r="BB293">
+        <v>10</v>
+      </c>
+      <c r="BC293">
+        <v>13</v>
+      </c>
+      <c r="BD293">
+        <v>1.74</v>
+      </c>
+      <c r="BE293">
+        <v>6.75</v>
+      </c>
+      <c r="BF293">
+        <v>2.3</v>
+      </c>
+      <c r="BG293">
+        <v>1.2</v>
+      </c>
+      <c r="BH293">
+        <v>3.95</v>
+      </c>
+      <c r="BI293">
+        <v>1.35</v>
+      </c>
+      <c r="BJ293">
+        <v>2.9</v>
+      </c>
+      <c r="BK293">
+        <v>1.58</v>
+      </c>
+      <c r="BL293">
+        <v>2.18</v>
+      </c>
+      <c r="BM293">
+        <v>1.93</v>
+      </c>
+      <c r="BN293">
+        <v>1.76</v>
+      </c>
+      <c r="BO293">
+        <v>2.43</v>
+      </c>
+      <c r="BP293">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1856" uniqueCount="433">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -859,6 +859,15 @@
     <t>['37', '73']</t>
   </si>
   <si>
+    <t>['2', '29']</t>
+  </si>
+  <si>
+    <t>['45+2', '74']</t>
+  </si>
+  <si>
+    <t>['67']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1043,9 +1052,6 @@
   </si>
   <si>
     <t>['10', '27', '34', '36', '45+5']</t>
-  </si>
-  <si>
-    <t>['67']</t>
   </si>
   <si>
     <t>['7', '17', '34', '76', '87']</t>
@@ -1298,6 +1304,15 @@
   </si>
   <si>
     <t>['28', '67', '90']</t>
+  </si>
+  <si>
+    <t>['90+2']</t>
+  </si>
+  <si>
+    <t>['51', '78', '90+10']</t>
+  </si>
+  <si>
+    <t>['34', '60']</t>
   </si>
 </sst>
 </file>
@@ -1659,7 +1674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP293"/>
+  <dimension ref="A1:BP299"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2121,7 +2136,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2533,7 +2548,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2817,7 +2832,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ6">
         <v>0.33</v>
@@ -2945,7 +2960,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -3151,7 +3166,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3232,7 +3247,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ8">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3438,7 +3453,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ9">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3563,7 +3578,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -4053,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ12">
         <v>1.13</v>
@@ -4262,7 +4277,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ13">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4674,7 +4689,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ15">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4877,7 +4892,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="AQ16">
         <v>1.73</v>
@@ -5083,10 +5098,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ17">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5211,7 +5226,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5417,7 +5432,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5701,7 +5716,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ20">
         <v>1.6</v>
@@ -5907,10 +5922,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ21">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -6241,7 +6256,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6322,7 +6337,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ23">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR23">
         <v>0.86</v>
@@ -6447,7 +6462,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -7065,7 +7080,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7271,7 +7286,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7477,7 +7492,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7558,7 +7573,7 @@
         <v>2</v>
       </c>
       <c r="AQ29">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR29">
         <v>1.08</v>
@@ -7761,7 +7776,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ30">
         <v>1.14</v>
@@ -7889,7 +7904,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8095,7 +8110,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8173,7 +8188,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="AQ32">
         <v>1.13</v>
@@ -8379,10 +8394,10 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ33">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR33">
         <v>1.6</v>
@@ -8507,7 +8522,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -8588,7 +8603,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ34">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR34">
         <v>1.29</v>
@@ -8997,7 +9012,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ36">
         <v>1.73</v>
@@ -9203,10 +9218,10 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ37">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR37">
         <v>1.98</v>
@@ -9331,7 +9346,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9412,7 +9427,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ38">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR38">
         <v>0.92</v>
@@ -9537,7 +9552,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9615,7 +9630,7 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ39">
         <v>1.4</v>
@@ -9743,7 +9758,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9949,7 +9964,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -10155,7 +10170,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10361,7 +10376,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10648,7 +10663,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ44">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR44">
         <v>1</v>
@@ -10851,7 +10866,7 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ45">
         <v>1.53</v>
@@ -11057,10 +11072,10 @@
         <v>0.5</v>
       </c>
       <c r="AP46">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="AQ46">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR46">
         <v>0.83</v>
@@ -11266,7 +11281,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ47">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR47">
         <v>1.75</v>
@@ -11881,7 +11896,7 @@
         <v>3</v>
       </c>
       <c r="AP50">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ50">
         <v>1.73</v>
@@ -12009,7 +12024,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -12087,7 +12102,7 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ51">
         <v>1.8</v>
@@ -12215,7 +12230,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12293,7 +12308,7 @@
         <v>3</v>
       </c>
       <c r="AP52">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ52">
         <v>1.4</v>
@@ -12421,7 +12436,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12708,7 +12723,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ54">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR54">
         <v>1.48</v>
@@ -12833,7 +12848,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -12914,7 +12929,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ55">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR55">
         <v>1.6</v>
@@ -13245,7 +13260,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13451,7 +13466,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13657,7 +13672,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13738,7 +13753,7 @@
         <v>0.47</v>
       </c>
       <c r="AQ59">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR59">
         <v>0.95</v>
@@ -13863,7 +13878,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -14069,7 +14084,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14147,7 +14162,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ61">
         <v>0.33</v>
@@ -14275,7 +14290,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14687,7 +14702,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14765,7 +14780,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ64">
         <v>1.47</v>
@@ -14893,7 +14908,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -14974,7 +14989,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ65">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR65">
         <v>1.33</v>
@@ -15099,7 +15114,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -16129,7 +16144,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16207,7 +16222,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ71">
         <v>1.14</v>
@@ -16541,7 +16556,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16622,7 +16637,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ73">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR73">
         <v>2.01</v>
@@ -16747,7 +16762,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16828,7 +16843,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ74">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR74">
         <v>1.31</v>
@@ -16953,7 +16968,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -17031,7 +17046,7 @@
         <v>1.33</v>
       </c>
       <c r="AP75">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ75">
         <v>1.53</v>
@@ -17159,7 +17174,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17237,10 +17252,10 @@
         <v>0.33</v>
       </c>
       <c r="AP76">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="AQ76">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR76">
         <v>0.91</v>
@@ -17365,7 +17380,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17446,7 +17461,7 @@
         <v>0.47</v>
       </c>
       <c r="AQ77">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR77">
         <v>1.11</v>
@@ -17649,7 +17664,7 @@
         <v>2.33</v>
       </c>
       <c r="AP78">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ78">
         <v>1.8</v>
@@ -17777,7 +17792,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17983,7 +17998,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18061,7 +18076,7 @@
         <v>3</v>
       </c>
       <c r="AP80">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ80">
         <v>1.4</v>
@@ -18270,7 +18285,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ81">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR81">
         <v>1.42</v>
@@ -18395,7 +18410,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18679,7 +18694,7 @@
         <v>0</v>
       </c>
       <c r="AP83">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ83">
         <v>0.33</v>
@@ -18807,7 +18822,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18885,7 +18900,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ84">
         <v>1</v>
@@ -19013,7 +19028,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -19219,7 +19234,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19300,7 +19315,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ86">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR86">
         <v>1.7</v>
@@ -19631,7 +19646,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -20043,7 +20058,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20249,7 +20264,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20533,7 +20548,7 @@
         <v>1.75</v>
       </c>
       <c r="AP92">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ92">
         <v>1.8</v>
@@ -20739,10 +20754,10 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="AQ93">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR93">
         <v>1.09</v>
@@ -20945,7 +20960,7 @@
         <v>2.5</v>
       </c>
       <c r="AP94">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ94">
         <v>1.4</v>
@@ -21154,7 +21169,7 @@
         <v>0.47</v>
       </c>
       <c r="AQ95">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR95">
         <v>1.12</v>
@@ -21357,7 +21372,7 @@
         <v>1.75</v>
       </c>
       <c r="AP96">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ96">
         <v>1.53</v>
@@ -21691,7 +21706,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21772,7 +21787,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ98">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR98">
         <v>1.11</v>
@@ -21897,7 +21912,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -21978,7 +21993,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ99">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR99">
         <v>1.99</v>
@@ -22103,7 +22118,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22390,7 +22405,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ101">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR101">
         <v>1.81</v>
@@ -22515,7 +22530,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22721,7 +22736,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23008,7 +23023,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ104">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR104">
         <v>1.57</v>
@@ -23417,7 +23432,7 @@
         <v>2</v>
       </c>
       <c r="AP106">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ106">
         <v>1.4</v>
@@ -23623,10 +23638,10 @@
         <v>2</v>
       </c>
       <c r="AP107">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ107">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR107">
         <v>1.75</v>
@@ -23832,7 +23847,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ108">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR108">
         <v>1.48</v>
@@ -23957,7 +23972,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -24163,7 +24178,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24244,7 +24259,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ110">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR110">
         <v>1.96</v>
@@ -24575,7 +24590,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24781,7 +24796,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -25068,7 +25083,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ114">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR114">
         <v>1.26</v>
@@ -25399,7 +25414,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25477,7 +25492,7 @@
         <v>1.4</v>
       </c>
       <c r="AP116">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ116">
         <v>1.53</v>
@@ -25605,7 +25620,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25686,7 +25701,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ117">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR117">
         <v>1.41</v>
@@ -25811,7 +25826,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25889,7 +25904,7 @@
         <v>0.8</v>
       </c>
       <c r="AP118">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ118">
         <v>1.14</v>
@@ -26017,7 +26032,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -26095,7 +26110,7 @@
         <v>2.6</v>
       </c>
       <c r="AP119">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="AQ119">
         <v>2.33</v>
@@ -26223,7 +26238,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26429,7 +26444,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26507,7 +26522,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ121">
         <v>1.13</v>
@@ -26635,7 +26650,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26713,7 +26728,7 @@
         <v>0</v>
       </c>
       <c r="AP122">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ122">
         <v>0.33</v>
@@ -26841,7 +26856,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -27128,7 +27143,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ124">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR124">
         <v>1.52</v>
@@ -27334,7 +27349,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ125">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR125">
         <v>1.7</v>
@@ -27459,7 +27474,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27665,7 +27680,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -27952,7 +27967,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ128">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR128">
         <v>1.43</v>
@@ -28158,7 +28173,7 @@
         <v>2</v>
       </c>
       <c r="AQ129">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR129">
         <v>1.64</v>
@@ -28283,7 +28298,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>343</v>
+        <v>283</v>
       </c>
       <c r="Q130">
         <v>2.2</v>
@@ -28567,7 +28582,7 @@
         <v>1.67</v>
       </c>
       <c r="AP131">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ131">
         <v>1.4</v>
@@ -28695,7 +28710,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28776,7 +28791,7 @@
         <v>0.47</v>
       </c>
       <c r="AQ132">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR132">
         <v>1.18</v>
@@ -29107,7 +29122,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29185,7 +29200,7 @@
         <v>2.17</v>
       </c>
       <c r="AP134">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="AQ134">
         <v>1.4</v>
@@ -29313,7 +29328,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -29391,7 +29406,7 @@
         <v>2.67</v>
       </c>
       <c r="AP135">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ135">
         <v>2.33</v>
@@ -29597,7 +29612,7 @@
         <v>1.83</v>
       </c>
       <c r="AP136">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ136">
         <v>1.73</v>
@@ -30012,7 +30027,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ138">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR138">
         <v>1.44</v>
@@ -30627,7 +30642,7 @@
         <v>1.17</v>
       </c>
       <c r="AP141">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ141">
         <v>1.14</v>
@@ -30755,7 +30770,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30961,7 +30976,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -31373,7 +31388,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31579,7 +31594,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31785,7 +31800,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31991,7 +32006,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -32197,7 +32212,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32609,7 +32624,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -32690,7 +32705,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ151">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR151">
         <v>1.14</v>
@@ -32896,7 +32911,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ152">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR152">
         <v>2.08</v>
@@ -33099,10 +33114,10 @@
         <v>0.71</v>
       </c>
       <c r="AP153">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ153">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR153">
         <v>1.32</v>
@@ -33227,7 +33242,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33305,7 +33320,7 @@
         <v>1.29</v>
       </c>
       <c r="AP154">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ154">
         <v>1.47</v>
@@ -33433,7 +33448,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33514,7 +33529,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ155">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR155">
         <v>1.52</v>
@@ -33639,7 +33654,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33717,10 +33732,10 @@
         <v>0.86</v>
       </c>
       <c r="AP156">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ156">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR156">
         <v>1.53</v>
@@ -33845,7 +33860,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33923,7 +33938,7 @@
         <v>0.86</v>
       </c>
       <c r="AP157">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ157">
         <v>1.13</v>
@@ -34051,7 +34066,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34129,7 +34144,7 @@
         <v>1</v>
       </c>
       <c r="AP158">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="AQ158">
         <v>1.14</v>
@@ -34338,7 +34353,7 @@
         <v>2</v>
       </c>
       <c r="AQ159">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR159">
         <v>1.69</v>
@@ -34541,7 +34556,7 @@
         <v>1.14</v>
       </c>
       <c r="AP160">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ160">
         <v>1.13</v>
@@ -34875,7 +34890,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -35081,7 +35096,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35287,7 +35302,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35493,7 +35508,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35905,7 +35920,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36111,7 +36126,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36523,7 +36538,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36807,10 +36822,10 @@
         <v>0.75</v>
       </c>
       <c r="AP171">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ171">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR171">
         <v>2.11</v>
@@ -36935,7 +36950,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37013,7 +37028,7 @@
         <v>1.13</v>
       </c>
       <c r="AP172">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="AQ172">
         <v>1.13</v>
@@ -37425,10 +37440,10 @@
         <v>1.25</v>
       </c>
       <c r="AP174">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ174">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR174">
         <v>1.48</v>
@@ -37553,7 +37568,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -37837,10 +37852,10 @@
         <v>1.13</v>
       </c>
       <c r="AP176">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ176">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR176">
         <v>1.74</v>
@@ -38171,7 +38186,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38249,10 +38264,10 @@
         <v>0.63</v>
       </c>
       <c r="AP178">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ178">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR178">
         <v>1.73</v>
@@ -38455,10 +38470,10 @@
         <v>0.13</v>
       </c>
       <c r="AP179">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ179">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR179">
         <v>1.54</v>
@@ -38664,7 +38679,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ180">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR180">
         <v>2.03</v>
@@ -38789,7 +38804,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38995,7 +39010,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39407,7 +39422,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39613,7 +39628,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39819,7 +39834,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -40231,7 +40246,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40437,7 +40452,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40643,7 +40658,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40849,7 +40864,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -41133,10 +41148,10 @@
         <v>0.78</v>
       </c>
       <c r="AP192">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ192">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR192">
         <v>1.73</v>
@@ -41261,7 +41276,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41342,7 +41357,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ193">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR193">
         <v>1.51</v>
@@ -41673,7 +41688,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41751,10 +41766,10 @@
         <v>0.22</v>
       </c>
       <c r="AP195">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="AQ195">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR195">
         <v>1.14</v>
@@ -41879,7 +41894,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -41957,7 +41972,7 @@
         <v>1.33</v>
       </c>
       <c r="AP196">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ196">
         <v>1.13</v>
@@ -42163,7 +42178,7 @@
         <v>1.8</v>
       </c>
       <c r="AP197">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ197">
         <v>1.8</v>
@@ -42291,7 +42306,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42372,7 +42387,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ198">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR198">
         <v>1.57</v>
@@ -42497,7 +42512,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42575,7 +42590,7 @@
         <v>1</v>
       </c>
       <c r="AP199">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ199">
         <v>1.13</v>
@@ -42703,7 +42718,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42909,7 +42924,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -43115,7 +43130,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43321,7 +43336,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43527,7 +43542,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43733,7 +43748,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -43814,7 +43829,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ205">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR205">
         <v>1.11</v>
@@ -44017,7 +44032,7 @@
         <v>0.9</v>
       </c>
       <c r="AP206">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ206">
         <v>1</v>
@@ -44145,7 +44160,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44226,7 +44241,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ207">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR207">
         <v>1.34</v>
@@ -44557,7 +44572,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44969,7 +44984,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45047,7 +45062,7 @@
         <v>1.45</v>
       </c>
       <c r="AP211">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ211">
         <v>1.53</v>
@@ -45175,7 +45190,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45256,7 +45271,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ212">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR212">
         <v>1.29</v>
@@ -45381,7 +45396,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45587,7 +45602,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45793,7 +45808,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -45874,7 +45889,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ215">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR215">
         <v>1.97</v>
@@ -45999,7 +46014,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -46205,7 +46220,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46411,7 +46426,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46617,7 +46632,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46823,7 +46838,7 @@
         <v>240</v>
       </c>
       <c r="P220" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q220">
         <v>1.73</v>
@@ -47107,7 +47122,7 @@
         <v>2.09</v>
       </c>
       <c r="AP221">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ221">
         <v>1.73</v>
@@ -47235,7 +47250,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -47313,10 +47328,10 @@
         <v>0.7</v>
       </c>
       <c r="AP222">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ222">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR222">
         <v>1.58</v>
@@ -47519,10 +47534,10 @@
         <v>0.9</v>
       </c>
       <c r="AP223">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ223">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR223">
         <v>1.79</v>
@@ -47647,7 +47662,7 @@
         <v>107</v>
       </c>
       <c r="P224" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Q224">
         <v>6</v>
@@ -47725,7 +47740,7 @@
         <v>1.64</v>
       </c>
       <c r="AP224">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="AQ224">
         <v>1.6</v>
@@ -47853,7 +47868,7 @@
         <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q225">
         <v>6.5</v>
@@ -48059,7 +48074,7 @@
         <v>243</v>
       </c>
       <c r="P226" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Q226">
         <v>2.38</v>
@@ -48137,7 +48152,7 @@
         <v>1.91</v>
       </c>
       <c r="AP226">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ226">
         <v>1.4</v>
@@ -48265,7 +48280,7 @@
         <v>155</v>
       </c>
       <c r="P227" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48346,7 +48361,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ227">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR227">
         <v>1.4</v>
@@ -48471,7 +48486,7 @@
         <v>244</v>
       </c>
       <c r="P228" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Q228">
         <v>1.91</v>
@@ -48552,7 +48567,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ228">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR228">
         <v>1.71</v>
@@ -48883,7 +48898,7 @@
         <v>91</v>
       </c>
       <c r="P230" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="Q230">
         <v>2.88</v>
@@ -49295,7 +49310,7 @@
         <v>95</v>
       </c>
       <c r="P232" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Q232">
         <v>2.2</v>
@@ -49373,7 +49388,7 @@
         <v>1.45</v>
       </c>
       <c r="AP232">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ232">
         <v>1.47</v>
@@ -49582,7 +49597,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ233">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR233">
         <v>1.37</v>
@@ -49707,7 +49722,7 @@
         <v>151</v>
       </c>
       <c r="P234" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q234">
         <v>2.6</v>
@@ -49913,7 +49928,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Q235">
         <v>4.5</v>
@@ -49991,7 +50006,7 @@
         <v>2.45</v>
       </c>
       <c r="AP235">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ235">
         <v>2.33</v>
@@ -50200,7 +50215,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ236">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR236">
         <v>1.21</v>
@@ -50325,7 +50340,7 @@
         <v>91</v>
       </c>
       <c r="P237" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50531,7 +50546,7 @@
         <v>91</v>
       </c>
       <c r="P238" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Q238">
         <v>2.75</v>
@@ -50612,7 +50627,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ238">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR238">
         <v>1.51</v>
@@ -50943,7 +50958,7 @@
         <v>249</v>
       </c>
       <c r="P240" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Q240">
         <v>1.8</v>
@@ -51149,7 +51164,7 @@
         <v>250</v>
       </c>
       <c r="P241" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Q241">
         <v>6</v>
@@ -51433,7 +51448,7 @@
         <v>1.75</v>
       </c>
       <c r="AP242">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ242">
         <v>1.4</v>
@@ -51561,7 +51576,7 @@
         <v>91</v>
       </c>
       <c r="P243" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Q243">
         <v>9</v>
@@ -51767,7 +51782,7 @@
         <v>203</v>
       </c>
       <c r="P244" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Q244">
         <v>5</v>
@@ -51845,7 +51860,7 @@
         <v>1.58</v>
       </c>
       <c r="AP244">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="AQ244">
         <v>1.53</v>
@@ -52051,7 +52066,7 @@
         <v>1.75</v>
       </c>
       <c r="AP245">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ245">
         <v>1.6</v>
@@ -52260,7 +52275,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ246">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR246">
         <v>1.24</v>
@@ -52672,7 +52687,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ248">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR248">
         <v>1.52</v>
@@ -52797,7 +52812,7 @@
         <v>254</v>
       </c>
       <c r="P249" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Q249">
         <v>2.63</v>
@@ -52878,7 +52893,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ249">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR249">
         <v>1.43</v>
@@ -53003,7 +53018,7 @@
         <v>255</v>
       </c>
       <c r="P250" t="s">
-        <v>343</v>
+        <v>283</v>
       </c>
       <c r="Q250">
         <v>1.57</v>
@@ -53081,7 +53096,7 @@
         <v>0.75</v>
       </c>
       <c r="AP250">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ250">
         <v>1</v>
@@ -53415,7 +53430,7 @@
         <v>256</v>
       </c>
       <c r="P252" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Q252">
         <v>4</v>
@@ -53621,7 +53636,7 @@
         <v>91</v>
       </c>
       <c r="P253" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q253">
         <v>3.6</v>
@@ -53702,7 +53717,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ253">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR253">
         <v>1.19</v>
@@ -53827,7 +53842,7 @@
         <v>257</v>
       </c>
       <c r="P254" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Q254">
         <v>3.25</v>
@@ -54033,7 +54048,7 @@
         <v>91</v>
       </c>
       <c r="P255" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Q255">
         <v>5</v>
@@ -54111,7 +54126,7 @@
         <v>1.46</v>
       </c>
       <c r="AP255">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="AQ255">
         <v>1.53</v>
@@ -54239,7 +54254,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q256">
         <v>3.75</v>
@@ -54445,7 +54460,7 @@
         <v>91</v>
       </c>
       <c r="P257" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Q257">
         <v>1.73</v>
@@ -54729,7 +54744,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP258">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ258">
         <v>1</v>
@@ -54857,7 +54872,7 @@
         <v>91</v>
       </c>
       <c r="P259" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Q259">
         <v>2.75</v>
@@ -54938,7 +54953,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ259">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR259">
         <v>1.64</v>
@@ -55063,7 +55078,7 @@
         <v>258</v>
       </c>
       <c r="P260" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q260">
         <v>3.1</v>
@@ -55269,7 +55284,7 @@
         <v>259</v>
       </c>
       <c r="P261" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Q261">
         <v>2.38</v>
@@ -55347,7 +55362,7 @@
         <v>1.77</v>
       </c>
       <c r="AP261">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ261">
         <v>1.73</v>
@@ -55475,7 +55490,7 @@
         <v>91</v>
       </c>
       <c r="P262" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="Q262">
         <v>3.1</v>
@@ -55553,7 +55568,7 @@
         <v>2.29</v>
       </c>
       <c r="AP262">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ262">
         <v>2.33</v>
@@ -55681,7 +55696,7 @@
         <v>260</v>
       </c>
       <c r="P263" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q263">
         <v>3.2</v>
@@ -55762,7 +55777,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ263">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR263">
         <v>1.48</v>
@@ -55887,7 +55902,7 @@
         <v>261</v>
       </c>
       <c r="P264" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="Q264">
         <v>3.5</v>
@@ -56171,7 +56186,7 @@
         <v>1.69</v>
       </c>
       <c r="AP265">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ265">
         <v>1.53</v>
@@ -56711,7 +56726,7 @@
         <v>264</v>
       </c>
       <c r="P268" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="Q268">
         <v>2.05</v>
@@ -56792,7 +56807,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ268">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR268">
         <v>1.55</v>
@@ -56998,7 +57013,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ269">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR269">
         <v>1.65</v>
@@ -57407,7 +57422,7 @@
         <v>1.62</v>
       </c>
       <c r="AP271">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ271">
         <v>1.6</v>
@@ -57616,7 +57631,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ272">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR272">
         <v>1.27</v>
@@ -57947,7 +57962,7 @@
         <v>269</v>
       </c>
       <c r="P274" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="Q274">
         <v>1.4</v>
@@ -58025,7 +58040,7 @@
         <v>0.36</v>
       </c>
       <c r="AP274">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ274">
         <v>0.33</v>
@@ -58153,7 +58168,7 @@
         <v>270</v>
       </c>
       <c r="P275" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q275">
         <v>2.5</v>
@@ -58231,7 +58246,7 @@
         <v>1.69</v>
       </c>
       <c r="AP275">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ275">
         <v>1.47</v>
@@ -58440,7 +58455,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ276">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AR276">
         <v>1.51</v>
@@ -58646,7 +58661,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ277">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR277">
         <v>1.64</v>
@@ -58852,7 +58867,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ278">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR278">
         <v>1.27</v>
@@ -59058,7 +59073,7 @@
         <v>2</v>
       </c>
       <c r="AQ279">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR279">
         <v>1.96</v>
@@ -59183,7 +59198,7 @@
         <v>273</v>
       </c>
       <c r="P280" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Q280">
         <v>2.88</v>
@@ -59389,7 +59404,7 @@
         <v>274</v>
       </c>
       <c r="P281" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q281">
         <v>5.5</v>
@@ -59595,7 +59610,7 @@
         <v>91</v>
       </c>
       <c r="P282" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q282">
         <v>3.5</v>
@@ -59801,7 +59816,7 @@
         <v>275</v>
       </c>
       <c r="P283" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="Q283">
         <v>4</v>
@@ -59879,7 +59894,7 @@
         <v>0.86</v>
       </c>
       <c r="AP283">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="AQ283">
         <v>1</v>
@@ -60007,7 +60022,7 @@
         <v>276</v>
       </c>
       <c r="P284" t="s">
-        <v>343</v>
+        <v>283</v>
       </c>
       <c r="Q284">
         <v>2.88</v>
@@ -60213,7 +60228,7 @@
         <v>277</v>
       </c>
       <c r="P285" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Q285">
         <v>4</v>
@@ -60419,7 +60434,7 @@
         <v>278</v>
       </c>
       <c r="P286" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Q286">
         <v>2.2</v>
@@ -60497,7 +60512,7 @@
         <v>1.57</v>
       </c>
       <c r="AP286">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ286">
         <v>1.53</v>
@@ -60625,7 +60640,7 @@
         <v>195</v>
       </c>
       <c r="P287" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="Q287">
         <v>2.25</v>
@@ -60703,10 +60718,10 @@
         <v>1.08</v>
       </c>
       <c r="AP287">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ287">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR287">
         <v>1.74</v>
@@ -61243,7 +61258,7 @@
         <v>91</v>
       </c>
       <c r="P290" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Q290">
         <v>4.33</v>
@@ -62018,6 +62033,1242 @@
       </c>
       <c r="BP293">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="294" spans="1:68">
+      <c r="A294" s="1">
+        <v>293</v>
+      </c>
+      <c r="B294">
+        <v>7466977</v>
+      </c>
+      <c r="C294" t="s">
+        <v>68</v>
+      </c>
+      <c r="D294" t="s">
+        <v>69</v>
+      </c>
+      <c r="E294" s="2">
+        <v>45749.65625</v>
+      </c>
+      <c r="F294">
+        <v>30</v>
+      </c>
+      <c r="G294" t="s">
+        <v>84</v>
+      </c>
+      <c r="H294" t="s">
+        <v>82</v>
+      </c>
+      <c r="I294">
+        <v>1</v>
+      </c>
+      <c r="J294">
+        <v>0</v>
+      </c>
+      <c r="K294">
+        <v>1</v>
+      </c>
+      <c r="L294">
+        <v>1</v>
+      </c>
+      <c r="M294">
+        <v>1</v>
+      </c>
+      <c r="N294">
+        <v>2</v>
+      </c>
+      <c r="O294" t="s">
+        <v>172</v>
+      </c>
+      <c r="P294" t="s">
+        <v>430</v>
+      </c>
+      <c r="Q294">
+        <v>5.5</v>
+      </c>
+      <c r="R294">
+        <v>2.3</v>
+      </c>
+      <c r="S294">
+        <v>2.2</v>
+      </c>
+      <c r="T294">
+        <v>1.36</v>
+      </c>
+      <c r="U294">
+        <v>3</v>
+      </c>
+      <c r="V294">
+        <v>2.63</v>
+      </c>
+      <c r="W294">
+        <v>1.44</v>
+      </c>
+      <c r="X294">
+        <v>7</v>
+      </c>
+      <c r="Y294">
+        <v>1.1</v>
+      </c>
+      <c r="Z294">
+        <v>5.4</v>
+      </c>
+      <c r="AA294">
+        <v>4</v>
+      </c>
+      <c r="AB294">
+        <v>1.65</v>
+      </c>
+      <c r="AC294">
+        <v>1.05</v>
+      </c>
+      <c r="AD294">
+        <v>9.5</v>
+      </c>
+      <c r="AE294">
+        <v>1.25</v>
+      </c>
+      <c r="AF294">
+        <v>3.75</v>
+      </c>
+      <c r="AG294">
+        <v>1.65</v>
+      </c>
+      <c r="AH294">
+        <v>2.1</v>
+      </c>
+      <c r="AI294">
+        <v>1.8</v>
+      </c>
+      <c r="AJ294">
+        <v>1.95</v>
+      </c>
+      <c r="AK294">
+        <v>2.2</v>
+      </c>
+      <c r="AL294">
+        <v>1.24</v>
+      </c>
+      <c r="AM294">
+        <v>1.17</v>
+      </c>
+      <c r="AN294">
+        <v>0.29</v>
+      </c>
+      <c r="AO294">
+        <v>1.69</v>
+      </c>
+      <c r="AP294">
+        <v>0.33</v>
+      </c>
+      <c r="AQ294">
+        <v>1.64</v>
+      </c>
+      <c r="AR294">
+        <v>1.19</v>
+      </c>
+      <c r="AS294">
+        <v>1.38</v>
+      </c>
+      <c r="AT294">
+        <v>2.57</v>
+      </c>
+      <c r="AU294">
+        <v>3</v>
+      </c>
+      <c r="AV294">
+        <v>4</v>
+      </c>
+      <c r="AW294">
+        <v>6</v>
+      </c>
+      <c r="AX294">
+        <v>6</v>
+      </c>
+      <c r="AY294">
+        <v>11</v>
+      </c>
+      <c r="AZ294">
+        <v>11</v>
+      </c>
+      <c r="BA294">
+        <v>2</v>
+      </c>
+      <c r="BB294">
+        <v>2</v>
+      </c>
+      <c r="BC294">
+        <v>4</v>
+      </c>
+      <c r="BD294">
+        <v>2.75</v>
+      </c>
+      <c r="BE294">
+        <v>6.75</v>
+      </c>
+      <c r="BF294">
+        <v>1.52</v>
+      </c>
+      <c r="BG294">
+        <v>1.24</v>
+      </c>
+      <c r="BH294">
+        <v>3.55</v>
+      </c>
+      <c r="BI294">
+        <v>1.43</v>
+      </c>
+      <c r="BJ294">
+        <v>2.55</v>
+      </c>
+      <c r="BK294">
+        <v>1.71</v>
+      </c>
+      <c r="BL294">
+        <v>2</v>
+      </c>
+      <c r="BM294">
+        <v>2.08</v>
+      </c>
+      <c r="BN294">
+        <v>1.65</v>
+      </c>
+      <c r="BO294">
+        <v>2.65</v>
+      </c>
+      <c r="BP294">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="295" spans="1:68">
+      <c r="A295" s="1">
+        <v>294</v>
+      </c>
+      <c r="B295">
+        <v>7466975</v>
+      </c>
+      <c r="C295" t="s">
+        <v>68</v>
+      </c>
+      <c r="D295" t="s">
+        <v>69</v>
+      </c>
+      <c r="E295" s="2">
+        <v>45749.65625</v>
+      </c>
+      <c r="F295">
+        <v>30</v>
+      </c>
+      <c r="G295" t="s">
+        <v>85</v>
+      </c>
+      <c r="H295" t="s">
+        <v>79</v>
+      </c>
+      <c r="I295">
+        <v>2</v>
+      </c>
+      <c r="J295">
+        <v>0</v>
+      </c>
+      <c r="K295">
+        <v>2</v>
+      </c>
+      <c r="L295">
+        <v>2</v>
+      </c>
+      <c r="M295">
+        <v>0</v>
+      </c>
+      <c r="N295">
+        <v>2</v>
+      </c>
+      <c r="O295" t="s">
+        <v>281</v>
+      </c>
+      <c r="P295" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q295">
+        <v>1.53</v>
+      </c>
+      <c r="R295">
+        <v>3.1</v>
+      </c>
+      <c r="S295">
+        <v>10</v>
+      </c>
+      <c r="T295">
+        <v>1.2</v>
+      </c>
+      <c r="U295">
+        <v>4.33</v>
+      </c>
+      <c r="V295">
+        <v>1.91</v>
+      </c>
+      <c r="W295">
+        <v>1.8</v>
+      </c>
+      <c r="X295">
+        <v>4</v>
+      </c>
+      <c r="Y295">
+        <v>1.22</v>
+      </c>
+      <c r="Z295">
+        <v>1.15</v>
+      </c>
+      <c r="AA295">
+        <v>9</v>
+      </c>
+      <c r="AB295">
+        <v>14</v>
+      </c>
+      <c r="AC295">
+        <v>1.01</v>
+      </c>
+      <c r="AD295">
+        <v>26</v>
+      </c>
+      <c r="AE295">
+        <v>1.1</v>
+      </c>
+      <c r="AF295">
+        <v>6.5</v>
+      </c>
+      <c r="AG295">
+        <v>1.33</v>
+      </c>
+      <c r="AH295">
+        <v>3.2</v>
+      </c>
+      <c r="AI295">
+        <v>1.95</v>
+      </c>
+      <c r="AJ295">
+        <v>1.8</v>
+      </c>
+      <c r="AK295">
+        <v>1.03</v>
+      </c>
+      <c r="AL295">
+        <v>1.08</v>
+      </c>
+      <c r="AM295">
+        <v>4.8</v>
+      </c>
+      <c r="AN295">
+        <v>1.93</v>
+      </c>
+      <c r="AO295">
+        <v>0.57</v>
+      </c>
+      <c r="AP295">
+        <v>2</v>
+      </c>
+      <c r="AQ295">
+        <v>0.53</v>
+      </c>
+      <c r="AR295">
+        <v>1.96</v>
+      </c>
+      <c r="AS295">
+        <v>1.02</v>
+      </c>
+      <c r="AT295">
+        <v>2.98</v>
+      </c>
+      <c r="AU295">
+        <v>6</v>
+      </c>
+      <c r="AV295">
+        <v>0</v>
+      </c>
+      <c r="AW295">
+        <v>6</v>
+      </c>
+      <c r="AX295">
+        <v>3</v>
+      </c>
+      <c r="AY295">
+        <v>18</v>
+      </c>
+      <c r="AZ295">
+        <v>3</v>
+      </c>
+      <c r="BA295">
+        <v>5</v>
+      </c>
+      <c r="BB295">
+        <v>0</v>
+      </c>
+      <c r="BC295">
+        <v>5</v>
+      </c>
+      <c r="BD295">
+        <v>1.06</v>
+      </c>
+      <c r="BE295">
+        <v>14</v>
+      </c>
+      <c r="BF295">
+        <v>9</v>
+      </c>
+      <c r="BG295">
+        <v>1.11</v>
+      </c>
+      <c r="BH295">
+        <v>5.3</v>
+      </c>
+      <c r="BI295">
+        <v>1.2</v>
+      </c>
+      <c r="BJ295">
+        <v>3.8</v>
+      </c>
+      <c r="BK295">
+        <v>1.36</v>
+      </c>
+      <c r="BL295">
+        <v>2.85</v>
+      </c>
+      <c r="BM295">
+        <v>1.56</v>
+      </c>
+      <c r="BN295">
+        <v>2.23</v>
+      </c>
+      <c r="BO295">
+        <v>1.86</v>
+      </c>
+      <c r="BP295">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="296" spans="1:68">
+      <c r="A296" s="1">
+        <v>295</v>
+      </c>
+      <c r="B296">
+        <v>7466976</v>
+      </c>
+      <c r="C296" t="s">
+        <v>68</v>
+      </c>
+      <c r="D296" t="s">
+        <v>69</v>
+      </c>
+      <c r="E296" s="2">
+        <v>45749.65625</v>
+      </c>
+      <c r="F296">
+        <v>30</v>
+      </c>
+      <c r="G296" t="s">
+        <v>74</v>
+      </c>
+      <c r="H296" t="s">
+        <v>77</v>
+      </c>
+      <c r="I296">
+        <v>1</v>
+      </c>
+      <c r="J296">
+        <v>0</v>
+      </c>
+      <c r="K296">
+        <v>1</v>
+      </c>
+      <c r="L296">
+        <v>2</v>
+      </c>
+      <c r="M296">
+        <v>1</v>
+      </c>
+      <c r="N296">
+        <v>3</v>
+      </c>
+      <c r="O296" t="s">
+        <v>282</v>
+      </c>
+      <c r="P296" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q296">
+        <v>2.2</v>
+      </c>
+      <c r="R296">
+        <v>2.5</v>
+      </c>
+      <c r="S296">
+        <v>4.33</v>
+      </c>
+      <c r="T296">
+        <v>1.25</v>
+      </c>
+      <c r="U296">
+        <v>3.75</v>
+      </c>
+      <c r="V296">
+        <v>2.2</v>
+      </c>
+      <c r="W296">
+        <v>1.62</v>
+      </c>
+      <c r="X296">
+        <v>5</v>
+      </c>
+      <c r="Y296">
+        <v>1.17</v>
+      </c>
+      <c r="Z296">
+        <v>1.71</v>
+      </c>
+      <c r="AA296">
+        <v>4.5</v>
+      </c>
+      <c r="AB296">
+        <v>4.1</v>
+      </c>
+      <c r="AC296">
+        <v>1.01</v>
+      </c>
+      <c r="AD296">
+        <v>17</v>
+      </c>
+      <c r="AE296">
+        <v>1.14</v>
+      </c>
+      <c r="AF296">
+        <v>5.5</v>
+      </c>
+      <c r="AG296">
+        <v>1.42</v>
+      </c>
+      <c r="AH296">
+        <v>2.74</v>
+      </c>
+      <c r="AI296">
+        <v>1.5</v>
+      </c>
+      <c r="AJ296">
+        <v>2.5</v>
+      </c>
+      <c r="AK296">
+        <v>1.21</v>
+      </c>
+      <c r="AL296">
+        <v>1.21</v>
+      </c>
+      <c r="AM296">
+        <v>2.15</v>
+      </c>
+      <c r="AN296">
+        <v>1.77</v>
+      </c>
+      <c r="AO296">
+        <v>1.21</v>
+      </c>
+      <c r="AP296">
+        <v>1.86</v>
+      </c>
+      <c r="AQ296">
+        <v>1.13</v>
+      </c>
+      <c r="AR296">
+        <v>1.61</v>
+      </c>
+      <c r="AS296">
+        <v>1.27</v>
+      </c>
+      <c r="AT296">
+        <v>2.88</v>
+      </c>
+      <c r="AU296">
+        <v>5</v>
+      </c>
+      <c r="AV296">
+        <v>4</v>
+      </c>
+      <c r="AW296">
+        <v>17</v>
+      </c>
+      <c r="AX296">
+        <v>9</v>
+      </c>
+      <c r="AY296">
+        <v>26</v>
+      </c>
+      <c r="AZ296">
+        <v>18</v>
+      </c>
+      <c r="BA296">
+        <v>4</v>
+      </c>
+      <c r="BB296">
+        <v>5</v>
+      </c>
+      <c r="BC296">
+        <v>9</v>
+      </c>
+      <c r="BD296">
+        <v>1.3</v>
+      </c>
+      <c r="BE296">
+        <v>8</v>
+      </c>
+      <c r="BF296">
+        <v>3.65</v>
+      </c>
+      <c r="BG296">
+        <v>1.12</v>
+      </c>
+      <c r="BH296">
+        <v>5.1</v>
+      </c>
+      <c r="BI296">
+        <v>1.23</v>
+      </c>
+      <c r="BJ296">
+        <v>3.65</v>
+      </c>
+      <c r="BK296">
+        <v>1.4</v>
+      </c>
+      <c r="BL296">
+        <v>2.65</v>
+      </c>
+      <c r="BM296">
+        <v>1.64</v>
+      </c>
+      <c r="BN296">
+        <v>2.1</v>
+      </c>
+      <c r="BO296">
+        <v>1.97</v>
+      </c>
+      <c r="BP296">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="297" spans="1:68">
+      <c r="A297" s="1">
+        <v>296</v>
+      </c>
+      <c r="B297">
+        <v>7466971</v>
+      </c>
+      <c r="C297" t="s">
+        <v>68</v>
+      </c>
+      <c r="D297" t="s">
+        <v>69</v>
+      </c>
+      <c r="E297" s="2">
+        <v>45749.65625</v>
+      </c>
+      <c r="F297">
+        <v>30</v>
+      </c>
+      <c r="G297" t="s">
+        <v>80</v>
+      </c>
+      <c r="H297" t="s">
+        <v>86</v>
+      </c>
+      <c r="I297">
+        <v>0</v>
+      </c>
+      <c r="J297">
+        <v>0</v>
+      </c>
+      <c r="K297">
+        <v>0</v>
+      </c>
+      <c r="L297">
+        <v>0</v>
+      </c>
+      <c r="M297">
+        <v>3</v>
+      </c>
+      <c r="N297">
+        <v>3</v>
+      </c>
+      <c r="O297" t="s">
+        <v>91</v>
+      </c>
+      <c r="P297" t="s">
+        <v>431</v>
+      </c>
+      <c r="Q297">
+        <v>2.6</v>
+      </c>
+      <c r="R297">
+        <v>2.4</v>
+      </c>
+      <c r="S297">
+        <v>3.75</v>
+      </c>
+      <c r="T297">
+        <v>1.29</v>
+      </c>
+      <c r="U297">
+        <v>3.5</v>
+      </c>
+      <c r="V297">
+        <v>2.25</v>
+      </c>
+      <c r="W297">
+        <v>1.57</v>
+      </c>
+      <c r="X297">
+        <v>5.5</v>
+      </c>
+      <c r="Y297">
+        <v>1.14</v>
+      </c>
+      <c r="Z297">
+        <v>1.95</v>
+      </c>
+      <c r="AA297">
+        <v>4</v>
+      </c>
+      <c r="AB297">
+        <v>3.4</v>
+      </c>
+      <c r="AC297">
+        <v>1.03</v>
+      </c>
+      <c r="AD297">
+        <v>11</v>
+      </c>
+      <c r="AE297">
+        <v>1.18</v>
+      </c>
+      <c r="AF297">
+        <v>4.75</v>
+      </c>
+      <c r="AG297">
+        <v>1.61</v>
+      </c>
+      <c r="AH297">
+        <v>2.2</v>
+      </c>
+      <c r="AI297">
+        <v>1.5</v>
+      </c>
+      <c r="AJ297">
+        <v>2.5</v>
+      </c>
+      <c r="AK297">
+        <v>1.32</v>
+      </c>
+      <c r="AL297">
+        <v>1.26</v>
+      </c>
+      <c r="AM297">
+        <v>1.75</v>
+      </c>
+      <c r="AN297">
+        <v>1.71</v>
+      </c>
+      <c r="AO297">
+        <v>1.21</v>
+      </c>
+      <c r="AP297">
+        <v>1.6</v>
+      </c>
+      <c r="AQ297">
+        <v>1.33</v>
+      </c>
+      <c r="AR297">
+        <v>1.58</v>
+      </c>
+      <c r="AS297">
+        <v>1.16</v>
+      </c>
+      <c r="AT297">
+        <v>2.74</v>
+      </c>
+      <c r="AU297">
+        <v>5</v>
+      </c>
+      <c r="AV297">
+        <v>6</v>
+      </c>
+      <c r="AW297">
+        <v>7</v>
+      </c>
+      <c r="AX297">
+        <v>3</v>
+      </c>
+      <c r="AY297">
+        <v>13</v>
+      </c>
+      <c r="AZ297">
+        <v>9</v>
+      </c>
+      <c r="BA297">
+        <v>4</v>
+      </c>
+      <c r="BB297">
+        <v>0</v>
+      </c>
+      <c r="BC297">
+        <v>4</v>
+      </c>
+      <c r="BD297">
+        <v>1.72</v>
+      </c>
+      <c r="BE297">
+        <v>6.75</v>
+      </c>
+      <c r="BF297">
+        <v>2.33</v>
+      </c>
+      <c r="BG297">
+        <v>1.19</v>
+      </c>
+      <c r="BH297">
+        <v>4.1</v>
+      </c>
+      <c r="BI297">
+        <v>1.32</v>
+      </c>
+      <c r="BJ297">
+        <v>3</v>
+      </c>
+      <c r="BK297">
+        <v>1.55</v>
+      </c>
+      <c r="BL297">
+        <v>2.28</v>
+      </c>
+      <c r="BM297">
+        <v>1.88</v>
+      </c>
+      <c r="BN297">
+        <v>1.81</v>
+      </c>
+      <c r="BO297">
+        <v>2.32</v>
+      </c>
+      <c r="BP297">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="298" spans="1:68">
+      <c r="A298" s="1">
+        <v>297</v>
+      </c>
+      <c r="B298">
+        <v>7466969</v>
+      </c>
+      <c r="C298" t="s">
+        <v>68</v>
+      </c>
+      <c r="D298" t="s">
+        <v>69</v>
+      </c>
+      <c r="E298" s="2">
+        <v>45749.65625</v>
+      </c>
+      <c r="F298">
+        <v>30</v>
+      </c>
+      <c r="G298" t="s">
+        <v>88</v>
+      </c>
+      <c r="H298" t="s">
+        <v>71</v>
+      </c>
+      <c r="I298">
+        <v>0</v>
+      </c>
+      <c r="J298">
+        <v>1</v>
+      </c>
+      <c r="K298">
+        <v>1</v>
+      </c>
+      <c r="L298">
+        <v>1</v>
+      </c>
+      <c r="M298">
+        <v>2</v>
+      </c>
+      <c r="N298">
+        <v>3</v>
+      </c>
+      <c r="O298" t="s">
+        <v>283</v>
+      </c>
+      <c r="P298" t="s">
+        <v>432</v>
+      </c>
+      <c r="Q298">
+        <v>1.83</v>
+      </c>
+      <c r="R298">
+        <v>2.45</v>
+      </c>
+      <c r="S298">
+        <v>6</v>
+      </c>
+      <c r="T298">
+        <v>1.28</v>
+      </c>
+      <c r="U298">
+        <v>3.3</v>
+      </c>
+      <c r="V298">
+        <v>2.25</v>
+      </c>
+      <c r="W298">
+        <v>1.57</v>
+      </c>
+      <c r="X298">
+        <v>5</v>
+      </c>
+      <c r="Y298">
+        <v>1.14</v>
+      </c>
+      <c r="Z298">
+        <v>1.4</v>
+      </c>
+      <c r="AA298">
+        <v>4.9</v>
+      </c>
+      <c r="AB298">
+        <v>7</v>
+      </c>
+      <c r="AC298">
+        <v>1.03</v>
+      </c>
+      <c r="AD298">
+        <v>11</v>
+      </c>
+      <c r="AE298">
+        <v>1.17</v>
+      </c>
+      <c r="AF298">
+        <v>5</v>
+      </c>
+      <c r="AG298">
+        <v>1.57</v>
+      </c>
+      <c r="AH298">
+        <v>2.3</v>
+      </c>
+      <c r="AI298">
+        <v>1.78</v>
+      </c>
+      <c r="AJ298">
+        <v>1.9</v>
+      </c>
+      <c r="AK298">
+        <v>1.09</v>
+      </c>
+      <c r="AL298">
+        <v>1.17</v>
+      </c>
+      <c r="AM298">
+        <v>2.9</v>
+      </c>
+      <c r="AN298">
+        <v>1.5</v>
+      </c>
+      <c r="AO298">
+        <v>0.71</v>
+      </c>
+      <c r="AP298">
+        <v>1.4</v>
+      </c>
+      <c r="AQ298">
+        <v>0.87</v>
+      </c>
+      <c r="AR298">
+        <v>1.79</v>
+      </c>
+      <c r="AS298">
+        <v>0.99</v>
+      </c>
+      <c r="AT298">
+        <v>2.78</v>
+      </c>
+      <c r="AU298">
+        <v>8</v>
+      </c>
+      <c r="AV298">
+        <v>3</v>
+      </c>
+      <c r="AW298">
+        <v>16</v>
+      </c>
+      <c r="AX298">
+        <v>8</v>
+      </c>
+      <c r="AY298">
+        <v>30</v>
+      </c>
+      <c r="AZ298">
+        <v>13</v>
+      </c>
+      <c r="BA298">
+        <v>8</v>
+      </c>
+      <c r="BB298">
+        <v>3</v>
+      </c>
+      <c r="BC298">
+        <v>11</v>
+      </c>
+      <c r="BD298">
+        <v>1.22</v>
+      </c>
+      <c r="BE298">
+        <v>8.5</v>
+      </c>
+      <c r="BF298">
+        <v>4.4</v>
+      </c>
+      <c r="BG298">
+        <v>1.15</v>
+      </c>
+      <c r="BH298">
+        <v>4.6</v>
+      </c>
+      <c r="BI298">
+        <v>1.28</v>
+      </c>
+      <c r="BJ298">
+        <v>3.3</v>
+      </c>
+      <c r="BK298">
+        <v>1.48</v>
+      </c>
+      <c r="BL298">
+        <v>2.45</v>
+      </c>
+      <c r="BM298">
+        <v>1.73</v>
+      </c>
+      <c r="BN298">
+        <v>1.96</v>
+      </c>
+      <c r="BO298">
+        <v>2.12</v>
+      </c>
+      <c r="BP298">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="299" spans="1:68">
+      <c r="A299" s="1">
+        <v>298</v>
+      </c>
+      <c r="B299">
+        <v>7466978</v>
+      </c>
+      <c r="C299" t="s">
+        <v>68</v>
+      </c>
+      <c r="D299" t="s">
+        <v>69</v>
+      </c>
+      <c r="E299" s="2">
+        <v>45749.66666666666</v>
+      </c>
+      <c r="F299">
+        <v>30</v>
+      </c>
+      <c r="G299" t="s">
+        <v>89</v>
+      </c>
+      <c r="H299" t="s">
+        <v>73</v>
+      </c>
+      <c r="I299">
+        <v>0</v>
+      </c>
+      <c r="J299">
+        <v>0</v>
+      </c>
+      <c r="K299">
+        <v>0</v>
+      </c>
+      <c r="L299">
+        <v>1</v>
+      </c>
+      <c r="M299">
+        <v>0</v>
+      </c>
+      <c r="N299">
+        <v>1</v>
+      </c>
+      <c r="O299" t="s">
+        <v>97</v>
+      </c>
+      <c r="P299" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q299">
+        <v>1.91</v>
+      </c>
+      <c r="R299">
+        <v>2.4</v>
+      </c>
+      <c r="S299">
+        <v>7.5</v>
+      </c>
+      <c r="T299">
+        <v>1.33</v>
+      </c>
+      <c r="U299">
+        <v>3.25</v>
+      </c>
+      <c r="V299">
+        <v>2.63</v>
+      </c>
+      <c r="W299">
+        <v>1.44</v>
+      </c>
+      <c r="X299">
+        <v>7</v>
+      </c>
+      <c r="Y299">
+        <v>1.1</v>
+      </c>
+      <c r="Z299">
+        <v>1.33</v>
+      </c>
+      <c r="AA299">
+        <v>5.2</v>
+      </c>
+      <c r="AB299">
+        <v>9</v>
+      </c>
+      <c r="AC299">
+        <v>1.04</v>
+      </c>
+      <c r="AD299">
+        <v>10</v>
+      </c>
+      <c r="AE299">
+        <v>1.22</v>
+      </c>
+      <c r="AF299">
+        <v>4</v>
+      </c>
+      <c r="AG299">
+        <v>1.61</v>
+      </c>
+      <c r="AH299">
+        <v>2.15</v>
+      </c>
+      <c r="AI299">
+        <v>2.05</v>
+      </c>
+      <c r="AJ299">
+        <v>1.7</v>
+      </c>
+      <c r="AK299">
+        <v>1.08</v>
+      </c>
+      <c r="AL299">
+        <v>1.17</v>
+      </c>
+      <c r="AM299">
+        <v>3</v>
+      </c>
+      <c r="AN299">
+        <v>2.5</v>
+      </c>
+      <c r="AO299">
+        <v>1.07</v>
+      </c>
+      <c r="AP299">
+        <v>2.53</v>
+      </c>
+      <c r="AQ299">
+        <v>1</v>
+      </c>
+      <c r="AR299">
+        <v>1.87</v>
+      </c>
+      <c r="AS299">
+        <v>1.14</v>
+      </c>
+      <c r="AT299">
+        <v>3.01</v>
+      </c>
+      <c r="AU299">
+        <v>4</v>
+      </c>
+      <c r="AV299">
+        <v>0</v>
+      </c>
+      <c r="AW299">
+        <v>14</v>
+      </c>
+      <c r="AX299">
+        <v>6</v>
+      </c>
+      <c r="AY299">
+        <v>26</v>
+      </c>
+      <c r="AZ299">
+        <v>9</v>
+      </c>
+      <c r="BA299">
+        <v>11</v>
+      </c>
+      <c r="BB299">
+        <v>5</v>
+      </c>
+      <c r="BC299">
+        <v>16</v>
+      </c>
+      <c r="BD299">
+        <v>1.15</v>
+      </c>
+      <c r="BE299">
+        <v>9.5</v>
+      </c>
+      <c r="BF299">
+        <v>5.6</v>
+      </c>
+      <c r="BG299">
+        <v>1.18</v>
+      </c>
+      <c r="BH299">
+        <v>4.1</v>
+      </c>
+      <c r="BI299">
+        <v>1.3</v>
+      </c>
+      <c r="BJ299">
+        <v>3.05</v>
+      </c>
+      <c r="BK299">
+        <v>1.52</v>
+      </c>
+      <c r="BL299">
+        <v>2.33</v>
+      </c>
+      <c r="BM299">
+        <v>1.81</v>
+      </c>
+      <c r="BN299">
+        <v>1.88</v>
+      </c>
+      <c r="BO299">
+        <v>2.23</v>
+      </c>
+      <c r="BP299">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1856" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1862" uniqueCount="434">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -868,6 +868,9 @@
     <t>['67']</t>
   </si>
   <si>
+    <t>['50']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1674,7 +1677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP299"/>
+  <dimension ref="A1:BP300"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2136,7 +2139,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2548,7 +2551,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2960,7 +2963,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -3166,7 +3169,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3578,7 +3581,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3656,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ10">
         <v>1.4</v>
@@ -3865,7 +3868,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ11">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -5226,7 +5229,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5432,7 +5435,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -6256,7 +6259,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6462,7 +6465,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -7080,7 +7083,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7286,7 +7289,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7492,7 +7495,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7570,7 +7573,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ29">
         <v>1.64</v>
@@ -7779,7 +7782,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ30">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR30">
         <v>0.47</v>
@@ -7904,7 +7907,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8110,7 +8113,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8522,7 +8525,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -9346,7 +9349,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9552,7 +9555,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9758,7 +9761,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9964,7 +9967,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -10170,7 +10173,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10376,7 +10379,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -12024,7 +12027,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -12230,7 +12233,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12436,7 +12439,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12848,7 +12851,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -13260,7 +13263,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13338,7 +13341,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ57">
         <v>1.53</v>
@@ -13466,7 +13469,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13672,7 +13675,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13878,7 +13881,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13959,7 +13962,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ60">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR60">
         <v>1.43</v>
@@ -14084,7 +14087,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14290,7 +14293,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14702,7 +14705,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14908,7 +14911,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -15114,7 +15117,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -15810,7 +15813,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ69">
         <v>1.73</v>
@@ -16144,7 +16147,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16225,7 +16228,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ71">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR71">
         <v>1.59</v>
@@ -16556,7 +16559,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16762,7 +16765,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16968,7 +16971,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -17174,7 +17177,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17380,7 +17383,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17792,7 +17795,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17998,7 +18001,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18410,7 +18413,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18822,7 +18825,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -19028,7 +19031,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -19234,7 +19237,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19646,7 +19649,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19724,7 +19727,7 @@
         <v>1.25</v>
       </c>
       <c r="AP88">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ88">
         <v>1.6</v>
@@ -19933,7 +19936,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ89">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR89">
         <v>1.28</v>
@@ -20058,7 +20061,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20264,7 +20267,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -21706,7 +21709,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21912,7 +21915,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -22118,7 +22121,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22530,7 +22533,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22736,7 +22739,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23972,7 +23975,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -24178,7 +24181,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24462,7 +24465,7 @@
         <v>1.4</v>
       </c>
       <c r="AP111">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ111">
         <v>1.8</v>
@@ -24590,7 +24593,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24796,7 +24799,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -25414,7 +25417,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25620,7 +25623,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25826,7 +25829,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -25907,7 +25910,7 @@
         <v>2</v>
       </c>
       <c r="AQ118">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR118">
         <v>2.34</v>
@@ -26032,7 +26035,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -26238,7 +26241,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26444,7 +26447,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26650,7 +26653,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26856,7 +26859,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -27474,7 +27477,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27680,7 +27683,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -28170,7 +28173,7 @@
         <v>1.67</v>
       </c>
       <c r="AP129">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ129">
         <v>1.33</v>
@@ -28710,7 +28713,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -29122,7 +29125,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29328,7 +29331,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -30645,7 +30648,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ141">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR141">
         <v>1.64</v>
@@ -30770,7 +30773,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30976,7 +30979,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -31388,7 +31391,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31594,7 +31597,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31800,7 +31803,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -32006,7 +32009,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -32212,7 +32215,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32624,7 +32627,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -33242,7 +33245,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33448,7 +33451,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33654,7 +33657,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33860,7 +33863,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -34066,7 +34069,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34147,7 +34150,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ158">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR158">
         <v>1.06</v>
@@ -34350,7 +34353,7 @@
         <v>0.14</v>
       </c>
       <c r="AP159">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ159">
         <v>1.13</v>
@@ -34890,7 +34893,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -35096,7 +35099,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35302,7 +35305,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35508,7 +35511,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35920,7 +35923,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36126,7 +36129,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36538,7 +36541,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36950,7 +36953,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37237,7 +37240,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ173">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR173">
         <v>1.56</v>
@@ -37568,7 +37571,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -37646,7 +37649,7 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ175">
         <v>1.47</v>
@@ -38186,7 +38189,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38804,7 +38807,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -39010,7 +39013,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39422,7 +39425,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39628,7 +39631,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39834,7 +39837,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -40246,7 +40249,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40452,7 +40455,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40658,7 +40661,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40864,7 +40867,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -41276,7 +41279,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41688,7 +41691,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41894,7 +41897,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -42306,7 +42309,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42512,7 +42515,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42718,7 +42721,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42924,7 +42927,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -43002,7 +43005,7 @@
         <v>1.5</v>
       </c>
       <c r="AP201">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ201">
         <v>1.53</v>
@@ -43130,7 +43133,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43336,7 +43339,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43542,7 +43545,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43748,7 +43751,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -44160,7 +44163,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44447,7 +44450,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ208">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR208">
         <v>1.98</v>
@@ -44572,7 +44575,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44984,7 +44987,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45190,7 +45193,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45396,7 +45399,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45602,7 +45605,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45808,7 +45811,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -46014,7 +46017,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -46220,7 +46223,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46426,7 +46429,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46507,7 +46510,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ218">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR218">
         <v>1.33</v>
@@ -46632,7 +46635,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46838,7 +46841,7 @@
         <v>240</v>
       </c>
       <c r="P220" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q220">
         <v>1.73</v>
@@ -46916,7 +46919,7 @@
         <v>0.82</v>
       </c>
       <c r="AP220">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ220">
         <v>1</v>
@@ -47250,7 +47253,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -47662,7 +47665,7 @@
         <v>107</v>
       </c>
       <c r="P224" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q224">
         <v>6</v>
@@ -47868,7 +47871,7 @@
         <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q225">
         <v>6.5</v>
@@ -48074,7 +48077,7 @@
         <v>243</v>
       </c>
       <c r="P226" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q226">
         <v>2.38</v>
@@ -48280,7 +48283,7 @@
         <v>155</v>
       </c>
       <c r="P227" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48486,7 +48489,7 @@
         <v>244</v>
       </c>
       <c r="P228" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q228">
         <v>1.91</v>
@@ -48898,7 +48901,7 @@
         <v>91</v>
       </c>
       <c r="P230" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q230">
         <v>2.88</v>
@@ -49310,7 +49313,7 @@
         <v>95</v>
       </c>
       <c r="P232" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q232">
         <v>2.2</v>
@@ -49722,7 +49725,7 @@
         <v>151</v>
       </c>
       <c r="P234" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q234">
         <v>2.6</v>
@@ -49928,7 +49931,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q235">
         <v>4.5</v>
@@ -50340,7 +50343,7 @@
         <v>91</v>
       </c>
       <c r="P237" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50421,7 +50424,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ237">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR237">
         <v>1.59</v>
@@ -50546,7 +50549,7 @@
         <v>91</v>
       </c>
       <c r="P238" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q238">
         <v>2.75</v>
@@ -50958,7 +50961,7 @@
         <v>249</v>
       </c>
       <c r="P240" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q240">
         <v>1.8</v>
@@ -51036,7 +51039,7 @@
         <v>1.18</v>
       </c>
       <c r="AP240">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ240">
         <v>1.13</v>
@@ -51164,7 +51167,7 @@
         <v>250</v>
       </c>
       <c r="P241" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q241">
         <v>6</v>
@@ -51576,7 +51579,7 @@
         <v>91</v>
       </c>
       <c r="P243" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q243">
         <v>9</v>
@@ -51782,7 +51785,7 @@
         <v>203</v>
       </c>
       <c r="P244" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q244">
         <v>5</v>
@@ -52812,7 +52815,7 @@
         <v>254</v>
       </c>
       <c r="P249" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q249">
         <v>2.63</v>
@@ -53430,7 +53433,7 @@
         <v>256</v>
       </c>
       <c r="P252" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q252">
         <v>4</v>
@@ -53636,7 +53639,7 @@
         <v>91</v>
       </c>
       <c r="P253" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q253">
         <v>3.6</v>
@@ -53842,7 +53845,7 @@
         <v>257</v>
       </c>
       <c r="P254" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q254">
         <v>3.25</v>
@@ -54048,7 +54051,7 @@
         <v>91</v>
       </c>
       <c r="P255" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q255">
         <v>5</v>
@@ -54254,7 +54257,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q256">
         <v>3.75</v>
@@ -54335,7 +54338,7 @@
         <v>0.47</v>
       </c>
       <c r="AQ256">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR256">
         <v>1.19</v>
@@ -54460,7 +54463,7 @@
         <v>91</v>
       </c>
       <c r="P257" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q257">
         <v>1.73</v>
@@ -54872,7 +54875,7 @@
         <v>91</v>
       </c>
       <c r="P259" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q259">
         <v>2.75</v>
@@ -55078,7 +55081,7 @@
         <v>258</v>
       </c>
       <c r="P260" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q260">
         <v>3.1</v>
@@ -55284,7 +55287,7 @@
         <v>259</v>
       </c>
       <c r="P261" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q261">
         <v>2.38</v>
@@ -55490,7 +55493,7 @@
         <v>91</v>
       </c>
       <c r="P262" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q262">
         <v>3.1</v>
@@ -55696,7 +55699,7 @@
         <v>260</v>
       </c>
       <c r="P263" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q263">
         <v>3.2</v>
@@ -55902,7 +55905,7 @@
         <v>261</v>
       </c>
       <c r="P264" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q264">
         <v>3.5</v>
@@ -56392,7 +56395,7 @@
         <v>0.38</v>
       </c>
       <c r="AP266">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ266">
         <v>0.33</v>
@@ -56726,7 +56729,7 @@
         <v>264</v>
       </c>
       <c r="P268" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q268">
         <v>2.05</v>
@@ -57962,7 +57965,7 @@
         <v>269</v>
       </c>
       <c r="P274" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q274">
         <v>1.4</v>
@@ -58168,7 +58171,7 @@
         <v>270</v>
       </c>
       <c r="P275" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q275">
         <v>2.5</v>
@@ -59070,7 +59073,7 @@
         <v>0.62</v>
       </c>
       <c r="AP279">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ279">
         <v>0.53</v>
@@ -59198,7 +59201,7 @@
         <v>273</v>
       </c>
       <c r="P280" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q280">
         <v>2.88</v>
@@ -59404,7 +59407,7 @@
         <v>274</v>
       </c>
       <c r="P281" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q281">
         <v>5.5</v>
@@ -59610,7 +59613,7 @@
         <v>91</v>
       </c>
       <c r="P282" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q282">
         <v>3.5</v>
@@ -59816,7 +59819,7 @@
         <v>275</v>
       </c>
       <c r="P283" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q283">
         <v>4</v>
@@ -60228,7 +60231,7 @@
         <v>277</v>
       </c>
       <c r="P285" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q285">
         <v>4</v>
@@ -60434,7 +60437,7 @@
         <v>278</v>
       </c>
       <c r="P286" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q286">
         <v>2.2</v>
@@ -60640,7 +60643,7 @@
         <v>195</v>
       </c>
       <c r="P287" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q287">
         <v>2.25</v>
@@ -60927,7 +60930,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ288">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR288">
         <v>1.6</v>
@@ -61258,7 +61261,7 @@
         <v>91</v>
       </c>
       <c r="P290" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q290">
         <v>4.33</v>
@@ -62082,7 +62085,7 @@
         <v>172</v>
       </c>
       <c r="P294" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q294">
         <v>5.5</v>
@@ -62494,7 +62497,7 @@
         <v>282</v>
       </c>
       <c r="P296" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q296">
         <v>2.2</v>
@@ -62700,7 +62703,7 @@
         <v>91</v>
       </c>
       <c r="P297" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q297">
         <v>2.6</v>
@@ -62906,7 +62909,7 @@
         <v>283</v>
       </c>
       <c r="P298" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q298">
         <v>1.83</v>
@@ -63269,6 +63272,212 @@
       </c>
       <c r="BP299">
         <v>1.57</v>
+      </c>
+    </row>
+    <row r="300" spans="1:68">
+      <c r="A300" s="1">
+        <v>299</v>
+      </c>
+      <c r="B300">
+        <v>7466974</v>
+      </c>
+      <c r="C300" t="s">
+        <v>68</v>
+      </c>
+      <c r="D300" t="s">
+        <v>69</v>
+      </c>
+      <c r="E300" s="2">
+        <v>45750.66666666666</v>
+      </c>
+      <c r="F300">
+        <v>30</v>
+      </c>
+      <c r="G300" t="s">
+        <v>78</v>
+      </c>
+      <c r="H300" t="s">
+        <v>81</v>
+      </c>
+      <c r="I300">
+        <v>0</v>
+      </c>
+      <c r="J300">
+        <v>0</v>
+      </c>
+      <c r="K300">
+        <v>0</v>
+      </c>
+      <c r="L300">
+        <v>1</v>
+      </c>
+      <c r="M300">
+        <v>0</v>
+      </c>
+      <c r="N300">
+        <v>1</v>
+      </c>
+      <c r="O300" t="s">
+        <v>284</v>
+      </c>
+      <c r="P300" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q300">
+        <v>2.1</v>
+      </c>
+      <c r="R300">
+        <v>2.63</v>
+      </c>
+      <c r="S300">
+        <v>4.5</v>
+      </c>
+      <c r="T300">
+        <v>1.22</v>
+      </c>
+      <c r="U300">
+        <v>4</v>
+      </c>
+      <c r="V300">
+        <v>2</v>
+      </c>
+      <c r="W300">
+        <v>1.73</v>
+      </c>
+      <c r="X300">
+        <v>4.33</v>
+      </c>
+      <c r="Y300">
+        <v>1.2</v>
+      </c>
+      <c r="Z300">
+        <v>1.65</v>
+      </c>
+      <c r="AA300">
+        <v>4.5</v>
+      </c>
+      <c r="AB300">
+        <v>4.5</v>
+      </c>
+      <c r="AC300">
+        <v>1.01</v>
+      </c>
+      <c r="AD300">
+        <v>17</v>
+      </c>
+      <c r="AE300">
+        <v>1.12</v>
+      </c>
+      <c r="AF300">
+        <v>6</v>
+      </c>
+      <c r="AG300">
+        <v>1.36</v>
+      </c>
+      <c r="AH300">
+        <v>2.99</v>
+      </c>
+      <c r="AI300">
+        <v>1.44</v>
+      </c>
+      <c r="AJ300">
+        <v>2.63</v>
+      </c>
+      <c r="AK300">
+        <v>1.19</v>
+      </c>
+      <c r="AL300">
+        <v>1.2</v>
+      </c>
+      <c r="AM300">
+        <v>2.2</v>
+      </c>
+      <c r="AN300">
+        <v>2</v>
+      </c>
+      <c r="AO300">
+        <v>1.14</v>
+      </c>
+      <c r="AP300">
+        <v>2.07</v>
+      </c>
+      <c r="AQ300">
+        <v>1.07</v>
+      </c>
+      <c r="AR300">
+        <v>2</v>
+      </c>
+      <c r="AS300">
+        <v>1.58</v>
+      </c>
+      <c r="AT300">
+        <v>3.58</v>
+      </c>
+      <c r="AU300">
+        <v>6</v>
+      </c>
+      <c r="AV300">
+        <v>3</v>
+      </c>
+      <c r="AW300">
+        <v>6</v>
+      </c>
+      <c r="AX300">
+        <v>6</v>
+      </c>
+      <c r="AY300">
+        <v>14</v>
+      </c>
+      <c r="AZ300">
+        <v>11</v>
+      </c>
+      <c r="BA300">
+        <v>4</v>
+      </c>
+      <c r="BB300">
+        <v>6</v>
+      </c>
+      <c r="BC300">
+        <v>10</v>
+      </c>
+      <c r="BD300">
+        <v>1.49</v>
+      </c>
+      <c r="BE300">
+        <v>7.5</v>
+      </c>
+      <c r="BF300">
+        <v>2.8</v>
+      </c>
+      <c r="BG300">
+        <v>1.13</v>
+      </c>
+      <c r="BH300">
+        <v>4.9</v>
+      </c>
+      <c r="BI300">
+        <v>1.24</v>
+      </c>
+      <c r="BJ300">
+        <v>3.55</v>
+      </c>
+      <c r="BK300">
+        <v>1.41</v>
+      </c>
+      <c r="BL300">
+        <v>2.63</v>
+      </c>
+      <c r="BM300">
+        <v>1.66</v>
+      </c>
+      <c r="BN300">
+        <v>2.06</v>
+      </c>
+      <c r="BO300">
+        <v>2</v>
+      </c>
+      <c r="BP300">
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1862" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="440">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -871,6 +871,15 @@
     <t>['50']</t>
   </si>
   <si>
+    <t>['61', '68']</t>
+  </si>
+  <si>
+    <t>['3', '55']</t>
+  </si>
+  <si>
+    <t>['13', '15']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1317,6 +1326,15 @@
   <si>
     <t>['34', '60']</t>
   </si>
+  <si>
+    <t>['34']</t>
+  </si>
+  <si>
+    <t>['38', '79']</t>
+  </si>
+  <si>
+    <t>['72', '84']</t>
+  </si>
 </sst>
 </file>
 
@@ -1677,7 +1695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP300"/>
+  <dimension ref="A1:BP305"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2139,7 +2157,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2217,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AQ3">
         <v>2.33</v>
@@ -2426,7 +2444,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ4">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2551,7 +2569,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2629,10 +2647,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ5">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2963,7 +2981,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -3044,7 +3062,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ7">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3169,7 +3187,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3581,7 +3599,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -4483,7 +4501,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ14">
         <v>1.13</v>
@@ -4898,7 +4916,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ16">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5229,7 +5247,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5307,10 +5325,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ18">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5435,7 +5453,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -6134,7 +6152,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ22">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR22">
         <v>1.72</v>
@@ -6259,7 +6277,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6465,7 +6483,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6543,7 +6561,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AQ24">
         <v>1.47</v>
@@ -6752,7 +6770,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR25">
         <v>1.78</v>
@@ -7083,7 +7101,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7161,10 +7179,10 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ27">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR27">
         <v>0.83</v>
@@ -7289,7 +7307,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7495,7 +7513,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7907,7 +7925,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8113,7 +8131,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8525,7 +8543,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -8603,7 +8621,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ34">
         <v>0.53</v>
@@ -9018,7 +9036,7 @@
         <v>2.53</v>
       </c>
       <c r="AQ36">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR36">
         <v>1.93</v>
@@ -9349,7 +9367,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9427,7 +9445,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ38">
         <v>1</v>
@@ -9555,7 +9573,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9761,7 +9779,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9842,7 +9860,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ40">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR40">
         <v>1.93</v>
@@ -9967,7 +9985,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -10173,7 +10191,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10379,7 +10397,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10872,7 +10890,7 @@
         <v>2.53</v>
       </c>
       <c r="AQ45">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR45">
         <v>1.78</v>
@@ -11487,10 +11505,10 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR48">
         <v>1.44</v>
@@ -11693,7 +11711,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ49">
         <v>1.13</v>
@@ -11902,7 +11920,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ50">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR50">
         <v>1.67</v>
@@ -12027,7 +12045,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -12108,7 +12126,7 @@
         <v>2</v>
       </c>
       <c r="AQ51">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR51">
         <v>2.05</v>
@@ -12233,7 +12251,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12439,7 +12457,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12723,7 +12741,7 @@
         <v>0.5</v>
       </c>
       <c r="AP54">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ54">
         <v>1.64</v>
@@ -12851,7 +12869,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -13263,7 +13281,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13344,7 +13362,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ57">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR57">
         <v>1.39</v>
@@ -13469,7 +13487,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13675,7 +13693,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13753,7 +13771,7 @@
         <v>3</v>
       </c>
       <c r="AP59">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AQ59">
         <v>1.33</v>
@@ -13881,7 +13899,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -14087,7 +14105,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14293,7 +14311,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14371,7 +14389,7 @@
         <v>3</v>
       </c>
       <c r="AP62">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ62">
         <v>2.33</v>
@@ -14580,7 +14598,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ63">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR63">
         <v>1.12</v>
@@ -14705,7 +14723,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14911,7 +14929,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -15117,7 +15135,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -15198,7 +15216,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ66">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR66">
         <v>1.43</v>
@@ -15607,7 +15625,7 @@
         <v>1.33</v>
       </c>
       <c r="AP68">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ68">
         <v>1.6</v>
@@ -15816,7 +15834,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ69">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR69">
         <v>1.45</v>
@@ -16019,7 +16037,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ70">
         <v>1.13</v>
@@ -16147,7 +16165,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16559,7 +16577,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16765,7 +16783,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16971,7 +16989,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -17052,7 +17070,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ75">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR75">
         <v>0.91</v>
@@ -17177,7 +17195,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17383,7 +17401,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17461,7 +17479,7 @@
         <v>0.33</v>
       </c>
       <c r="AP77">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AQ77">
         <v>1</v>
@@ -17670,7 +17688,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ78">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR78">
         <v>1.65</v>
@@ -17795,7 +17813,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -18001,7 +18019,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18413,7 +18431,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18494,7 +18512,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ82">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR82">
         <v>1.04</v>
@@ -18825,7 +18843,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18906,7 +18924,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ84">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR84">
         <v>1.51</v>
@@ -19031,7 +19049,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -19109,10 +19127,10 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ85">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR85">
         <v>1.28</v>
@@ -19237,7 +19255,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19521,7 +19539,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ87">
         <v>1.47</v>
@@ -19649,7 +19667,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -19933,7 +19951,7 @@
         <v>1</v>
       </c>
       <c r="AP89">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ89">
         <v>1.07</v>
@@ -20061,7 +20079,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20267,7 +20285,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20554,7 +20572,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ92">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR92">
         <v>1.13</v>
@@ -21169,7 +21187,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AQ95">
         <v>0.53</v>
@@ -21378,7 +21396,7 @@
         <v>2.53</v>
       </c>
       <c r="AQ96">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR96">
         <v>1.78</v>
@@ -21709,7 +21727,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21915,7 +21933,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -22121,7 +22139,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22533,7 +22551,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22614,7 +22632,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ102">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR102">
         <v>1.76</v>
@@ -22739,7 +22757,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22817,7 +22835,7 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ103">
         <v>1.47</v>
@@ -23975,7 +23993,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -24181,7 +24199,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24468,7 +24486,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ111">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR111">
         <v>1.72</v>
@@ -24593,7 +24611,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24799,7 +24817,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -24880,7 +24898,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ113">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR113">
         <v>1.98</v>
@@ -25083,7 +25101,7 @@
         <v>0</v>
       </c>
       <c r="AP114">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ114">
         <v>1.13</v>
@@ -25292,7 +25310,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ115">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR115">
         <v>2.22</v>
@@ -25417,7 +25435,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25498,7 +25516,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ116">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR116">
         <v>1.57</v>
@@ -25623,7 +25641,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25701,7 +25719,7 @@
         <v>0.4</v>
       </c>
       <c r="AP117">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ117">
         <v>1.64</v>
@@ -25829,7 +25847,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -26035,7 +26053,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -26241,7 +26259,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26319,7 +26337,7 @@
         <v>1</v>
       </c>
       <c r="AP120">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AQ120">
         <v>1.13</v>
@@ -26447,7 +26465,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26653,7 +26671,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26859,7 +26877,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -26940,7 +26958,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ123">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR123">
         <v>1.13</v>
@@ -27477,7 +27495,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27555,7 +27573,7 @@
         <v>1.33</v>
       </c>
       <c r="AP126">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ126">
         <v>1.6</v>
@@ -27683,7 +27701,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -27764,7 +27782,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ127">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR127">
         <v>1.54</v>
@@ -28713,7 +28731,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28791,7 +28809,7 @@
         <v>0.5</v>
       </c>
       <c r="AP132">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AQ132">
         <v>1.64</v>
@@ -29125,7 +29143,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29331,7 +29349,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -29618,7 +29636,7 @@
         <v>2</v>
       </c>
       <c r="AQ136">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR136">
         <v>2.3</v>
@@ -29821,10 +29839,10 @@
         <v>0.83</v>
       </c>
       <c r="AP137">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ137">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR137">
         <v>1.42</v>
@@ -30027,7 +30045,7 @@
         <v>0.17</v>
       </c>
       <c r="AP138">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ138">
         <v>1.13</v>
@@ -30442,7 +30460,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ140">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR140">
         <v>1.88</v>
@@ -30773,7 +30791,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30851,7 +30869,7 @@
         <v>1.43</v>
       </c>
       <c r="AP142">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ142">
         <v>1.4</v>
@@ -30979,7 +30997,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -31263,7 +31281,7 @@
         <v>0.14</v>
       </c>
       <c r="AP144">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ144">
         <v>0.33</v>
@@ -31391,7 +31409,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31472,7 +31490,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ145">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR145">
         <v>1.4</v>
@@ -31597,7 +31615,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31678,7 +31696,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ146">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR146">
         <v>1.74</v>
@@ -31803,7 +31821,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31881,10 +31899,10 @@
         <v>1.14</v>
       </c>
       <c r="AP147">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AQ147">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR147">
         <v>1.16</v>
@@ -32009,7 +32027,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -32090,7 +32108,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ148">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR148">
         <v>1.08</v>
@@ -32215,7 +32233,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32502,7 +32520,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ150">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR150">
         <v>1.48</v>
@@ -32627,7 +32645,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -33245,7 +33263,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33451,7 +33469,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33657,7 +33675,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33863,7 +33881,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -34069,7 +34087,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34765,7 +34783,7 @@
         <v>1.38</v>
       </c>
       <c r="AP161">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ161">
         <v>1.4</v>
@@ -34893,7 +34911,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -34974,7 +34992,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ162">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR162">
         <v>1.71</v>
@@ -35099,7 +35117,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35180,7 +35198,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ163">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR163">
         <v>1.48</v>
@@ -35305,7 +35323,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35383,7 +35401,7 @@
         <v>1.13</v>
       </c>
       <c r="AP164">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AQ164">
         <v>1.6</v>
@@ -35511,7 +35529,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35589,10 +35607,10 @@
         <v>1.5</v>
       </c>
       <c r="AP165">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ165">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR165">
         <v>1.31</v>
@@ -35923,7 +35941,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36004,7 +36022,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ167">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR167">
         <v>1.06</v>
@@ -36129,7 +36147,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36210,7 +36228,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ168">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR168">
         <v>1.46</v>
@@ -36413,7 +36431,7 @@
         <v>2.38</v>
       </c>
       <c r="AP169">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ169">
         <v>1.4</v>
@@ -36541,7 +36559,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36953,7 +36971,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37571,7 +37589,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -38189,7 +38207,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38807,7 +38825,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -39013,7 +39031,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39094,7 +39112,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ182">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR182">
         <v>1.74</v>
@@ -39297,7 +39315,7 @@
         <v>0.22</v>
       </c>
       <c r="AP183">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ183">
         <v>0.33</v>
@@ -39425,7 +39443,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39506,7 +39524,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ184">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR184">
         <v>1.59</v>
@@ -39631,7 +39649,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39709,10 +39727,10 @@
         <v>1.89</v>
       </c>
       <c r="AP185">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ185">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR185">
         <v>1.32</v>
@@ -39837,7 +39855,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -40121,7 +40139,7 @@
         <v>2.22</v>
       </c>
       <c r="AP187">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AQ187">
         <v>1.4</v>
@@ -40249,7 +40267,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40327,10 +40345,10 @@
         <v>1.33</v>
       </c>
       <c r="AP188">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ188">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR188">
         <v>1.51</v>
@@ -40455,7 +40473,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40661,7 +40679,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40742,7 +40760,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ190">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR190">
         <v>1.66</v>
@@ -40867,7 +40885,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -41279,7 +41297,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41357,7 +41375,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP193">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ193">
         <v>0.53</v>
@@ -41563,7 +41581,7 @@
         <v>2</v>
       </c>
       <c r="AP194">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ194">
         <v>1.4</v>
@@ -41691,7 +41709,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41897,7 +41915,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -42184,7 +42202,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ197">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR197">
         <v>1.62</v>
@@ -42309,7 +42327,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42515,7 +42533,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42721,7 +42739,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42802,7 +42820,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ200">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR200">
         <v>1.18</v>
@@ -42927,7 +42945,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -43008,7 +43026,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ201">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR201">
         <v>1.75</v>
@@ -43133,7 +43151,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43339,7 +43357,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43545,7 +43563,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43751,7 +43769,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -44038,7 +44056,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ206">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR206">
         <v>1.56</v>
@@ -44163,7 +44181,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44241,7 +44259,7 @@
         <v>1.11</v>
       </c>
       <c r="AP207">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ207">
         <v>1.33</v>
@@ -44575,7 +44593,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44653,10 +44671,10 @@
         <v>1.3</v>
       </c>
       <c r="AP209">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AQ209">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR209">
         <v>1.16</v>
@@ -44987,7 +45005,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45068,7 +45086,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ211">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR211">
         <v>1.61</v>
@@ -45193,7 +45211,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45399,7 +45417,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45605,7 +45623,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45811,7 +45829,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -46017,7 +46035,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -46098,7 +46116,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ216">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR216">
         <v>1.58</v>
@@ -46223,7 +46241,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46429,7 +46447,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46507,7 +46525,7 @@
         <v>1</v>
       </c>
       <c r="AP218">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ218">
         <v>1.07</v>
@@ -46635,7 +46653,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46713,7 +46731,7 @@
         <v>1.36</v>
       </c>
       <c r="AP219">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AQ219">
         <v>1.4</v>
@@ -46841,7 +46859,7 @@
         <v>240</v>
       </c>
       <c r="P220" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q220">
         <v>1.73</v>
@@ -46922,7 +46940,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ220">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR220">
         <v>1.85</v>
@@ -47128,7 +47146,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ221">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR221">
         <v>1.77</v>
@@ -47253,7 +47271,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -47665,7 +47683,7 @@
         <v>107</v>
       </c>
       <c r="P224" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="Q224">
         <v>6</v>
@@ -47871,7 +47889,7 @@
         <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q225">
         <v>6.5</v>
@@ -47952,7 +47970,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ225">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR225">
         <v>1.21</v>
@@ -48077,7 +48095,7 @@
         <v>243</v>
       </c>
       <c r="P226" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="Q226">
         <v>2.38</v>
@@ -48283,7 +48301,7 @@
         <v>155</v>
       </c>
       <c r="P227" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48361,7 +48379,7 @@
         <v>0.5</v>
       </c>
       <c r="AP227">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ227">
         <v>1.13</v>
@@ -48489,7 +48507,7 @@
         <v>244</v>
       </c>
       <c r="P228" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="Q228">
         <v>1.91</v>
@@ -48773,7 +48791,7 @@
         <v>1.2</v>
       </c>
       <c r="AP229">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ229">
         <v>1.13</v>
@@ -48901,7 +48919,7 @@
         <v>91</v>
       </c>
       <c r="P230" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="Q230">
         <v>2.88</v>
@@ -49188,7 +49206,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ231">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR231">
         <v>1.47</v>
@@ -49313,7 +49331,7 @@
         <v>95</v>
       </c>
       <c r="P232" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="Q232">
         <v>2.2</v>
@@ -49597,7 +49615,7 @@
         <v>0.73</v>
       </c>
       <c r="AP233">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ233">
         <v>0.53</v>
@@ -49725,7 +49743,7 @@
         <v>151</v>
       </c>
       <c r="P234" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="Q234">
         <v>2.6</v>
@@ -49803,7 +49821,7 @@
         <v>0.17</v>
       </c>
       <c r="AP234">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AQ234">
         <v>0.33</v>
@@ -49931,7 +49949,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="Q235">
         <v>4.5</v>
@@ -50343,7 +50361,7 @@
         <v>91</v>
       </c>
       <c r="P237" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50549,7 +50567,7 @@
         <v>91</v>
       </c>
       <c r="P238" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="Q238">
         <v>2.75</v>
@@ -50961,7 +50979,7 @@
         <v>249</v>
       </c>
       <c r="P240" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="Q240">
         <v>1.8</v>
@@ -51167,7 +51185,7 @@
         <v>250</v>
       </c>
       <c r="P241" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="Q241">
         <v>6</v>
@@ -51245,7 +51263,7 @@
         <v>2.5</v>
       </c>
       <c r="AP241">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ241">
         <v>2.33</v>
@@ -51579,7 +51597,7 @@
         <v>91</v>
       </c>
       <c r="P243" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="Q243">
         <v>9</v>
@@ -51660,7 +51678,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ243">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR243">
         <v>1.2</v>
@@ -51785,7 +51803,7 @@
         <v>203</v>
       </c>
       <c r="P244" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="Q244">
         <v>5</v>
@@ -51866,7 +51884,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ244">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR244">
         <v>1.15</v>
@@ -52484,7 +52502,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ247">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR247">
         <v>1.54</v>
@@ -52687,7 +52705,7 @@
         <v>0.82</v>
       </c>
       <c r="AP248">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ248">
         <v>0.87</v>
@@ -52815,7 +52833,7 @@
         <v>254</v>
       </c>
       <c r="P249" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="Q249">
         <v>2.63</v>
@@ -52893,7 +52911,7 @@
         <v>0.91</v>
       </c>
       <c r="AP249">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ249">
         <v>1</v>
@@ -53102,7 +53120,7 @@
         <v>2.53</v>
       </c>
       <c r="AQ250">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR250">
         <v>1.85</v>
@@ -53433,7 +53451,7 @@
         <v>256</v>
       </c>
       <c r="P252" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="Q252">
         <v>4</v>
@@ -53511,7 +53529,7 @@
         <v>2.38</v>
       </c>
       <c r="AP252">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ252">
         <v>2.33</v>
@@ -53639,7 +53657,7 @@
         <v>91</v>
       </c>
       <c r="P253" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="Q253">
         <v>3.6</v>
@@ -53845,7 +53863,7 @@
         <v>257</v>
       </c>
       <c r="P254" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="Q254">
         <v>3.25</v>
@@ -53923,7 +53941,7 @@
         <v>1.08</v>
       </c>
       <c r="AP254">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ254">
         <v>1.13</v>
@@ -54051,7 +54069,7 @@
         <v>91</v>
       </c>
       <c r="P255" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="Q255">
         <v>5</v>
@@ -54132,7 +54150,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ255">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR255">
         <v>1.18</v>
@@ -54257,7 +54275,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="Q256">
         <v>3.75</v>
@@ -54335,7 +54353,7 @@
         <v>1.08</v>
       </c>
       <c r="AP256">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AQ256">
         <v>1.07</v>
@@ -54463,7 +54481,7 @@
         <v>91</v>
       </c>
       <c r="P257" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="Q257">
         <v>1.73</v>
@@ -54750,7 +54768,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ258">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR258">
         <v>1.79</v>
@@ -54875,7 +54893,7 @@
         <v>91</v>
       </c>
       <c r="P259" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="Q259">
         <v>2.75</v>
@@ -55081,7 +55099,7 @@
         <v>258</v>
       </c>
       <c r="P260" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q260">
         <v>3.1</v>
@@ -55159,7 +55177,7 @@
         <v>1.62</v>
       </c>
       <c r="AP260">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ260">
         <v>1.4</v>
@@ -55287,7 +55305,7 @@
         <v>259</v>
       </c>
       <c r="P261" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="Q261">
         <v>2.38</v>
@@ -55368,7 +55386,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ261">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR261">
         <v>1.6</v>
@@ -55493,7 +55511,7 @@
         <v>91</v>
       </c>
       <c r="P262" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="Q262">
         <v>3.1</v>
@@ -55699,7 +55717,7 @@
         <v>260</v>
       </c>
       <c r="P263" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q263">
         <v>3.2</v>
@@ -55777,7 +55795,7 @@
         <v>1.17</v>
       </c>
       <c r="AP263">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ263">
         <v>1.33</v>
@@ -55905,7 +55923,7 @@
         <v>261</v>
       </c>
       <c r="P264" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="Q264">
         <v>3.5</v>
@@ -56192,7 +56210,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ265">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR265">
         <v>1.6</v>
@@ -56729,7 +56747,7 @@
         <v>264</v>
       </c>
       <c r="P268" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="Q268">
         <v>2.05</v>
@@ -57222,7 +57240,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ270">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR270">
         <v>1.5</v>
@@ -57965,7 +57983,7 @@
         <v>269</v>
       </c>
       <c r="P274" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="Q274">
         <v>1.4</v>
@@ -58171,7 +58189,7 @@
         <v>270</v>
       </c>
       <c r="P275" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q275">
         <v>2.5</v>
@@ -58455,7 +58473,7 @@
         <v>0.77</v>
       </c>
       <c r="AP276">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ276">
         <v>0.87</v>
@@ -59201,7 +59219,7 @@
         <v>273</v>
       </c>
       <c r="P280" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="Q280">
         <v>2.88</v>
@@ -59282,7 +59300,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ280">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR280">
         <v>1.76</v>
@@ -59407,7 +59425,7 @@
         <v>274</v>
       </c>
       <c r="P281" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q281">
         <v>5.5</v>
@@ -59488,7 +59506,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ281">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR281">
         <v>1.53</v>
@@ -59613,7 +59631,7 @@
         <v>91</v>
       </c>
       <c r="P282" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q282">
         <v>3.5</v>
@@ -59819,7 +59837,7 @@
         <v>275</v>
       </c>
       <c r="P283" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="Q283">
         <v>4</v>
@@ -59900,7 +59918,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ283">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR283">
         <v>1.16</v>
@@ -60103,7 +60121,7 @@
         <v>1.23</v>
       </c>
       <c r="AP284">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ284">
         <v>1.13</v>
@@ -60231,7 +60249,7 @@
         <v>277</v>
       </c>
       <c r="P285" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="Q285">
         <v>4</v>
@@ -60309,10 +60327,10 @@
         <v>1.64</v>
       </c>
       <c r="AP285">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AQ285">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AR285">
         <v>1.24</v>
@@ -60437,7 +60455,7 @@
         <v>278</v>
       </c>
       <c r="P286" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="Q286">
         <v>2.2</v>
@@ -60518,7 +60536,7 @@
         <v>2</v>
       </c>
       <c r="AQ286">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR286">
         <v>1.99</v>
@@ -60643,7 +60661,7 @@
         <v>195</v>
       </c>
       <c r="P287" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="Q287">
         <v>2.25</v>
@@ -61261,7 +61279,7 @@
         <v>91</v>
       </c>
       <c r="P290" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="Q290">
         <v>4.33</v>
@@ -62085,7 +62103,7 @@
         <v>172</v>
       </c>
       <c r="P294" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="Q294">
         <v>5.5</v>
@@ -62497,7 +62515,7 @@
         <v>282</v>
       </c>
       <c r="P296" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Q296">
         <v>2.2</v>
@@ -62703,7 +62721,7 @@
         <v>91</v>
       </c>
       <c r="P297" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="Q297">
         <v>2.6</v>
@@ -62909,7 +62927,7 @@
         <v>283</v>
       </c>
       <c r="P298" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="Q298">
         <v>1.83</v>
@@ -63478,6 +63496,1036 @@
       </c>
       <c r="BP300">
         <v>1.7</v>
+      </c>
+    </row>
+    <row r="301" spans="1:68">
+      <c r="A301" s="1">
+        <v>300</v>
+      </c>
+      <c r="B301">
+        <v>7466982</v>
+      </c>
+      <c r="C301" t="s">
+        <v>68</v>
+      </c>
+      <c r="D301" t="s">
+        <v>69</v>
+      </c>
+      <c r="E301" s="2">
+        <v>45752.35416666666</v>
+      </c>
+      <c r="F301">
+        <v>31</v>
+      </c>
+      <c r="G301" t="s">
+        <v>73</v>
+      </c>
+      <c r="H301" t="s">
+        <v>72</v>
+      </c>
+      <c r="I301">
+        <v>0</v>
+      </c>
+      <c r="J301">
+        <v>1</v>
+      </c>
+      <c r="K301">
+        <v>1</v>
+      </c>
+      <c r="L301">
+        <v>1</v>
+      </c>
+      <c r="M301">
+        <v>1</v>
+      </c>
+      <c r="N301">
+        <v>2</v>
+      </c>
+      <c r="O301" t="s">
+        <v>180</v>
+      </c>
+      <c r="P301" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q301">
+        <v>6</v>
+      </c>
+      <c r="R301">
+        <v>2.05</v>
+      </c>
+      <c r="S301">
+        <v>2.38</v>
+      </c>
+      <c r="T301">
+        <v>1.5</v>
+      </c>
+      <c r="U301">
+        <v>2.5</v>
+      </c>
+      <c r="V301">
+        <v>3.5</v>
+      </c>
+      <c r="W301">
+        <v>1.29</v>
+      </c>
+      <c r="X301">
+        <v>10</v>
+      </c>
+      <c r="Y301">
+        <v>1.06</v>
+      </c>
+      <c r="Z301">
+        <v>5.8</v>
+      </c>
+      <c r="AA301">
+        <v>3.5</v>
+      </c>
+      <c r="AB301">
+        <v>1.69</v>
+      </c>
+      <c r="AC301">
+        <v>1.09</v>
+      </c>
+      <c r="AD301">
+        <v>7</v>
+      </c>
+      <c r="AE301">
+        <v>1.44</v>
+      </c>
+      <c r="AF301">
+        <v>2.75</v>
+      </c>
+      <c r="AG301">
+        <v>2.2</v>
+      </c>
+      <c r="AH301">
+        <v>1.6</v>
+      </c>
+      <c r="AI301">
+        <v>2.1</v>
+      </c>
+      <c r="AJ301">
+        <v>1.67</v>
+      </c>
+      <c r="AK301">
+        <v>2.05</v>
+      </c>
+      <c r="AL301">
+        <v>1.3</v>
+      </c>
+      <c r="AM301">
+        <v>1.16</v>
+      </c>
+      <c r="AN301">
+        <v>1.27</v>
+      </c>
+      <c r="AO301">
+        <v>1.8</v>
+      </c>
+      <c r="AP301">
+        <v>1.25</v>
+      </c>
+      <c r="AQ301">
+        <v>1.75</v>
+      </c>
+      <c r="AR301">
+        <v>1.43</v>
+      </c>
+      <c r="AS301">
+        <v>1.39</v>
+      </c>
+      <c r="AT301">
+        <v>2.82</v>
+      </c>
+      <c r="AU301">
+        <v>3</v>
+      </c>
+      <c r="AV301">
+        <v>6</v>
+      </c>
+      <c r="AW301">
+        <v>3</v>
+      </c>
+      <c r="AX301">
+        <v>9</v>
+      </c>
+      <c r="AY301">
+        <v>7</v>
+      </c>
+      <c r="AZ301">
+        <v>20</v>
+      </c>
+      <c r="BA301">
+        <v>3</v>
+      </c>
+      <c r="BB301">
+        <v>8</v>
+      </c>
+      <c r="BC301">
+        <v>11</v>
+      </c>
+      <c r="BD301">
+        <v>4.75</v>
+      </c>
+      <c r="BE301">
+        <v>8.5</v>
+      </c>
+      <c r="BF301">
+        <v>1.29</v>
+      </c>
+      <c r="BG301">
+        <v>1.22</v>
+      </c>
+      <c r="BH301">
+        <v>3.9</v>
+      </c>
+      <c r="BI301">
+        <v>1.41</v>
+      </c>
+      <c r="BJ301">
+        <v>2.7</v>
+      </c>
+      <c r="BK301">
+        <v>1.72</v>
+      </c>
+      <c r="BL301">
+        <v>1.98</v>
+      </c>
+      <c r="BM301">
+        <v>2.2</v>
+      </c>
+      <c r="BN301">
+        <v>1.58</v>
+      </c>
+      <c r="BO301">
+        <v>3</v>
+      </c>
+      <c r="BP301">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="302" spans="1:68">
+      <c r="A302" s="1">
+        <v>301</v>
+      </c>
+      <c r="B302">
+        <v>7466988</v>
+      </c>
+      <c r="C302" t="s">
+        <v>68</v>
+      </c>
+      <c r="D302" t="s">
+        <v>69</v>
+      </c>
+      <c r="E302" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F302">
+        <v>31</v>
+      </c>
+      <c r="G302" t="s">
+        <v>76</v>
+      </c>
+      <c r="H302" t="s">
+        <v>88</v>
+      </c>
+      <c r="I302">
+        <v>0</v>
+      </c>
+      <c r="J302">
+        <v>1</v>
+      </c>
+      <c r="K302">
+        <v>1</v>
+      </c>
+      <c r="L302">
+        <v>2</v>
+      </c>
+      <c r="M302">
+        <v>2</v>
+      </c>
+      <c r="N302">
+        <v>4</v>
+      </c>
+      <c r="O302" t="s">
+        <v>285</v>
+      </c>
+      <c r="P302" t="s">
+        <v>438</v>
+      </c>
+      <c r="Q302">
+        <v>3.6</v>
+      </c>
+      <c r="R302">
+        <v>2.25</v>
+      </c>
+      <c r="S302">
+        <v>2.75</v>
+      </c>
+      <c r="T302">
+        <v>1.33</v>
+      </c>
+      <c r="U302">
+        <v>3.25</v>
+      </c>
+      <c r="V302">
+        <v>2.63</v>
+      </c>
+      <c r="W302">
+        <v>1.44</v>
+      </c>
+      <c r="X302">
+        <v>6.5</v>
+      </c>
+      <c r="Y302">
+        <v>1.11</v>
+      </c>
+      <c r="Z302">
+        <v>3.2</v>
+      </c>
+      <c r="AA302">
+        <v>3.5</v>
+      </c>
+      <c r="AB302">
+        <v>2.2</v>
+      </c>
+      <c r="AC302">
+        <v>1.05</v>
+      </c>
+      <c r="AD302">
+        <v>9.5</v>
+      </c>
+      <c r="AE302">
+        <v>1.25</v>
+      </c>
+      <c r="AF302">
+        <v>3.8</v>
+      </c>
+      <c r="AG302">
+        <v>1.7</v>
+      </c>
+      <c r="AH302">
+        <v>2.05</v>
+      </c>
+      <c r="AI302">
+        <v>1.62</v>
+      </c>
+      <c r="AJ302">
+        <v>2.2</v>
+      </c>
+      <c r="AK302">
+        <v>1.6</v>
+      </c>
+      <c r="AL302">
+        <v>1.3</v>
+      </c>
+      <c r="AM302">
+        <v>1.37</v>
+      </c>
+      <c r="AN302">
+        <v>1.13</v>
+      </c>
+      <c r="AO302">
+        <v>1.53</v>
+      </c>
+      <c r="AP302">
+        <v>1.13</v>
+      </c>
+      <c r="AQ302">
+        <v>1.5</v>
+      </c>
+      <c r="AR302">
+        <v>1.26</v>
+      </c>
+      <c r="AS302">
+        <v>1.71</v>
+      </c>
+      <c r="AT302">
+        <v>2.97</v>
+      </c>
+      <c r="AU302">
+        <v>4</v>
+      </c>
+      <c r="AV302">
+        <v>5</v>
+      </c>
+      <c r="AW302">
+        <v>6</v>
+      </c>
+      <c r="AX302">
+        <v>7</v>
+      </c>
+      <c r="AY302">
+        <v>12</v>
+      </c>
+      <c r="AZ302">
+        <v>12</v>
+      </c>
+      <c r="BA302">
+        <v>4</v>
+      </c>
+      <c r="BB302">
+        <v>7</v>
+      </c>
+      <c r="BC302">
+        <v>11</v>
+      </c>
+      <c r="BD302">
+        <v>2.55</v>
+      </c>
+      <c r="BE302">
+        <v>7</v>
+      </c>
+      <c r="BF302">
+        <v>1.71</v>
+      </c>
+      <c r="BG302">
+        <v>1.14</v>
+      </c>
+      <c r="BH302">
+        <v>5</v>
+      </c>
+      <c r="BI302">
+        <v>1.29</v>
+      </c>
+      <c r="BJ302">
+        <v>3.3</v>
+      </c>
+      <c r="BK302">
+        <v>1.52</v>
+      </c>
+      <c r="BL302">
+        <v>2.35</v>
+      </c>
+      <c r="BM302">
+        <v>1.9</v>
+      </c>
+      <c r="BN302">
+        <v>1.78</v>
+      </c>
+      <c r="BO302">
+        <v>2.5</v>
+      </c>
+      <c r="BP302">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="303" spans="1:68">
+      <c r="A303" s="1">
+        <v>302</v>
+      </c>
+      <c r="B303">
+        <v>7466981</v>
+      </c>
+      <c r="C303" t="s">
+        <v>68</v>
+      </c>
+      <c r="D303" t="s">
+        <v>69</v>
+      </c>
+      <c r="E303" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F303">
+        <v>31</v>
+      </c>
+      <c r="G303" t="s">
+        <v>82</v>
+      </c>
+      <c r="H303" t="s">
+        <v>80</v>
+      </c>
+      <c r="I303">
+        <v>1</v>
+      </c>
+      <c r="J303">
+        <v>1</v>
+      </c>
+      <c r="K303">
+        <v>2</v>
+      </c>
+      <c r="L303">
+        <v>2</v>
+      </c>
+      <c r="M303">
+        <v>1</v>
+      </c>
+      <c r="N303">
+        <v>3</v>
+      </c>
+      <c r="O303" t="s">
+        <v>286</v>
+      </c>
+      <c r="P303" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q303">
+        <v>3.1</v>
+      </c>
+      <c r="R303">
+        <v>2.25</v>
+      </c>
+      <c r="S303">
+        <v>3.25</v>
+      </c>
+      <c r="T303">
+        <v>1.33</v>
+      </c>
+      <c r="U303">
+        <v>3.25</v>
+      </c>
+      <c r="V303">
+        <v>2.63</v>
+      </c>
+      <c r="W303">
+        <v>1.44</v>
+      </c>
+      <c r="X303">
+        <v>6.5</v>
+      </c>
+      <c r="Y303">
+        <v>1.11</v>
+      </c>
+      <c r="Z303">
+        <v>2.5</v>
+      </c>
+      <c r="AA303">
+        <v>3.5</v>
+      </c>
+      <c r="AB303">
+        <v>2.7</v>
+      </c>
+      <c r="AC303">
+        <v>1.05</v>
+      </c>
+      <c r="AD303">
+        <v>9.5</v>
+      </c>
+      <c r="AE303">
+        <v>1.25</v>
+      </c>
+      <c r="AF303">
+        <v>3.85</v>
+      </c>
+      <c r="AG303">
+        <v>1.7</v>
+      </c>
+      <c r="AH303">
+        <v>2.05</v>
+      </c>
+      <c r="AI303">
+        <v>1.62</v>
+      </c>
+      <c r="AJ303">
+        <v>2.2</v>
+      </c>
+      <c r="AK303">
+        <v>1.42</v>
+      </c>
+      <c r="AL303">
+        <v>1.3</v>
+      </c>
+      <c r="AM303">
+        <v>1.53</v>
+      </c>
+      <c r="AN303">
+        <v>1.13</v>
+      </c>
+      <c r="AO303">
+        <v>1.53</v>
+      </c>
+      <c r="AP303">
+        <v>1.25</v>
+      </c>
+      <c r="AQ303">
+        <v>1.44</v>
+      </c>
+      <c r="AR303">
+        <v>1.54</v>
+      </c>
+      <c r="AS303">
+        <v>1.47</v>
+      </c>
+      <c r="AT303">
+        <v>3.01</v>
+      </c>
+      <c r="AU303">
+        <v>4</v>
+      </c>
+      <c r="AV303">
+        <v>6</v>
+      </c>
+      <c r="AW303">
+        <v>5</v>
+      </c>
+      <c r="AX303">
+        <v>6</v>
+      </c>
+      <c r="AY303">
+        <v>11</v>
+      </c>
+      <c r="AZ303">
+        <v>14</v>
+      </c>
+      <c r="BA303">
+        <v>2</v>
+      </c>
+      <c r="BB303">
+        <v>4</v>
+      </c>
+      <c r="BC303">
+        <v>6</v>
+      </c>
+      <c r="BD303">
+        <v>2.05</v>
+      </c>
+      <c r="BE303">
+        <v>6.75</v>
+      </c>
+      <c r="BF303">
+        <v>2.05</v>
+      </c>
+      <c r="BG303">
+        <v>1.17</v>
+      </c>
+      <c r="BH303">
+        <v>4.5</v>
+      </c>
+      <c r="BI303">
+        <v>1.34</v>
+      </c>
+      <c r="BJ303">
+        <v>2.95</v>
+      </c>
+      <c r="BK303">
+        <v>1.61</v>
+      </c>
+      <c r="BL303">
+        <v>2.15</v>
+      </c>
+      <c r="BM303">
+        <v>2.05</v>
+      </c>
+      <c r="BN303">
+        <v>1.68</v>
+      </c>
+      <c r="BO303">
+        <v>2.75</v>
+      </c>
+      <c r="BP303">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="304" spans="1:68">
+      <c r="A304" s="1">
+        <v>303</v>
+      </c>
+      <c r="B304">
+        <v>7466984</v>
+      </c>
+      <c r="C304" t="s">
+        <v>68</v>
+      </c>
+      <c r="D304" t="s">
+        <v>69</v>
+      </c>
+      <c r="E304" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F304">
+        <v>31</v>
+      </c>
+      <c r="G304" t="s">
+        <v>71</v>
+      </c>
+      <c r="H304" t="s">
+        <v>87</v>
+      </c>
+      <c r="I304">
+        <v>1</v>
+      </c>
+      <c r="J304">
+        <v>0</v>
+      </c>
+      <c r="K304">
+        <v>1</v>
+      </c>
+      <c r="L304">
+        <v>1</v>
+      </c>
+      <c r="M304">
+        <v>2</v>
+      </c>
+      <c r="N304">
+        <v>3</v>
+      </c>
+      <c r="O304" t="s">
+        <v>133</v>
+      </c>
+      <c r="P304" t="s">
+        <v>439</v>
+      </c>
+      <c r="Q304">
+        <v>3.5</v>
+      </c>
+      <c r="R304">
+        <v>2.1</v>
+      </c>
+      <c r="S304">
+        <v>3.1</v>
+      </c>
+      <c r="T304">
+        <v>1.4</v>
+      </c>
+      <c r="U304">
+        <v>2.75</v>
+      </c>
+      <c r="V304">
+        <v>3</v>
+      </c>
+      <c r="W304">
+        <v>1.36</v>
+      </c>
+      <c r="X304">
+        <v>8</v>
+      </c>
+      <c r="Y304">
+        <v>1.08</v>
+      </c>
+      <c r="Z304">
+        <v>3</v>
+      </c>
+      <c r="AA304">
+        <v>3.4</v>
+      </c>
+      <c r="AB304">
+        <v>2.35</v>
+      </c>
+      <c r="AC304">
+        <v>1.07</v>
+      </c>
+      <c r="AD304">
+        <v>8</v>
+      </c>
+      <c r="AE304">
+        <v>1.35</v>
+      </c>
+      <c r="AF304">
+        <v>3.1</v>
+      </c>
+      <c r="AG304">
+        <v>2</v>
+      </c>
+      <c r="AH304">
+        <v>1.8</v>
+      </c>
+      <c r="AI304">
+        <v>1.8</v>
+      </c>
+      <c r="AJ304">
+        <v>1.95</v>
+      </c>
+      <c r="AK304">
+        <v>1.5</v>
+      </c>
+      <c r="AL304">
+        <v>1.33</v>
+      </c>
+      <c r="AM304">
+        <v>1.42</v>
+      </c>
+      <c r="AN304">
+        <v>0.47</v>
+      </c>
+      <c r="AO304">
+        <v>1</v>
+      </c>
+      <c r="AP304">
+        <v>0.44</v>
+      </c>
+      <c r="AQ304">
+        <v>1.13</v>
+      </c>
+      <c r="AR304">
+        <v>1.26</v>
+      </c>
+      <c r="AS304">
+        <v>1.3</v>
+      </c>
+      <c r="AT304">
+        <v>2.56</v>
+      </c>
+      <c r="AU304">
+        <v>3</v>
+      </c>
+      <c r="AV304">
+        <v>8</v>
+      </c>
+      <c r="AW304">
+        <v>4</v>
+      </c>
+      <c r="AX304">
+        <v>15</v>
+      </c>
+      <c r="AY304">
+        <v>8</v>
+      </c>
+      <c r="AZ304">
+        <v>28</v>
+      </c>
+      <c r="BA304">
+        <v>4</v>
+      </c>
+      <c r="BB304">
+        <v>8</v>
+      </c>
+      <c r="BC304">
+        <v>12</v>
+      </c>
+      <c r="BD304">
+        <v>1.85</v>
+      </c>
+      <c r="BE304">
+        <v>6.75</v>
+      </c>
+      <c r="BF304">
+        <v>2.3</v>
+      </c>
+      <c r="BG304">
+        <v>1.2</v>
+      </c>
+      <c r="BH304">
+        <v>4.1</v>
+      </c>
+      <c r="BI304">
+        <v>1.38</v>
+      </c>
+      <c r="BJ304">
+        <v>2.75</v>
+      </c>
+      <c r="BK304">
+        <v>1.68</v>
+      </c>
+      <c r="BL304">
+        <v>2.05</v>
+      </c>
+      <c r="BM304">
+        <v>2.15</v>
+      </c>
+      <c r="BN304">
+        <v>1.6</v>
+      </c>
+      <c r="BO304">
+        <v>2.95</v>
+      </c>
+      <c r="BP304">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="305" spans="1:68">
+      <c r="A305" s="1">
+        <v>304</v>
+      </c>
+      <c r="B305">
+        <v>7466979</v>
+      </c>
+      <c r="C305" t="s">
+        <v>68</v>
+      </c>
+      <c r="D305" t="s">
+        <v>69</v>
+      </c>
+      <c r="E305" s="2">
+        <v>45752.5625</v>
+      </c>
+      <c r="F305">
+        <v>31</v>
+      </c>
+      <c r="G305" t="s">
+        <v>86</v>
+      </c>
+      <c r="H305" t="s">
+        <v>75</v>
+      </c>
+      <c r="I305">
+        <v>2</v>
+      </c>
+      <c r="J305">
+        <v>0</v>
+      </c>
+      <c r="K305">
+        <v>2</v>
+      </c>
+      <c r="L305">
+        <v>2</v>
+      </c>
+      <c r="M305">
+        <v>1</v>
+      </c>
+      <c r="N305">
+        <v>3</v>
+      </c>
+      <c r="O305" t="s">
+        <v>287</v>
+      </c>
+      <c r="P305" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q305">
+        <v>2.63</v>
+      </c>
+      <c r="R305">
+        <v>2.3</v>
+      </c>
+      <c r="S305">
+        <v>3.75</v>
+      </c>
+      <c r="T305">
+        <v>1.33</v>
+      </c>
+      <c r="U305">
+        <v>3.25</v>
+      </c>
+      <c r="V305">
+        <v>2.63</v>
+      </c>
+      <c r="W305">
+        <v>1.44</v>
+      </c>
+      <c r="X305">
+        <v>6.5</v>
+      </c>
+      <c r="Y305">
+        <v>1.11</v>
+      </c>
+      <c r="Z305">
+        <v>1.95</v>
+      </c>
+      <c r="AA305">
+        <v>3.7</v>
+      </c>
+      <c r="AB305">
+        <v>3.7</v>
+      </c>
+      <c r="AC305">
+        <v>1.05</v>
+      </c>
+      <c r="AD305">
+        <v>9.5</v>
+      </c>
+      <c r="AE305">
+        <v>1.25</v>
+      </c>
+      <c r="AF305">
+        <v>3.9</v>
+      </c>
+      <c r="AG305">
+        <v>1.73</v>
+      </c>
+      <c r="AH305">
+        <v>2</v>
+      </c>
+      <c r="AI305">
+        <v>1.62</v>
+      </c>
+      <c r="AJ305">
+        <v>2.2</v>
+      </c>
+      <c r="AK305">
+        <v>1.28</v>
+      </c>
+      <c r="AL305">
+        <v>1.28</v>
+      </c>
+      <c r="AM305">
+        <v>1.78</v>
+      </c>
+      <c r="AN305">
+        <v>1.87</v>
+      </c>
+      <c r="AO305">
+        <v>1.73</v>
+      </c>
+      <c r="AP305">
+        <v>1.94</v>
+      </c>
+      <c r="AQ305">
+        <v>1.63</v>
+      </c>
+      <c r="AR305">
+        <v>1.6</v>
+      </c>
+      <c r="AS305">
+        <v>1.38</v>
+      </c>
+      <c r="AT305">
+        <v>2.98</v>
+      </c>
+      <c r="AU305">
+        <v>9</v>
+      </c>
+      <c r="AV305">
+        <v>4</v>
+      </c>
+      <c r="AW305">
+        <v>9</v>
+      </c>
+      <c r="AX305">
+        <v>16</v>
+      </c>
+      <c r="AY305">
+        <v>20</v>
+      </c>
+      <c r="AZ305">
+        <v>21</v>
+      </c>
+      <c r="BA305">
+        <v>4</v>
+      </c>
+      <c r="BB305">
+        <v>4</v>
+      </c>
+      <c r="BC305">
+        <v>8</v>
+      </c>
+      <c r="BD305">
+        <v>1.3</v>
+      </c>
+      <c r="BE305">
+        <v>8.25</v>
+      </c>
+      <c r="BF305">
+        <v>4.6</v>
+      </c>
+      <c r="BG305">
+        <v>1.13</v>
+      </c>
+      <c r="BH305">
+        <v>5.25</v>
+      </c>
+      <c r="BI305">
+        <v>1.27</v>
+      </c>
+      <c r="BJ305">
+        <v>3.4</v>
+      </c>
+      <c r="BK305">
+        <v>1.5</v>
+      </c>
+      <c r="BL305">
+        <v>2.4</v>
+      </c>
+      <c r="BM305">
+        <v>1.83</v>
+      </c>
+      <c r="BN305">
+        <v>1.85</v>
+      </c>
+      <c r="BO305">
+        <v>2.37</v>
+      </c>
+      <c r="BP305">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1916" uniqueCount="443">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -880,6 +880,12 @@
     <t>['13', '15']</t>
   </si>
   <si>
+    <t>['13', '42', '90+6']</t>
+  </si>
+  <si>
+    <t>['23', '32', '37']</t>
+  </si>
+  <si>
     <t>['60', '65']</t>
   </si>
   <si>
@@ -1335,6 +1341,9 @@
   <si>
     <t>['72', '84']</t>
   </si>
+  <si>
+    <t>['14', '72']</t>
+  </si>
 </sst>
 </file>
 
@@ -1695,7 +1704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP305"/>
+  <dimension ref="A1:BP309"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2029,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ2">
         <v>1.47</v>
@@ -2157,7 +2166,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q3">
         <v>6.5</v>
@@ -2238,7 +2247,7 @@
         <v>0.44</v>
       </c>
       <c r="AQ3">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2569,7 +2578,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -2856,7 +2865,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ6">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2981,7 +2990,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -3187,7 +3196,7 @@
         <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3471,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ9">
         <v>1.64</v>
@@ -3599,7 +3608,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -3680,7 +3689,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ10">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -4295,7 +4304,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ13">
         <v>1</v>
@@ -4707,7 +4716,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ15">
         <v>0.53</v>
@@ -5247,7 +5256,7 @@
         <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5453,7 +5462,7 @@
         <v>102</v>
       </c>
       <c r="P19" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q19">
         <v>4.5</v>
@@ -5534,7 +5543,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ19">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -6277,7 +6286,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q23">
         <v>4.75</v>
@@ -6483,7 +6492,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
@@ -6973,10 +6982,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ26">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR26">
         <v>1.29</v>
@@ -7101,7 +7110,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -7307,7 +7316,7 @@
         <v>110</v>
       </c>
       <c r="P28" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q28">
         <v>6</v>
@@ -7388,7 +7397,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ28">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR28">
         <v>1.25</v>
@@ -7513,7 +7522,7 @@
         <v>111</v>
       </c>
       <c r="P29" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q29">
         <v>2.1</v>
@@ -7925,7 +7934,7 @@
         <v>91</v>
       </c>
       <c r="P31" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8003,10 +8012,10 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ31">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR31">
         <v>1.62</v>
@@ -8131,7 +8140,7 @@
         <v>91</v>
       </c>
       <c r="P32" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8543,7 +8552,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -8827,7 +8836,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ35">
         <v>1.13</v>
@@ -9367,7 +9376,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -9573,7 +9582,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q39">
         <v>3.6</v>
@@ -9654,7 +9663,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ39">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR39">
         <v>1.56</v>
@@ -9779,7 +9788,7 @@
         <v>91</v>
       </c>
       <c r="P40" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9857,7 +9866,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ40">
         <v>1.75</v>
@@ -9985,7 +9994,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -10191,7 +10200,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10272,7 +10281,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ42">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR42">
         <v>1.11</v>
@@ -10397,7 +10406,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -10475,7 +10484,7 @@
         <v>2</v>
       </c>
       <c r="AP43">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ43">
         <v>1.6</v>
@@ -11299,7 +11308,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ47">
         <v>1.13</v>
@@ -12045,7 +12054,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q51">
         <v>2.4</v>
@@ -12251,7 +12260,7 @@
         <v>125</v>
       </c>
       <c r="P52" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q52">
         <v>4.75</v>
@@ -12332,7 +12341,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ52">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR52">
         <v>0.75</v>
@@ -12457,7 +12466,7 @@
         <v>91</v>
       </c>
       <c r="P53" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12869,7 +12878,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q55">
         <v>1.57</v>
@@ -13153,7 +13162,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ56">
         <v>1.13</v>
@@ -13281,7 +13290,7 @@
         <v>129</v>
       </c>
       <c r="P57" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13487,7 +13496,7 @@
         <v>130</v>
       </c>
       <c r="P58" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q58">
         <v>6.5</v>
@@ -13568,7 +13577,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ58">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR58">
         <v>1.42</v>
@@ -13693,7 +13702,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q59">
         <v>4.33</v>
@@ -13899,7 +13908,7 @@
         <v>91</v>
       </c>
       <c r="P60" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13977,7 +13986,7 @@
         <v>0.5</v>
       </c>
       <c r="AP60">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ60">
         <v>1.07</v>
@@ -14105,7 +14114,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q61">
         <v>2.1</v>
@@ -14186,7 +14195,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ61">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR61">
         <v>1.76</v>
@@ -14311,7 +14320,7 @@
         <v>91</v>
       </c>
       <c r="P62" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q62">
         <v>5.5</v>
@@ -14392,7 +14401,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ62">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR62">
         <v>1.29</v>
@@ -14723,7 +14732,7 @@
         <v>134</v>
       </c>
       <c r="P64" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -14929,7 +14938,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q65">
         <v>2.38</v>
@@ -15135,7 +15144,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -15213,7 +15222,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ66">
         <v>1.13</v>
@@ -15422,7 +15431,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ67">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR67">
         <v>2.4</v>
@@ -16165,7 +16174,7 @@
         <v>138</v>
       </c>
       <c r="P71" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q71">
         <v>3.2</v>
@@ -16449,7 +16458,7 @@
         <v>1.67</v>
       </c>
       <c r="AP72">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ72">
         <v>1.13</v>
@@ -16577,7 +16586,7 @@
         <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16655,7 +16664,7 @@
         <v>2.33</v>
       </c>
       <c r="AP73">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ73">
         <v>1.33</v>
@@ -16783,7 +16792,7 @@
         <v>140</v>
       </c>
       <c r="P74" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q74">
         <v>2.1</v>
@@ -16861,7 +16870,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ74">
         <v>1.13</v>
@@ -16989,7 +16998,7 @@
         <v>91</v>
       </c>
       <c r="P75" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -17195,7 +17204,7 @@
         <v>141</v>
       </c>
       <c r="P76" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -17401,7 +17410,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17813,7 +17822,7 @@
         <v>143</v>
       </c>
       <c r="P79" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q79">
         <v>7</v>
@@ -17894,7 +17903,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ79">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR79">
         <v>1.27</v>
@@ -18019,7 +18028,7 @@
         <v>144</v>
       </c>
       <c r="P80" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q80">
         <v>2.2</v>
@@ -18100,7 +18109,7 @@
         <v>2.53</v>
       </c>
       <c r="AQ80">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR80">
         <v>1.97</v>
@@ -18431,7 +18440,7 @@
         <v>94</v>
       </c>
       <c r="P82" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q82">
         <v>3.4</v>
@@ -18718,7 +18727,7 @@
         <v>2</v>
       </c>
       <c r="AQ83">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR83">
         <v>2.31</v>
@@ -18843,7 +18852,7 @@
         <v>146</v>
       </c>
       <c r="P84" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -19049,7 +19058,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q85">
         <v>2.5</v>
@@ -19255,7 +19264,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q86">
         <v>2.25</v>
@@ -19333,7 +19342,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ86">
         <v>0.87</v>
@@ -19667,7 +19676,7 @@
         <v>150</v>
       </c>
       <c r="P88" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q88">
         <v>2.3</v>
@@ -20079,7 +20088,7 @@
         <v>152</v>
       </c>
       <c r="P90" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20285,7 +20294,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20366,7 +20375,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ91">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR91">
         <v>2.46</v>
@@ -20984,7 +20993,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ94">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR94">
         <v>1.6</v>
@@ -21727,7 +21736,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q98">
         <v>3.2</v>
@@ -21933,7 +21942,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q99">
         <v>2.38</v>
@@ -22011,7 +22020,7 @@
         <v>2.5</v>
       </c>
       <c r="AP99">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ99">
         <v>1.33</v>
@@ -22139,7 +22148,7 @@
         <v>162</v>
       </c>
       <c r="P100" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q100">
         <v>3</v>
@@ -22217,10 +22226,10 @@
         <v>2.25</v>
       </c>
       <c r="AP100">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ100">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR100">
         <v>1.55</v>
@@ -22423,7 +22432,7 @@
         <v>0</v>
       </c>
       <c r="AP101">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ101">
         <v>1.13</v>
@@ -22551,7 +22560,7 @@
         <v>164</v>
       </c>
       <c r="P102" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -22629,7 +22638,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ102">
         <v>1.5</v>
@@ -22757,7 +22766,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23250,7 +23259,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ105">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR105">
         <v>1.17</v>
@@ -23456,7 +23465,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ106">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR106">
         <v>1.54</v>
@@ -23865,7 +23874,7 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ108">
         <v>0.53</v>
@@ -23993,7 +24002,7 @@
         <v>169</v>
       </c>
       <c r="P109" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
@@ -24199,7 +24208,7 @@
         <v>170</v>
       </c>
       <c r="P110" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q110">
         <v>1.62</v>
@@ -24277,7 +24286,7 @@
         <v>0.4</v>
       </c>
       <c r="AP110">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ110">
         <v>0.87</v>
@@ -24611,7 +24620,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24692,7 +24701,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ112">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR112">
         <v>1.12</v>
@@ -24817,7 +24826,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -24895,7 +24904,7 @@
         <v>0.4</v>
       </c>
       <c r="AP113">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ113">
         <v>1.13</v>
@@ -25435,7 +25444,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q116">
         <v>2.88</v>
@@ -25641,7 +25650,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25847,7 +25856,7 @@
         <v>91</v>
       </c>
       <c r="P118" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q118">
         <v>1.95</v>
@@ -26053,7 +26062,7 @@
         <v>176</v>
       </c>
       <c r="P119" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q119">
         <v>8</v>
@@ -26134,7 +26143,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ119">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR119">
         <v>1.07</v>
@@ -26259,7 +26268,7 @@
         <v>177</v>
       </c>
       <c r="P120" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q120">
         <v>4.75</v>
@@ -26465,7 +26474,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q121">
         <v>2</v>
@@ -26671,7 +26680,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q122">
         <v>1.91</v>
@@ -26752,7 +26761,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ122">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR122">
         <v>1.46</v>
@@ -26877,7 +26886,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q123">
         <v>3.25</v>
@@ -27367,7 +27376,7 @@
         <v>0.83</v>
       </c>
       <c r="AP125">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ125">
         <v>0.53</v>
@@ -27495,7 +27504,7 @@
         <v>149</v>
       </c>
       <c r="P126" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27701,7 +27710,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q127">
         <v>6</v>
@@ -27985,7 +27994,7 @@
         <v>0.83</v>
       </c>
       <c r="AP128">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ128">
         <v>1</v>
@@ -28397,7 +28406,7 @@
         <v>1.33</v>
       </c>
       <c r="AP130">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ130">
         <v>1.47</v>
@@ -28606,7 +28615,7 @@
         <v>2.53</v>
       </c>
       <c r="AQ131">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR131">
         <v>1.72</v>
@@ -28731,7 +28740,7 @@
         <v>91</v>
       </c>
       <c r="P132" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -29143,7 +29152,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29224,7 +29233,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ134">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR134">
         <v>1.08</v>
@@ -29349,7 +29358,7 @@
         <v>189</v>
       </c>
       <c r="P135" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q135">
         <v>4</v>
@@ -29430,7 +29439,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ135">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR135">
         <v>1.25</v>
@@ -30457,7 +30466,7 @@
         <v>1.67</v>
       </c>
       <c r="AP140">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ140">
         <v>1.44</v>
@@ -30791,7 +30800,7 @@
         <v>196</v>
       </c>
       <c r="P142" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q142">
         <v>5.5</v>
@@ -30872,7 +30881,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ142">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR142">
         <v>1.38</v>
@@ -30997,7 +31006,7 @@
         <v>197</v>
       </c>
       <c r="P143" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q143">
         <v>3.2</v>
@@ -31075,7 +31084,7 @@
         <v>1.29</v>
       </c>
       <c r="AP143">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ143">
         <v>1.6</v>
@@ -31284,7 +31293,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ144">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR144">
         <v>1.54</v>
@@ -31409,7 +31418,7 @@
         <v>198</v>
       </c>
       <c r="P145" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q145">
         <v>2.25</v>
@@ -31487,7 +31496,7 @@
         <v>1.57</v>
       </c>
       <c r="AP145">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ145">
         <v>1.63</v>
@@ -31615,7 +31624,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31693,7 +31702,7 @@
         <v>1.57</v>
       </c>
       <c r="AP146">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ146">
         <v>1.75</v>
@@ -31821,7 +31830,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -32027,7 +32036,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q148">
         <v>4.75</v>
@@ -32233,7 +32242,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q149">
         <v>3</v>
@@ -32311,10 +32320,10 @@
         <v>2.29</v>
       </c>
       <c r="AP149">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ149">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR149">
         <v>1.84</v>
@@ -32645,7 +32654,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q151">
         <v>2.5</v>
@@ -33263,7 +33272,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q154">
         <v>1.73</v>
@@ -33469,7 +33478,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q155">
         <v>3.2</v>
@@ -33675,7 +33684,7 @@
         <v>90</v>
       </c>
       <c r="P156" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33881,7 +33890,7 @@
         <v>117</v>
       </c>
       <c r="P157" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -34087,7 +34096,7 @@
         <v>91</v>
       </c>
       <c r="P158" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q158">
         <v>4</v>
@@ -34786,7 +34795,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ161">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR161">
         <v>1.54</v>
@@ -34911,7 +34920,7 @@
         <v>91</v>
       </c>
       <c r="P162" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q162">
         <v>2.88</v>
@@ -34989,7 +34998,7 @@
         <v>1.75</v>
       </c>
       <c r="AP162">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ162">
         <v>1.63</v>
@@ -35117,7 +35126,7 @@
         <v>125</v>
       </c>
       <c r="P163" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q163">
         <v>3.25</v>
@@ -35323,7 +35332,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q164">
         <v>4.5</v>
@@ -35529,7 +35538,7 @@
         <v>188</v>
       </c>
       <c r="P165" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q165">
         <v>5.5</v>
@@ -35813,10 +35822,10 @@
         <v>0.13</v>
       </c>
       <c r="AP166">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ166">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR166">
         <v>1.59</v>
@@ -35941,7 +35950,7 @@
         <v>91</v>
       </c>
       <c r="P167" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36147,7 +36156,7 @@
         <v>91</v>
       </c>
       <c r="P168" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q168">
         <v>2.38</v>
@@ -36225,7 +36234,7 @@
         <v>1.38</v>
       </c>
       <c r="AP168">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ168">
         <v>1.5</v>
@@ -36434,7 +36443,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ169">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR169">
         <v>1.39</v>
@@ -36559,7 +36568,7 @@
         <v>210</v>
       </c>
       <c r="P170" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36637,10 +36646,10 @@
         <v>2.43</v>
       </c>
       <c r="AP170">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ170">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR170">
         <v>1.79</v>
@@ -36971,7 +36980,7 @@
         <v>91</v>
       </c>
       <c r="P172" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q172">
         <v>3.6</v>
@@ -37589,7 +37598,7 @@
         <v>133</v>
       </c>
       <c r="P175" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q175">
         <v>1.95</v>
@@ -38207,7 +38216,7 @@
         <v>215</v>
       </c>
       <c r="P178" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q178">
         <v>1.4</v>
@@ -38825,7 +38834,7 @@
         <v>91</v>
       </c>
       <c r="P181" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q181">
         <v>7</v>
@@ -38906,7 +38915,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ181">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR181">
         <v>1.08</v>
@@ -39031,7 +39040,7 @@
         <v>216</v>
       </c>
       <c r="P182" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q182">
         <v>1.91</v>
@@ -39109,7 +39118,7 @@
         <v>0.89</v>
       </c>
       <c r="AP182">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ182">
         <v>1.13</v>
@@ -39318,7 +39327,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ183">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR183">
         <v>1.34</v>
@@ -39443,7 +39452,7 @@
         <v>218</v>
       </c>
       <c r="P184" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q184">
         <v>3</v>
@@ -39521,7 +39530,7 @@
         <v>1.56</v>
       </c>
       <c r="AP184">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ184">
         <v>1.5</v>
@@ -39649,7 +39658,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -39855,7 +39864,7 @@
         <v>91</v>
       </c>
       <c r="P186" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q186">
         <v>5.5</v>
@@ -39936,7 +39945,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ186">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR186">
         <v>1.43</v>
@@ -40142,7 +40151,7 @@
         <v>0.44</v>
       </c>
       <c r="AQ187">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR187">
         <v>1.17</v>
@@ -40267,7 +40276,7 @@
         <v>220</v>
       </c>
       <c r="P188" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40473,7 +40482,7 @@
         <v>91</v>
       </c>
       <c r="P189" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q189">
         <v>3.2</v>
@@ -40551,7 +40560,7 @@
         <v>1.33</v>
       </c>
       <c r="AP189">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ189">
         <v>1.6</v>
@@ -40679,7 +40688,7 @@
         <v>221</v>
       </c>
       <c r="P190" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q190">
         <v>6</v>
@@ -40757,7 +40766,7 @@
         <v>1.67</v>
       </c>
       <c r="AP190">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ190">
         <v>1.75</v>
@@ -40885,7 +40894,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q191">
         <v>3.2</v>
@@ -40963,7 +40972,7 @@
         <v>1.5</v>
       </c>
       <c r="AP191">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ191">
         <v>1.6</v>
@@ -41297,7 +41306,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q193">
         <v>1.8</v>
@@ -41584,7 +41593,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ194">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR194">
         <v>1.41</v>
@@ -41709,7 +41718,7 @@
         <v>91</v>
       </c>
       <c r="P195" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q195">
         <v>3.2</v>
@@ -41915,7 +41924,7 @@
         <v>226</v>
       </c>
       <c r="P196" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q196">
         <v>1.73</v>
@@ -42327,7 +42336,7 @@
         <v>228</v>
       </c>
       <c r="P198" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q198">
         <v>2.1</v>
@@ -42405,7 +42414,7 @@
         <v>0.89</v>
       </c>
       <c r="AP198">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ198">
         <v>0.87</v>
@@ -42533,7 +42542,7 @@
         <v>229</v>
       </c>
       <c r="P199" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q199">
         <v>1.67</v>
@@ -42739,7 +42748,7 @@
         <v>91</v>
       </c>
       <c r="P200" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q200">
         <v>3.6</v>
@@ -42945,7 +42954,7 @@
         <v>230</v>
       </c>
       <c r="P201" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q201">
         <v>2.1</v>
@@ -43151,7 +43160,7 @@
         <v>231</v>
       </c>
       <c r="P202" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q202">
         <v>3.25</v>
@@ -43357,7 +43366,7 @@
         <v>232</v>
       </c>
       <c r="P203" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q203">
         <v>4.33</v>
@@ -43435,10 +43444,10 @@
         <v>1.4</v>
       </c>
       <c r="AP203">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ203">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR203">
         <v>1.57</v>
@@ -43563,7 +43572,7 @@
         <v>233</v>
       </c>
       <c r="P204" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q204">
         <v>4.75</v>
@@ -43644,7 +43653,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ204">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR204">
         <v>1.5</v>
@@ -43769,7 +43778,7 @@
         <v>91</v>
       </c>
       <c r="P205" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q205">
         <v>4</v>
@@ -44181,7 +44190,7 @@
         <v>91</v>
       </c>
       <c r="P207" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -44593,7 +44602,7 @@
         <v>91</v>
       </c>
       <c r="P209" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Q209">
         <v>4</v>
@@ -44877,10 +44886,10 @@
         <v>0.2</v>
       </c>
       <c r="AP210">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ210">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR210">
         <v>1.48</v>
@@ -45005,7 +45014,7 @@
         <v>111</v>
       </c>
       <c r="P211" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45211,7 +45220,7 @@
         <v>91</v>
       </c>
       <c r="P212" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45417,7 +45426,7 @@
         <v>91</v>
       </c>
       <c r="P213" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -45495,10 +45504,10 @@
         <v>2.4</v>
       </c>
       <c r="AP213">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ213">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR213">
         <v>1.61</v>
@@ -45623,7 +45632,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Q214">
         <v>4</v>
@@ -45829,7 +45838,7 @@
         <v>237</v>
       </c>
       <c r="P215" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Q215">
         <v>2</v>
@@ -46035,7 +46044,7 @@
         <v>94</v>
       </c>
       <c r="P216" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Q216">
         <v>2.63</v>
@@ -46113,7 +46122,7 @@
         <v>1.45</v>
       </c>
       <c r="AP216">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ216">
         <v>1.44</v>
@@ -46241,7 +46250,7 @@
         <v>238</v>
       </c>
       <c r="P217" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Q217">
         <v>1.95</v>
@@ -46322,7 +46331,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ217">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR217">
         <v>1.44</v>
@@ -46447,7 +46456,7 @@
         <v>239</v>
       </c>
       <c r="P218" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Q218">
         <v>3.25</v>
@@ -46653,7 +46662,7 @@
         <v>91</v>
       </c>
       <c r="P219" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="Q219">
         <v>7</v>
@@ -46734,7 +46743,7 @@
         <v>0.44</v>
       </c>
       <c r="AQ219">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR219">
         <v>1.13</v>
@@ -46859,7 +46868,7 @@
         <v>240</v>
       </c>
       <c r="P220" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q220">
         <v>1.73</v>
@@ -47271,7 +47280,7 @@
         <v>91</v>
       </c>
       <c r="P222" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Q222">
         <v>2.2</v>
@@ -47683,7 +47692,7 @@
         <v>107</v>
       </c>
       <c r="P224" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q224">
         <v>6</v>
@@ -47889,7 +47898,7 @@
         <v>91</v>
       </c>
       <c r="P225" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q225">
         <v>6.5</v>
@@ -48095,7 +48104,7 @@
         <v>243</v>
       </c>
       <c r="P226" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Q226">
         <v>2.38</v>
@@ -48176,7 +48185,7 @@
         <v>2</v>
       </c>
       <c r="AQ226">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR226">
         <v>2.02</v>
@@ -48301,7 +48310,7 @@
         <v>155</v>
       </c>
       <c r="P227" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
@@ -48507,7 +48516,7 @@
         <v>244</v>
       </c>
       <c r="P228" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Q228">
         <v>1.91</v>
@@ -48585,7 +48594,7 @@
         <v>0.5</v>
       </c>
       <c r="AP228">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ228">
         <v>0.53</v>
@@ -48919,7 +48928,7 @@
         <v>91</v>
       </c>
       <c r="P230" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Q230">
         <v>2.88</v>
@@ -48997,7 +49006,7 @@
         <v>1</v>
       </c>
       <c r="AP230">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ230">
         <v>1.13</v>
@@ -49331,7 +49340,7 @@
         <v>95</v>
       </c>
       <c r="P232" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Q232">
         <v>2.2</v>
@@ -49743,7 +49752,7 @@
         <v>151</v>
       </c>
       <c r="P234" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Q234">
         <v>2.6</v>
@@ -49824,7 +49833,7 @@
         <v>0.44</v>
       </c>
       <c r="AQ234">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR234">
         <v>1.13</v>
@@ -49949,7 +49958,7 @@
         <v>91</v>
       </c>
       <c r="P235" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Q235">
         <v>4.5</v>
@@ -50030,7 +50039,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ235">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR235">
         <v>1.81</v>
@@ -50361,7 +50370,7 @@
         <v>91</v>
       </c>
       <c r="P237" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50439,7 +50448,7 @@
         <v>0.91</v>
       </c>
       <c r="AP237">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ237">
         <v>1.07</v>
@@ -50567,7 +50576,7 @@
         <v>91</v>
       </c>
       <c r="P238" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q238">
         <v>2.75</v>
@@ -50645,7 +50654,7 @@
         <v>1.45</v>
       </c>
       <c r="AP238">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ238">
         <v>1.64</v>
@@ -50854,7 +50863,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ239">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR239">
         <v>2</v>
@@ -50979,7 +50988,7 @@
         <v>249</v>
       </c>
       <c r="P240" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Q240">
         <v>1.8</v>
@@ -51185,7 +51194,7 @@
         <v>250</v>
       </c>
       <c r="P241" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Q241">
         <v>6</v>
@@ -51266,7 +51275,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ241">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR241">
         <v>1.39</v>
@@ -51472,7 +51481,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ242">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR242">
         <v>1.61</v>
@@ -51597,7 +51606,7 @@
         <v>91</v>
       </c>
       <c r="P243" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Q243">
         <v>9</v>
@@ -51803,7 +51812,7 @@
         <v>203</v>
       </c>
       <c r="P244" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q244">
         <v>5</v>
@@ -52499,7 +52508,7 @@
         <v>1.92</v>
       </c>
       <c r="AP247">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ247">
         <v>1.63</v>
@@ -52833,7 +52842,7 @@
         <v>254</v>
       </c>
       <c r="P249" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Q249">
         <v>2.63</v>
@@ -53323,7 +53332,7 @@
         <v>1.18</v>
       </c>
       <c r="AP251">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ251">
         <v>1.13</v>
@@ -53451,7 +53460,7 @@
         <v>256</v>
       </c>
       <c r="P252" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Q252">
         <v>4</v>
@@ -53532,7 +53541,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ252">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR252">
         <v>1.61</v>
@@ -53657,7 +53666,7 @@
         <v>91</v>
       </c>
       <c r="P253" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Q253">
         <v>3.6</v>
@@ -53863,7 +53872,7 @@
         <v>257</v>
       </c>
       <c r="P254" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="Q254">
         <v>3.25</v>
@@ -54069,7 +54078,7 @@
         <v>91</v>
       </c>
       <c r="P255" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="Q255">
         <v>5</v>
@@ -54275,7 +54284,7 @@
         <v>117</v>
       </c>
       <c r="P256" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="Q256">
         <v>3.75</v>
@@ -54481,7 +54490,7 @@
         <v>91</v>
       </c>
       <c r="P257" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="Q257">
         <v>1.73</v>
@@ -54893,7 +54902,7 @@
         <v>91</v>
       </c>
       <c r="P259" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Q259">
         <v>2.75</v>
@@ -54971,7 +54980,7 @@
         <v>1.58</v>
       </c>
       <c r="AP259">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ259">
         <v>1.64</v>
@@ -55099,7 +55108,7 @@
         <v>258</v>
       </c>
       <c r="P260" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q260">
         <v>3.1</v>
@@ -55180,7 +55189,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ260">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR260">
         <v>1.6</v>
@@ -55305,7 +55314,7 @@
         <v>259</v>
       </c>
       <c r="P261" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="Q261">
         <v>2.38</v>
@@ -55511,7 +55520,7 @@
         <v>91</v>
       </c>
       <c r="P262" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Q262">
         <v>3.1</v>
@@ -55592,7 +55601,7 @@
         <v>2</v>
       </c>
       <c r="AQ262">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AR262">
         <v>1.96</v>
@@ -55717,7 +55726,7 @@
         <v>260</v>
       </c>
       <c r="P263" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q263">
         <v>3.2</v>
@@ -55923,7 +55932,7 @@
         <v>261</v>
       </c>
       <c r="P264" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Q264">
         <v>3.5</v>
@@ -56416,7 +56425,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ266">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR266">
         <v>1.91</v>
@@ -56619,10 +56628,10 @@
         <v>1.38</v>
       </c>
       <c r="AP267">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ267">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR267">
         <v>1.78</v>
@@ -56747,7 +56756,7 @@
         <v>264</v>
       </c>
       <c r="P268" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="Q268">
         <v>2.05</v>
@@ -56825,7 +56834,7 @@
         <v>0.83</v>
       </c>
       <c r="AP268">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ268">
         <v>0.87</v>
@@ -57031,7 +57040,7 @@
         <v>1.08</v>
       </c>
       <c r="AP269">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ269">
         <v>1</v>
@@ -57858,7 +57867,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ273">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR273">
         <v>1.46</v>
@@ -57983,7 +57992,7 @@
         <v>269</v>
       </c>
       <c r="P274" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Q274">
         <v>1.4</v>
@@ -58064,7 +58073,7 @@
         <v>2.53</v>
       </c>
       <c r="AQ274">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR274">
         <v>1.79</v>
@@ -58189,7 +58198,7 @@
         <v>270</v>
       </c>
       <c r="P275" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q275">
         <v>2.5</v>
@@ -58679,7 +58688,7 @@
         <v>1.08</v>
       </c>
       <c r="AP277">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ277">
         <v>1.33</v>
@@ -59219,7 +59228,7 @@
         <v>273</v>
       </c>
       <c r="P280" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="Q280">
         <v>2.88</v>
@@ -59297,7 +59306,7 @@
         <v>1.57</v>
       </c>
       <c r="AP280">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ280">
         <v>1.5</v>
@@ -59425,7 +59434,7 @@
         <v>274</v>
       </c>
       <c r="P281" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q281">
         <v>5.5</v>
@@ -59503,7 +59512,7 @@
         <v>1.86</v>
       </c>
       <c r="AP281">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ281">
         <v>1.75</v>
@@ -59631,7 +59640,7 @@
         <v>91</v>
       </c>
       <c r="P282" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q282">
         <v>3.5</v>
@@ -59837,7 +59846,7 @@
         <v>275</v>
       </c>
       <c r="P283" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="Q283">
         <v>4</v>
@@ -60249,7 +60258,7 @@
         <v>277</v>
       </c>
       <c r="P285" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="Q285">
         <v>4</v>
@@ -60455,7 +60464,7 @@
         <v>278</v>
       </c>
       <c r="P286" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="Q286">
         <v>2.2</v>
@@ -60661,7 +60670,7 @@
         <v>195</v>
       </c>
       <c r="P287" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="Q287">
         <v>2.25</v>
@@ -60945,7 +60954,7 @@
         <v>1.23</v>
       </c>
       <c r="AP288">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ288">
         <v>1.07</v>
@@ -61154,7 +61163,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ289">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AR289">
         <v>1.99</v>
@@ -61279,7 +61288,7 @@
         <v>91</v>
       </c>
       <c r="P290" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="Q290">
         <v>4.33</v>
@@ -62103,7 +62112,7 @@
         <v>172</v>
       </c>
       <c r="P294" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="Q294">
         <v>5.5</v>
@@ -62515,7 +62524,7 @@
         <v>282</v>
       </c>
       <c r="P296" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q296">
         <v>2.2</v>
@@ -62721,7 +62730,7 @@
         <v>91</v>
       </c>
       <c r="P297" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q297">
         <v>2.6</v>
@@ -62927,7 +62936,7 @@
         <v>283</v>
       </c>
       <c r="P298" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="Q298">
         <v>1.83</v>
@@ -63545,7 +63554,7 @@
         <v>180</v>
       </c>
       <c r="P301" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Q301">
         <v>6</v>
@@ -63751,7 +63760,7 @@
         <v>285</v>
       </c>
       <c r="P302" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="Q302">
         <v>3.6</v>
@@ -64163,7 +64172,7 @@
         <v>133</v>
       </c>
       <c r="P304" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="Q304">
         <v>3.5</v>
@@ -64526,6 +64535,830 @@
       </c>
       <c r="BP305">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="306" spans="1:68">
+      <c r="A306" s="1">
+        <v>305</v>
+      </c>
+      <c r="B306">
+        <v>7466987</v>
+      </c>
+      <c r="C306" t="s">
+        <v>68</v>
+      </c>
+      <c r="D306" t="s">
+        <v>69</v>
+      </c>
+      <c r="E306" s="2">
+        <v>45753.41666666666</v>
+      </c>
+      <c r="F306">
+        <v>31</v>
+      </c>
+      <c r="G306" t="s">
+        <v>81</v>
+      </c>
+      <c r="H306" t="s">
+        <v>84</v>
+      </c>
+      <c r="I306">
+        <v>2</v>
+      </c>
+      <c r="J306">
+        <v>0</v>
+      </c>
+      <c r="K306">
+        <v>2</v>
+      </c>
+      <c r="L306">
+        <v>3</v>
+      </c>
+      <c r="M306">
+        <v>1</v>
+      </c>
+      <c r="N306">
+        <v>4</v>
+      </c>
+      <c r="O306" t="s">
+        <v>288</v>
+      </c>
+      <c r="P306" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q306">
+        <v>1.83</v>
+      </c>
+      <c r="R306">
+        <v>2.75</v>
+      </c>
+      <c r="S306">
+        <v>6</v>
+      </c>
+      <c r="T306">
+        <v>1.22</v>
+      </c>
+      <c r="U306">
+        <v>4</v>
+      </c>
+      <c r="V306">
+        <v>2</v>
+      </c>
+      <c r="W306">
+        <v>1.73</v>
+      </c>
+      <c r="X306">
+        <v>4.33</v>
+      </c>
+      <c r="Y306">
+        <v>1.2</v>
+      </c>
+      <c r="Z306">
+        <v>1.37</v>
+      </c>
+      <c r="AA306">
+        <v>5.6</v>
+      </c>
+      <c r="AB306">
+        <v>7</v>
+      </c>
+      <c r="AC306">
+        <v>1.01</v>
+      </c>
+      <c r="AD306">
+        <v>23</v>
+      </c>
+      <c r="AE306">
+        <v>1.11</v>
+      </c>
+      <c r="AF306">
+        <v>6.25</v>
+      </c>
+      <c r="AG306">
+        <v>1.37</v>
+      </c>
+      <c r="AH306">
+        <v>2.94</v>
+      </c>
+      <c r="AI306">
+        <v>1.57</v>
+      </c>
+      <c r="AJ306">
+        <v>2.25</v>
+      </c>
+      <c r="AK306">
+        <v>1.11</v>
+      </c>
+      <c r="AL306">
+        <v>1.16</v>
+      </c>
+      <c r="AM306">
+        <v>2.9</v>
+      </c>
+      <c r="AN306">
+        <v>1.2</v>
+      </c>
+      <c r="AO306">
+        <v>0.33</v>
+      </c>
+      <c r="AP306">
+        <v>1.31</v>
+      </c>
+      <c r="AQ306">
+        <v>0.31</v>
+      </c>
+      <c r="AR306">
+        <v>1.74</v>
+      </c>
+      <c r="AS306">
+        <v>1.05</v>
+      </c>
+      <c r="AT306">
+        <v>2.79</v>
+      </c>
+      <c r="AU306">
+        <v>9</v>
+      </c>
+      <c r="AV306">
+        <v>5</v>
+      </c>
+      <c r="AW306">
+        <v>5</v>
+      </c>
+      <c r="AX306">
+        <v>8</v>
+      </c>
+      <c r="AY306">
+        <v>16</v>
+      </c>
+      <c r="AZ306">
+        <v>16</v>
+      </c>
+      <c r="BA306">
+        <v>4</v>
+      </c>
+      <c r="BB306">
+        <v>1</v>
+      </c>
+      <c r="BC306">
+        <v>5</v>
+      </c>
+      <c r="BD306">
+        <v>1.35</v>
+      </c>
+      <c r="BE306">
+        <v>7.5</v>
+      </c>
+      <c r="BF306">
+        <v>3.45</v>
+      </c>
+      <c r="BG306">
+        <v>1.14</v>
+      </c>
+      <c r="BH306">
+        <v>4.8</v>
+      </c>
+      <c r="BI306">
+        <v>1.24</v>
+      </c>
+      <c r="BJ306">
+        <v>3.55</v>
+      </c>
+      <c r="BK306">
+        <v>1.41</v>
+      </c>
+      <c r="BL306">
+        <v>2.65</v>
+      </c>
+      <c r="BM306">
+        <v>1.65</v>
+      </c>
+      <c r="BN306">
+        <v>2.08</v>
+      </c>
+      <c r="BO306">
+        <v>1.97</v>
+      </c>
+      <c r="BP306">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="307" spans="1:68">
+      <c r="A307" s="1">
+        <v>306</v>
+      </c>
+      <c r="B307">
+        <v>7466983</v>
+      </c>
+      <c r="C307" t="s">
+        <v>68</v>
+      </c>
+      <c r="D307" t="s">
+        <v>69</v>
+      </c>
+      <c r="E307" s="2">
+        <v>45753.41666666666</v>
+      </c>
+      <c r="F307">
+        <v>31</v>
+      </c>
+      <c r="G307" t="s">
+        <v>83</v>
+      </c>
+      <c r="H307" t="s">
+        <v>89</v>
+      </c>
+      <c r="I307">
+        <v>3</v>
+      </c>
+      <c r="J307">
+        <v>1</v>
+      </c>
+      <c r="K307">
+        <v>4</v>
+      </c>
+      <c r="L307">
+        <v>3</v>
+      </c>
+      <c r="M307">
+        <v>2</v>
+      </c>
+      <c r="N307">
+        <v>5</v>
+      </c>
+      <c r="O307" t="s">
+        <v>289</v>
+      </c>
+      <c r="P307" t="s">
+        <v>442</v>
+      </c>
+      <c r="Q307">
+        <v>4.5</v>
+      </c>
+      <c r="R307">
+        <v>2.25</v>
+      </c>
+      <c r="S307">
+        <v>2.4</v>
+      </c>
+      <c r="T307">
+        <v>1.36</v>
+      </c>
+      <c r="U307">
+        <v>3</v>
+      </c>
+      <c r="V307">
+        <v>2.63</v>
+      </c>
+      <c r="W307">
+        <v>1.44</v>
+      </c>
+      <c r="X307">
+        <v>7</v>
+      </c>
+      <c r="Y307">
+        <v>1.1</v>
+      </c>
+      <c r="Z307">
+        <v>4.2</v>
+      </c>
+      <c r="AA307">
+        <v>3.8</v>
+      </c>
+      <c r="AB307">
+        <v>1.83</v>
+      </c>
+      <c r="AC307">
+        <v>1.05</v>
+      </c>
+      <c r="AD307">
+        <v>9.5</v>
+      </c>
+      <c r="AE307">
+        <v>1.25</v>
+      </c>
+      <c r="AF307">
+        <v>3.75</v>
+      </c>
+      <c r="AG307">
+        <v>1.75</v>
+      </c>
+      <c r="AH307">
+        <v>1.95</v>
+      </c>
+      <c r="AI307">
+        <v>1.7</v>
+      </c>
+      <c r="AJ307">
+        <v>2.05</v>
+      </c>
+      <c r="AK307">
+        <v>1.88</v>
+      </c>
+      <c r="AL307">
+        <v>1.27</v>
+      </c>
+      <c r="AM307">
+        <v>1.24</v>
+      </c>
+      <c r="AN307">
+        <v>1.53</v>
+      </c>
+      <c r="AO307">
+        <v>2.33</v>
+      </c>
+      <c r="AP307">
+        <v>1.63</v>
+      </c>
+      <c r="AQ307">
+        <v>2.19</v>
+      </c>
+      <c r="AR307">
+        <v>1.6</v>
+      </c>
+      <c r="AS307">
+        <v>1.96</v>
+      </c>
+      <c r="AT307">
+        <v>3.56</v>
+      </c>
+      <c r="AU307">
+        <v>7</v>
+      </c>
+      <c r="AV307">
+        <v>7</v>
+      </c>
+      <c r="AW307">
+        <v>6</v>
+      </c>
+      <c r="AX307">
+        <v>8</v>
+      </c>
+      <c r="AY307">
+        <v>14</v>
+      </c>
+      <c r="AZ307">
+        <v>16</v>
+      </c>
+      <c r="BA307">
+        <v>4</v>
+      </c>
+      <c r="BB307">
+        <v>4</v>
+      </c>
+      <c r="BC307">
+        <v>8</v>
+      </c>
+      <c r="BD307">
+        <v>2.32</v>
+      </c>
+      <c r="BE307">
+        <v>6.75</v>
+      </c>
+      <c r="BF307">
+        <v>1.73</v>
+      </c>
+      <c r="BG307">
+        <v>1.23</v>
+      </c>
+      <c r="BH307">
+        <v>3.65</v>
+      </c>
+      <c r="BI307">
+        <v>1.41</v>
+      </c>
+      <c r="BJ307">
+        <v>2.65</v>
+      </c>
+      <c r="BK307">
+        <v>1.67</v>
+      </c>
+      <c r="BL307">
+        <v>2.04</v>
+      </c>
+      <c r="BM307">
+        <v>2.06</v>
+      </c>
+      <c r="BN307">
+        <v>1.66</v>
+      </c>
+      <c r="BO307">
+        <v>2.55</v>
+      </c>
+      <c r="BP307">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="308" spans="1:68">
+      <c r="A308" s="1">
+        <v>307</v>
+      </c>
+      <c r="B308">
+        <v>7466980</v>
+      </c>
+      <c r="C308" t="s">
+        <v>68</v>
+      </c>
+      <c r="D308" t="s">
+        <v>69</v>
+      </c>
+      <c r="E308" s="2">
+        <v>45753.41666666666</v>
+      </c>
+      <c r="F308">
+        <v>31</v>
+      </c>
+      <c r="G308" t="s">
+        <v>77</v>
+      </c>
+      <c r="H308" t="s">
+        <v>78</v>
+      </c>
+      <c r="I308">
+        <v>0</v>
+      </c>
+      <c r="J308">
+        <v>0</v>
+      </c>
+      <c r="K308">
+        <v>0</v>
+      </c>
+      <c r="L308">
+        <v>0</v>
+      </c>
+      <c r="M308">
+        <v>0</v>
+      </c>
+      <c r="N308">
+        <v>0</v>
+      </c>
+      <c r="O308" t="s">
+        <v>91</v>
+      </c>
+      <c r="P308" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q308">
+        <v>3.4</v>
+      </c>
+      <c r="R308">
+        <v>2.4</v>
+      </c>
+      <c r="S308">
+        <v>2.63</v>
+      </c>
+      <c r="T308">
+        <v>1.29</v>
+      </c>
+      <c r="U308">
+        <v>3.5</v>
+      </c>
+      <c r="V308">
+        <v>2.25</v>
+      </c>
+      <c r="W308">
+        <v>1.57</v>
+      </c>
+      <c r="X308">
+        <v>5.5</v>
+      </c>
+      <c r="Y308">
+        <v>1.14</v>
+      </c>
+      <c r="Z308">
+        <v>3.1</v>
+      </c>
+      <c r="AA308">
+        <v>3.8</v>
+      </c>
+      <c r="AB308">
+        <v>2.15</v>
+      </c>
+      <c r="AC308">
+        <v>1.01</v>
+      </c>
+      <c r="AD308">
+        <v>13</v>
+      </c>
+      <c r="AE308">
+        <v>1.17</v>
+      </c>
+      <c r="AF308">
+        <v>5</v>
+      </c>
+      <c r="AG308">
+        <v>1.5</v>
+      </c>
+      <c r="AH308">
+        <v>2.48</v>
+      </c>
+      <c r="AI308">
+        <v>1.5</v>
+      </c>
+      <c r="AJ308">
+        <v>2.5</v>
+      </c>
+      <c r="AK308">
+        <v>1.7</v>
+      </c>
+      <c r="AL308">
+        <v>1.26</v>
+      </c>
+      <c r="AM308">
+        <v>1.35</v>
+      </c>
+      <c r="AN308">
+        <v>1.6</v>
+      </c>
+      <c r="AO308">
+        <v>1.4</v>
+      </c>
+      <c r="AP308">
+        <v>1.56</v>
+      </c>
+      <c r="AQ308">
+        <v>1.38</v>
+      </c>
+      <c r="AR308">
+        <v>1.65</v>
+      </c>
+      <c r="AS308">
+        <v>1.52</v>
+      </c>
+      <c r="AT308">
+        <v>3.17</v>
+      </c>
+      <c r="AU308">
+        <v>3</v>
+      </c>
+      <c r="AV308">
+        <v>6</v>
+      </c>
+      <c r="AW308">
+        <v>7</v>
+      </c>
+      <c r="AX308">
+        <v>16</v>
+      </c>
+      <c r="AY308">
+        <v>12</v>
+      </c>
+      <c r="AZ308">
+        <v>28</v>
+      </c>
+      <c r="BA308">
+        <v>3</v>
+      </c>
+      <c r="BB308">
+        <v>6</v>
+      </c>
+      <c r="BC308">
+        <v>9</v>
+      </c>
+      <c r="BD308">
+        <v>2.7</v>
+      </c>
+      <c r="BE308">
+        <v>6.75</v>
+      </c>
+      <c r="BF308">
+        <v>1.55</v>
+      </c>
+      <c r="BG308">
+        <v>1.2</v>
+      </c>
+      <c r="BH308">
+        <v>3.9</v>
+      </c>
+      <c r="BI308">
+        <v>1.36</v>
+      </c>
+      <c r="BJ308">
+        <v>2.8</v>
+      </c>
+      <c r="BK308">
+        <v>1.6</v>
+      </c>
+      <c r="BL308">
+        <v>2.17</v>
+      </c>
+      <c r="BM308">
+        <v>1.95</v>
+      </c>
+      <c r="BN308">
+        <v>1.75</v>
+      </c>
+      <c r="BO308">
+        <v>2.43</v>
+      </c>
+      <c r="BP308">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="309" spans="1:68">
+      <c r="A309" s="1">
+        <v>308</v>
+      </c>
+      <c r="B309">
+        <v>7466986</v>
+      </c>
+      <c r="C309" t="s">
+        <v>68</v>
+      </c>
+      <c r="D309" t="s">
+        <v>69</v>
+      </c>
+      <c r="E309" s="2">
+        <v>45753.52083333334</v>
+      </c>
+      <c r="F309">
+        <v>31</v>
+      </c>
+      <c r="G309" t="s">
+        <v>70</v>
+      </c>
+      <c r="H309" t="s">
+        <v>85</v>
+      </c>
+      <c r="I309">
+        <v>0</v>
+      </c>
+      <c r="J309">
+        <v>0</v>
+      </c>
+      <c r="K309">
+        <v>0</v>
+      </c>
+      <c r="L309">
+        <v>0</v>
+      </c>
+      <c r="M309">
+        <v>0</v>
+      </c>
+      <c r="N309">
+        <v>0</v>
+      </c>
+      <c r="O309" t="s">
+        <v>91</v>
+      </c>
+      <c r="P309" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q309">
+        <v>3.6</v>
+      </c>
+      <c r="R309">
+        <v>2.38</v>
+      </c>
+      <c r="S309">
+        <v>2.63</v>
+      </c>
+      <c r="T309">
+        <v>1.3</v>
+      </c>
+      <c r="U309">
+        <v>3.4</v>
+      </c>
+      <c r="V309">
+        <v>2.38</v>
+      </c>
+      <c r="W309">
+        <v>1.53</v>
+      </c>
+      <c r="X309">
+        <v>6</v>
+      </c>
+      <c r="Y309">
+        <v>1.13</v>
+      </c>
+      <c r="Z309">
+        <v>3.3</v>
+      </c>
+      <c r="AA309">
+        <v>3.6</v>
+      </c>
+      <c r="AB309">
+        <v>2.1</v>
+      </c>
+      <c r="AC309">
+        <v>1.04</v>
+      </c>
+      <c r="AD309">
+        <v>10</v>
+      </c>
+      <c r="AE309">
+        <v>1.2</v>
+      </c>
+      <c r="AF309">
+        <v>4.33</v>
+      </c>
+      <c r="AG309">
+        <v>1.62</v>
+      </c>
+      <c r="AH309">
+        <v>2.3</v>
+      </c>
+      <c r="AI309">
+        <v>1.53</v>
+      </c>
+      <c r="AJ309">
+        <v>2.38</v>
+      </c>
+      <c r="AK309">
+        <v>1.68</v>
+      </c>
+      <c r="AL309">
+        <v>1.28</v>
+      </c>
+      <c r="AM309">
+        <v>1.33</v>
+      </c>
+      <c r="AN309">
+        <v>1.33</v>
+      </c>
+      <c r="AO309">
+        <v>1.4</v>
+      </c>
+      <c r="AP309">
+        <v>1.31</v>
+      </c>
+      <c r="AQ309">
+        <v>1.38</v>
+      </c>
+      <c r="AR309">
+        <v>1.52</v>
+      </c>
+      <c r="AS309">
+        <v>1.8</v>
+      </c>
+      <c r="AT309">
+        <v>3.32</v>
+      </c>
+      <c r="AU309">
+        <v>3</v>
+      </c>
+      <c r="AV309">
+        <v>6</v>
+      </c>
+      <c r="AW309">
+        <v>11</v>
+      </c>
+      <c r="AX309">
+        <v>4</v>
+      </c>
+      <c r="AY309">
+        <v>20</v>
+      </c>
+      <c r="AZ309">
+        <v>11</v>
+      </c>
+      <c r="BA309">
+        <v>5</v>
+      </c>
+      <c r="BB309">
+        <v>3</v>
+      </c>
+      <c r="BC309">
+        <v>8</v>
+      </c>
+      <c r="BD309">
+        <v>2.55</v>
+      </c>
+      <c r="BE309">
+        <v>7</v>
+      </c>
+      <c r="BF309">
+        <v>1.58</v>
+      </c>
+      <c r="BG309">
+        <v>1.18</v>
+      </c>
+      <c r="BH309">
+        <v>4.1</v>
+      </c>
+      <c r="BI309">
+        <v>1.32</v>
+      </c>
+      <c r="BJ309">
+        <v>3.05</v>
+      </c>
+      <c r="BK309">
+        <v>1.54</v>
+      </c>
+      <c r="BL309">
+        <v>2.3</v>
+      </c>
+      <c r="BM309">
+        <v>1.84</v>
+      </c>
+      <c r="BN309">
+        <v>1.84</v>
+      </c>
+      <c r="BO309">
+        <v>2.32</v>
+      </c>
+      <c r="BP309">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1916" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1922" uniqueCount="444">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1344,6 +1344,9 @@
   <si>
     <t>['14', '72']</t>
   </si>
+  <si>
+    <t>['2', '11', '34']</t>
+  </si>
 </sst>
 </file>
 
@@ -1704,7 +1707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP309"/>
+  <dimension ref="A1:BP310"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3892,7 +3895,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ11">
         <v>1.07</v>
@@ -5749,7 +5752,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ20">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -6364,7 +6367,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ23">
         <v>1.33</v>
@@ -10075,7 +10078,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ41">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR41">
         <v>1.34</v>
@@ -10487,7 +10490,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ43">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR43">
         <v>1.79</v>
@@ -10690,7 +10693,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ44">
         <v>1</v>
@@ -14604,7 +14607,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ63">
         <v>1.5</v>
@@ -15637,7 +15640,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ68">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR68">
         <v>1.37</v>
@@ -18518,7 +18521,7 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ82">
         <v>1.63</v>
@@ -19757,7 +19760,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ88">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR88">
         <v>1.67</v>
@@ -24083,7 +24086,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ109">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR109">
         <v>1.61</v>
@@ -24698,7 +24701,7 @@
         <v>2</v>
       </c>
       <c r="AP112">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ112">
         <v>1.38</v>
@@ -27585,7 +27588,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ126">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR126">
         <v>1.38</v>
@@ -29024,7 +29027,7 @@
         <v>1.33</v>
       </c>
       <c r="AP133">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ133">
         <v>1.13</v>
@@ -31087,7 +31090,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ143">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR143">
         <v>1.7</v>
@@ -32114,7 +32117,7 @@
         <v>1.43</v>
       </c>
       <c r="AP148">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ148">
         <v>1.44</v>
@@ -35413,7 +35416,7 @@
         <v>0.44</v>
       </c>
       <c r="AQ164">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR164">
         <v>1.2</v>
@@ -36028,7 +36031,7 @@
         <v>0.63</v>
       </c>
       <c r="AP167">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ167">
         <v>1.13</v>
@@ -38912,7 +38915,7 @@
         <v>1.22</v>
       </c>
       <c r="AP181">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ181">
         <v>1.38</v>
@@ -40563,7 +40566,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ189">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR189">
         <v>1.54</v>
@@ -40975,7 +40978,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ191">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR191">
         <v>1.71</v>
@@ -43856,7 +43859,7 @@
         <v>1.11</v>
       </c>
       <c r="AP205">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ205">
         <v>1.64</v>
@@ -45710,7 +45713,7 @@
         <v>1.3</v>
       </c>
       <c r="AP214">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ214">
         <v>1.47</v>
@@ -47773,7 +47776,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ224">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR224">
         <v>1.11</v>
@@ -51684,7 +51687,7 @@
         <v>1.83</v>
       </c>
       <c r="AP243">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ243">
         <v>1.75</v>
@@ -52099,7 +52102,7 @@
         <v>2</v>
       </c>
       <c r="AQ245">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR245">
         <v>1.98</v>
@@ -53744,7 +53747,7 @@
         <v>0.92</v>
       </c>
       <c r="AP253">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ253">
         <v>1.13</v>
@@ -57455,7 +57458,7 @@
         <v>2.53</v>
       </c>
       <c r="AQ271">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR271">
         <v>1.81</v>
@@ -59721,7 +59724,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ282">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AR282">
         <v>1.26</v>
@@ -61366,7 +61369,7 @@
         <v>1.08</v>
       </c>
       <c r="AP290">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ290">
         <v>1.13</v>
@@ -65359,6 +65362,212 @@
       </c>
       <c r="BP309">
         <v>1.53</v>
+      </c>
+    </row>
+    <row r="310" spans="1:68">
+      <c r="A310" s="1">
+        <v>309</v>
+      </c>
+      <c r="B310">
+        <v>7466985</v>
+      </c>
+      <c r="C310" t="s">
+        <v>68</v>
+      </c>
+      <c r="D310" t="s">
+        <v>69</v>
+      </c>
+      <c r="E310" s="2">
+        <v>45754.66666666666</v>
+      </c>
+      <c r="F310">
+        <v>31</v>
+      </c>
+      <c r="G310" t="s">
+        <v>79</v>
+      </c>
+      <c r="H310" t="s">
+        <v>74</v>
+      </c>
+      <c r="I310">
+        <v>0</v>
+      </c>
+      <c r="J310">
+        <v>3</v>
+      </c>
+      <c r="K310">
+        <v>3</v>
+      </c>
+      <c r="L310">
+        <v>0</v>
+      </c>
+      <c r="M310">
+        <v>3</v>
+      </c>
+      <c r="N310">
+        <v>3</v>
+      </c>
+      <c r="O310" t="s">
+        <v>91</v>
+      </c>
+      <c r="P310" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q310">
+        <v>6</v>
+      </c>
+      <c r="R310">
+        <v>2.5</v>
+      </c>
+      <c r="S310">
+        <v>2</v>
+      </c>
+      <c r="T310">
+        <v>1.3</v>
+      </c>
+      <c r="U310">
+        <v>3.4</v>
+      </c>
+      <c r="V310">
+        <v>2.38</v>
+      </c>
+      <c r="W310">
+        <v>1.53</v>
+      </c>
+      <c r="X310">
+        <v>5.5</v>
+      </c>
+      <c r="Y310">
+        <v>1.14</v>
+      </c>
+      <c r="Z310">
+        <v>5.8</v>
+      </c>
+      <c r="AA310">
+        <v>4.4</v>
+      </c>
+      <c r="AB310">
+        <v>1.54</v>
+      </c>
+      <c r="AC310">
+        <v>1.03</v>
+      </c>
+      <c r="AD310">
+        <v>11</v>
+      </c>
+      <c r="AE310">
+        <v>1.18</v>
+      </c>
+      <c r="AF310">
+        <v>4.75</v>
+      </c>
+      <c r="AG310">
+        <v>1.57</v>
+      </c>
+      <c r="AH310">
+        <v>2.3</v>
+      </c>
+      <c r="AI310">
+        <v>1.7</v>
+      </c>
+      <c r="AJ310">
+        <v>2.05</v>
+      </c>
+      <c r="AK310">
+        <v>2.5</v>
+      </c>
+      <c r="AL310">
+        <v>1.2</v>
+      </c>
+      <c r="AM310">
+        <v>1.13</v>
+      </c>
+      <c r="AN310">
+        <v>0.6</v>
+      </c>
+      <c r="AO310">
+        <v>1.6</v>
+      </c>
+      <c r="AP310">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AQ310">
+        <v>1.69</v>
+      </c>
+      <c r="AR310">
+        <v>1.21</v>
+      </c>
+      <c r="AS310">
+        <v>1.35</v>
+      </c>
+      <c r="AT310">
+        <v>2.56</v>
+      </c>
+      <c r="AU310">
+        <v>-1</v>
+      </c>
+      <c r="AV310">
+        <v>-1</v>
+      </c>
+      <c r="AW310">
+        <v>-1</v>
+      </c>
+      <c r="AX310">
+        <v>-1</v>
+      </c>
+      <c r="AY310">
+        <v>-1</v>
+      </c>
+      <c r="AZ310">
+        <v>-1</v>
+      </c>
+      <c r="BA310">
+        <v>-1</v>
+      </c>
+      <c r="BB310">
+        <v>-1</v>
+      </c>
+      <c r="BC310">
+        <v>-1</v>
+      </c>
+      <c r="BD310">
+        <v>3.45</v>
+      </c>
+      <c r="BE310">
+        <v>7.5</v>
+      </c>
+      <c r="BF310">
+        <v>1.34</v>
+      </c>
+      <c r="BG310">
+        <v>1.2</v>
+      </c>
+      <c r="BH310">
+        <v>3.9</v>
+      </c>
+      <c r="BI310">
+        <v>1.36</v>
+      </c>
+      <c r="BJ310">
+        <v>2.8</v>
+      </c>
+      <c r="BK310">
+        <v>1.58</v>
+      </c>
+      <c r="BL310">
+        <v>2.17</v>
+      </c>
+      <c r="BM310">
+        <v>1.95</v>
+      </c>
+      <c r="BN310">
+        <v>1.75</v>
+      </c>
+      <c r="BO310">
+        <v>2.43</v>
+      </c>
+      <c r="BP310">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Premier League_20242025.xlsx
@@ -65504,31 +65504,31 @@
         <v>2.56</v>
       </c>
       <c r="AU310">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AV310">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AW310">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AX310">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AY310">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AZ310">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="BA310">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BB310">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC310">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="BD310">
         <v>3.45</v>
